--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -934,7 +934,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2 h offline cap</t>
+          <t>2 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0 h offline cap</t>
+          <t>0 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4 h offline cap</t>
+          <t>4 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2 h offline cap</t>
+          <t>2 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6 h offline cap</t>
+          <t>6 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4 h offline cap</t>
+          <t>4 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8 h offline cap</t>
+          <t>8 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6 h offline cap</t>
+          <t>6 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>10 h offline cap</t>
+          <t>10 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8 h offline cap</t>
+          <t>8 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>12 h offline cap</t>
+          <t>12 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10 h offline cap</t>
+          <t>10 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14 h offline cap</t>
+          <t>14 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12 h offline cap</t>
+          <t>12 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>16 h offline cap</t>
+          <t>16 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14 h offline cap</t>
+          <t>14 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>18 h offline cap</t>
+          <t>18 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>16 h offline cap</t>
+          <t>16 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>20 h offline cap</t>
+          <t>20 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>18 h offline cap</t>
+          <t>18 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Offline progression cap (0h until first install)</t>
+          <t>Offline progression cap: +2 h per install on top of the 1 h base (24 h max)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>22 h offline cap</t>
+          <t>22 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>20 h offline cap</t>
+          <t>20 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>24 h offline cap</t>
+          <t>24 h added to the 1 h offline cap</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>22 h offline cap</t>
+          <t>22 h added to the 1 h offline cap</t>
         </is>
       </c>
     </row>
@@ -43465,7 +43465,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Cooling, Heat Reduction, VM Windows: 1 per tier. Background Services: 2 per tier, 2h each -&gt; 24h offline cap at max.</t>
+          <t xml:space="preserve">  • Cooling, Heat Reduction, VM Windows: 1 per tier. Background Services: 2 per tier, 2h each on top of a 1h base -&gt; 24h offline cap at max (code caps at 24).</t>
         </is>
       </c>
     </row>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="1098">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -2557,13 +2557,19 @@
     <t xml:space="preserve">hacking.clean_exit</t>
   </si>
   <si>
-    <t xml:space="preserve">30 dmg</t>
+    <t xml:space="preserve">+25 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Legal assistant cache</t>
   </si>
   <si>
-    <t xml:space="preserve">5 firewall dmg</t>
+    <t xml:space="preserve">+3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">2.5 /s bandwidth regen</t>
@@ -2596,13 +2602,16 @@
     <t xml:space="preserve">hacking.evasion</t>
   </si>
   <si>
-    <t xml:space="preserve">35 dmg</t>
+    <t xml:space="preserve">+38 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Receptionist cache</t>
   </si>
   <si>
-    <t xml:space="preserve">7 firewall dmg</t>
+    <t xml:space="preserve">11 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">3.5 /s bandwidth regen</t>
@@ -2635,13 +2644,19 @@
     <t xml:space="preserve">hacking.recycler</t>
   </si>
   <si>
-    <t xml:space="preserve">40 dmg</t>
+    <t xml:space="preserve">+50 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Teller Cache</t>
   </si>
   <si>
-    <t xml:space="preserve">9 firewall dmg</t>
+    <t xml:space="preserve">+6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">4.5 /s bandwidth regen</t>
@@ -2674,13 +2689,19 @@
     <t xml:space="preserve">hacking.siphon</t>
   </si>
   <si>
-    <t xml:space="preserve">45 dmg</t>
+    <t xml:space="preserve">+62 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Secretary cache</t>
   </si>
   <si>
-    <t xml:space="preserve">11 firewall dmg</t>
+    <t xml:space="preserve">+7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">5.5 /s bandwidth regen</t>
@@ -2713,13 +2734,19 @@
     <t xml:space="preserve">hacking.dead_mans_switch</t>
   </si>
   <si>
-    <t xml:space="preserve">50 dmg</t>
+    <t xml:space="preserve">+100 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Clerk Cache</t>
   </si>
   <si>
-    <t xml:space="preserve">13 firewall dmg</t>
+    <t xml:space="preserve">+12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">6.5 /s bandwidth regen</t>
@@ -3993,8 +4020,8 @@
         <v>27</v>
       </c>
       <c r="L2" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B2-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D2-1)/Inputs!$B$12,0)</f>
-        <v>70</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B2-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D2-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -4047,8 +4074,8 @@
         <v>27</v>
       </c>
       <c r="L3" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B3-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D3-1)/Inputs!$B$12,0)</f>
-        <v>81</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B3-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D3-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -4101,8 +4128,8 @@
         <v>43</v>
       </c>
       <c r="L4" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B4-1),0)</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$9*Inputs!$B$10^(B4-1),0))</f>
+        <v>1</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -4155,8 +4182,8 @@
         <v>27</v>
       </c>
       <c r="L5" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B5-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D5-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B5-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D5-1)/Inputs!$B$12,0))</f>
+        <v>11</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -4209,8 +4236,8 @@
         <v>27</v>
       </c>
       <c r="L6" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B6-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D6-1)/Inputs!$B$12,0)</f>
-        <v>123</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B6-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D6-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -4263,8 +4290,8 @@
         <v>27</v>
       </c>
       <c r="L7" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B7-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D7-1)/Inputs!$B$12,0)</f>
-        <v>141</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B7-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D7-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -4317,8 +4344,8 @@
         <v>27</v>
       </c>
       <c r="L8" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B8-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D8-1)/Inputs!$B$12,0)</f>
-        <v>162</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B8-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D8-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -4371,8 +4398,8 @@
         <v>27</v>
       </c>
       <c r="L9" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B9-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D9-1)/Inputs!$B$12,0)</f>
-        <v>187</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B9-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D9-1)/Inputs!$B$12,0))</f>
+        <v>19</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -4425,8 +4452,8 @@
         <v>43</v>
       </c>
       <c r="L10" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B10-1),0)</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$9*Inputs!$B$10^(B10-1),0))</f>
+        <v>1</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -4477,15 +4504,14 @@
         <v>27</v>
       </c>
       <c r="L11" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B11-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D11-1)/Inputs!$B$12,0)</f>
-        <v>247</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B11-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D11-1)/Inputs!$B$12,0))</f>
+        <v>25</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>91</v>
       </c>
       <c r="N11" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>28</v>
@@ -4537,8 +4563,8 @@
         <v>98</v>
       </c>
       <c r="L12" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B12-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D12-1)/Inputs!$B$12,0)</f>
-        <v>77</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B12-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D12-1)/Inputs!$B$12,0))</f>
+        <v>54</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -4591,8 +4617,8 @@
         <v>98</v>
       </c>
       <c r="L13" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B13-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D13-1)/Inputs!$B$12,0)</f>
-        <v>89</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B13-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D13-1)/Inputs!$B$12,0))</f>
+        <v>62</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -4645,8 +4671,8 @@
         <v>43</v>
       </c>
       <c r="L14" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B14-1),0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$9*Inputs!$B$10^(B14-1),0))</f>
+        <v>11</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -4699,8 +4725,8 @@
         <v>98</v>
       </c>
       <c r="L15" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B15-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D15-1)/Inputs!$B$12,0)</f>
-        <v>117</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B15-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D15-1)/Inputs!$B$12,0))</f>
+        <v>82</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -4753,8 +4779,8 @@
         <v>98</v>
       </c>
       <c r="L16" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B16-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D16-1)/Inputs!$B$12,0)</f>
-        <v>135</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B16-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D16-1)/Inputs!$B$12,0))</f>
+        <v>95</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -4807,8 +4833,8 @@
         <v>98</v>
       </c>
       <c r="L17" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B17-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D17-1)/Inputs!$B$12,0)</f>
-        <v>155</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B17-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D17-1)/Inputs!$B$12,0))</f>
+        <v>109</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -4861,8 +4887,8 @@
         <v>98</v>
       </c>
       <c r="L18" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B18-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D18-1)/Inputs!$B$12,0)</f>
-        <v>179</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B18-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D18-1)/Inputs!$B$12,0))</f>
+        <v>125</v>
       </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -4915,8 +4941,8 @@
         <v>98</v>
       </c>
       <c r="L19" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B19-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D19-1)/Inputs!$B$12,0)</f>
-        <v>205</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B19-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D19-1)/Inputs!$B$12,0))</f>
+        <v>144</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
@@ -4969,8 +4995,8 @@
         <v>43</v>
       </c>
       <c r="L20" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B20-1),0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$9*Inputs!$B$10^(B20-1),0))</f>
+        <v>11</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
@@ -5021,15 +5047,14 @@
         <v>98</v>
       </c>
       <c r="L21" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B21-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D21-1)/Inputs!$B$12,0)</f>
-        <v>272</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B21-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D21-1)/Inputs!$B$12,0))</f>
+        <v>190</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>118</v>
       </c>
       <c r="N21" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>28</v>
@@ -5081,8 +5106,8 @@
         <v>124</v>
       </c>
       <c r="L22" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B22-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D22-1)/Inputs!$B$12,0)</f>
-        <v>85</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B22-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D22-1)/Inputs!$B$12,0))</f>
+        <v>72</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -5135,8 +5160,8 @@
         <v>124</v>
       </c>
       <c r="L23" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B23-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D23-1)/Inputs!$B$12,0)</f>
-        <v>98</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B23-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D23-1)/Inputs!$B$12,0))</f>
+        <v>83</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -5189,8 +5214,8 @@
         <v>43</v>
       </c>
       <c r="L24" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B24-1),0)</f>
-        <v>23</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$9*Inputs!$B$10^(B24-1),0))</f>
+        <v>19</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -5243,8 +5268,8 @@
         <v>124</v>
       </c>
       <c r="L25" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B25-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D25-1)/Inputs!$B$12,0)</f>
-        <v>129</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B25-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D25-1)/Inputs!$B$12,0))</f>
+        <v>110</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -5297,8 +5322,8 @@
         <v>124</v>
       </c>
       <c r="L26" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B26-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D26-1)/Inputs!$B$12,0)</f>
-        <v>149</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B26-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D26-1)/Inputs!$B$12,0))</f>
+        <v>126</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -5351,8 +5376,8 @@
         <v>124</v>
       </c>
       <c r="L27" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B27-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D27-1)/Inputs!$B$12,0)</f>
-        <v>171</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B27-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D27-1)/Inputs!$B$12,0))</f>
+        <v>145</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -5405,8 +5430,8 @@
         <v>124</v>
       </c>
       <c r="L28" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B28-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D28-1)/Inputs!$B$12,0)</f>
-        <v>196</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B28-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D28-1)/Inputs!$B$12,0))</f>
+        <v>167</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -5459,8 +5484,8 @@
         <v>124</v>
       </c>
       <c r="L29" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B29-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D29-1)/Inputs!$B$12,0)</f>
-        <v>226</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B29-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D29-1)/Inputs!$B$12,0))</f>
+        <v>192</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
@@ -5513,8 +5538,8 @@
         <v>43</v>
       </c>
       <c r="L30" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B30-1),0)</f>
-        <v>23</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$9*Inputs!$B$10^(B30-1),0))</f>
+        <v>19</v>
       </c>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
@@ -5565,14 +5590,13 @@
         <v>124</v>
       </c>
       <c r="L31" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B31-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D31-1)/Inputs!$B$12,0)</f>
-        <v>299</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B31-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D31-1)/Inputs!$B$12,0))</f>
+        <v>254</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>144</v>
       </c>
       <c r="N31" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O31" s="6" t="s">
@@ -5625,8 +5649,8 @@
         <v>150</v>
       </c>
       <c r="L32" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B32-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D32-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B32-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D32-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -5679,8 +5703,8 @@
         <v>150</v>
       </c>
       <c r="L33" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B33-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D33-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B33-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D33-1)/Inputs!$B$12,0))</f>
+        <v>81</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -5733,8 +5757,8 @@
         <v>43</v>
       </c>
       <c r="L34" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B34-1),0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$9*Inputs!$B$10^(B34-1),0))</f>
+        <v>25</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -5787,8 +5811,8 @@
         <v>150</v>
       </c>
       <c r="L35" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B35-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D35-1)/Inputs!$B$12,0)</f>
-        <v>142</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B35-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D35-1)/Inputs!$B$12,0))</f>
+        <v>107</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -5841,8 +5865,8 @@
         <v>150</v>
       </c>
       <c r="L36" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B36-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D36-1)/Inputs!$B$12,0)</f>
-        <v>163</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B36-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D36-1)/Inputs!$B$12,0))</f>
+        <v>123</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -5895,8 +5919,8 @@
         <v>150</v>
       </c>
       <c r="L37" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B37-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D37-1)/Inputs!$B$12,0)</f>
-        <v>188</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B37-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D37-1)/Inputs!$B$12,0))</f>
+        <v>141</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -5949,8 +5973,8 @@
         <v>150</v>
       </c>
       <c r="L38" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B38-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D38-1)/Inputs!$B$12,0)</f>
-        <v>216</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B38-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D38-1)/Inputs!$B$12,0))</f>
+        <v>162</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -6003,8 +6027,8 @@
         <v>150</v>
       </c>
       <c r="L39" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B39-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D39-1)/Inputs!$B$12,0)</f>
-        <v>248</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B39-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D39-1)/Inputs!$B$12,0))</f>
+        <v>186</v>
       </c>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
@@ -6057,8 +6081,8 @@
         <v>43</v>
       </c>
       <c r="L40" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B40-1),0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$9*Inputs!$B$10^(B40-1),0))</f>
+        <v>25</v>
       </c>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
@@ -6109,14 +6133,13 @@
         <v>150</v>
       </c>
       <c r="L41" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B41-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D41-1)/Inputs!$B$12,0)</f>
-        <v>329</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B41-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D41-1)/Inputs!$B$12,0))</f>
+        <v>246</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>170</v>
       </c>
       <c r="N41" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O41" s="6" t="s">
@@ -6169,8 +6192,8 @@
         <v>176</v>
       </c>
       <c r="L42" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B42-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D42-1)/Inputs!$B$12,0)</f>
-        <v>103</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B42-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D42-1)/Inputs!$B$12,0))</f>
+        <v>77</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6223,8 +6246,8 @@
         <v>176</v>
       </c>
       <c r="L43" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B43-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D43-1)/Inputs!$B$12,0)</f>
-        <v>118</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B43-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D43-1)/Inputs!$B$12,0))</f>
+        <v>89</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -6277,8 +6300,8 @@
         <v>43</v>
       </c>
       <c r="L44" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B44-1),0)</f>
-        <v>51</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$9*Inputs!$B$10^(B44-1),0))</f>
+        <v>38</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6331,8 +6354,8 @@
         <v>176</v>
       </c>
       <c r="L45" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B45-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D45-1)/Inputs!$B$12,0)</f>
-        <v>156</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B45-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D45-1)/Inputs!$B$12,0))</f>
+        <v>117</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6385,8 +6408,8 @@
         <v>176</v>
       </c>
       <c r="L46" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B46-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D46-1)/Inputs!$B$12,0)</f>
-        <v>180</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B46-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D46-1)/Inputs!$B$12,0))</f>
+        <v>135</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6439,8 +6462,8 @@
         <v>176</v>
       </c>
       <c r="L47" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B47-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D47-1)/Inputs!$B$12,0)</f>
-        <v>207</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B47-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D47-1)/Inputs!$B$12,0))</f>
+        <v>155</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -6493,8 +6516,8 @@
         <v>176</v>
       </c>
       <c r="L48" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B48-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D48-1)/Inputs!$B$12,0)</f>
-        <v>238</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B48-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D48-1)/Inputs!$B$12,0))</f>
+        <v>178</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -6547,8 +6570,8 @@
         <v>176</v>
       </c>
       <c r="L49" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B49-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D49-1)/Inputs!$B$12,0)</f>
-        <v>273</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B49-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D49-1)/Inputs!$B$12,0))</f>
+        <v>205</v>
       </c>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
@@ -6601,8 +6624,8 @@
         <v>43</v>
       </c>
       <c r="L50" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B50-1),0)</f>
-        <v>51</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$9*Inputs!$B$10^(B50-1),0))</f>
+        <v>38</v>
       </c>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
@@ -6653,14 +6676,13 @@
         <v>176</v>
       </c>
       <c r="L51" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B51-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D51-1)/Inputs!$B$12,0)</f>
-        <v>361</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B51-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D51-1)/Inputs!$B$12,0))</f>
+        <v>271</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>196</v>
       </c>
       <c r="N51" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O51" s="6" t="s">
@@ -6713,7 +6735,7 @@
         <v>202</v>
       </c>
       <c r="L52" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B52-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D52-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B52-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D52-1)/Inputs!$B$12,0))</f>
         <v>113</v>
       </c>
       <c r="M52" s="2"/>
@@ -6767,7 +6789,7 @@
         <v>202</v>
       </c>
       <c r="L53" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B53-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D53-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B53-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D53-1)/Inputs!$B$12,0))</f>
         <v>130</v>
       </c>
       <c r="M53" s="2"/>
@@ -6821,7 +6843,7 @@
         <v>43</v>
       </c>
       <c r="L54" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B54-1),0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$9*Inputs!$B$10^(B54-1),0))</f>
         <v>76</v>
       </c>
       <c r="M54" s="2"/>
@@ -6875,7 +6897,7 @@
         <v>202</v>
       </c>
       <c r="L55" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B55-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D55-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B55-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D55-1)/Inputs!$B$12,0))</f>
         <v>172</v>
       </c>
       <c r="M55" s="2"/>
@@ -6929,7 +6951,7 @@
         <v>202</v>
       </c>
       <c r="L56" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B56-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D56-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B56-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D56-1)/Inputs!$B$12,0))</f>
         <v>198</v>
       </c>
       <c r="M56" s="2"/>
@@ -6983,7 +7005,7 @@
         <v>202</v>
       </c>
       <c r="L57" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B57-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D57-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B57-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D57-1)/Inputs!$B$12,0))</f>
         <v>227</v>
       </c>
       <c r="M57" s="2"/>
@@ -7037,7 +7059,7 @@
         <v>202</v>
       </c>
       <c r="L58" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B58-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D58-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B58-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D58-1)/Inputs!$B$12,0))</f>
         <v>261</v>
       </c>
       <c r="M58" s="2"/>
@@ -7091,7 +7113,7 @@
         <v>202</v>
       </c>
       <c r="L59" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B59-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D59-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B59-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D59-1)/Inputs!$B$12,0))</f>
         <v>301</v>
       </c>
       <c r="M59" s="4"/>
@@ -7145,7 +7167,7 @@
         <v>43</v>
       </c>
       <c r="L60" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$9*Inputs!$B$10^(B60-1),0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$9*Inputs!$B$10^(B60-1),0))</f>
         <v>76</v>
       </c>
       <c r="M60" s="4"/>
@@ -7197,14 +7219,13 @@
         <v>202</v>
       </c>
       <c r="L61" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B61-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D61-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B61-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D61-1)/Inputs!$B$12,0))</f>
         <v>398</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>222</v>
       </c>
       <c r="N61" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O61" s="6" t="s">
@@ -7257,8 +7278,8 @@
         <v>27</v>
       </c>
       <c r="L62" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B62-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D62-1)/Inputs!$B$12,0)</f>
-        <v>70</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B62-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D62-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7311,8 +7332,8 @@
         <v>27</v>
       </c>
       <c r="L63" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B63-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D63-1)/Inputs!$B$12,0)</f>
-        <v>81</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B63-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D63-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -7365,8 +7386,8 @@
         <v>27</v>
       </c>
       <c r="L64" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B64-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D64-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B64-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D64-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -7419,8 +7440,8 @@
         <v>27</v>
       </c>
       <c r="L65" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B65-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D65-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B65-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D65-1)/Inputs!$B$12,0))</f>
+        <v>11</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -7473,8 +7494,8 @@
         <v>27</v>
       </c>
       <c r="L66" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B66-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D66-1)/Inputs!$B$12,0)</f>
-        <v>123</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B66-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D66-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -7527,8 +7548,8 @@
         <v>27</v>
       </c>
       <c r="L67" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B67-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D67-1)/Inputs!$B$12,0)</f>
-        <v>141</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B67-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D67-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -7581,8 +7602,8 @@
         <v>27</v>
       </c>
       <c r="L68" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B68-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D68-1)/Inputs!$B$12,0)</f>
-        <v>162</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B68-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D68-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -7635,8 +7656,8 @@
         <v>27</v>
       </c>
       <c r="L69" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B69-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D69-1)/Inputs!$B$12,0)</f>
-        <v>187</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B69-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D69-1)/Inputs!$B$12,0))</f>
+        <v>19</v>
       </c>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -7689,8 +7710,8 @@
         <v>27</v>
       </c>
       <c r="L70" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B70-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D70-1)/Inputs!$B$12,0)</f>
-        <v>215</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B70-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D70-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
@@ -7741,15 +7762,14 @@
         <v>27</v>
       </c>
       <c r="L71" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B71-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D71-1)/Inputs!$B$12,0)</f>
-        <v>247</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B71-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D71-1)/Inputs!$B$12,0))</f>
+        <v>25</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>264</v>
       </c>
       <c r="N71" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>28</v>
@@ -7801,8 +7821,8 @@
         <v>98</v>
       </c>
       <c r="L72" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B72-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D72-1)/Inputs!$B$12,0)</f>
-        <v>77</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B72-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D72-1)/Inputs!$B$12,0))</f>
+        <v>54</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -7855,8 +7875,8 @@
         <v>98</v>
       </c>
       <c r="L73" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B73-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D73-1)/Inputs!$B$12,0)</f>
-        <v>89</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B73-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D73-1)/Inputs!$B$12,0))</f>
+        <v>62</v>
       </c>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
@@ -7909,8 +7929,8 @@
         <v>98</v>
       </c>
       <c r="L74" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B74-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D74-1)/Inputs!$B$12,0)</f>
-        <v>102</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B74-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D74-1)/Inputs!$B$12,0))</f>
+        <v>71</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -7963,8 +7983,8 @@
         <v>98</v>
       </c>
       <c r="L75" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B75-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D75-1)/Inputs!$B$12,0)</f>
-        <v>117</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B75-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D75-1)/Inputs!$B$12,0))</f>
+        <v>82</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -8017,8 +8037,8 @@
         <v>98</v>
       </c>
       <c r="L76" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B76-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D76-1)/Inputs!$B$12,0)</f>
-        <v>135</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B76-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D76-1)/Inputs!$B$12,0))</f>
+        <v>95</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -8071,8 +8091,8 @@
         <v>98</v>
       </c>
       <c r="L77" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B77-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D77-1)/Inputs!$B$12,0)</f>
-        <v>155</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B77-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D77-1)/Inputs!$B$12,0))</f>
+        <v>109</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -8125,8 +8145,8 @@
         <v>98</v>
       </c>
       <c r="L78" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B78-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D78-1)/Inputs!$B$12,0)</f>
-        <v>179</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B78-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D78-1)/Inputs!$B$12,0))</f>
+        <v>125</v>
       </c>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
@@ -8179,8 +8199,8 @@
         <v>98</v>
       </c>
       <c r="L79" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B79-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D79-1)/Inputs!$B$12,0)</f>
-        <v>205</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B79-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D79-1)/Inputs!$B$12,0))</f>
+        <v>144</v>
       </c>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
@@ -8233,8 +8253,8 @@
         <v>98</v>
       </c>
       <c r="L80" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B80-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D80-1)/Inputs!$B$12,0)</f>
-        <v>236</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B80-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D80-1)/Inputs!$B$12,0))</f>
+        <v>165</v>
       </c>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
@@ -8285,15 +8305,14 @@
         <v>98</v>
       </c>
       <c r="L81" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B81-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D81-1)/Inputs!$B$12,0)</f>
-        <v>272</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B81-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D81-1)/Inputs!$B$12,0))</f>
+        <v>190</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>278</v>
       </c>
       <c r="N81" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>28</v>
@@ -8345,8 +8364,8 @@
         <v>124</v>
       </c>
       <c r="L82" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B82-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D82-1)/Inputs!$B$12,0)</f>
-        <v>85</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B82-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D82-1)/Inputs!$B$12,0))</f>
+        <v>72</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -8399,8 +8418,8 @@
         <v>124</v>
       </c>
       <c r="L83" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B83-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D83-1)/Inputs!$B$12,0)</f>
-        <v>98</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B83-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D83-1)/Inputs!$B$12,0))</f>
+        <v>83</v>
       </c>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
@@ -8453,8 +8472,8 @@
         <v>124</v>
       </c>
       <c r="L84" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B84-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D84-1)/Inputs!$B$12,0)</f>
-        <v>112</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B84-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D84-1)/Inputs!$B$12,0))</f>
+        <v>95</v>
       </c>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
@@ -8507,8 +8526,8 @@
         <v>124</v>
       </c>
       <c r="L85" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B85-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D85-1)/Inputs!$B$12,0)</f>
-        <v>129</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B85-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D85-1)/Inputs!$B$12,0))</f>
+        <v>110</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -8561,8 +8580,8 @@
         <v>124</v>
       </c>
       <c r="L86" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B86-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D86-1)/Inputs!$B$12,0)</f>
-        <v>149</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B86-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D86-1)/Inputs!$B$12,0))</f>
+        <v>126</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -8615,8 +8634,8 @@
         <v>124</v>
       </c>
       <c r="L87" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B87-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D87-1)/Inputs!$B$12,0)</f>
-        <v>171</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B87-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D87-1)/Inputs!$B$12,0))</f>
+        <v>145</v>
       </c>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
@@ -8669,8 +8688,8 @@
         <v>124</v>
       </c>
       <c r="L88" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B88-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D88-1)/Inputs!$B$12,0)</f>
-        <v>196</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B88-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D88-1)/Inputs!$B$12,0))</f>
+        <v>167</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -8723,8 +8742,8 @@
         <v>124</v>
       </c>
       <c r="L89" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B89-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D89-1)/Inputs!$B$12,0)</f>
-        <v>226</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B89-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D89-1)/Inputs!$B$12,0))</f>
+        <v>192</v>
       </c>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
@@ -8777,8 +8796,8 @@
         <v>124</v>
       </c>
       <c r="L90" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B90-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D90-1)/Inputs!$B$12,0)</f>
-        <v>260</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B90-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D90-1)/Inputs!$B$12,0))</f>
+        <v>221</v>
       </c>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
@@ -8829,14 +8848,13 @@
         <v>124</v>
       </c>
       <c r="L91" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B91-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D91-1)/Inputs!$B$12,0)</f>
-        <v>299</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B91-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D91-1)/Inputs!$B$12,0))</f>
+        <v>254</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>292</v>
       </c>
       <c r="N91" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O91" s="6" t="s">
@@ -8889,8 +8907,8 @@
         <v>150</v>
       </c>
       <c r="L92" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B92-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D92-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B92-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D92-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -8943,8 +8961,8 @@
         <v>150</v>
       </c>
       <c r="L93" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B93-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D93-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B93-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D93-1)/Inputs!$B$12,0))</f>
+        <v>81</v>
       </c>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
@@ -8997,8 +9015,8 @@
         <v>150</v>
       </c>
       <c r="L94" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B94-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D94-1)/Inputs!$B$12,0)</f>
-        <v>124</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B94-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D94-1)/Inputs!$B$12,0))</f>
+        <v>93</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
@@ -9051,8 +9069,8 @@
         <v>150</v>
       </c>
       <c r="L95" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B95-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D95-1)/Inputs!$B$12,0)</f>
-        <v>142</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B95-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D95-1)/Inputs!$B$12,0))</f>
+        <v>107</v>
       </c>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
@@ -9105,8 +9123,8 @@
         <v>150</v>
       </c>
       <c r="L96" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B96-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D96-1)/Inputs!$B$12,0)</f>
-        <v>163</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B96-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D96-1)/Inputs!$B$12,0))</f>
+        <v>123</v>
       </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
@@ -9159,8 +9177,8 @@
         <v>150</v>
       </c>
       <c r="L97" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B97-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D97-1)/Inputs!$B$12,0)</f>
-        <v>188</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B97-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D97-1)/Inputs!$B$12,0))</f>
+        <v>141</v>
       </c>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
@@ -9213,8 +9231,8 @@
         <v>150</v>
       </c>
       <c r="L98" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B98-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D98-1)/Inputs!$B$12,0)</f>
-        <v>216</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B98-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D98-1)/Inputs!$B$12,0))</f>
+        <v>162</v>
       </c>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
@@ -9267,8 +9285,8 @@
         <v>150</v>
       </c>
       <c r="L99" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B99-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D99-1)/Inputs!$B$12,0)</f>
-        <v>248</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B99-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D99-1)/Inputs!$B$12,0))</f>
+        <v>186</v>
       </c>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
@@ -9321,8 +9339,8 @@
         <v>150</v>
       </c>
       <c r="L100" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B100-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D100-1)/Inputs!$B$12,0)</f>
-        <v>286</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B100-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D100-1)/Inputs!$B$12,0))</f>
+        <v>214</v>
       </c>
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
@@ -9373,14 +9391,13 @@
         <v>150</v>
       </c>
       <c r="L101" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B101-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D101-1)/Inputs!$B$12,0)</f>
-        <v>329</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B101-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D101-1)/Inputs!$B$12,0))</f>
+        <v>246</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>306</v>
       </c>
       <c r="N101" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O101" s="6" t="s">
@@ -9433,8 +9450,8 @@
         <v>176</v>
       </c>
       <c r="L102" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B102-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D102-1)/Inputs!$B$12,0)</f>
-        <v>103</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B102-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D102-1)/Inputs!$B$12,0))</f>
+        <v>77</v>
       </c>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
@@ -9487,8 +9504,8 @@
         <v>176</v>
       </c>
       <c r="L103" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B103-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D103-1)/Inputs!$B$12,0)</f>
-        <v>118</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B103-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D103-1)/Inputs!$B$12,0))</f>
+        <v>89</v>
       </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -9541,8 +9558,8 @@
         <v>176</v>
       </c>
       <c r="L104" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B104-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D104-1)/Inputs!$B$12,0)</f>
-        <v>136</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B104-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D104-1)/Inputs!$B$12,0))</f>
+        <v>102</v>
       </c>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
@@ -9595,8 +9612,8 @@
         <v>176</v>
       </c>
       <c r="L105" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B105-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D105-1)/Inputs!$B$12,0)</f>
-        <v>156</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B105-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D105-1)/Inputs!$B$12,0))</f>
+        <v>117</v>
       </c>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
@@ -9649,8 +9666,8 @@
         <v>176</v>
       </c>
       <c r="L106" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B106-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D106-1)/Inputs!$B$12,0)</f>
-        <v>180</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B106-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D106-1)/Inputs!$B$12,0))</f>
+        <v>135</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -9703,8 +9720,8 @@
         <v>176</v>
       </c>
       <c r="L107" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B107-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D107-1)/Inputs!$B$12,0)</f>
-        <v>207</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B107-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D107-1)/Inputs!$B$12,0))</f>
+        <v>155</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -9757,8 +9774,8 @@
         <v>176</v>
       </c>
       <c r="L108" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B108-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D108-1)/Inputs!$B$12,0)</f>
-        <v>238</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B108-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D108-1)/Inputs!$B$12,0))</f>
+        <v>178</v>
       </c>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
@@ -9811,8 +9828,8 @@
         <v>176</v>
       </c>
       <c r="L109" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B109-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D109-1)/Inputs!$B$12,0)</f>
-        <v>273</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B109-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D109-1)/Inputs!$B$12,0))</f>
+        <v>205</v>
       </c>
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
@@ -9865,8 +9882,8 @@
         <v>176</v>
       </c>
       <c r="L110" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B110-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D110-1)/Inputs!$B$12,0)</f>
-        <v>314</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B110-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D110-1)/Inputs!$B$12,0))</f>
+        <v>236</v>
       </c>
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
@@ -9917,14 +9934,13 @@
         <v>176</v>
       </c>
       <c r="L111" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B111-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D111-1)/Inputs!$B$12,0)</f>
-        <v>361</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B111-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D111-1)/Inputs!$B$12,0))</f>
+        <v>271</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>320</v>
       </c>
       <c r="N111" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O111" s="6" t="s">
@@ -9977,7 +9993,7 @@
         <v>202</v>
       </c>
       <c r="L112" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B112-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D112-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B112-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D112-1)/Inputs!$B$12,0))</f>
         <v>113</v>
       </c>
       <c r="M112" s="2"/>
@@ -10031,7 +10047,7 @@
         <v>202</v>
       </c>
       <c r="L113" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B113-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D113-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B113-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D113-1)/Inputs!$B$12,0))</f>
         <v>130</v>
       </c>
       <c r="M113" s="2"/>
@@ -10085,7 +10101,7 @@
         <v>202</v>
       </c>
       <c r="L114" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B114-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D114-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B114-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D114-1)/Inputs!$B$12,0))</f>
         <v>149</v>
       </c>
       <c r="M114" s="2"/>
@@ -10139,7 +10155,7 @@
         <v>202</v>
       </c>
       <c r="L115" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B115-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D115-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B115-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D115-1)/Inputs!$B$12,0))</f>
         <v>172</v>
       </c>
       <c r="M115" s="2"/>
@@ -10193,7 +10209,7 @@
         <v>202</v>
       </c>
       <c r="L116" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B116-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D116-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B116-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D116-1)/Inputs!$B$12,0))</f>
         <v>198</v>
       </c>
       <c r="M116" s="2"/>
@@ -10247,7 +10263,7 @@
         <v>202</v>
       </c>
       <c r="L117" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B117-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D117-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B117-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D117-1)/Inputs!$B$12,0))</f>
         <v>227</v>
       </c>
       <c r="M117" s="2"/>
@@ -10301,7 +10317,7 @@
         <v>202</v>
       </c>
       <c r="L118" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B118-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D118-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B118-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D118-1)/Inputs!$B$12,0))</f>
         <v>261</v>
       </c>
       <c r="M118" s="2"/>
@@ -10355,7 +10371,7 @@
         <v>202</v>
       </c>
       <c r="L119" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B119-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D119-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B119-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D119-1)/Inputs!$B$12,0))</f>
         <v>301</v>
       </c>
       <c r="M119" s="4"/>
@@ -10409,7 +10425,7 @@
         <v>202</v>
       </c>
       <c r="L120" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B120-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D120-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B120-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D120-1)/Inputs!$B$12,0))</f>
         <v>346</v>
       </c>
       <c r="M120" s="4"/>
@@ -10461,14 +10477,13 @@
         <v>202</v>
       </c>
       <c r="L121" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B121-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D121-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B121-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D121-1)/Inputs!$B$12,0))</f>
         <v>398</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>334</v>
       </c>
       <c r="N121" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O121" s="6" t="s">
@@ -10521,8 +10536,8 @@
         <v>338</v>
       </c>
       <c r="L122" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B122-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D122-1)/Inputs!$B$12,0)</f>
-        <v>38</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B122-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D122-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -10575,8 +10590,8 @@
         <v>338</v>
       </c>
       <c r="L123" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B123-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D123-1)/Inputs!$B$12,0)</f>
-        <v>44</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B123-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D123-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -10629,8 +10644,8 @@
         <v>338</v>
       </c>
       <c r="L124" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B124-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D124-1)/Inputs!$B$12,0)</f>
-        <v>50</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B124-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D124-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -10683,8 +10698,8 @@
         <v>338</v>
       </c>
       <c r="L125" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B125-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D125-1)/Inputs!$B$12,0)</f>
-        <v>58</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B125-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D125-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -10737,8 +10752,8 @@
         <v>338</v>
       </c>
       <c r="L126" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B126-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D126-1)/Inputs!$B$12,0)</f>
-        <v>67</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B126-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D126-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -10791,8 +10806,8 @@
         <v>338</v>
       </c>
       <c r="L127" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B127-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D127-1)/Inputs!$B$12,0)</f>
-        <v>77</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B127-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D127-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -10845,8 +10860,8 @@
         <v>338</v>
       </c>
       <c r="L128" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B128-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D128-1)/Inputs!$B$12,0)</f>
-        <v>88</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B128-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D128-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -10899,8 +10914,8 @@
         <v>338</v>
       </c>
       <c r="L129" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B129-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D129-1)/Inputs!$B$12,0)</f>
-        <v>102</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B129-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D129-1)/Inputs!$B$12,0))</f>
+        <v>10</v>
       </c>
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
@@ -10953,8 +10968,8 @@
         <v>338</v>
       </c>
       <c r="L130" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B130-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D130-1)/Inputs!$B$12,0)</f>
-        <v>117</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B130-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D130-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
@@ -11005,15 +11020,14 @@
         <v>338</v>
       </c>
       <c r="L131" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B131-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D131-1)/Inputs!$B$12,0)</f>
-        <v>134</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B131-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D131-1)/Inputs!$B$12,0))</f>
+        <v>13</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>368</v>
       </c>
       <c r="N131" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>339</v>
@@ -11065,8 +11079,8 @@
         <v>370</v>
       </c>
       <c r="L132" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B132-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D132-1)/Inputs!$B$12,0)</f>
-        <v>42</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B132-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D132-1)/Inputs!$B$12,0))</f>
+        <v>29</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -11119,8 +11133,8 @@
         <v>370</v>
       </c>
       <c r="L133" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B133-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D133-1)/Inputs!$B$12,0)</f>
-        <v>48</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B133-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D133-1)/Inputs!$B$12,0))</f>
+        <v>34</v>
       </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
@@ -11173,8 +11187,8 @@
         <v>370</v>
       </c>
       <c r="L134" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B134-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D134-1)/Inputs!$B$12,0)</f>
-        <v>56</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B134-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D134-1)/Inputs!$B$12,0))</f>
+        <v>39</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -11227,8 +11241,8 @@
         <v>370</v>
       </c>
       <c r="L135" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B135-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D135-1)/Inputs!$B$12,0)</f>
-        <v>64</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B135-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D135-1)/Inputs!$B$12,0))</f>
+        <v>45</v>
       </c>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
@@ -11281,8 +11295,8 @@
         <v>370</v>
       </c>
       <c r="L136" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B136-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D136-1)/Inputs!$B$12,0)</f>
-        <v>73</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B136-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D136-1)/Inputs!$B$12,0))</f>
+        <v>51</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -11335,8 +11349,8 @@
         <v>370</v>
       </c>
       <c r="L137" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B137-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D137-1)/Inputs!$B$12,0)</f>
-        <v>84</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B137-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D137-1)/Inputs!$B$12,0))</f>
+        <v>59</v>
       </c>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
@@ -11389,8 +11403,8 @@
         <v>370</v>
       </c>
       <c r="L138" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B138-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D138-1)/Inputs!$B$12,0)</f>
-        <v>97</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B138-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D138-1)/Inputs!$B$12,0))</f>
+        <v>68</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -11443,8 +11457,8 @@
         <v>370</v>
       </c>
       <c r="L139" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B139-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D139-1)/Inputs!$B$12,0)</f>
-        <v>112</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B139-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D139-1)/Inputs!$B$12,0))</f>
+        <v>78</v>
       </c>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
@@ -11497,8 +11511,8 @@
         <v>370</v>
       </c>
       <c r="L140" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B140-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D140-1)/Inputs!$B$12,0)</f>
-        <v>128</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B140-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D140-1)/Inputs!$B$12,0))</f>
+        <v>90</v>
       </c>
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
@@ -11549,15 +11563,14 @@
         <v>370</v>
       </c>
       <c r="L141" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B141-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D141-1)/Inputs!$B$12,0)</f>
-        <v>148</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B141-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D141-1)/Inputs!$B$12,0))</f>
+        <v>103</v>
       </c>
       <c r="M141" s="6" t="s">
         <v>379</v>
       </c>
       <c r="N141" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>339</v>
@@ -11609,8 +11622,8 @@
         <v>381</v>
       </c>
       <c r="L142" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B142-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D142-1)/Inputs!$B$12,0)</f>
-        <v>46</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B142-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D142-1)/Inputs!$B$12,0))</f>
+        <v>39</v>
       </c>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
@@ -11663,8 +11676,8 @@
         <v>381</v>
       </c>
       <c r="L143" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B143-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D143-1)/Inputs!$B$12,0)</f>
-        <v>53</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B143-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D143-1)/Inputs!$B$12,0))</f>
+        <v>45</v>
       </c>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
@@ -11717,8 +11730,8 @@
         <v>381</v>
       </c>
       <c r="L144" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B144-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D144-1)/Inputs!$B$12,0)</f>
-        <v>61</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B144-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D144-1)/Inputs!$B$12,0))</f>
+        <v>52</v>
       </c>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
@@ -11771,8 +11784,8 @@
         <v>381</v>
       </c>
       <c r="L145" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B145-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D145-1)/Inputs!$B$12,0)</f>
-        <v>70</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B145-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D145-1)/Inputs!$B$12,0))</f>
+        <v>60</v>
       </c>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
@@ -11825,8 +11838,8 @@
         <v>381</v>
       </c>
       <c r="L146" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B146-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D146-1)/Inputs!$B$12,0)</f>
-        <v>81</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B146-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D146-1)/Inputs!$B$12,0))</f>
+        <v>69</v>
       </c>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
@@ -11879,8 +11892,8 @@
         <v>381</v>
       </c>
       <c r="L147" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B147-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D147-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B147-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D147-1)/Inputs!$B$12,0))</f>
+        <v>79</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -11933,8 +11946,8 @@
         <v>381</v>
       </c>
       <c r="L148" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B148-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D148-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B148-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D148-1)/Inputs!$B$12,0))</f>
+        <v>91</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -11987,8 +12000,8 @@
         <v>381</v>
       </c>
       <c r="L149" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B149-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D149-1)/Inputs!$B$12,0)</f>
-        <v>123</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B149-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D149-1)/Inputs!$B$12,0))</f>
+        <v>104</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -12041,8 +12054,8 @@
         <v>381</v>
       </c>
       <c r="L150" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B150-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D150-1)/Inputs!$B$12,0)</f>
-        <v>141</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B150-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D150-1)/Inputs!$B$12,0))</f>
+        <v>120</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -12093,14 +12106,13 @@
         <v>381</v>
       </c>
       <c r="L151" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B151-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D151-1)/Inputs!$B$12,0)</f>
-        <v>162</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B151-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D151-1)/Inputs!$B$12,0))</f>
+        <v>138</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>390</v>
       </c>
       <c r="N151" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O151" s="6" t="s">
@@ -12153,8 +12165,8 @@
         <v>392</v>
       </c>
       <c r="L152" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B152-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D152-1)/Inputs!$B$12,0)</f>
-        <v>51</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B152-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D152-1)/Inputs!$B$12,0))</f>
+        <v>38</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -12207,8 +12219,8 @@
         <v>392</v>
       </c>
       <c r="L153" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B153-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D153-1)/Inputs!$B$12,0)</f>
-        <v>58</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B153-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D153-1)/Inputs!$B$12,0))</f>
+        <v>44</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
@@ -12261,8 +12273,8 @@
         <v>392</v>
       </c>
       <c r="L154" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B154-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D154-1)/Inputs!$B$12,0)</f>
-        <v>67</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B154-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D154-1)/Inputs!$B$12,0))</f>
+        <v>50</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -12315,8 +12327,8 @@
         <v>392</v>
       </c>
       <c r="L155" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B155-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D155-1)/Inputs!$B$12,0)</f>
-        <v>77</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B155-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D155-1)/Inputs!$B$12,0))</f>
+        <v>58</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -12369,8 +12381,8 @@
         <v>392</v>
       </c>
       <c r="L156" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B156-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D156-1)/Inputs!$B$12,0)</f>
-        <v>89</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B156-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D156-1)/Inputs!$B$12,0))</f>
+        <v>67</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -12423,8 +12435,8 @@
         <v>392</v>
       </c>
       <c r="L157" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B157-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D157-1)/Inputs!$B$12,0)</f>
-        <v>102</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B157-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D157-1)/Inputs!$B$12,0))</f>
+        <v>77</v>
       </c>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
@@ -12477,8 +12489,8 @@
         <v>392</v>
       </c>
       <c r="L158" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B158-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D158-1)/Inputs!$B$12,0)</f>
-        <v>118</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B158-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D158-1)/Inputs!$B$12,0))</f>
+        <v>88</v>
       </c>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
@@ -12531,8 +12543,8 @@
         <v>392</v>
       </c>
       <c r="L159" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B159-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D159-1)/Inputs!$B$12,0)</f>
-        <v>135</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B159-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D159-1)/Inputs!$B$12,0))</f>
+        <v>101</v>
       </c>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
@@ -12585,8 +12597,8 @@
         <v>392</v>
       </c>
       <c r="L160" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B160-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D160-1)/Inputs!$B$12,0)</f>
-        <v>155</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B160-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D160-1)/Inputs!$B$12,0))</f>
+        <v>117</v>
       </c>
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
@@ -12637,14 +12649,13 @@
         <v>392</v>
       </c>
       <c r="L161" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B161-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D161-1)/Inputs!$B$12,0)</f>
-        <v>179</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B161-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D161-1)/Inputs!$B$12,0))</f>
+        <v>134</v>
       </c>
       <c r="M161" s="6" t="s">
         <v>401</v>
       </c>
       <c r="N161" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O161" s="6" t="s">
@@ -12697,8 +12708,8 @@
         <v>403</v>
       </c>
       <c r="L162" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B162-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D162-1)/Inputs!$B$12,0)</f>
-        <v>56</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B162-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D162-1)/Inputs!$B$12,0))</f>
+        <v>42</v>
       </c>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
@@ -12751,8 +12762,8 @@
         <v>403</v>
       </c>
       <c r="L163" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B163-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D163-1)/Inputs!$B$12,0)</f>
-        <v>64</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B163-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D163-1)/Inputs!$B$12,0))</f>
+        <v>48</v>
       </c>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
@@ -12805,8 +12816,8 @@
         <v>403</v>
       </c>
       <c r="L164" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B164-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D164-1)/Inputs!$B$12,0)</f>
-        <v>74</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B164-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D164-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
@@ -12859,8 +12870,8 @@
         <v>403</v>
       </c>
       <c r="L165" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B165-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D165-1)/Inputs!$B$12,0)</f>
-        <v>85</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B165-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D165-1)/Inputs!$B$12,0))</f>
+        <v>64</v>
       </c>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
@@ -12913,8 +12924,8 @@
         <v>403</v>
       </c>
       <c r="L166" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B166-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D166-1)/Inputs!$B$12,0)</f>
-        <v>98</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B166-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D166-1)/Inputs!$B$12,0))</f>
+        <v>73</v>
       </c>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
@@ -12967,8 +12978,8 @@
         <v>403</v>
       </c>
       <c r="L167" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B167-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D167-1)/Inputs!$B$12,0)</f>
-        <v>112</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B167-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D167-1)/Inputs!$B$12,0))</f>
+        <v>84</v>
       </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
@@ -13021,8 +13032,8 @@
         <v>403</v>
       </c>
       <c r="L168" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B168-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D168-1)/Inputs!$B$12,0)</f>
-        <v>129</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B168-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D168-1)/Inputs!$B$12,0))</f>
+        <v>97</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -13075,8 +13086,8 @@
         <v>403</v>
       </c>
       <c r="L169" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B169-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D169-1)/Inputs!$B$12,0)</f>
-        <v>149</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B169-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D169-1)/Inputs!$B$12,0))</f>
+        <v>111</v>
       </c>
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
@@ -13129,8 +13140,8 @@
         <v>403</v>
       </c>
       <c r="L170" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B170-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D170-1)/Inputs!$B$12,0)</f>
-        <v>171</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B170-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D170-1)/Inputs!$B$12,0))</f>
+        <v>128</v>
       </c>
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
@@ -13181,14 +13192,13 @@
         <v>403</v>
       </c>
       <c r="L171" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B171-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D171-1)/Inputs!$B$12,0)</f>
-        <v>197</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B171-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D171-1)/Inputs!$B$12,0))</f>
+        <v>147</v>
       </c>
       <c r="M171" s="6" t="s">
         <v>411</v>
       </c>
       <c r="N171" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O171" s="6" t="s">
@@ -13241,7 +13251,7 @@
         <v>413</v>
       </c>
       <c r="L172" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B172-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D172-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B172-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D172-1)/Inputs!$B$12,0))</f>
         <v>61</v>
       </c>
       <c r="M172" s="2"/>
@@ -13295,7 +13305,7 @@
         <v>413</v>
       </c>
       <c r="L173" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B173-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D173-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B173-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D173-1)/Inputs!$B$12,0))</f>
         <v>71</v>
       </c>
       <c r="M173" s="2"/>
@@ -13349,7 +13359,7 @@
         <v>413</v>
       </c>
       <c r="L174" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B174-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D174-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B174-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D174-1)/Inputs!$B$12,0))</f>
         <v>81</v>
       </c>
       <c r="M174" s="2"/>
@@ -13403,7 +13413,7 @@
         <v>413</v>
       </c>
       <c r="L175" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B175-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D175-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B175-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D175-1)/Inputs!$B$12,0))</f>
         <v>93</v>
       </c>
       <c r="M175" s="2"/>
@@ -13457,7 +13467,7 @@
         <v>413</v>
       </c>
       <c r="L176" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B176-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D176-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B176-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D176-1)/Inputs!$B$12,0))</f>
         <v>108</v>
       </c>
       <c r="M176" s="2"/>
@@ -13511,7 +13521,7 @@
         <v>413</v>
       </c>
       <c r="L177" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B177-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D177-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B177-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D177-1)/Inputs!$B$12,0))</f>
         <v>124</v>
       </c>
       <c r="M177" s="2"/>
@@ -13565,7 +13575,7 @@
         <v>413</v>
       </c>
       <c r="L178" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B178-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D178-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B178-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D178-1)/Inputs!$B$12,0))</f>
         <v>142</v>
       </c>
       <c r="M178" s="2"/>
@@ -13619,7 +13629,7 @@
         <v>413</v>
       </c>
       <c r="L179" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B179-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D179-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B179-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D179-1)/Inputs!$B$12,0))</f>
         <v>164</v>
       </c>
       <c r="M179" s="4"/>
@@ -13673,7 +13683,7 @@
         <v>413</v>
       </c>
       <c r="L180" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B180-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D180-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B180-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D180-1)/Inputs!$B$12,0))</f>
         <v>188</v>
       </c>
       <c r="M180" s="4"/>
@@ -13725,14 +13735,13 @@
         <v>413</v>
       </c>
       <c r="L181" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B181-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D181-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B181-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D181-1)/Inputs!$B$12,0))</f>
         <v>216</v>
       </c>
       <c r="M181" s="6" t="s">
         <v>422</v>
       </c>
       <c r="N181" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O181" s="6" t="s">
@@ -13785,8 +13794,8 @@
         <v>426</v>
       </c>
       <c r="L182" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B182-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D182-1)/Inputs!$B$12,0)</f>
-        <v>46</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B182-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D182-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
@@ -13839,8 +13848,8 @@
         <v>426</v>
       </c>
       <c r="L183" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B183-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D183-1)/Inputs!$B$12,0)</f>
-        <v>53</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B183-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D183-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
@@ -13893,8 +13902,8 @@
         <v>426</v>
       </c>
       <c r="L184" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B184-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D184-1)/Inputs!$B$12,0)</f>
-        <v>61</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B184-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D184-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
@@ -13947,8 +13956,8 @@
         <v>426</v>
       </c>
       <c r="L185" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B185-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D185-1)/Inputs!$B$12,0)</f>
-        <v>70</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B185-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D185-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
@@ -14001,8 +14010,8 @@
         <v>426</v>
       </c>
       <c r="L186" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B186-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D186-1)/Inputs!$B$12,0)</f>
-        <v>81</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B186-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D186-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
@@ -14055,8 +14064,8 @@
         <v>426</v>
       </c>
       <c r="L187" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B187-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D187-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B187-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D187-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
@@ -14109,8 +14118,8 @@
         <v>426</v>
       </c>
       <c r="L188" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B188-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D188-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B188-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D188-1)/Inputs!$B$12,0))</f>
+        <v>11</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -14163,8 +14172,8 @@
         <v>426</v>
       </c>
       <c r="L189" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B189-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D189-1)/Inputs!$B$12,0)</f>
-        <v>123</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B189-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D189-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M189" s="4"/>
       <c r="N189" s="4"/>
@@ -14217,8 +14226,8 @@
         <v>426</v>
       </c>
       <c r="L190" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B190-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D190-1)/Inputs!$B$12,0)</f>
-        <v>141</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B190-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D190-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M190" s="4"/>
       <c r="N190" s="4"/>
@@ -14269,15 +14278,14 @@
         <v>426</v>
       </c>
       <c r="L191" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B191-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D191-1)/Inputs!$B$12,0)</f>
-        <v>162</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B191-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D191-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M191" s="6" t="s">
         <v>454</v>
       </c>
       <c r="N191" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O191" s="6" t="s">
         <v>427</v>
@@ -14329,8 +14337,8 @@
         <v>456</v>
       </c>
       <c r="L192" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B192-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D192-1)/Inputs!$B$12,0)</f>
-        <v>51</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B192-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D192-1)/Inputs!$B$12,0))</f>
+        <v>36</v>
       </c>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
@@ -14383,8 +14391,8 @@
         <v>456</v>
       </c>
       <c r="L193" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B193-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D193-1)/Inputs!$B$12,0)</f>
-        <v>58</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B193-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D193-1)/Inputs!$B$12,0))</f>
+        <v>41</v>
       </c>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
@@ -14437,8 +14445,8 @@
         <v>456</v>
       </c>
       <c r="L194" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B194-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D194-1)/Inputs!$B$12,0)</f>
-        <v>67</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B194-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D194-1)/Inputs!$B$12,0))</f>
+        <v>47</v>
       </c>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
@@ -14491,8 +14499,8 @@
         <v>456</v>
       </c>
       <c r="L195" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B195-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D195-1)/Inputs!$B$12,0)</f>
-        <v>77</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B195-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D195-1)/Inputs!$B$12,0))</f>
+        <v>54</v>
       </c>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
@@ -14545,8 +14553,8 @@
         <v>456</v>
       </c>
       <c r="L196" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B196-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D196-1)/Inputs!$B$12,0)</f>
-        <v>89</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B196-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D196-1)/Inputs!$B$12,0))</f>
+        <v>62</v>
       </c>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
@@ -14599,8 +14607,8 @@
         <v>456</v>
       </c>
       <c r="L197" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B197-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D197-1)/Inputs!$B$12,0)</f>
-        <v>102</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B197-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D197-1)/Inputs!$B$12,0))</f>
+        <v>72</v>
       </c>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
@@ -14653,8 +14661,8 @@
         <v>456</v>
       </c>
       <c r="L198" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B198-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D198-1)/Inputs!$B$12,0)</f>
-        <v>117</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B198-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D198-1)/Inputs!$B$12,0))</f>
+        <v>82</v>
       </c>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
@@ -14707,8 +14715,8 @@
         <v>456</v>
       </c>
       <c r="L199" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B199-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D199-1)/Inputs!$B$12,0)</f>
-        <v>135</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B199-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D199-1)/Inputs!$B$12,0))</f>
+        <v>95</v>
       </c>
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
@@ -14761,8 +14769,8 @@
         <v>456</v>
       </c>
       <c r="L200" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B200-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D200-1)/Inputs!$B$12,0)</f>
-        <v>155</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B200-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D200-1)/Inputs!$B$12,0))</f>
+        <v>109</v>
       </c>
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
@@ -14813,15 +14821,14 @@
         <v>456</v>
       </c>
       <c r="L201" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B201-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D201-1)/Inputs!$B$12,0)</f>
-        <v>179</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B201-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D201-1)/Inputs!$B$12,0))</f>
+        <v>125</v>
       </c>
       <c r="M201" s="6" t="s">
         <v>465</v>
       </c>
       <c r="N201" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O201" s="6" t="s">
         <v>427</v>
@@ -14873,8 +14880,8 @@
         <v>467</v>
       </c>
       <c r="L202" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B202-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D202-1)/Inputs!$B$12,0)</f>
-        <v>56</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B202-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D202-1)/Inputs!$B$12,0))</f>
+        <v>47</v>
       </c>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
@@ -14927,8 +14934,8 @@
         <v>467</v>
       </c>
       <c r="L203" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B203-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D203-1)/Inputs!$B$12,0)</f>
-        <v>64</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B203-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D203-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
@@ -14981,8 +14988,8 @@
         <v>467</v>
       </c>
       <c r="L204" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B204-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D204-1)/Inputs!$B$12,0)</f>
-        <v>74</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B204-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D204-1)/Inputs!$B$12,0))</f>
+        <v>63</v>
       </c>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
@@ -15035,8 +15042,8 @@
         <v>467</v>
       </c>
       <c r="L205" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B205-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D205-1)/Inputs!$B$12,0)</f>
-        <v>85</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B205-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D205-1)/Inputs!$B$12,0))</f>
+        <v>72</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
@@ -15089,8 +15096,8 @@
         <v>467</v>
       </c>
       <c r="L206" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B206-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D206-1)/Inputs!$B$12,0)</f>
-        <v>98</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B206-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D206-1)/Inputs!$B$12,0))</f>
+        <v>83</v>
       </c>
       <c r="M206" s="2"/>
       <c r="N206" s="2"/>
@@ -15143,8 +15150,8 @@
         <v>467</v>
       </c>
       <c r="L207" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B207-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D207-1)/Inputs!$B$12,0)</f>
-        <v>112</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B207-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D207-1)/Inputs!$B$12,0))</f>
+        <v>96</v>
       </c>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
@@ -15197,8 +15204,8 @@
         <v>467</v>
       </c>
       <c r="L208" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B208-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D208-1)/Inputs!$B$12,0)</f>
-        <v>129</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B208-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D208-1)/Inputs!$B$12,0))</f>
+        <v>110</v>
       </c>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
@@ -15251,8 +15258,8 @@
         <v>467</v>
       </c>
       <c r="L209" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B209-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D209-1)/Inputs!$B$12,0)</f>
-        <v>149</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B209-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D209-1)/Inputs!$B$12,0))</f>
+        <v>126</v>
       </c>
       <c r="M209" s="4"/>
       <c r="N209" s="4"/>
@@ -15305,8 +15312,8 @@
         <v>467</v>
       </c>
       <c r="L210" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B210-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D210-1)/Inputs!$B$12,0)</f>
-        <v>171</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B210-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D210-1)/Inputs!$B$12,0))</f>
+        <v>145</v>
       </c>
       <c r="M210" s="4"/>
       <c r="N210" s="4"/>
@@ -15357,14 +15364,13 @@
         <v>467</v>
       </c>
       <c r="L211" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B211-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D211-1)/Inputs!$B$12,0)</f>
-        <v>197</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B211-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D211-1)/Inputs!$B$12,0))</f>
+        <v>167</v>
       </c>
       <c r="M211" s="6" t="s">
         <v>476</v>
       </c>
       <c r="N211" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O211" s="6" t="s">
@@ -15417,8 +15423,8 @@
         <v>478</v>
       </c>
       <c r="L212" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B212-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D212-1)/Inputs!$B$12,0)</f>
-        <v>61</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B212-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D212-1)/Inputs!$B$12,0))</f>
+        <v>46</v>
       </c>
       <c r="M212" s="2"/>
       <c r="N212" s="2"/>
@@ -15471,8 +15477,8 @@
         <v>478</v>
       </c>
       <c r="L213" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B213-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D213-1)/Inputs!$B$12,0)</f>
-        <v>71</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B213-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D213-1)/Inputs!$B$12,0))</f>
+        <v>53</v>
       </c>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
@@ -15525,8 +15531,8 @@
         <v>478</v>
       </c>
       <c r="L214" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B214-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D214-1)/Inputs!$B$12,0)</f>
-        <v>81</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B214-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D214-1)/Inputs!$B$12,0))</f>
+        <v>61</v>
       </c>
       <c r="M214" s="2"/>
       <c r="N214" s="2"/>
@@ -15579,8 +15585,8 @@
         <v>478</v>
       </c>
       <c r="L215" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B215-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D215-1)/Inputs!$B$12,0)</f>
-        <v>93</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B215-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D215-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M215" s="2"/>
       <c r="N215" s="2"/>
@@ -15633,8 +15639,8 @@
         <v>478</v>
       </c>
       <c r="L216" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B216-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D216-1)/Inputs!$B$12,0)</f>
-        <v>107</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B216-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D216-1)/Inputs!$B$12,0))</f>
+        <v>81</v>
       </c>
       <c r="M216" s="2"/>
       <c r="N216" s="2"/>
@@ -15687,8 +15693,8 @@
         <v>478</v>
       </c>
       <c r="L217" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B217-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D217-1)/Inputs!$B$12,0)</f>
-        <v>124</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B217-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D217-1)/Inputs!$B$12,0))</f>
+        <v>93</v>
       </c>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
@@ -15741,8 +15747,8 @@
         <v>478</v>
       </c>
       <c r="L218" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B218-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D218-1)/Inputs!$B$12,0)</f>
-        <v>142</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B218-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D218-1)/Inputs!$B$12,0))</f>
+        <v>107</v>
       </c>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
@@ -15795,8 +15801,8 @@
         <v>478</v>
       </c>
       <c r="L219" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B219-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D219-1)/Inputs!$B$12,0)</f>
-        <v>163</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B219-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D219-1)/Inputs!$B$12,0))</f>
+        <v>123</v>
       </c>
       <c r="M219" s="4"/>
       <c r="N219" s="4"/>
@@ -15849,8 +15855,8 @@
         <v>478</v>
       </c>
       <c r="L220" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B220-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D220-1)/Inputs!$B$12,0)</f>
-        <v>188</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B220-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D220-1)/Inputs!$B$12,0))</f>
+        <v>141</v>
       </c>
       <c r="M220" s="4"/>
       <c r="N220" s="4"/>
@@ -15901,14 +15907,13 @@
         <v>478</v>
       </c>
       <c r="L221" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B221-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D221-1)/Inputs!$B$12,0)</f>
-        <v>216</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B221-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D221-1)/Inputs!$B$12,0))</f>
+        <v>162</v>
       </c>
       <c r="M221" s="6" t="s">
         <v>487</v>
       </c>
       <c r="N221" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O221" s="6" t="s">
@@ -15961,8 +15966,8 @@
         <v>489</v>
       </c>
       <c r="L222" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B222-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D222-1)/Inputs!$B$12,0)</f>
-        <v>68</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B222-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D222-1)/Inputs!$B$12,0))</f>
+        <v>51</v>
       </c>
       <c r="M222" s="2"/>
       <c r="N222" s="2"/>
@@ -16015,8 +16020,8 @@
         <v>489</v>
       </c>
       <c r="L223" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B223-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D223-1)/Inputs!$B$12,0)</f>
-        <v>78</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B223-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D223-1)/Inputs!$B$12,0))</f>
+        <v>58</v>
       </c>
       <c r="M223" s="2"/>
       <c r="N223" s="2"/>
@@ -16069,8 +16074,8 @@
         <v>489</v>
       </c>
       <c r="L224" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B224-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D224-1)/Inputs!$B$12,0)</f>
-        <v>89</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B224-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D224-1)/Inputs!$B$12,0))</f>
+        <v>67</v>
       </c>
       <c r="M224" s="2"/>
       <c r="N224" s="2"/>
@@ -16123,8 +16128,8 @@
         <v>489</v>
       </c>
       <c r="L225" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B225-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D225-1)/Inputs!$B$12,0)</f>
-        <v>103</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B225-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D225-1)/Inputs!$B$12,0))</f>
+        <v>77</v>
       </c>
       <c r="M225" s="2"/>
       <c r="N225" s="2"/>
@@ -16177,8 +16182,8 @@
         <v>489</v>
       </c>
       <c r="L226" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B226-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D226-1)/Inputs!$B$12,0)</f>
-        <v>118</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B226-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D226-1)/Inputs!$B$12,0))</f>
+        <v>89</v>
       </c>
       <c r="M226" s="2"/>
       <c r="N226" s="2"/>
@@ -16231,8 +16236,8 @@
         <v>489</v>
       </c>
       <c r="L227" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B227-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D227-1)/Inputs!$B$12,0)</f>
-        <v>136</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B227-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D227-1)/Inputs!$B$12,0))</f>
+        <v>102</v>
       </c>
       <c r="M227" s="2"/>
       <c r="N227" s="2"/>
@@ -16285,8 +16290,8 @@
         <v>489</v>
       </c>
       <c r="L228" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B228-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D228-1)/Inputs!$B$12,0)</f>
-        <v>156</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B228-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D228-1)/Inputs!$B$12,0))</f>
+        <v>117</v>
       </c>
       <c r="M228" s="2"/>
       <c r="N228" s="2"/>
@@ -16339,8 +16344,8 @@
         <v>489</v>
       </c>
       <c r="L229" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B229-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D229-1)/Inputs!$B$12,0)</f>
-        <v>180</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B229-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D229-1)/Inputs!$B$12,0))</f>
+        <v>135</v>
       </c>
       <c r="M229" s="4"/>
       <c r="N229" s="4"/>
@@ -16393,8 +16398,8 @@
         <v>489</v>
       </c>
       <c r="L230" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B230-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D230-1)/Inputs!$B$12,0)</f>
-        <v>207</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B230-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D230-1)/Inputs!$B$12,0))</f>
+        <v>155</v>
       </c>
       <c r="M230" s="4"/>
       <c r="N230" s="4"/>
@@ -16445,14 +16450,13 @@
         <v>489</v>
       </c>
       <c r="L231" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B231-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D231-1)/Inputs!$B$12,0)</f>
-        <v>238</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B231-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D231-1)/Inputs!$B$12,0))</f>
+        <v>178</v>
       </c>
       <c r="M231" s="6" t="s">
         <v>497</v>
       </c>
       <c r="N231" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O231" s="6" t="s">
@@ -16505,7 +16509,7 @@
         <v>499</v>
       </c>
       <c r="L232" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B232-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D232-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B232-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D232-1)/Inputs!$B$12,0))</f>
         <v>74</v>
       </c>
       <c r="M232" s="2"/>
@@ -16559,7 +16563,7 @@
         <v>499</v>
       </c>
       <c r="L233" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B233-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D233-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B233-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D233-1)/Inputs!$B$12,0))</f>
         <v>86</v>
       </c>
       <c r="M233" s="2"/>
@@ -16613,7 +16617,7 @@
         <v>499</v>
       </c>
       <c r="L234" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B234-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D234-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B234-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D234-1)/Inputs!$B$12,0))</f>
         <v>98</v>
       </c>
       <c r="M234" s="2"/>
@@ -16667,7 +16671,7 @@
         <v>499</v>
       </c>
       <c r="L235" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B235-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D235-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B235-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D235-1)/Inputs!$B$12,0))</f>
         <v>113</v>
       </c>
       <c r="M235" s="2"/>
@@ -16721,7 +16725,7 @@
         <v>499</v>
       </c>
       <c r="L236" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B236-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D236-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B236-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D236-1)/Inputs!$B$12,0))</f>
         <v>130</v>
       </c>
       <c r="M236" s="2"/>
@@ -16775,7 +16779,7 @@
         <v>499</v>
       </c>
       <c r="L237" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B237-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D237-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B237-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D237-1)/Inputs!$B$12,0))</f>
         <v>150</v>
       </c>
       <c r="M237" s="2"/>
@@ -16829,7 +16833,7 @@
         <v>499</v>
       </c>
       <c r="L238" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B238-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D238-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B238-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D238-1)/Inputs!$B$12,0))</f>
         <v>172</v>
       </c>
       <c r="M238" s="2"/>
@@ -16883,7 +16887,7 @@
         <v>499</v>
       </c>
       <c r="L239" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B239-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D239-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B239-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D239-1)/Inputs!$B$12,0))</f>
         <v>198</v>
       </c>
       <c r="M239" s="4"/>
@@ -16937,7 +16941,7 @@
         <v>499</v>
       </c>
       <c r="L240" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B240-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D240-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B240-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D240-1)/Inputs!$B$12,0))</f>
         <v>227</v>
       </c>
       <c r="M240" s="4"/>
@@ -16989,14 +16993,13 @@
         <v>499</v>
       </c>
       <c r="L241" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B241-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D241-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B241-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D241-1)/Inputs!$B$12,0))</f>
         <v>262</v>
       </c>
       <c r="M241" s="6" t="s">
         <v>508</v>
       </c>
       <c r="N241" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O241" s="6" t="s">
@@ -17049,8 +17052,8 @@
         <v>512</v>
       </c>
       <c r="L242" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B242-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D242-1)/Inputs!$B$12,0)</f>
-        <v>26</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B242-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D242-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
@@ -17103,8 +17106,8 @@
         <v>512</v>
       </c>
       <c r="L243" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B243-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D243-1)/Inputs!$B$12,0)</f>
-        <v>30</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B243-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D243-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
@@ -17157,8 +17160,8 @@
         <v>512</v>
       </c>
       <c r="L244" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B244-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D244-1)/Inputs!$B$12,0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B244-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D244-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
@@ -17211,8 +17214,8 @@
         <v>512</v>
       </c>
       <c r="L245" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B245-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D245-1)/Inputs!$B$12,0)</f>
-        <v>39</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B245-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D245-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
@@ -17265,8 +17268,8 @@
         <v>512</v>
       </c>
       <c r="L246" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B246-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D246-1)/Inputs!$B$12,0)</f>
-        <v>45</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B246-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D246-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
@@ -17319,8 +17322,8 @@
         <v>512</v>
       </c>
       <c r="L247" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B247-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D247-1)/Inputs!$B$12,0)</f>
-        <v>52</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B247-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D247-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
@@ -17373,8 +17376,8 @@
         <v>512</v>
       </c>
       <c r="L248" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B248-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D248-1)/Inputs!$B$12,0)</f>
-        <v>60</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B248-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D248-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
@@ -17427,8 +17430,8 @@
         <v>512</v>
       </c>
       <c r="L249" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B249-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D249-1)/Inputs!$B$12,0)</f>
-        <v>69</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B249-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D249-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
@@ -17481,8 +17484,8 @@
         <v>512</v>
       </c>
       <c r="L250" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B250-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D250-1)/Inputs!$B$12,0)</f>
-        <v>79</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B250-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D250-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
@@ -17533,15 +17536,14 @@
         <v>512</v>
       </c>
       <c r="L251" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B251-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D251-1)/Inputs!$B$12,0)</f>
-        <v>91</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B251-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D251-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M251" s="6" t="s">
         <v>536</v>
       </c>
       <c r="N251" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O251" s="6" t="s">
         <v>513</v>
@@ -17593,8 +17595,8 @@
         <v>538</v>
       </c>
       <c r="L252" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B252-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D252-1)/Inputs!$B$12,0)</f>
-        <v>28</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B252-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D252-1)/Inputs!$B$12,0))</f>
+        <v>20</v>
       </c>
       <c r="M252" s="2"/>
       <c r="N252" s="2"/>
@@ -17647,8 +17649,8 @@
         <v>538</v>
       </c>
       <c r="L253" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B253-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D253-1)/Inputs!$B$12,0)</f>
-        <v>33</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B253-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D253-1)/Inputs!$B$12,0))</f>
+        <v>23</v>
       </c>
       <c r="M253" s="2"/>
       <c r="N253" s="2"/>
@@ -17701,8 +17703,8 @@
         <v>538</v>
       </c>
       <c r="L254" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B254-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D254-1)/Inputs!$B$12,0)</f>
-        <v>38</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B254-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D254-1)/Inputs!$B$12,0))</f>
+        <v>26</v>
       </c>
       <c r="M254" s="2"/>
       <c r="N254" s="2"/>
@@ -17755,8 +17757,8 @@
         <v>538</v>
       </c>
       <c r="L255" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B255-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D255-1)/Inputs!$B$12,0)</f>
-        <v>43</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B255-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D255-1)/Inputs!$B$12,0))</f>
+        <v>30</v>
       </c>
       <c r="M255" s="2"/>
       <c r="N255" s="2"/>
@@ -17809,8 +17811,8 @@
         <v>538</v>
       </c>
       <c r="L256" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B256-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D256-1)/Inputs!$B$12,0)</f>
-        <v>50</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B256-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D256-1)/Inputs!$B$12,0))</f>
+        <v>35</v>
       </c>
       <c r="M256" s="2"/>
       <c r="N256" s="2"/>
@@ -17863,8 +17865,8 @@
         <v>538</v>
       </c>
       <c r="L257" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B257-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D257-1)/Inputs!$B$12,0)</f>
-        <v>57</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B257-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D257-1)/Inputs!$B$12,0))</f>
+        <v>40</v>
       </c>
       <c r="M257" s="2"/>
       <c r="N257" s="2"/>
@@ -17917,8 +17919,8 @@
         <v>538</v>
       </c>
       <c r="L258" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B258-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D258-1)/Inputs!$B$12,0)</f>
-        <v>66</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B258-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D258-1)/Inputs!$B$12,0))</f>
+        <v>46</v>
       </c>
       <c r="M258" s="2"/>
       <c r="N258" s="2"/>
@@ -17971,8 +17973,8 @@
         <v>538</v>
       </c>
       <c r="L259" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B259-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D259-1)/Inputs!$B$12,0)</f>
-        <v>76</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B259-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D259-1)/Inputs!$B$12,0))</f>
+        <v>53</v>
       </c>
       <c r="M259" s="4"/>
       <c r="N259" s="4"/>
@@ -18025,8 +18027,8 @@
         <v>538</v>
       </c>
       <c r="L260" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B260-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D260-1)/Inputs!$B$12,0)</f>
-        <v>87</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B260-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D260-1)/Inputs!$B$12,0))</f>
+        <v>61</v>
       </c>
       <c r="M260" s="4"/>
       <c r="N260" s="4"/>
@@ -18077,15 +18079,14 @@
         <v>538</v>
       </c>
       <c r="L261" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B261-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D261-1)/Inputs!$B$12,0)</f>
-        <v>100</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B261-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D261-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M261" s="6" t="s">
         <v>546</v>
       </c>
       <c r="N261" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O261" s="6" t="s">
         <v>513</v>
@@ -18137,8 +18138,8 @@
         <v>548</v>
       </c>
       <c r="L262" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B262-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D262-1)/Inputs!$B$12,0)</f>
-        <v>31</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B262-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D262-1)/Inputs!$B$12,0))</f>
+        <v>27</v>
       </c>
       <c r="M262" s="2"/>
       <c r="N262" s="2"/>
@@ -18191,8 +18192,8 @@
         <v>548</v>
       </c>
       <c r="L263" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B263-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D263-1)/Inputs!$B$12,0)</f>
-        <v>36</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B263-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D263-1)/Inputs!$B$12,0))</f>
+        <v>31</v>
       </c>
       <c r="M263" s="2"/>
       <c r="N263" s="2"/>
@@ -18245,8 +18246,8 @@
         <v>548</v>
       </c>
       <c r="L264" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B264-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D264-1)/Inputs!$B$12,0)</f>
-        <v>41</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B264-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D264-1)/Inputs!$B$12,0))</f>
+        <v>35</v>
       </c>
       <c r="M264" s="2"/>
       <c r="N264" s="2"/>
@@ -18299,8 +18300,8 @@
         <v>548</v>
       </c>
       <c r="L265" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B265-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D265-1)/Inputs!$B$12,0)</f>
-        <v>48</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B265-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D265-1)/Inputs!$B$12,0))</f>
+        <v>40</v>
       </c>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
@@ -18353,8 +18354,8 @@
         <v>548</v>
       </c>
       <c r="L266" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B266-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D266-1)/Inputs!$B$12,0)</f>
-        <v>55</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B266-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D266-1)/Inputs!$B$12,0))</f>
+        <v>47</v>
       </c>
       <c r="M266" s="2"/>
       <c r="N266" s="2"/>
@@ -18407,8 +18408,8 @@
         <v>548</v>
       </c>
       <c r="L267" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B267-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D267-1)/Inputs!$B$12,0)</f>
-        <v>63</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B267-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D267-1)/Inputs!$B$12,0))</f>
+        <v>53</v>
       </c>
       <c r="M267" s="2"/>
       <c r="N267" s="2"/>
@@ -18461,8 +18462,8 @@
         <v>548</v>
       </c>
       <c r="L268" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B268-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D268-1)/Inputs!$B$12,0)</f>
-        <v>72</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B268-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D268-1)/Inputs!$B$12,0))</f>
+        <v>62</v>
       </c>
       <c r="M268" s="2"/>
       <c r="N268" s="2"/>
@@ -18515,8 +18516,8 @@
         <v>548</v>
       </c>
       <c r="L269" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B269-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D269-1)/Inputs!$B$12,0)</f>
-        <v>83</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B269-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D269-1)/Inputs!$B$12,0))</f>
+        <v>71</v>
       </c>
       <c r="M269" s="4"/>
       <c r="N269" s="4"/>
@@ -18569,8 +18570,8 @@
         <v>548</v>
       </c>
       <c r="L270" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B270-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D270-1)/Inputs!$B$12,0)</f>
-        <v>96</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B270-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D270-1)/Inputs!$B$12,0))</f>
+        <v>81</v>
       </c>
       <c r="M270" s="4"/>
       <c r="N270" s="4"/>
@@ -18621,14 +18622,13 @@
         <v>548</v>
       </c>
       <c r="L271" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B271-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D271-1)/Inputs!$B$12,0)</f>
-        <v>110</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B271-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D271-1)/Inputs!$B$12,0))</f>
+        <v>94</v>
       </c>
       <c r="M271" s="6" t="s">
         <v>555</v>
       </c>
       <c r="N271" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O271" s="6" t="s">
@@ -18681,8 +18681,8 @@
         <v>557</v>
       </c>
       <c r="L272" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B272-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D272-1)/Inputs!$B$12,0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B272-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D272-1)/Inputs!$B$12,0))</f>
+        <v>26</v>
       </c>
       <c r="M272" s="2"/>
       <c r="N272" s="2"/>
@@ -18735,8 +18735,8 @@
         <v>557</v>
       </c>
       <c r="L273" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B273-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D273-1)/Inputs!$B$12,0)</f>
-        <v>40</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B273-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D273-1)/Inputs!$B$12,0))</f>
+        <v>30</v>
       </c>
       <c r="M273" s="2"/>
       <c r="N273" s="2"/>
@@ -18789,8 +18789,8 @@
         <v>557</v>
       </c>
       <c r="L274" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B274-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D274-1)/Inputs!$B$12,0)</f>
-        <v>46</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B274-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D274-1)/Inputs!$B$12,0))</f>
+        <v>34</v>
       </c>
       <c r="M274" s="2"/>
       <c r="N274" s="2"/>
@@ -18843,8 +18843,8 @@
         <v>557</v>
       </c>
       <c r="L275" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B275-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D275-1)/Inputs!$B$12,0)</f>
-        <v>52</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B275-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D275-1)/Inputs!$B$12,0))</f>
+        <v>39</v>
       </c>
       <c r="M275" s="2"/>
       <c r="N275" s="2"/>
@@ -18897,8 +18897,8 @@
         <v>557</v>
       </c>
       <c r="L276" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B276-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D276-1)/Inputs!$B$12,0)</f>
-        <v>60</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B276-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D276-1)/Inputs!$B$12,0))</f>
+        <v>45</v>
       </c>
       <c r="M276" s="2"/>
       <c r="N276" s="2"/>
@@ -18951,8 +18951,8 @@
         <v>557</v>
       </c>
       <c r="L277" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B277-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D277-1)/Inputs!$B$12,0)</f>
-        <v>69</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B277-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D277-1)/Inputs!$B$12,0))</f>
+        <v>52</v>
       </c>
       <c r="M277" s="2"/>
       <c r="N277" s="2"/>
@@ -19005,8 +19005,8 @@
         <v>557</v>
       </c>
       <c r="L278" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B278-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D278-1)/Inputs!$B$12,0)</f>
-        <v>80</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B278-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D278-1)/Inputs!$B$12,0))</f>
+        <v>60</v>
       </c>
       <c r="M278" s="2"/>
       <c r="N278" s="2"/>
@@ -19059,8 +19059,8 @@
         <v>557</v>
       </c>
       <c r="L279" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B279-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D279-1)/Inputs!$B$12,0)</f>
-        <v>92</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B279-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D279-1)/Inputs!$B$12,0))</f>
+        <v>69</v>
       </c>
       <c r="M279" s="4"/>
       <c r="N279" s="4"/>
@@ -19113,8 +19113,8 @@
         <v>557</v>
       </c>
       <c r="L280" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B280-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D280-1)/Inputs!$B$12,0)</f>
-        <v>105</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B280-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D280-1)/Inputs!$B$12,0))</f>
+        <v>79</v>
       </c>
       <c r="M280" s="4"/>
       <c r="N280" s="4"/>
@@ -19165,14 +19165,13 @@
         <v>557</v>
       </c>
       <c r="L281" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B281-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D281-1)/Inputs!$B$12,0)</f>
-        <v>121</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B281-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D281-1)/Inputs!$B$12,0))</f>
+        <v>91</v>
       </c>
       <c r="M281" s="6" t="s">
         <v>565</v>
       </c>
       <c r="N281" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O281" s="6" t="s">
@@ -19225,8 +19224,8 @@
         <v>567</v>
       </c>
       <c r="L282" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B282-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D282-1)/Inputs!$B$12,0)</f>
-        <v>38</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B282-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D282-1)/Inputs!$B$12,0))</f>
+        <v>28</v>
       </c>
       <c r="M282" s="2"/>
       <c r="N282" s="2"/>
@@ -19279,8 +19278,8 @@
         <v>567</v>
       </c>
       <c r="L283" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B283-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D283-1)/Inputs!$B$12,0)</f>
-        <v>44</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B283-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D283-1)/Inputs!$B$12,0))</f>
+        <v>33</v>
       </c>
       <c r="M283" s="2"/>
       <c r="N283" s="2"/>
@@ -19333,8 +19332,8 @@
         <v>567</v>
       </c>
       <c r="L284" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B284-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D284-1)/Inputs!$B$12,0)</f>
-        <v>50</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B284-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D284-1)/Inputs!$B$12,0))</f>
+        <v>38</v>
       </c>
       <c r="M284" s="2"/>
       <c r="N284" s="2"/>
@@ -19387,8 +19386,8 @@
         <v>567</v>
       </c>
       <c r="L285" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B285-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D285-1)/Inputs!$B$12,0)</f>
-        <v>58</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B285-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D285-1)/Inputs!$B$12,0))</f>
+        <v>43</v>
       </c>
       <c r="M285" s="2"/>
       <c r="N285" s="2"/>
@@ -19441,8 +19440,8 @@
         <v>567</v>
       </c>
       <c r="L286" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B286-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D286-1)/Inputs!$B$12,0)</f>
-        <v>66</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B286-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D286-1)/Inputs!$B$12,0))</f>
+        <v>50</v>
       </c>
       <c r="M286" s="2"/>
       <c r="N286" s="2"/>
@@ -19495,8 +19494,8 @@
         <v>567</v>
       </c>
       <c r="L287" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B287-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D287-1)/Inputs!$B$12,0)</f>
-        <v>76</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B287-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D287-1)/Inputs!$B$12,0))</f>
+        <v>57</v>
       </c>
       <c r="M287" s="2"/>
       <c r="N287" s="2"/>
@@ -19549,8 +19548,8 @@
         <v>567</v>
       </c>
       <c r="L288" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B288-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D288-1)/Inputs!$B$12,0)</f>
-        <v>88</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B288-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D288-1)/Inputs!$B$12,0))</f>
+        <v>66</v>
       </c>
       <c r="M288" s="2"/>
       <c r="N288" s="2"/>
@@ -19603,8 +19602,8 @@
         <v>567</v>
       </c>
       <c r="L289" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B289-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D289-1)/Inputs!$B$12,0)</f>
-        <v>101</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B289-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D289-1)/Inputs!$B$12,0))</f>
+        <v>76</v>
       </c>
       <c r="M289" s="4"/>
       <c r="N289" s="4"/>
@@ -19657,8 +19656,8 @@
         <v>567</v>
       </c>
       <c r="L290" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B290-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D290-1)/Inputs!$B$12,0)</f>
-        <v>116</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B290-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D290-1)/Inputs!$B$12,0))</f>
+        <v>87</v>
       </c>
       <c r="M290" s="4"/>
       <c r="N290" s="4"/>
@@ -19709,14 +19708,13 @@
         <v>567</v>
       </c>
       <c r="L291" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B291-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D291-1)/Inputs!$B$12,0)</f>
-        <v>133</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B291-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D291-1)/Inputs!$B$12,0))</f>
+        <v>100</v>
       </c>
       <c r="M291" s="6" t="s">
         <v>573</v>
       </c>
       <c r="N291" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O291" s="6" t="s">
@@ -19769,7 +19767,7 @@
         <v>575</v>
       </c>
       <c r="L292" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B292-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D292-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B292-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D292-1)/Inputs!$B$12,0))</f>
         <v>42</v>
       </c>
       <c r="M292" s="2"/>
@@ -19823,7 +19821,7 @@
         <v>575</v>
       </c>
       <c r="L293" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B293-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D293-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B293-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D293-1)/Inputs!$B$12,0))</f>
         <v>48</v>
       </c>
       <c r="M293" s="2"/>
@@ -19877,7 +19875,7 @@
         <v>575</v>
       </c>
       <c r="L294" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B294-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D294-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B294-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D294-1)/Inputs!$B$12,0))</f>
         <v>55</v>
       </c>
       <c r="M294" s="2"/>
@@ -19931,7 +19929,7 @@
         <v>575</v>
       </c>
       <c r="L295" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B295-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D295-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B295-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D295-1)/Inputs!$B$12,0))</f>
         <v>63</v>
       </c>
       <c r="M295" s="2"/>
@@ -19985,7 +19983,7 @@
         <v>575</v>
       </c>
       <c r="L296" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B296-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D296-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B296-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D296-1)/Inputs!$B$12,0))</f>
         <v>73</v>
       </c>
       <c r="M296" s="2"/>
@@ -20039,7 +20037,7 @@
         <v>575</v>
       </c>
       <c r="L297" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B297-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D297-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B297-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D297-1)/Inputs!$B$12,0))</f>
         <v>84</v>
       </c>
       <c r="M297" s="2"/>
@@ -20093,7 +20091,7 @@
         <v>575</v>
       </c>
       <c r="L298" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B298-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D298-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B298-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D298-1)/Inputs!$B$12,0))</f>
         <v>96</v>
       </c>
       <c r="M298" s="2"/>
@@ -20147,7 +20145,7 @@
         <v>575</v>
       </c>
       <c r="L299" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B299-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D299-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B299-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D299-1)/Inputs!$B$12,0))</f>
         <v>111</v>
       </c>
       <c r="M299" s="4"/>
@@ -20201,7 +20199,7 @@
         <v>575</v>
       </c>
       <c r="L300" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B300-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D300-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B300-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D300-1)/Inputs!$B$12,0))</f>
         <v>127</v>
       </c>
       <c r="M300" s="4"/>
@@ -20253,14 +20251,13 @@
         <v>575</v>
       </c>
       <c r="L301" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B301-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D301-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B301-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D301-1)/Inputs!$B$12,0))</f>
         <v>146</v>
       </c>
       <c r="M301" s="6" t="s">
         <v>583</v>
       </c>
       <c r="N301" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O301" s="6" t="s">
@@ -20313,8 +20310,8 @@
         <v>587</v>
       </c>
       <c r="L302" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B302-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D302-1)/Inputs!$B$12,0)</f>
-        <v>41</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B302-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D302-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
@@ -20367,8 +20364,8 @@
         <v>587</v>
       </c>
       <c r="L303" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B303-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D303-1)/Inputs!$B$12,0)</f>
-        <v>47</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B303-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D303-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
@@ -20421,8 +20418,8 @@
         <v>587</v>
       </c>
       <c r="L304" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B304-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D304-1)/Inputs!$B$12,0)</f>
-        <v>54</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B304-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D304-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
@@ -20475,8 +20472,8 @@
         <v>587</v>
       </c>
       <c r="L305" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B305-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D305-1)/Inputs!$B$12,0)</f>
-        <v>62</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B305-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D305-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
@@ -20529,8 +20526,8 @@
         <v>587</v>
       </c>
       <c r="L306" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B306-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D306-1)/Inputs!$B$12,0)</f>
-        <v>71</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B306-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D306-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -20583,8 +20580,8 @@
         <v>587</v>
       </c>
       <c r="L307" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B307-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D307-1)/Inputs!$B$12,0)</f>
-        <v>82</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B307-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D307-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -20637,8 +20634,8 @@
         <v>587</v>
       </c>
       <c r="L308" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B308-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D308-1)/Inputs!$B$12,0)</f>
-        <v>94</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B308-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D308-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
@@ -20691,8 +20688,8 @@
         <v>587</v>
       </c>
       <c r="L309" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B309-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D309-1)/Inputs!$B$12,0)</f>
-        <v>108</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B309-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D309-1)/Inputs!$B$12,0))</f>
+        <v>11</v>
       </c>
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
@@ -20745,8 +20742,8 @@
         <v>587</v>
       </c>
       <c r="L310" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B310-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D310-1)/Inputs!$B$12,0)</f>
-        <v>124</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B310-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D310-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
@@ -20797,15 +20794,14 @@
         <v>587</v>
       </c>
       <c r="L311" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B311-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D311-1)/Inputs!$B$12,0)</f>
-        <v>143</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B311-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D311-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M311" s="6" t="s">
         <v>91</v>
       </c>
       <c r="N311" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O311" s="6" t="s">
         <v>588</v>
@@ -20857,8 +20853,8 @@
         <v>587</v>
       </c>
       <c r="L312" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B312-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D312-1)/Inputs!$B$12,0)</f>
-        <v>45</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B312-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D312-1)/Inputs!$B$12,0))</f>
+        <v>31</v>
       </c>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -20911,8 +20907,8 @@
         <v>587</v>
       </c>
       <c r="L313" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B313-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D313-1)/Inputs!$B$12,0)</f>
-        <v>51</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B313-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D313-1)/Inputs!$B$12,0))</f>
+        <v>36</v>
       </c>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -20965,8 +20961,8 @@
         <v>587</v>
       </c>
       <c r="L314" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B314-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D314-1)/Inputs!$B$12,0)</f>
-        <v>59</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B314-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D314-1)/Inputs!$B$12,0))</f>
+        <v>41</v>
       </c>
       <c r="M314" s="2"/>
       <c r="N314" s="2"/>
@@ -21019,8 +21015,8 @@
         <v>587</v>
       </c>
       <c r="L315" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B315-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D315-1)/Inputs!$B$12,0)</f>
-        <v>68</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B315-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D315-1)/Inputs!$B$12,0))</f>
+        <v>48</v>
       </c>
       <c r="M315" s="2"/>
       <c r="N315" s="2"/>
@@ -21073,8 +21069,8 @@
         <v>587</v>
       </c>
       <c r="L316" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B316-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D316-1)/Inputs!$B$12,0)</f>
-        <v>78</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B316-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D316-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M316" s="2"/>
       <c r="N316" s="2"/>
@@ -21127,8 +21123,8 @@
         <v>587</v>
       </c>
       <c r="L317" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B317-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D317-1)/Inputs!$B$12,0)</f>
-        <v>90</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B317-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D317-1)/Inputs!$B$12,0))</f>
+        <v>63</v>
       </c>
       <c r="M317" s="2"/>
       <c r="N317" s="2"/>
@@ -21181,8 +21177,8 @@
         <v>587</v>
       </c>
       <c r="L318" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B318-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D318-1)/Inputs!$B$12,0)</f>
-        <v>103</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B318-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D318-1)/Inputs!$B$12,0))</f>
+        <v>72</v>
       </c>
       <c r="M318" s="2"/>
       <c r="N318" s="2"/>
@@ -21235,8 +21231,8 @@
         <v>587</v>
       </c>
       <c r="L319" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B319-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D319-1)/Inputs!$B$12,0)</f>
-        <v>119</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B319-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D319-1)/Inputs!$B$12,0))</f>
+        <v>83</v>
       </c>
       <c r="M319" s="4"/>
       <c r="N319" s="4"/>
@@ -21289,8 +21285,8 @@
         <v>587</v>
       </c>
       <c r="L320" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B320-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D320-1)/Inputs!$B$12,0)</f>
-        <v>137</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B320-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D320-1)/Inputs!$B$12,0))</f>
+        <v>96</v>
       </c>
       <c r="M320" s="4"/>
       <c r="N320" s="4"/>
@@ -21341,15 +21337,14 @@
         <v>587</v>
       </c>
       <c r="L321" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B321-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D321-1)/Inputs!$B$12,0)</f>
-        <v>157</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B321-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D321-1)/Inputs!$B$12,0))</f>
+        <v>110</v>
       </c>
       <c r="M321" s="6" t="s">
         <v>118</v>
       </c>
       <c r="N321" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O321" s="6" t="s">
         <v>588</v>
@@ -21401,8 +21396,8 @@
         <v>587</v>
       </c>
       <c r="L322" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B322-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D322-1)/Inputs!$B$12,0)</f>
-        <v>49</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B322-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D322-1)/Inputs!$B$12,0))</f>
+        <v>42</v>
       </c>
       <c r="M322" s="2"/>
       <c r="N322" s="2"/>
@@ -21455,8 +21450,8 @@
         <v>587</v>
       </c>
       <c r="L323" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B323-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D323-1)/Inputs!$B$12,0)</f>
-        <v>57</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B323-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D323-1)/Inputs!$B$12,0))</f>
+        <v>48</v>
       </c>
       <c r="M323" s="2"/>
       <c r="N323" s="2"/>
@@ -21509,8 +21504,8 @@
         <v>587</v>
       </c>
       <c r="L324" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B324-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D324-1)/Inputs!$B$12,0)</f>
-        <v>65</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B324-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D324-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M324" s="2"/>
       <c r="N324" s="2"/>
@@ -21563,8 +21558,8 @@
         <v>587</v>
       </c>
       <c r="L325" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B325-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D325-1)/Inputs!$B$12,0)</f>
-        <v>75</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B325-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D325-1)/Inputs!$B$12,0))</f>
+        <v>64</v>
       </c>
       <c r="M325" s="2"/>
       <c r="N325" s="2"/>
@@ -21617,8 +21612,8 @@
         <v>587</v>
       </c>
       <c r="L326" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B326-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D326-1)/Inputs!$B$12,0)</f>
-        <v>86</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B326-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D326-1)/Inputs!$B$12,0))</f>
+        <v>73</v>
       </c>
       <c r="M326" s="2"/>
       <c r="N326" s="2"/>
@@ -21671,8 +21666,8 @@
         <v>587</v>
       </c>
       <c r="L327" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B327-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D327-1)/Inputs!$B$12,0)</f>
-        <v>99</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B327-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D327-1)/Inputs!$B$12,0))</f>
+        <v>84</v>
       </c>
       <c r="M327" s="2"/>
       <c r="N327" s="2"/>
@@ -21725,8 +21720,8 @@
         <v>587</v>
       </c>
       <c r="L328" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B328-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D328-1)/Inputs!$B$12,0)</f>
-        <v>114</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B328-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D328-1)/Inputs!$B$12,0))</f>
+        <v>97</v>
       </c>
       <c r="M328" s="2"/>
       <c r="N328" s="2"/>
@@ -21779,8 +21774,8 @@
         <v>587</v>
       </c>
       <c r="L329" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B329-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D329-1)/Inputs!$B$12,0)</f>
-        <v>131</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B329-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D329-1)/Inputs!$B$12,0))</f>
+        <v>111</v>
       </c>
       <c r="M329" s="4"/>
       <c r="N329" s="4"/>
@@ -21833,8 +21828,8 @@
         <v>587</v>
       </c>
       <c r="L330" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B330-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D330-1)/Inputs!$B$12,0)</f>
-        <v>150</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B330-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D330-1)/Inputs!$B$12,0))</f>
+        <v>128</v>
       </c>
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
@@ -21885,14 +21880,13 @@
         <v>587</v>
       </c>
       <c r="L331" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B331-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D331-1)/Inputs!$B$12,0)</f>
-        <v>173</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B331-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D331-1)/Inputs!$B$12,0))</f>
+        <v>147</v>
       </c>
       <c r="M331" s="6" t="s">
         <v>144</v>
       </c>
       <c r="N331" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O331" s="6" t="s">
@@ -21945,8 +21939,8 @@
         <v>587</v>
       </c>
       <c r="L332" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B332-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D332-1)/Inputs!$B$12,0)</f>
-        <v>54</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B332-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D332-1)/Inputs!$B$12,0))</f>
+        <v>41</v>
       </c>
       <c r="M332" s="2"/>
       <c r="N332" s="2"/>
@@ -21999,8 +21993,8 @@
         <v>587</v>
       </c>
       <c r="L333" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B333-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D333-1)/Inputs!$B$12,0)</f>
-        <v>62</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B333-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D333-1)/Inputs!$B$12,0))</f>
+        <v>47</v>
       </c>
       <c r="M333" s="2"/>
       <c r="N333" s="2"/>
@@ -22053,8 +22047,8 @@
         <v>587</v>
       </c>
       <c r="L334" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B334-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D334-1)/Inputs!$B$12,0)</f>
-        <v>72</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B334-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D334-1)/Inputs!$B$12,0))</f>
+        <v>54</v>
       </c>
       <c r="M334" s="2"/>
       <c r="N334" s="2"/>
@@ -22107,8 +22101,8 @@
         <v>587</v>
       </c>
       <c r="L335" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B335-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D335-1)/Inputs!$B$12,0)</f>
-        <v>82</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B335-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D335-1)/Inputs!$B$12,0))</f>
+        <v>62</v>
       </c>
       <c r="M335" s="2"/>
       <c r="N335" s="2"/>
@@ -22161,8 +22155,8 @@
         <v>587</v>
       </c>
       <c r="L336" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B336-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D336-1)/Inputs!$B$12,0)</f>
-        <v>95</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B336-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D336-1)/Inputs!$B$12,0))</f>
+        <v>71</v>
       </c>
       <c r="M336" s="2"/>
       <c r="N336" s="2"/>
@@ -22215,8 +22209,8 @@
         <v>587</v>
       </c>
       <c r="L337" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B337-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D337-1)/Inputs!$B$12,0)</f>
-        <v>109</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B337-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D337-1)/Inputs!$B$12,0))</f>
+        <v>82</v>
       </c>
       <c r="M337" s="2"/>
       <c r="N337" s="2"/>
@@ -22269,8 +22263,8 @@
         <v>587</v>
       </c>
       <c r="L338" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B338-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D338-1)/Inputs!$B$12,0)</f>
-        <v>125</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B338-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D338-1)/Inputs!$B$12,0))</f>
+        <v>94</v>
       </c>
       <c r="M338" s="2"/>
       <c r="N338" s="2"/>
@@ -22323,8 +22317,8 @@
         <v>587</v>
       </c>
       <c r="L339" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B339-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D339-1)/Inputs!$B$12,0)</f>
-        <v>144</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B339-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D339-1)/Inputs!$B$12,0))</f>
+        <v>108</v>
       </c>
       <c r="M339" s="4"/>
       <c r="N339" s="4"/>
@@ -22377,8 +22371,8 @@
         <v>587</v>
       </c>
       <c r="L340" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B340-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D340-1)/Inputs!$B$12,0)</f>
-        <v>165</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B340-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D340-1)/Inputs!$B$12,0))</f>
+        <v>124</v>
       </c>
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
@@ -22429,14 +22423,13 @@
         <v>587</v>
       </c>
       <c r="L341" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B341-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D341-1)/Inputs!$B$12,0)</f>
-        <v>190</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B341-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D341-1)/Inputs!$B$12,0))</f>
+        <v>143</v>
       </c>
       <c r="M341" s="6" t="s">
         <v>170</v>
       </c>
       <c r="N341" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O341" s="6" t="s">
@@ -22489,8 +22482,8 @@
         <v>587</v>
       </c>
       <c r="L342" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B342-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D342-1)/Inputs!$B$12,0)</f>
-        <v>59</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B342-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D342-1)/Inputs!$B$12,0))</f>
+        <v>45</v>
       </c>
       <c r="M342" s="2"/>
       <c r="N342" s="2"/>
@@ -22543,8 +22536,8 @@
         <v>587</v>
       </c>
       <c r="L343" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B343-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D343-1)/Inputs!$B$12,0)</f>
-        <v>68</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B343-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D343-1)/Inputs!$B$12,0))</f>
+        <v>51</v>
       </c>
       <c r="M343" s="2"/>
       <c r="N343" s="2"/>
@@ -22597,8 +22590,8 @@
         <v>587</v>
       </c>
       <c r="L344" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B344-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D344-1)/Inputs!$B$12,0)</f>
-        <v>79</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B344-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D344-1)/Inputs!$B$12,0))</f>
+        <v>59</v>
       </c>
       <c r="M344" s="2"/>
       <c r="N344" s="2"/>
@@ -22651,8 +22644,8 @@
         <v>587</v>
       </c>
       <c r="L345" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B345-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D345-1)/Inputs!$B$12,0)</f>
-        <v>90</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B345-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D345-1)/Inputs!$B$12,0))</f>
+        <v>68</v>
       </c>
       <c r="M345" s="2"/>
       <c r="N345" s="2"/>
@@ -22705,8 +22698,8 @@
         <v>587</v>
       </c>
       <c r="L346" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B346-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D346-1)/Inputs!$B$12,0)</f>
-        <v>104</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B346-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D346-1)/Inputs!$B$12,0))</f>
+        <v>78</v>
       </c>
       <c r="M346" s="2"/>
       <c r="N346" s="2"/>
@@ -22759,8 +22752,8 @@
         <v>587</v>
       </c>
       <c r="L347" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B347-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D347-1)/Inputs!$B$12,0)</f>
-        <v>120</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B347-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D347-1)/Inputs!$B$12,0))</f>
+        <v>90</v>
       </c>
       <c r="M347" s="2"/>
       <c r="N347" s="2"/>
@@ -22813,8 +22806,8 @@
         <v>587</v>
       </c>
       <c r="L348" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B348-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D348-1)/Inputs!$B$12,0)</f>
-        <v>138</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B348-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D348-1)/Inputs!$B$12,0))</f>
+        <v>103</v>
       </c>
       <c r="M348" s="2"/>
       <c r="N348" s="2"/>
@@ -22867,8 +22860,8 @@
         <v>587</v>
       </c>
       <c r="L349" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B349-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D349-1)/Inputs!$B$12,0)</f>
-        <v>158</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B349-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D349-1)/Inputs!$B$12,0))</f>
+        <v>119</v>
       </c>
       <c r="M349" s="4"/>
       <c r="N349" s="4"/>
@@ -22921,8 +22914,8 @@
         <v>587</v>
       </c>
       <c r="L350" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B350-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D350-1)/Inputs!$B$12,0)</f>
-        <v>182</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B350-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D350-1)/Inputs!$B$12,0))</f>
+        <v>136</v>
       </c>
       <c r="M350" s="4"/>
       <c r="N350" s="4"/>
@@ -22973,14 +22966,13 @@
         <v>587</v>
       </c>
       <c r="L351" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B351-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D351-1)/Inputs!$B$12,0)</f>
-        <v>209</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B351-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D351-1)/Inputs!$B$12,0))</f>
+        <v>157</v>
       </c>
       <c r="M351" s="6" t="s">
         <v>196</v>
       </c>
       <c r="N351" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O351" s="6" t="s">
@@ -23033,7 +23025,7 @@
         <v>587</v>
       </c>
       <c r="L352" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B352-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D352-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B352-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D352-1)/Inputs!$B$12,0))</f>
         <v>65</v>
       </c>
       <c r="M352" s="2"/>
@@ -23087,7 +23079,7 @@
         <v>587</v>
       </c>
       <c r="L353" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B353-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D353-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B353-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D353-1)/Inputs!$B$12,0))</f>
         <v>75</v>
       </c>
       <c r="M353" s="2"/>
@@ -23141,7 +23133,7 @@
         <v>587</v>
       </c>
       <c r="L354" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B354-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D354-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B354-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D354-1)/Inputs!$B$12,0))</f>
         <v>87</v>
       </c>
       <c r="M354" s="2"/>
@@ -23195,7 +23187,7 @@
         <v>587</v>
       </c>
       <c r="L355" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B355-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D355-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B355-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D355-1)/Inputs!$B$12,0))</f>
         <v>100</v>
       </c>
       <c r="M355" s="2"/>
@@ -23249,7 +23241,7 @@
         <v>587</v>
       </c>
       <c r="L356" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B356-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D356-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B356-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D356-1)/Inputs!$B$12,0))</f>
         <v>114</v>
       </c>
       <c r="M356" s="2"/>
@@ -23303,7 +23295,7 @@
         <v>587</v>
       </c>
       <c r="L357" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B357-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D357-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B357-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D357-1)/Inputs!$B$12,0))</f>
         <v>132</v>
       </c>
       <c r="M357" s="2"/>
@@ -23357,7 +23349,7 @@
         <v>587</v>
       </c>
       <c r="L358" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B358-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D358-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B358-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D358-1)/Inputs!$B$12,0))</f>
         <v>151</v>
       </c>
       <c r="M358" s="2"/>
@@ -23411,7 +23403,7 @@
         <v>587</v>
       </c>
       <c r="L359" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B359-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D359-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B359-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D359-1)/Inputs!$B$12,0))</f>
         <v>174</v>
       </c>
       <c r="M359" s="4"/>
@@ -23465,7 +23457,7 @@
         <v>587</v>
       </c>
       <c r="L360" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B360-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D360-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B360-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D360-1)/Inputs!$B$12,0))</f>
         <v>200</v>
       </c>
       <c r="M360" s="4"/>
@@ -23517,14 +23509,13 @@
         <v>587</v>
       </c>
       <c r="L361" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B361-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D361-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B361-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D361-1)/Inputs!$B$12,0))</f>
         <v>230</v>
       </c>
       <c r="M361" s="6" t="s">
         <v>222</v>
       </c>
       <c r="N361" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O361" s="6" t="s">
@@ -23577,8 +23568,8 @@
         <v>667</v>
       </c>
       <c r="L362" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B362-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D362-1)/Inputs!$B$12,0)</f>
-        <v>554</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B362-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D362-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M362" s="2"/>
       <c r="N362" s="2"/>
@@ -23631,8 +23622,8 @@
         <v>667</v>
       </c>
       <c r="L363" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B363-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D363-1)/Inputs!$B$12,0)</f>
-        <v>637</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B363-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D363-1)/Inputs!$B$12,0))</f>
+        <v>64</v>
       </c>
       <c r="M363" s="2"/>
       <c r="N363" s="2"/>
@@ -23685,8 +23676,8 @@
         <v>667</v>
       </c>
       <c r="L364" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B364-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D364-1)/Inputs!$B$12,0)</f>
-        <v>733</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B364-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D364-1)/Inputs!$B$12,0))</f>
+        <v>73</v>
       </c>
       <c r="M364" s="2"/>
       <c r="N364" s="2"/>
@@ -23739,8 +23730,8 @@
         <v>667</v>
       </c>
       <c r="L365" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B365-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D365-1)/Inputs!$B$12,0)</f>
-        <v>843</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B365-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D365-1)/Inputs!$B$12,0))</f>
+        <v>84</v>
       </c>
       <c r="M365" s="2"/>
       <c r="N365" s="2"/>
@@ -23793,8 +23784,8 @@
         <v>667</v>
       </c>
       <c r="L366" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B366-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D366-1)/Inputs!$B$12,0)</f>
-        <v>969</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B366-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D366-1)/Inputs!$B$12,0))</f>
+        <v>97</v>
       </c>
       <c r="M366" s="2"/>
       <c r="N366" s="2"/>
@@ -23847,8 +23838,8 @@
         <v>667</v>
       </c>
       <c r="L367" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B367-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D367-1)/Inputs!$B$12,0)</f>
-        <v>1114</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B367-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D367-1)/Inputs!$B$12,0))</f>
+        <v>111</v>
       </c>
       <c r="M367" s="2"/>
       <c r="N367" s="2"/>
@@ -23901,8 +23892,8 @@
         <v>667</v>
       </c>
       <c r="L368" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B368-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D368-1)/Inputs!$B$12,0)</f>
-        <v>1282</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B368-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D368-1)/Inputs!$B$12,0))</f>
+        <v>128</v>
       </c>
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
@@ -23955,8 +23946,8 @@
         <v>667</v>
       </c>
       <c r="L369" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B369-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D369-1)/Inputs!$B$12,0)</f>
-        <v>1474</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B369-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D369-1)/Inputs!$B$12,0))</f>
+        <v>147</v>
       </c>
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
@@ -24009,8 +24000,8 @@
         <v>667</v>
       </c>
       <c r="L370" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B370-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D370-1)/Inputs!$B$12,0)</f>
-        <v>1695</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B370-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D370-1)/Inputs!$B$12,0))</f>
+        <v>169</v>
       </c>
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
@@ -24061,15 +24052,14 @@
         <v>667</v>
       </c>
       <c r="L371" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B371-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D371-1)/Inputs!$B$12,0)</f>
-        <v>1949</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B371-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D371-1)/Inputs!$B$12,0))</f>
+        <v>195</v>
       </c>
       <c r="M371" s="6" t="s">
         <v>264</v>
       </c>
       <c r="N371" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O371" s="6" t="s">
         <v>668</v>
@@ -24121,8 +24111,8 @@
         <v>696</v>
       </c>
       <c r="L372" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B372-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D372-1)/Inputs!$B$12,0)</f>
-        <v>609</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B372-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D372-1)/Inputs!$B$12,0))</f>
+        <v>427</v>
       </c>
       <c r="M372" s="2"/>
       <c r="N372" s="2"/>
@@ -24175,8 +24165,8 @@
         <v>696</v>
       </c>
       <c r="L373" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B373-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D373-1)/Inputs!$B$12,0)</f>
-        <v>701</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B373-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D373-1)/Inputs!$B$12,0))</f>
+        <v>491</v>
       </c>
       <c r="M373" s="2"/>
       <c r="N373" s="2"/>
@@ -24229,8 +24219,8 @@
         <v>696</v>
       </c>
       <c r="L374" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B374-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D374-1)/Inputs!$B$12,0)</f>
-        <v>806</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B374-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D374-1)/Inputs!$B$12,0))</f>
+        <v>564</v>
       </c>
       <c r="M374" s="2"/>
       <c r="N374" s="2"/>
@@ -24283,8 +24273,8 @@
         <v>696</v>
       </c>
       <c r="L375" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B375-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D375-1)/Inputs!$B$12,0)</f>
-        <v>927</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B375-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D375-1)/Inputs!$B$12,0))</f>
+        <v>649</v>
       </c>
       <c r="M375" s="2"/>
       <c r="N375" s="2"/>
@@ -24337,8 +24327,8 @@
         <v>696</v>
       </c>
       <c r="L376" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B376-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D376-1)/Inputs!$B$12,0)</f>
-        <v>1066</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B376-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D376-1)/Inputs!$B$12,0))</f>
+        <v>746</v>
       </c>
       <c r="M376" s="2"/>
       <c r="N376" s="2"/>
@@ -24391,8 +24381,8 @@
         <v>696</v>
       </c>
       <c r="L377" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B377-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D377-1)/Inputs!$B$12,0)</f>
-        <v>1226</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B377-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D377-1)/Inputs!$B$12,0))</f>
+        <v>858</v>
       </c>
       <c r="M377" s="2"/>
       <c r="N377" s="2"/>
@@ -24445,8 +24435,8 @@
         <v>696</v>
       </c>
       <c r="L378" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B378-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D378-1)/Inputs!$B$12,0)</f>
-        <v>1410</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B378-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D378-1)/Inputs!$B$12,0))</f>
+        <v>987</v>
       </c>
       <c r="M378" s="4"/>
       <c r="N378" s="4"/>
@@ -24499,8 +24489,8 @@
         <v>696</v>
       </c>
       <c r="L379" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B379-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D379-1)/Inputs!$B$12,0)</f>
-        <v>1621</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B379-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D379-1)/Inputs!$B$12,0))</f>
+        <v>1135</v>
       </c>
       <c r="M379" s="4"/>
       <c r="N379" s="4"/>
@@ -24553,8 +24543,8 @@
         <v>696</v>
       </c>
       <c r="L380" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B380-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D380-1)/Inputs!$B$12,0)</f>
-        <v>1864</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B380-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D380-1)/Inputs!$B$12,0))</f>
+        <v>1305</v>
       </c>
       <c r="M380" s="4"/>
       <c r="N380" s="4"/>
@@ -24605,15 +24595,14 @@
         <v>696</v>
       </c>
       <c r="L381" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B381-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D381-1)/Inputs!$B$12,0)</f>
-        <v>2144</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B381-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D381-1)/Inputs!$B$12,0))</f>
+        <v>1501</v>
       </c>
       <c r="M381" s="6" t="s">
         <v>278</v>
       </c>
       <c r="N381" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O381" s="6" t="s">
         <v>668</v>
@@ -24665,8 +24654,8 @@
         <v>704</v>
       </c>
       <c r="L382" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B382-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D382-1)/Inputs!$B$12,0)</f>
-        <v>670</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B382-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D382-1)/Inputs!$B$12,0))</f>
+        <v>570</v>
       </c>
       <c r="M382" s="2"/>
       <c r="N382" s="2"/>
@@ -24719,8 +24708,8 @@
         <v>704</v>
       </c>
       <c r="L383" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B383-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D383-1)/Inputs!$B$12,0)</f>
-        <v>771</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B383-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D383-1)/Inputs!$B$12,0))</f>
+        <v>655</v>
       </c>
       <c r="M383" s="2"/>
       <c r="N383" s="2"/>
@@ -24773,8 +24762,8 @@
         <v>704</v>
       </c>
       <c r="L384" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B384-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D384-1)/Inputs!$B$12,0)</f>
-        <v>887</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B384-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D384-1)/Inputs!$B$12,0))</f>
+        <v>754</v>
       </c>
       <c r="M384" s="2"/>
       <c r="N384" s="2"/>
@@ -24827,8 +24816,8 @@
         <v>704</v>
       </c>
       <c r="L385" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B385-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D385-1)/Inputs!$B$12,0)</f>
-        <v>1020</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B385-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D385-1)/Inputs!$B$12,0))</f>
+        <v>867</v>
       </c>
       <c r="M385" s="2"/>
       <c r="N385" s="2"/>
@@ -24881,8 +24870,8 @@
         <v>704</v>
       </c>
       <c r="L386" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B386-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D386-1)/Inputs!$B$12,0)</f>
-        <v>1173</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B386-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D386-1)/Inputs!$B$12,0))</f>
+        <v>997</v>
       </c>
       <c r="M386" s="2"/>
       <c r="N386" s="2"/>
@@ -24935,8 +24924,8 @@
         <v>704</v>
       </c>
       <c r="L387" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B387-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D387-1)/Inputs!$B$12,0)</f>
-        <v>1349</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B387-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D387-1)/Inputs!$B$12,0))</f>
+        <v>1146</v>
       </c>
       <c r="M387" s="2"/>
       <c r="N387" s="2"/>
@@ -24989,8 +24978,8 @@
         <v>704</v>
       </c>
       <c r="L388" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B388-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D388-1)/Inputs!$B$12,0)</f>
-        <v>1551</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B388-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D388-1)/Inputs!$B$12,0))</f>
+        <v>1318</v>
       </c>
       <c r="M388" s="4"/>
       <c r="N388" s="4"/>
@@ -25043,8 +25032,8 @@
         <v>704</v>
       </c>
       <c r="L389" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B389-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D389-1)/Inputs!$B$12,0)</f>
-        <v>1783</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B389-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D389-1)/Inputs!$B$12,0))</f>
+        <v>1516</v>
       </c>
       <c r="M389" s="4"/>
       <c r="N389" s="4"/>
@@ -25097,8 +25086,8 @@
         <v>704</v>
       </c>
       <c r="L390" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B390-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D390-1)/Inputs!$B$12,0)</f>
-        <v>2051</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B390-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D390-1)/Inputs!$B$12,0))</f>
+        <v>1743</v>
       </c>
       <c r="M390" s="4"/>
       <c r="N390" s="4"/>
@@ -25149,14 +25138,13 @@
         <v>704</v>
       </c>
       <c r="L391" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B391-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D391-1)/Inputs!$B$12,0)</f>
-        <v>2359</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B391-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D391-1)/Inputs!$B$12,0))</f>
+        <v>2005</v>
       </c>
       <c r="M391" s="6" t="s">
         <v>292</v>
       </c>
       <c r="N391" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O391" s="6" t="s">
@@ -25209,8 +25197,8 @@
         <v>712</v>
       </c>
       <c r="L392" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B392-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D392-1)/Inputs!$B$12,0)</f>
-        <v>737</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B392-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D392-1)/Inputs!$B$12,0))</f>
+        <v>553</v>
       </c>
       <c r="M392" s="2"/>
       <c r="N392" s="2"/>
@@ -25263,8 +25251,8 @@
         <v>712</v>
       </c>
       <c r="L393" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B393-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D393-1)/Inputs!$B$12,0)</f>
-        <v>848</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B393-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D393-1)/Inputs!$B$12,0))</f>
+        <v>636</v>
       </c>
       <c r="M393" s="2"/>
       <c r="N393" s="2"/>
@@ -25317,8 +25305,8 @@
         <v>712</v>
       </c>
       <c r="L394" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B394-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D394-1)/Inputs!$B$12,0)</f>
-        <v>975</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B394-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D394-1)/Inputs!$B$12,0))</f>
+        <v>731</v>
       </c>
       <c r="M394" s="2"/>
       <c r="N394" s="2"/>
@@ -25371,8 +25359,8 @@
         <v>712</v>
       </c>
       <c r="L395" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B395-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D395-1)/Inputs!$B$12,0)</f>
-        <v>1122</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B395-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D395-1)/Inputs!$B$12,0))</f>
+        <v>841</v>
       </c>
       <c r="M395" s="2"/>
       <c r="N395" s="2"/>
@@ -25425,8 +25413,8 @@
         <v>712</v>
       </c>
       <c r="L396" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B396-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D396-1)/Inputs!$B$12,0)</f>
-        <v>1290</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B396-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D396-1)/Inputs!$B$12,0))</f>
+        <v>967</v>
       </c>
       <c r="M396" s="2"/>
       <c r="N396" s="2"/>
@@ -25479,8 +25467,8 @@
         <v>712</v>
       </c>
       <c r="L397" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B397-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D397-1)/Inputs!$B$12,0)</f>
-        <v>1483</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B397-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D397-1)/Inputs!$B$12,0))</f>
+        <v>1113</v>
       </c>
       <c r="M397" s="2"/>
       <c r="N397" s="2"/>
@@ -25533,8 +25521,8 @@
         <v>712</v>
       </c>
       <c r="L398" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B398-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D398-1)/Inputs!$B$12,0)</f>
-        <v>1706</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B398-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D398-1)/Inputs!$B$12,0))</f>
+        <v>1279</v>
       </c>
       <c r="M398" s="4"/>
       <c r="N398" s="4"/>
@@ -25587,8 +25575,8 @@
         <v>712</v>
       </c>
       <c r="L399" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B399-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D399-1)/Inputs!$B$12,0)</f>
-        <v>1962</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B399-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D399-1)/Inputs!$B$12,0))</f>
+        <v>1471</v>
       </c>
       <c r="M399" s="4"/>
       <c r="N399" s="4"/>
@@ -25641,8 +25629,8 @@
         <v>712</v>
       </c>
       <c r="L400" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B400-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D400-1)/Inputs!$B$12,0)</f>
-        <v>2256</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B400-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D400-1)/Inputs!$B$12,0))</f>
+        <v>1692</v>
       </c>
       <c r="M400" s="4"/>
       <c r="N400" s="4"/>
@@ -25693,14 +25681,13 @@
         <v>712</v>
       </c>
       <c r="L401" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B401-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D401-1)/Inputs!$B$12,0)</f>
-        <v>2594</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B401-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D401-1)/Inputs!$B$12,0))</f>
+        <v>1946</v>
       </c>
       <c r="M401" s="6" t="s">
         <v>306</v>
       </c>
       <c r="N401" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O401" s="6" t="s">
@@ -25753,8 +25740,8 @@
         <v>720</v>
       </c>
       <c r="L402" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B402-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D402-1)/Inputs!$B$12,0)</f>
-        <v>811</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B402-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D402-1)/Inputs!$B$12,0))</f>
+        <v>608</v>
       </c>
       <c r="M402" s="2"/>
       <c r="N402" s="2"/>
@@ -25807,8 +25794,8 @@
         <v>720</v>
       </c>
       <c r="L403" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B403-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D403-1)/Inputs!$B$12,0)</f>
-        <v>933</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B403-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D403-1)/Inputs!$B$12,0))</f>
+        <v>700</v>
       </c>
       <c r="M403" s="2"/>
       <c r="N403" s="2"/>
@@ -25861,8 +25848,8 @@
         <v>720</v>
       </c>
       <c r="L404" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B404-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D404-1)/Inputs!$B$12,0)</f>
-        <v>1073</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B404-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D404-1)/Inputs!$B$12,0))</f>
+        <v>805</v>
       </c>
       <c r="M404" s="2"/>
       <c r="N404" s="2"/>
@@ -25915,8 +25902,8 @@
         <v>720</v>
       </c>
       <c r="L405" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B405-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D405-1)/Inputs!$B$12,0)</f>
-        <v>1234</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B405-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D405-1)/Inputs!$B$12,0))</f>
+        <v>925</v>
       </c>
       <c r="M405" s="2"/>
       <c r="N405" s="2"/>
@@ -25969,8 +25956,8 @@
         <v>720</v>
       </c>
       <c r="L406" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B406-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D406-1)/Inputs!$B$12,0)</f>
-        <v>1419</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B406-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D406-1)/Inputs!$B$12,0))</f>
+        <v>1064</v>
       </c>
       <c r="M406" s="2"/>
       <c r="N406" s="2"/>
@@ -26023,8 +26010,8 @@
         <v>720</v>
       </c>
       <c r="L407" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B407-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D407-1)/Inputs!$B$12,0)</f>
-        <v>1632</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B407-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D407-1)/Inputs!$B$12,0))</f>
+        <v>1224</v>
       </c>
       <c r="M407" s="2"/>
       <c r="N407" s="2"/>
@@ -26077,8 +26064,8 @@
         <v>720</v>
       </c>
       <c r="L408" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B408-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D408-1)/Inputs!$B$12,0)</f>
-        <v>1876</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B408-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D408-1)/Inputs!$B$12,0))</f>
+        <v>1407</v>
       </c>
       <c r="M408" s="4"/>
       <c r="N408" s="4"/>
@@ -26131,8 +26118,8 @@
         <v>720</v>
       </c>
       <c r="L409" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B409-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D409-1)/Inputs!$B$12,0)</f>
-        <v>2158</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B409-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D409-1)/Inputs!$B$12,0))</f>
+        <v>1618</v>
       </c>
       <c r="M409" s="4"/>
       <c r="N409" s="4"/>
@@ -26185,8 +26172,8 @@
         <v>720</v>
       </c>
       <c r="L410" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B410-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D410-1)/Inputs!$B$12,0)</f>
-        <v>2482</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B410-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D410-1)/Inputs!$B$12,0))</f>
+        <v>1861</v>
       </c>
       <c r="M410" s="4"/>
       <c r="N410" s="4"/>
@@ -26237,14 +26224,13 @@
         <v>720</v>
       </c>
       <c r="L411" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B411-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D411-1)/Inputs!$B$12,0)</f>
-        <v>2854</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B411-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D411-1)/Inputs!$B$12,0))</f>
+        <v>2140</v>
       </c>
       <c r="M411" s="6" t="s">
         <v>320</v>
       </c>
       <c r="N411" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O411" s="6" t="s">
@@ -26297,7 +26283,7 @@
         <v>727</v>
       </c>
       <c r="L412" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B412-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D412-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B412-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D412-1)/Inputs!$B$12,0))</f>
         <v>892</v>
       </c>
       <c r="M412" s="2"/>
@@ -26351,7 +26337,7 @@
         <v>727</v>
       </c>
       <c r="L413" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B413-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D413-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B413-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D413-1)/Inputs!$B$12,0))</f>
         <v>1026</v>
       </c>
       <c r="M413" s="2"/>
@@ -26405,7 +26391,7 @@
         <v>727</v>
       </c>
       <c r="L414" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B414-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D414-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B414-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D414-1)/Inputs!$B$12,0))</f>
         <v>1180</v>
       </c>
       <c r="M414" s="2"/>
@@ -26459,7 +26445,7 @@
         <v>727</v>
       </c>
       <c r="L415" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B415-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D415-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B415-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D415-1)/Inputs!$B$12,0))</f>
         <v>1357</v>
       </c>
       <c r="M415" s="2"/>
@@ -26513,7 +26499,7 @@
         <v>727</v>
       </c>
       <c r="L416" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B416-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D416-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B416-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D416-1)/Inputs!$B$12,0))</f>
         <v>1561</v>
       </c>
       <c r="M416" s="2"/>
@@ -26567,7 +26553,7 @@
         <v>727</v>
       </c>
       <c r="L417" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B417-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D417-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B417-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D417-1)/Inputs!$B$12,0))</f>
         <v>1795</v>
       </c>
       <c r="M417" s="2"/>
@@ -26621,7 +26607,7 @@
         <v>727</v>
       </c>
       <c r="L418" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B418-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D418-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B418-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D418-1)/Inputs!$B$12,0))</f>
         <v>2064</v>
       </c>
       <c r="M418" s="4"/>
@@ -26675,7 +26661,7 @@
         <v>727</v>
       </c>
       <c r="L419" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B419-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D419-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B419-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D419-1)/Inputs!$B$12,0))</f>
         <v>2374</v>
       </c>
       <c r="M419" s="4"/>
@@ -26729,7 +26715,7 @@
         <v>727</v>
       </c>
       <c r="L420" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B420-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D420-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B420-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D420-1)/Inputs!$B$12,0))</f>
         <v>2730</v>
       </c>
       <c r="M420" s="4"/>
@@ -26781,14 +26767,13 @@
         <v>727</v>
       </c>
       <c r="L421" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B421-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D421-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B421-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D421-1)/Inputs!$B$12,0))</f>
         <v>3139</v>
       </c>
       <c r="M421" s="6" t="s">
         <v>334</v>
       </c>
       <c r="N421" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O421" s="6" t="s">
@@ -26841,8 +26826,8 @@
         <v>737</v>
       </c>
       <c r="L422" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0)</f>
-        <v>52</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
@@ -26895,8 +26880,8 @@
         <v>737</v>
       </c>
       <c r="L423" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0)</f>
-        <v>59</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M423" s="2"/>
       <c r="N423" s="2"/>
@@ -26949,8 +26934,8 @@
         <v>737</v>
       </c>
       <c r="L424" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0)</f>
-        <v>68</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M424" s="2"/>
       <c r="N424" s="2"/>
@@ -27003,8 +26988,8 @@
         <v>737</v>
       </c>
       <c r="L425" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0)</f>
-        <v>79</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M425" s="2"/>
       <c r="N425" s="2"/>
@@ -27057,8 +27042,8 @@
         <v>737</v>
       </c>
       <c r="L426" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0)</f>
-        <v>90</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M426" s="2"/>
       <c r="N426" s="2"/>
@@ -27111,8 +27096,8 @@
         <v>737</v>
       </c>
       <c r="L427" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0)</f>
-        <v>104</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0))</f>
+        <v>10</v>
       </c>
       <c r="M427" s="2"/>
       <c r="N427" s="2"/>
@@ -27165,8 +27150,8 @@
         <v>737</v>
       </c>
       <c r="L428" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0)</f>
-        <v>120</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M428" s="2"/>
       <c r="N428" s="2"/>
@@ -27219,8 +27204,8 @@
         <v>737</v>
       </c>
       <c r="L429" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0)</f>
-        <v>138</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
@@ -27273,8 +27258,8 @@
         <v>737</v>
       </c>
       <c r="L430" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0)</f>
-        <v>158</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
@@ -27325,15 +27310,14 @@
         <v>737</v>
       </c>
       <c r="L431" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12,0)</f>
-        <v>182</v>
+        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12,0))</f>
+        <v>18</v>
       </c>
       <c r="M431" s="6" t="s">
         <v>368</v>
       </c>
       <c r="N431" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O431" s="6" t="s">
         <v>738</v>
@@ -27385,8 +27369,8 @@
         <v>759</v>
       </c>
       <c r="L432" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B432-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D432-1)/Inputs!$B$12,0)</f>
-        <v>57</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B432-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D432-1)/Inputs!$B$12,0))</f>
+        <v>40</v>
       </c>
       <c r="M432" s="2"/>
       <c r="N432" s="2"/>
@@ -27439,8 +27423,8 @@
         <v>759</v>
       </c>
       <c r="L433" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B433-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D433-1)/Inputs!$B$12,0)</f>
-        <v>65</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B433-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D433-1)/Inputs!$B$12,0))</f>
+        <v>46</v>
       </c>
       <c r="M433" s="2"/>
       <c r="N433" s="2"/>
@@ -27493,8 +27477,8 @@
         <v>759</v>
       </c>
       <c r="L434" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B434-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D434-1)/Inputs!$B$12,0)</f>
-        <v>75</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B434-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D434-1)/Inputs!$B$12,0))</f>
+        <v>53</v>
       </c>
       <c r="M434" s="2"/>
       <c r="N434" s="2"/>
@@ -27547,8 +27531,8 @@
         <v>759</v>
       </c>
       <c r="L435" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B435-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D435-1)/Inputs!$B$12,0)</f>
-        <v>87</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B435-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D435-1)/Inputs!$B$12,0))</f>
+        <v>61</v>
       </c>
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
@@ -27601,8 +27585,8 @@
         <v>759</v>
       </c>
       <c r="L436" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B436-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D436-1)/Inputs!$B$12,0)</f>
-        <v>99</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B436-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D436-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M436" s="2"/>
       <c r="N436" s="2"/>
@@ -27655,8 +27639,8 @@
         <v>759</v>
       </c>
       <c r="L437" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B437-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D437-1)/Inputs!$B$12,0)</f>
-        <v>114</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B437-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D437-1)/Inputs!$B$12,0))</f>
+        <v>80</v>
       </c>
       <c r="M437" s="2"/>
       <c r="N437" s="2"/>
@@ -27709,8 +27693,8 @@
         <v>759</v>
       </c>
       <c r="L438" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B438-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D438-1)/Inputs!$B$12,0)</f>
-        <v>132</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B438-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D438-1)/Inputs!$B$12,0))</f>
+        <v>92</v>
       </c>
       <c r="M438" s="2"/>
       <c r="N438" s="2"/>
@@ -27763,8 +27747,8 @@
         <v>759</v>
       </c>
       <c r="L439" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B439-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D439-1)/Inputs!$B$12,0)</f>
-        <v>151</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B439-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D439-1)/Inputs!$B$12,0))</f>
+        <v>106</v>
       </c>
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
@@ -27817,8 +27801,8 @@
         <v>759</v>
       </c>
       <c r="L440" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B440-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D440-1)/Inputs!$B$12,0)</f>
-        <v>174</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B440-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D440-1)/Inputs!$B$12,0))</f>
+        <v>122</v>
       </c>
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
@@ -27869,15 +27853,14 @@
         <v>759</v>
       </c>
       <c r="L441" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B441-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D441-1)/Inputs!$B$12,0)</f>
-        <v>200</v>
+        <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B441-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D441-1)/Inputs!$B$12,0))</f>
+        <v>140</v>
       </c>
       <c r="M441" s="6" t="s">
         <v>379</v>
       </c>
       <c r="N441" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O441" s="6" t="s">
         <v>738</v>
@@ -27929,8 +27912,8 @@
         <v>765</v>
       </c>
       <c r="L442" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B442-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D442-1)/Inputs!$B$12,0)</f>
-        <v>63</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B442-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D442-1)/Inputs!$B$12,0))</f>
+        <v>53</v>
       </c>
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
@@ -27983,8 +27966,8 @@
         <v>765</v>
       </c>
       <c r="L443" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B443-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D443-1)/Inputs!$B$12,0)</f>
-        <v>72</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B443-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D443-1)/Inputs!$B$12,0))</f>
+        <v>61</v>
       </c>
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
@@ -28037,8 +28020,8 @@
         <v>765</v>
       </c>
       <c r="L444" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B444-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D444-1)/Inputs!$B$12,0)</f>
-        <v>83</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B444-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D444-1)/Inputs!$B$12,0))</f>
+        <v>70</v>
       </c>
       <c r="M444" s="2"/>
       <c r="N444" s="2"/>
@@ -28091,8 +28074,8 @@
         <v>765</v>
       </c>
       <c r="L445" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B445-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D445-1)/Inputs!$B$12,0)</f>
-        <v>95</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B445-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D445-1)/Inputs!$B$12,0))</f>
+        <v>81</v>
       </c>
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
@@ -28145,8 +28128,8 @@
         <v>765</v>
       </c>
       <c r="L446" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B446-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D446-1)/Inputs!$B$12,0)</f>
-        <v>109</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B446-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D446-1)/Inputs!$B$12,0))</f>
+        <v>93</v>
       </c>
       <c r="M446" s="2"/>
       <c r="N446" s="2"/>
@@ -28199,8 +28182,8 @@
         <v>765</v>
       </c>
       <c r="L447" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B447-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D447-1)/Inputs!$B$12,0)</f>
-        <v>126</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B447-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D447-1)/Inputs!$B$12,0))</f>
+        <v>107</v>
       </c>
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
@@ -28253,8 +28236,8 @@
         <v>765</v>
       </c>
       <c r="L448" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B448-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D448-1)/Inputs!$B$12,0)</f>
-        <v>145</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B448-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D448-1)/Inputs!$B$12,0))</f>
+        <v>123</v>
       </c>
       <c r="M448" s="2"/>
       <c r="N448" s="2"/>
@@ -28307,8 +28290,8 @@
         <v>765</v>
       </c>
       <c r="L449" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B449-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D449-1)/Inputs!$B$12,0)</f>
-        <v>166</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B449-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D449-1)/Inputs!$B$12,0))</f>
+        <v>141</v>
       </c>
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
@@ -28361,8 +28344,8 @@
         <v>765</v>
       </c>
       <c r="L450" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B450-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D450-1)/Inputs!$B$12,0)</f>
-        <v>191</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B450-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D450-1)/Inputs!$B$12,0))</f>
+        <v>163</v>
       </c>
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
@@ -28413,14 +28396,13 @@
         <v>765</v>
       </c>
       <c r="L451" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B451-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D451-1)/Inputs!$B$12,0)</f>
-        <v>220</v>
+        <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B451-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D451-1)/Inputs!$B$12,0))</f>
+        <v>187</v>
       </c>
       <c r="M451" s="6" t="s">
         <v>390</v>
       </c>
       <c r="N451" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O451" s="6" t="s">
@@ -28473,8 +28455,8 @@
         <v>771</v>
       </c>
       <c r="L452" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B452-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D452-1)/Inputs!$B$12,0)</f>
-        <v>69</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B452-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D452-1)/Inputs!$B$12,0))</f>
+        <v>52</v>
       </c>
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
@@ -28527,8 +28509,8 @@
         <v>771</v>
       </c>
       <c r="L453" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B453-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D453-1)/Inputs!$B$12,0)</f>
-        <v>79</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B453-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D453-1)/Inputs!$B$12,0))</f>
+        <v>59</v>
       </c>
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
@@ -28581,8 +28563,8 @@
         <v>771</v>
       </c>
       <c r="L454" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B454-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D454-1)/Inputs!$B$12,0)</f>
-        <v>91</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B454-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D454-1)/Inputs!$B$12,0))</f>
+        <v>68</v>
       </c>
       <c r="M454" s="2"/>
       <c r="N454" s="2"/>
@@ -28635,8 +28617,8 @@
         <v>771</v>
       </c>
       <c r="L455" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B455-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D455-1)/Inputs!$B$12,0)</f>
-        <v>105</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B455-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D455-1)/Inputs!$B$12,0))</f>
+        <v>79</v>
       </c>
       <c r="M455" s="2"/>
       <c r="N455" s="2"/>
@@ -28689,8 +28671,8 @@
         <v>771</v>
       </c>
       <c r="L456" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B456-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D456-1)/Inputs!$B$12,0)</f>
-        <v>120</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B456-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D456-1)/Inputs!$B$12,0))</f>
+        <v>90</v>
       </c>
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
@@ -28743,8 +28725,8 @@
         <v>771</v>
       </c>
       <c r="L457" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B457-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D457-1)/Inputs!$B$12,0)</f>
-        <v>138</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B457-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D457-1)/Inputs!$B$12,0))</f>
+        <v>104</v>
       </c>
       <c r="M457" s="2"/>
       <c r="N457" s="2"/>
@@ -28797,8 +28779,8 @@
         <v>771</v>
       </c>
       <c r="L458" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B458-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D458-1)/Inputs!$B$12,0)</f>
-        <v>159</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B458-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D458-1)/Inputs!$B$12,0))</f>
+        <v>119</v>
       </c>
       <c r="M458" s="2"/>
       <c r="N458" s="2"/>
@@ -28851,8 +28833,8 @@
         <v>771</v>
       </c>
       <c r="L459" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B459-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D459-1)/Inputs!$B$12,0)</f>
-        <v>183</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B459-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D459-1)/Inputs!$B$12,0))</f>
+        <v>137</v>
       </c>
       <c r="M459" s="4"/>
       <c r="N459" s="4"/>
@@ -28905,8 +28887,8 @@
         <v>771</v>
       </c>
       <c r="L460" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B460-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D460-1)/Inputs!$B$12,0)</f>
-        <v>211</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B460-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D460-1)/Inputs!$B$12,0))</f>
+        <v>158</v>
       </c>
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
@@ -28957,14 +28939,13 @@
         <v>771</v>
       </c>
       <c r="L461" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B461-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D461-1)/Inputs!$B$12,0)</f>
-        <v>242</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B461-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D461-1)/Inputs!$B$12,0))</f>
+        <v>182</v>
       </c>
       <c r="M461" s="6" t="s">
         <v>401</v>
       </c>
       <c r="N461" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O461" s="6" t="s">
@@ -29017,8 +28998,8 @@
         <v>777</v>
       </c>
       <c r="L462" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B462-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D462-1)/Inputs!$B$12,0)</f>
-        <v>76</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B462-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D462-1)/Inputs!$B$12,0))</f>
+        <v>57</v>
       </c>
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
@@ -29071,8 +29052,8 @@
         <v>777</v>
       </c>
       <c r="L463" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B463-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D463-1)/Inputs!$B$12,0)</f>
-        <v>87</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B463-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D463-1)/Inputs!$B$12,0))</f>
+        <v>65</v>
       </c>
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
@@ -29125,8 +29106,8 @@
         <v>777</v>
       </c>
       <c r="L464" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B464-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D464-1)/Inputs!$B$12,0)</f>
-        <v>100</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B464-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D464-1)/Inputs!$B$12,0))</f>
+        <v>75</v>
       </c>
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
@@ -29179,8 +29160,8 @@
         <v>777</v>
       </c>
       <c r="L465" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B465-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D465-1)/Inputs!$B$12,0)</f>
-        <v>115</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B465-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D465-1)/Inputs!$B$12,0))</f>
+        <v>86</v>
       </c>
       <c r="M465" s="2"/>
       <c r="N465" s="2"/>
@@ -29233,8 +29214,8 @@
         <v>777</v>
       </c>
       <c r="L466" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B466-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D466-1)/Inputs!$B$12,0)</f>
-        <v>132</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B466-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D466-1)/Inputs!$B$12,0))</f>
+        <v>99</v>
       </c>
       <c r="M466" s="2"/>
       <c r="N466" s="2"/>
@@ -29287,8 +29268,8 @@
         <v>777</v>
       </c>
       <c r="L467" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B467-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D467-1)/Inputs!$B$12,0)</f>
-        <v>152</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B467-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D467-1)/Inputs!$B$12,0))</f>
+        <v>114</v>
       </c>
       <c r="M467" s="2"/>
       <c r="N467" s="2"/>
@@ -29341,8 +29322,8 @@
         <v>777</v>
       </c>
       <c r="L468" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B468-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D468-1)/Inputs!$B$12,0)</f>
-        <v>175</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B468-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D468-1)/Inputs!$B$12,0))</f>
+        <v>131</v>
       </c>
       <c r="M468" s="2"/>
       <c r="N468" s="2"/>
@@ -29395,8 +29376,8 @@
         <v>777</v>
       </c>
       <c r="L469" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B469-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D469-1)/Inputs!$B$12,0)</f>
-        <v>201</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B469-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D469-1)/Inputs!$B$12,0))</f>
+        <v>151</v>
       </c>
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
@@ -29449,8 +29430,8 @@
         <v>777</v>
       </c>
       <c r="L470" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B470-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D470-1)/Inputs!$B$12,0)</f>
-        <v>232</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B470-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D470-1)/Inputs!$B$12,0))</f>
+        <v>174</v>
       </c>
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
@@ -29501,14 +29482,13 @@
         <v>777</v>
       </c>
       <c r="L471" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B471-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D471-1)/Inputs!$B$12,0)</f>
-        <v>266</v>
+        <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B471-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D471-1)/Inputs!$B$12,0))</f>
+        <v>200</v>
       </c>
       <c r="M471" s="6" t="s">
         <v>411</v>
       </c>
       <c r="N471" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O471" s="6" t="s">
@@ -29561,7 +29541,7 @@
         <v>782</v>
       </c>
       <c r="L472" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B472-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D472-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B472-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D472-1)/Inputs!$B$12,0))</f>
         <v>83</v>
       </c>
       <c r="M472" s="2"/>
@@ -29615,7 +29595,7 @@
         <v>782</v>
       </c>
       <c r="L473" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B473-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D473-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B473-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D473-1)/Inputs!$B$12,0))</f>
         <v>96</v>
       </c>
       <c r="M473" s="2"/>
@@ -29669,7 +29649,7 @@
         <v>782</v>
       </c>
       <c r="L474" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B474-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D474-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B474-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D474-1)/Inputs!$B$12,0))</f>
         <v>110</v>
       </c>
       <c r="M474" s="2"/>
@@ -29723,7 +29703,7 @@
         <v>782</v>
       </c>
       <c r="L475" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B475-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D475-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B475-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D475-1)/Inputs!$B$12,0))</f>
         <v>127</v>
       </c>
       <c r="M475" s="2"/>
@@ -29777,7 +29757,7 @@
         <v>782</v>
       </c>
       <c r="L476" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B476-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D476-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B476-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D476-1)/Inputs!$B$12,0))</f>
         <v>146</v>
       </c>
       <c r="M476" s="2"/>
@@ -29831,7 +29811,7 @@
         <v>782</v>
       </c>
       <c r="L477" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B477-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D477-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B477-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D477-1)/Inputs!$B$12,0))</f>
         <v>168</v>
       </c>
       <c r="M477" s="2"/>
@@ -29885,7 +29865,7 @@
         <v>782</v>
       </c>
       <c r="L478" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B478-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D478-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B478-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D478-1)/Inputs!$B$12,0))</f>
         <v>193</v>
       </c>
       <c r="M478" s="2"/>
@@ -29939,7 +29919,7 @@
         <v>782</v>
       </c>
       <c r="L479" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B479-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D479-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B479-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D479-1)/Inputs!$B$12,0))</f>
         <v>222</v>
       </c>
       <c r="M479" s="4"/>
@@ -29993,7 +29973,7 @@
         <v>782</v>
       </c>
       <c r="L480" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B480-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D480-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B480-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D480-1)/Inputs!$B$12,0))</f>
         <v>255</v>
       </c>
       <c r="M480" s="4"/>
@@ -30045,14 +30025,13 @@
         <v>782</v>
       </c>
       <c r="L481" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B481-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D481-1)/Inputs!$B$12,0)</f>
+        <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B481-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D481-1)/Inputs!$B$12,0))</f>
         <v>293</v>
       </c>
       <c r="M481" s="6" t="s">
         <v>422</v>
       </c>
       <c r="N481" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O481" s="6" t="s">
@@ -30105,8 +30084,8 @@
         <v>793</v>
       </c>
       <c r="L482" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B482-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D482-1)/Inputs!$B$12,0)</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D482-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
@@ -30159,8 +30138,8 @@
         <v>793</v>
       </c>
       <c r="L483" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B483-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D483-1)/Inputs!$B$12,0)</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D483-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
@@ -30213,8 +30192,8 @@
         <v>793</v>
       </c>
       <c r="L484" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B484-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D484-1)/Inputs!$B$12,0)</f>
-        <v>13</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D484-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M484" s="2"/>
       <c r="N484" s="2"/>
@@ -30267,8 +30246,8 @@
         <v>793</v>
       </c>
       <c r="L485" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B485-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D485-1)/Inputs!$B$12,0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D485-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M485" s="2"/>
       <c r="N485" s="2"/>
@@ -30321,8 +30300,8 @@
         <v>793</v>
       </c>
       <c r="L486" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B486-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D486-1)/Inputs!$B$12,0)</f>
-        <v>18</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D486-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
@@ -30375,8 +30354,8 @@
         <v>793</v>
       </c>
       <c r="L487" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B487-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D487-1)/Inputs!$B$12,0)</f>
-        <v>20</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D487-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M487" s="2"/>
       <c r="N487" s="2"/>
@@ -30429,8 +30408,8 @@
         <v>793</v>
       </c>
       <c r="L488" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B488-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D488-1)/Inputs!$B$12,0)</f>
-        <v>23</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D488-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
@@ -30483,8 +30462,8 @@
         <v>793</v>
       </c>
       <c r="L489" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B489-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D489-1)/Inputs!$B$12,0)</f>
-        <v>27</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D489-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
@@ -30537,8 +30516,8 @@
         <v>793</v>
       </c>
       <c r="L490" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B490-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D490-1)/Inputs!$B$12,0)</f>
-        <v>31</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D490-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
@@ -30589,15 +30568,14 @@
         <v>793</v>
       </c>
       <c r="L491" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B491-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D491-1)/Inputs!$B$12,0)</f>
-        <v>36</v>
+        <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D491-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M491" s="6" t="s">
         <v>454</v>
       </c>
       <c r="N491" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O491" s="6" t="s">
         <v>794</v>
@@ -30640,17 +30618,17 @@
         <v>790</v>
       </c>
       <c r="I492" s="2" t="s">
-        <v>791</v>
+        <v>842</v>
       </c>
       <c r="J492" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K492" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L492" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B492-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D492-1)/Inputs!$B$12,0)</f>
-        <v>11</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D492-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M492" s="2"/>
       <c r="N492" s="2"/>
@@ -30662,7 +30640,7 @@
         <v>795</v>
       </c>
       <c r="R492" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="S492" s="2" t="s">
         <v>792</v>
@@ -30694,17 +30672,17 @@
         <v>798</v>
       </c>
       <c r="I493" s="2" t="s">
-        <v>799</v>
+        <v>845</v>
       </c>
       <c r="J493" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="K493" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="K493" s="3" t="s">
-        <v>843</v>
-      </c>
       <c r="L493" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B493-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D493-1)/Inputs!$B$12,0)</f>
-        <v>13</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D493-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M493" s="2"/>
       <c r="N493" s="2"/>
@@ -30716,7 +30694,7 @@
         <v>801</v>
       </c>
       <c r="R493" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S493" s="2" t="s">
         <v>800</v>
@@ -30751,14 +30729,14 @@
         <v>805</v>
       </c>
       <c r="J494" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="K494" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L494" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B494-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D494-1)/Inputs!$B$12,0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D494-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M494" s="2"/>
       <c r="N494" s="2"/>
@@ -30805,14 +30783,14 @@
         <v>805</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="K495" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L495" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B495-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D495-1)/Inputs!$B$12,0)</f>
-        <v>17</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D495-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M495" s="2"/>
       <c r="N495" s="2"/>
@@ -30827,7 +30805,7 @@
         <v>0.5</v>
       </c>
       <c r="S495" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30859,14 +30837,14 @@
         <v>812</v>
       </c>
       <c r="J496" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="K496" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L496" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B496-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D496-1)/Inputs!$B$12,0)</f>
-        <v>19</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D496-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M496" s="2"/>
       <c r="N496" s="2"/>
@@ -30913,14 +30891,14 @@
         <v>818</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="K497" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L497" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B497-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D497-1)/Inputs!$B$12,0)</f>
-        <v>22</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D497-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M497" s="2"/>
       <c r="N497" s="2"/>
@@ -30967,14 +30945,14 @@
         <v>824</v>
       </c>
       <c r="J498" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="K498" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L498" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B498-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D498-1)/Inputs!$B$12,0)</f>
-        <v>26</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D498-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
@@ -31021,14 +30999,14 @@
         <v>363</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="K499" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L499" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B499-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D499-1)/Inputs!$B$12,0)</f>
-        <v>30</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D499-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
@@ -31075,14 +31053,14 @@
         <v>835</v>
       </c>
       <c r="J500" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="K500" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L500" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B500-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D500-1)/Inputs!$B$12,0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D500-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
@@ -31120,35 +31098,34 @@
         <v>87</v>
       </c>
       <c r="G501" s="6" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="H501" s="7" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="I501" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L501" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B501-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D501-1)/Inputs!$B$12,0)</f>
-        <v>39</v>
+        <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D501-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M501" s="6" t="s">
         <v>465</v>
       </c>
       <c r="N501" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O501" s="6" t="s">
         <v>794</v>
       </c>
       <c r="P501" s="7"/>
       <c r="Q501" s="6" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="R501" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31184,17 +31161,17 @@
         <v>790</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>791</v>
+        <v>857</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="K502" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L502" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B502-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D502-1)/Inputs!$B$12,0)</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D502-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M502" s="2"/>
       <c r="N502" s="2"/>
@@ -31206,10 +31183,10 @@
         <v>795</v>
       </c>
       <c r="R502" s="2" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31238,17 +31215,17 @@
         <v>798</v>
       </c>
       <c r="I503" s="2" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="K503" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L503" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B503-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D503-1)/Inputs!$B$12,0)</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D503-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M503" s="2"/>
       <c r="N503" s="2"/>
@@ -31260,10 +31237,10 @@
         <v>801</v>
       </c>
       <c r="R503" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S503" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31295,14 +31272,14 @@
         <v>805</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="K504" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L504" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B504-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D504-1)/Inputs!$B$12,0)</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D504-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M504" s="2"/>
       <c r="N504" s="2"/>
@@ -31317,7 +31294,7 @@
         <v>0.5</v>
       </c>
       <c r="S504" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31349,14 +31326,14 @@
         <v>805</v>
       </c>
       <c r="J505" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="K505" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="K505" s="3" t="s">
-        <v>856</v>
-      </c>
       <c r="L505" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B505-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D505-1)/Inputs!$B$12,0)</f>
-        <v>19</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D505-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M505" s="2"/>
       <c r="N505" s="2"/>
@@ -31371,7 +31348,7 @@
         <v>0.5</v>
       </c>
       <c r="S505" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31403,14 +31380,14 @@
         <v>812</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L506" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B506-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D506-1)/Inputs!$B$12,0)</f>
-        <v>21</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D506-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M506" s="2"/>
       <c r="N506" s="2"/>
@@ -31425,7 +31402,7 @@
         <v>5</v>
       </c>
       <c r="S506" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31457,14 +31434,14 @@
         <v>818</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="K507" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L507" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B507-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D507-1)/Inputs!$B$12,0)</f>
-        <v>25</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D507-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M507" s="2"/>
       <c r="N507" s="2"/>
@@ -31479,7 +31456,7 @@
         <v>0.01</v>
       </c>
       <c r="S507" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31511,14 +31488,14 @@
         <v>824</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="K508" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L508" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B508-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D508-1)/Inputs!$B$12,0)</f>
-        <v>28</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D508-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M508" s="4"/>
       <c r="N508" s="4"/>
@@ -31533,7 +31510,7 @@
         <v>1</v>
       </c>
       <c r="S508" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31565,14 +31542,14 @@
         <v>363</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="K509" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L509" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B509-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D509-1)/Inputs!$B$12,0)</f>
-        <v>32</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D509-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M509" s="4"/>
       <c r="N509" s="4"/>
@@ -31587,7 +31564,7 @@
         <v>0.1</v>
       </c>
       <c r="S509" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31619,14 +31596,14 @@
         <v>835</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="K510" s="5" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L510" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B510-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D510-1)/Inputs!$B$12,0)</f>
-        <v>37</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D510-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M510" s="4"/>
       <c r="N510" s="4"/>
@@ -31641,7 +31618,7 @@
         <v>0.1</v>
       </c>
       <c r="S510" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31664,27 +31641,26 @@
         <v>87</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="H511" s="7" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J511" s="6"/>
       <c r="K511" s="7" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="L511" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B511-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D511-1)/Inputs!$B$12,0)</f>
-        <v>43</v>
+        <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D511-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M511" s="6" t="s">
         <v>476</v>
       </c>
       <c r="N511" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O511" s="6" t="s">
@@ -31692,7 +31668,7 @@
       </c>
       <c r="P511" s="7"/>
       <c r="Q511" s="6" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="R511" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31728,17 +31704,17 @@
         <v>790</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>791</v>
+        <v>871</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="K512" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L512" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B512-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D512-1)/Inputs!$B$12,0)</f>
-        <v>13</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D512-1)/Inputs!$B$12,0))</f>
+        <v>1</v>
       </c>
       <c r="M512" s="2"/>
       <c r="N512" s="2"/>
@@ -31750,10 +31726,10 @@
         <v>795</v>
       </c>
       <c r="R512" s="2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="S512" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31782,17 +31758,17 @@
         <v>798</v>
       </c>
       <c r="I513" s="2" t="s">
-        <v>799</v>
+        <v>874</v>
       </c>
       <c r="J513" s="2" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="K513" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L513" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B513-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D513-1)/Inputs!$B$12,0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D513-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M513" s="2"/>
       <c r="N513" s="2"/>
@@ -31804,10 +31780,10 @@
         <v>801</v>
       </c>
       <c r="R513" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S513" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31839,14 +31815,14 @@
         <v>805</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="K514" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L514" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B514-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D514-1)/Inputs!$B$12,0)</f>
-        <v>18</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D514-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M514" s="2"/>
       <c r="N514" s="2"/>
@@ -31861,7 +31837,7 @@
         <v>0.5</v>
       </c>
       <c r="S514" s="2" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31893,14 +31869,14 @@
         <v>805</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="K515" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L515" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B515-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D515-1)/Inputs!$B$12,0)</f>
-        <v>20</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D515-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M515" s="2"/>
       <c r="N515" s="2"/>
@@ -31915,7 +31891,7 @@
         <v>0.5</v>
       </c>
       <c r="S515" s="2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31947,14 +31923,14 @@
         <v>812</v>
       </c>
       <c r="J516" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="K516" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="K516" s="3" t="s">
-        <v>869</v>
-      </c>
       <c r="L516" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B516-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D516-1)/Inputs!$B$12,0)</f>
-        <v>24</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D516-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M516" s="2"/>
       <c r="N516" s="2"/>
@@ -31969,7 +31945,7 @@
         <v>5</v>
       </c>
       <c r="S516" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32001,14 +31977,14 @@
         <v>818</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="K517" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L517" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B517-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D517-1)/Inputs!$B$12,0)</f>
-        <v>27</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D517-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M517" s="2"/>
       <c r="N517" s="2"/>
@@ -32023,7 +31999,7 @@
         <v>0.01</v>
       </c>
       <c r="S517" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32055,14 +32031,14 @@
         <v>824</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="K518" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L518" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B518-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D518-1)/Inputs!$B$12,0)</f>
-        <v>31</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D518-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
@@ -32077,7 +32053,7 @@
         <v>1</v>
       </c>
       <c r="S518" s="4" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32109,14 +32085,14 @@
         <v>363</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="K519" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L519" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B519-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D519-1)/Inputs!$B$12,0)</f>
-        <v>36</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D519-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M519" s="4"/>
       <c r="N519" s="4"/>
@@ -32131,7 +32107,7 @@
         <v>0.1</v>
       </c>
       <c r="S519" s="4" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32163,14 +32139,14 @@
         <v>835</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="K520" s="5" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L520" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B520-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D520-1)/Inputs!$B$12,0)</f>
-        <v>41</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D520-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
@@ -32185,7 +32161,7 @@
         <v>0.1</v>
       </c>
       <c r="S520" s="4" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32208,27 +32184,26 @@
         <v>87</v>
       </c>
       <c r="G521" s="6" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="H521" s="7" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="I521" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J521" s="6"/>
       <c r="K521" s="7" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="L521" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B521-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D521-1)/Inputs!$B$12,0)</f>
-        <v>47</v>
+        <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D521-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M521" s="6" t="s">
         <v>487</v>
       </c>
       <c r="N521" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O521" s="6" t="s">
@@ -32236,7 +32211,7 @@
       </c>
       <c r="P521" s="7"/>
       <c r="Q521" s="6" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="R521" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32272,17 +32247,17 @@
         <v>790</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>791</v>
+        <v>886</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="K522" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L522" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B522-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D522-1)/Inputs!$B$12,0)</f>
-        <v>15</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D522-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M522" s="2"/>
       <c r="N522" s="2"/>
@@ -32294,10 +32269,10 @@
         <v>795</v>
       </c>
       <c r="R522" s="2" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="S522" s="2" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32326,17 +32301,17 @@
         <v>798</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>799</v>
+        <v>889</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="K523" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L523" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B523-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D523-1)/Inputs!$B$12,0)</f>
-        <v>17</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D523-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M523" s="2"/>
       <c r="N523" s="2"/>
@@ -32348,10 +32323,10 @@
         <v>801</v>
       </c>
       <c r="R523" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S523" s="2" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32383,14 +32358,14 @@
         <v>805</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="K524" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L524" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B524-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D524-1)/Inputs!$B$12,0)</f>
-        <v>20</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D524-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M524" s="2"/>
       <c r="N524" s="2"/>
@@ -32405,7 +32380,7 @@
         <v>0.5</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32437,14 +32412,14 @@
         <v>805</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L525" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B525-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D525-1)/Inputs!$B$12,0)</f>
-        <v>22</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D525-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M525" s="2"/>
       <c r="N525" s="2"/>
@@ -32459,7 +32434,7 @@
         <v>0.5</v>
       </c>
       <c r="S525" s="2" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32491,14 +32466,14 @@
         <v>812</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="K526" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L526" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B526-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D526-1)/Inputs!$B$12,0)</f>
-        <v>26</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D526-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
@@ -32513,7 +32488,7 @@
         <v>5</v>
       </c>
       <c r="S526" s="2" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32545,14 +32520,14 @@
         <v>818</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="K527" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L527" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B527-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D527-1)/Inputs!$B$12,0)</f>
-        <v>30</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D527-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
@@ -32567,7 +32542,7 @@
         <v>0.01</v>
       </c>
       <c r="S527" s="2" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32599,14 +32574,14 @@
         <v>824</v>
       </c>
       <c r="J528" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="K528" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="K528" s="5" t="s">
-        <v>882</v>
-      </c>
       <c r="L528" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B528-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D528-1)/Inputs!$B$12,0)</f>
-        <v>34</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D528-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
@@ -32621,7 +32596,7 @@
         <v>1</v>
       </c>
       <c r="S528" s="4" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32653,14 +32628,14 @@
         <v>363</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="K529" s="5" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L529" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B529-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D529-1)/Inputs!$B$12,0)</f>
-        <v>39</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D529-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M529" s="4"/>
       <c r="N529" s="4"/>
@@ -32675,7 +32650,7 @@
         <v>0.1</v>
       </c>
       <c r="S529" s="4" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32707,14 +32682,14 @@
         <v>835</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="K530" s="5" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L530" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B530-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D530-1)/Inputs!$B$12,0)</f>
-        <v>45</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D530-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
@@ -32729,7 +32704,7 @@
         <v>0.1</v>
       </c>
       <c r="S530" s="4" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32752,27 +32727,26 @@
         <v>87</v>
       </c>
       <c r="G531" s="6" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="H531" s="7" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="I531" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J531" s="6"/>
       <c r="K531" s="7" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="L531" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B531-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D531-1)/Inputs!$B$12,0)</f>
-        <v>52</v>
+        <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D531-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M531" s="6" t="s">
         <v>497</v>
       </c>
       <c r="N531" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O531" s="6" t="s">
@@ -32780,7 +32754,7 @@
       </c>
       <c r="P531" s="7"/>
       <c r="Q531" s="6" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="R531" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32816,17 +32790,17 @@
         <v>790</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>791</v>
+        <v>901</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="K532" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L532" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B532-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D532-1)/Inputs!$B$12,0)</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D532-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
@@ -32838,10 +32812,10 @@
         <v>795</v>
       </c>
       <c r="R532" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="S532" s="2" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32870,17 +32844,17 @@
         <v>798</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>799</v>
+        <v>904</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="K533" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L533" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B533-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D533-1)/Inputs!$B$12,0)</f>
-        <v>19</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D533-1)/Inputs!$B$12,0))</f>
+        <v>2</v>
       </c>
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
@@ -32892,10 +32866,10 @@
         <v>801</v>
       </c>
       <c r="R533" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S533" s="2" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32927,14 +32901,14 @@
         <v>805</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
       <c r="K534" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L534" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B534-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D534-1)/Inputs!$B$12,0)</f>
-        <v>22</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D534-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M534" s="2"/>
       <c r="N534" s="2"/>
@@ -32949,7 +32923,7 @@
         <v>0.5</v>
       </c>
       <c r="S534" s="2" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32981,14 +32955,14 @@
         <v>805</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>898</v>
+        <v>907</v>
       </c>
       <c r="K535" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L535" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B535-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D535-1)/Inputs!$B$12,0)</f>
-        <v>25</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D535-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
@@ -33003,7 +32977,7 @@
         <v>0.5</v>
       </c>
       <c r="S535" s="2" t="s">
-        <v>897</v>
+        <v>906</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33035,14 +33009,14 @@
         <v>812</v>
       </c>
       <c r="J536" s="2" t="s">
-        <v>899</v>
+        <v>908</v>
       </c>
       <c r="K536" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L536" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B536-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D536-1)/Inputs!$B$12,0)</f>
-        <v>28</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D536-1)/Inputs!$B$12,0))</f>
+        <v>3</v>
       </c>
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
@@ -33057,7 +33031,7 @@
         <v>5</v>
       </c>
       <c r="S536" s="2" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33089,14 +33063,14 @@
         <v>818</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>900</v>
+        <v>909</v>
       </c>
       <c r="K537" s="3" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L537" s="2" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B537-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D537-1)/Inputs!$B$12,0)</f>
-        <v>33</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D537-1)/Inputs!$B$12,0))</f>
+        <v>4</v>
       </c>
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
@@ -33111,7 +33085,7 @@
         <v>0.01</v>
       </c>
       <c r="S537" s="2" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33143,14 +33117,14 @@
         <v>824</v>
       </c>
       <c r="J538" s="4" t="s">
-        <v>901</v>
+        <v>910</v>
       </c>
       <c r="K538" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L538" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B538-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D538-1)/Inputs!$B$12,0)</f>
-        <v>38</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D538-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
@@ -33165,7 +33139,7 @@
         <v>1</v>
       </c>
       <c r="S538" s="4" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33197,14 +33171,14 @@
         <v>363</v>
       </c>
       <c r="J539" s="4" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="K539" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L539" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B539-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D539-1)/Inputs!$B$12,0)</f>
-        <v>43</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D539-1)/Inputs!$B$12,0))</f>
+        <v>5</v>
       </c>
       <c r="M539" s="4"/>
       <c r="N539" s="4"/>
@@ -33219,7 +33193,7 @@
         <v>0.1</v>
       </c>
       <c r="S539" s="4" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33251,14 +33225,14 @@
         <v>835</v>
       </c>
       <c r="J540" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K540" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="K540" s="5" t="s">
-        <v>895</v>
-      </c>
       <c r="L540" s="4" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B540-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D540-1)/Inputs!$B$12,0)</f>
-        <v>50</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D540-1)/Inputs!$B$12,0))</f>
+        <v>6</v>
       </c>
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
@@ -33273,7 +33247,7 @@
         <v>0.1</v>
       </c>
       <c r="S540" s="4" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33296,27 +33270,26 @@
         <v>87</v>
       </c>
       <c r="G541" s="6" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="H541" s="7" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="I541" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J541" s="6"/>
       <c r="K541" s="7" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="L541" s="6" t="n">
-        <f aca="false">ROUND(Inputs!$B$4*Inputs!$B$5^(B541-1)*INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D541-1)/Inputs!$B$12,0)</f>
-        <v>57</v>
+        <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D541-1)/Inputs!$B$12,0))</f>
+        <v>7</v>
       </c>
       <c r="M541" s="6" t="s">
         <v>508</v>
       </c>
       <c r="N541" s="6" t="n">
-        <f aca="false">Inputs!$B$8</f>
         <v>2</v>
       </c>
       <c r="O541" s="6" t="s">
@@ -33324,7 +33297,7 @@
       </c>
       <c r="P541" s="7"/>
       <c r="Q541" s="6" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="R541" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -33363,12 +33336,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>908</v>
+        <v>917</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>2</v>
@@ -33376,7 +33349,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>909</v>
+        <v>918</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.1</v>
@@ -33384,7 +33357,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>910</v>
+        <v>919</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1.15</v>
@@ -33392,7 +33365,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>911</v>
+        <v>920</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1.25</v>
@@ -33400,7 +33373,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>912</v>
+        <v>921</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2</v>
@@ -33408,7 +33381,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>913</v>
+        <v>922</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>10</v>
@@ -33416,7 +33389,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1.5</v>
@@ -33424,7 +33397,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">(B6^10-1)/(B6-1)</f>
@@ -33436,13 +33409,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>916</v>
+        <v>925</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>918</v>
+        <v>927</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33450,13 +33423,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>570</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33464,13 +33437,13 @@
         <v>339</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>930</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>922</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33478,13 +33451,13 @@
         <v>427</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>923</v>
+        <v>932</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33492,13 +33465,13 @@
         <v>513</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>210</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33506,13 +33479,13 @@
         <v>588</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>330</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33520,13 +33493,13 @@
         <v>668</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33534,13 +33507,13 @@
         <v>738</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>420</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33548,13 +33521,13 @@
         <v>794</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>933</v>
+        <v>942</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>82</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>934</v>
+        <v>943</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33562,28 +33535,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>936</v>
+        <v>945</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>937</v>
+        <v>946</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>938</v>
+        <v>947</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -33610,7 +33583,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33618,22 +33591,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>943</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>944</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33641,22 +33614,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>945</v>
+        <v>954</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33664,17 +33637,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>950</v>
+        <v>959</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>951</v>
+        <v>960</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33682,22 +33655,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>952</v>
+        <v>961</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>953</v>
+        <v>962</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>954</v>
+        <v>963</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>955</v>
+        <v>964</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33705,22 +33678,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>956</v>
+        <v>965</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>957</v>
+        <v>966</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>958</v>
+        <v>967</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>959</v>
+        <v>968</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33728,22 +33701,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>960</v>
+        <v>969</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>962</v>
+        <v>971</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>963</v>
+        <v>972</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33751,37 +33724,37 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>964</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>966</v>
+        <v>975</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>967</v>
+        <v>976</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>968</v>
+        <v>977</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>969</v>
+        <v>978</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>970</v>
+        <v>979</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33789,42 +33762,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>971</v>
+        <v>980</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>975</v>
+        <v>984</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>976</v>
+        <v>985</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>977</v>
+        <v>986</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>978</v>
+        <v>987</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33832,32 +33805,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>979</v>
+        <v>988</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33865,32 +33838,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>985</v>
+        <v>994</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>989</v>
+        <v>998</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>990</v>
+        <v>999</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33898,27 +33871,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>991</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>993</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>994</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>995</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33926,32 +33899,32 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>996</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>998</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>999</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1000</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1001</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33959,22 +33932,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1002</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1003</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1004</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33982,47 +33955,47 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34030,22 +34003,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1015</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1016</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1017</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1018</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34053,22 +34026,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1019</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1020</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1021</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1022</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34076,42 +34049,42 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1023</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1024</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1025</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1026</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1027</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1028</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1029</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1030</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34119,42 +34092,42 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1031</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1032</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1033</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1034</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1035</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1036</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1037</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1038</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34162,17 +34135,17 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
-        <v>1039</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1041</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>
@@ -34200,12 +34173,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1042</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1043</v>
+        <v>1052</v>
       </c>
       <c r="B3" s="17" t="n">
         <v>100</v>
@@ -34213,7 +34186,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1044</v>
+        <v>1053</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>5</v>
@@ -34221,7 +34194,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1045</v>
+        <v>1054</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>100</v>
@@ -34232,25 +34205,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1046</v>
+        <v>1055</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1048</v>
+        <v>1057</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1049</v>
+        <v>1058</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1051</v>
+        <v>1060</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>1050</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34435,7 +34408,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1052</v>
+        <v>1061</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>99</v>
@@ -34465,27 +34438,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1053</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1054</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1055</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1056</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>1057</v>
+        <v>1066</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>0.05</v>
@@ -34493,7 +34466,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>0.01</v>
@@ -34501,7 +34474,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>12.5</v>
@@ -34509,7 +34482,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>1060</v>
+        <v>1069</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>6.25</v>
@@ -34520,22 +34493,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>1061</v>
+        <v>1070</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>1062</v>
+        <v>1071</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>1047</v>
+        <v>1056</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>1063</v>
+        <v>1072</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>1064</v>
+        <v>1073</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1065</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34714,12 +34687,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1066</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1067</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -34756,16 +34729,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1068</v>
+        <v>1077</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1069</v>
+        <v>1078</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1070</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34777,15 +34750,15 @@
       </c>
       <c r="C2" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A2,'All Upgrades'!$B$2:$B$541,B2,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1118</v>
+        <v>112</v>
       </c>
       <c r="D2" s="23" t="n">
         <f aca="false">C2/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>1.56912280701754</v>
+        <v>0.15719298245614</v>
       </c>
       <c r="E2" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A2,'All Upgrades'!$B$2:$B$541,B2)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34797,15 +34770,15 @@
       </c>
       <c r="C3" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A3,'All Upgrades'!$B$2:$B$541,B3,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1229</v>
+        <v>861</v>
       </c>
       <c r="D3" s="23" t="n">
         <f aca="false">C3/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>1.72491228070175</v>
+        <v>1.20842105263158</v>
       </c>
       <c r="E3" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A3,'All Upgrades'!$B$2:$B$541,B3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34817,11 +34790,11 @@
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A4,'All Upgrades'!$B$2:$B$541,B4,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1353</v>
+        <v>1149</v>
       </c>
       <c r="D4" s="23" t="n">
         <f aca="false">C4/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>1.89894736842105</v>
+        <v>1.61263157894737</v>
       </c>
       <c r="E4" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A4,'All Upgrades'!$B$2:$B$541,B4)</f>
@@ -34837,11 +34810,11 @@
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A5,'All Upgrades'!$B$2:$B$541,B5,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1486</v>
+        <v>1116</v>
       </c>
       <c r="D5" s="23" t="n">
         <f aca="false">C5/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.08561403508772</v>
+        <v>1.56631578947368</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A5,'All Upgrades'!$B$2:$B$541,B5)</f>
@@ -34857,11 +34830,11 @@
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A6,'All Upgrades'!$B$2:$B$541,B6,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1636</v>
+        <v>1227</v>
       </c>
       <c r="D6" s="23" t="n">
         <f aca="false">C6/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.29614035087719</v>
+        <v>1.72210526315789</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A6,'All Upgrades'!$B$2:$B$541,B6)</f>
@@ -34897,15 +34870,15 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A8,'All Upgrades'!$B$2:$B$541,B8,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1426</v>
+        <v>142</v>
       </c>
       <c r="D8" s="23" t="n">
         <f aca="false">C8/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.00140350877193</v>
+        <v>0.199298245614035</v>
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A8,'All Upgrades'!$B$2:$B$541,B8)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34917,15 +34890,15 @@
       </c>
       <c r="C9" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A9,'All Upgrades'!$B$2:$B$541,B9,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1567</v>
+        <v>1097</v>
       </c>
       <c r="D9" s="23" t="n">
         <f aca="false">C9/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19929824561404</v>
+        <v>1.53964912280702</v>
       </c>
       <c r="E9" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A9,'All Upgrades'!$B$2:$B$541,B9)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34937,11 +34910,11 @@
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A10,'All Upgrades'!$B$2:$B$541,B10,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1725</v>
+        <v>1465</v>
       </c>
       <c r="D10" s="23" t="n">
         <f aca="false">C10/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.42105263157895</v>
+        <v>2.05614035087719</v>
       </c>
       <c r="E10" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A10,'All Upgrades'!$B$2:$B$541,B10)</f>
@@ -34957,11 +34930,11 @@
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A11,'All Upgrades'!$B$2:$B$541,B11,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1896</v>
+        <v>1423</v>
       </c>
       <c r="D11" s="23" t="n">
         <f aca="false">C11/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66105263157895</v>
+        <v>1.99719298245614</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A11,'All Upgrades'!$B$2:$B$541,B11)</f>
@@ -34977,11 +34950,11 @@
       </c>
       <c r="C12" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A12,'All Upgrades'!$B$2:$B$541,B12,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>2086</v>
+        <v>1565</v>
       </c>
       <c r="D12" s="23" t="n">
         <f aca="false">C12/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92771929824561</v>
+        <v>2.19649122807018</v>
       </c>
       <c r="E12" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A12,'All Upgrades'!$B$2:$B$541,B12)</f>
@@ -35017,15 +34990,15 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A14,'All Upgrades'!$B$2:$B$541,B14,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>775</v>
+        <v>78</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">C14*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2</v>
+        <v>0.201290322580645</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A14,'All Upgrades'!$B$2:$B$541,B14)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35037,15 +35010,15 @@
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A15,'All Upgrades'!$B$2:$B$541,B15,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>852</v>
+        <v>596</v>
       </c>
       <c r="D15" s="23" t="n">
         <f aca="false">C15*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19870967741936</v>
+        <v>1.53806451612903</v>
       </c>
       <c r="E15" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A15,'All Upgrades'!$B$2:$B$541,B15)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35057,11 +35030,11 @@
       </c>
       <c r="C16" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A16,'All Upgrades'!$B$2:$B$541,B16,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>937</v>
+        <v>797</v>
       </c>
       <c r="D16" s="23" t="n">
         <f aca="false">C16*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.41806451612903</v>
+        <v>2.05677419354839</v>
       </c>
       <c r="E16" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A16,'All Upgrades'!$B$2:$B$541,B16)</f>
@@ -35077,11 +35050,11 @@
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A17,'All Upgrades'!$B$2:$B$541,B17,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1031</v>
+        <v>774</v>
       </c>
       <c r="D17" s="23" t="n">
         <f aca="false">C17*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66064516129032</v>
+        <v>1.99741935483871</v>
       </c>
       <c r="E17" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A17,'All Upgrades'!$B$2:$B$541,B17)</f>
@@ -35097,11 +35070,11 @@
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A18,'All Upgrades'!$B$2:$B$541,B18,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1135</v>
+        <v>849</v>
       </c>
       <c r="D18" s="23" t="n">
         <f aca="false">C18*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92903225806452</v>
+        <v>2.19096774193548</v>
       </c>
       <c r="E18" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A18,'All Upgrades'!$B$2:$B$541,B18)</f>
@@ -35137,15 +35110,15 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A20,'All Upgrades'!$B$2:$B$541,B20,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>937</v>
+        <v>93</v>
       </c>
       <c r="D20" s="23" t="n">
         <f aca="false">C20/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>1.99893333333333</v>
+        <v>0.1984</v>
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A20,'All Upgrades'!$B$2:$B$541,B20)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35157,15 +35130,15 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A21,'All Upgrades'!$B$2:$B$541,B21,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1030</v>
+        <v>723</v>
       </c>
       <c r="D21" s="23" t="n">
         <f aca="false">C21/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19733333333333</v>
+        <v>1.5424</v>
       </c>
       <c r="E21" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A21,'All Upgrades'!$B$2:$B$541,B21)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35177,11 +35150,11 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A22,'All Upgrades'!$B$2:$B$541,B22,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1135</v>
+        <v>964</v>
       </c>
       <c r="D22" s="23" t="n">
         <f aca="false">C22/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.42133333333333</v>
+        <v>2.05653333333333</v>
       </c>
       <c r="E22" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A22,'All Upgrades'!$B$2:$B$541,B22)</f>
@@ -35197,11 +35170,11 @@
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A23,'All Upgrades'!$B$2:$B$541,B23,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1246</v>
+        <v>937</v>
       </c>
       <c r="D23" s="23" t="n">
         <f aca="false">C23/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.65813333333333</v>
+        <v>1.99893333333333</v>
       </c>
       <c r="E23" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A23,'All Upgrades'!$B$2:$B$541,B23)</f>
@@ -35217,11 +35190,11 @@
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A24,'All Upgrades'!$B$2:$B$541,B24,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1373</v>
+        <v>1029</v>
       </c>
       <c r="D24" s="23" t="n">
         <f aca="false">C24/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92906666666667</v>
+        <v>2.1952</v>
       </c>
       <c r="E24" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A24,'All Upgrades'!$B$2:$B$541,B24)</f>
@@ -35257,15 +35230,15 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A26,'All Upgrades'!$B$2:$B$541,B26,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>525</v>
+        <v>53</v>
       </c>
       <c r="D26" s="23" t="n">
         <f aca="false">C26/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2</v>
+        <v>0.201904761904762</v>
       </c>
       <c r="E26" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A26,'All Upgrades'!$B$2:$B$541,B26)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35277,15 +35250,15 @@
       </c>
       <c r="C27" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A27,'All Upgrades'!$B$2:$B$541,B27,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>578</v>
+        <v>404</v>
       </c>
       <c r="D27" s="23" t="n">
         <f aca="false">C27/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.20190476190476</v>
+        <v>1.53904761904762</v>
       </c>
       <c r="E27" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A27,'All Upgrades'!$B$2:$B$541,B27)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35297,11 +35270,11 @@
       </c>
       <c r="C28" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A28,'All Upgrades'!$B$2:$B$541,B28,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>635</v>
+        <v>541</v>
       </c>
       <c r="D28" s="23" t="n">
         <f aca="false">C28/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.41904761904762</v>
+        <v>2.06095238095238</v>
       </c>
       <c r="E28" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A28,'All Upgrades'!$B$2:$B$541,B28)</f>
@@ -35317,11 +35290,11 @@
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A29,'All Upgrades'!$B$2:$B$541,B29,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>699</v>
+        <v>525</v>
       </c>
       <c r="D29" s="23" t="n">
         <f aca="false">C29/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66285714285714</v>
+        <v>2</v>
       </c>
       <c r="E29" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A29,'All Upgrades'!$B$2:$B$541,B29)</f>
@@ -35337,11 +35310,11 @@
       </c>
       <c r="C30" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A30,'All Upgrades'!$B$2:$B$541,B30,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>770</v>
+        <v>578</v>
       </c>
       <c r="D30" s="23" t="n">
         <f aca="false">C30/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.93333333333333</v>
+        <v>2.20190476190476</v>
       </c>
       <c r="E30" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A30,'All Upgrades'!$B$2:$B$541,B30)</f>
@@ -35377,15 +35350,15 @@
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A32,'All Upgrades'!$B$2:$B$541,B32,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>826</v>
+        <v>81</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">C32/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.00242424242424</v>
+        <v>0.196363636363636</v>
       </c>
       <c r="E32" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A32,'All Upgrades'!$B$2:$B$541,B32)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35397,15 +35370,15 @@
       </c>
       <c r="C33" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A33,'All Upgrades'!$B$2:$B$541,B33,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>907</v>
+        <v>635</v>
       </c>
       <c r="D33" s="23" t="n">
         <f aca="false">C33/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19878787878788</v>
+        <v>1.53939393939394</v>
       </c>
       <c r="E33" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A33,'All Upgrades'!$B$2:$B$541,B33)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35417,11 +35390,11 @@
       </c>
       <c r="C34" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A34,'All Upgrades'!$B$2:$B$541,B34,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>999</v>
+        <v>849</v>
       </c>
       <c r="D34" s="23" t="n">
         <f aca="false">C34/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.42181818181818</v>
+        <v>2.05818181818182</v>
       </c>
       <c r="E34" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A34,'All Upgrades'!$B$2:$B$541,B34)</f>
@@ -35437,11 +35410,11 @@
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A35,'All Upgrades'!$B$2:$B$541,B35,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1098</v>
+        <v>826</v>
       </c>
       <c r="D35" s="23" t="n">
         <f aca="false">C35/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66181818181818</v>
+        <v>2.00242424242424</v>
       </c>
       <c r="E35" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A35,'All Upgrades'!$B$2:$B$541,B35)</f>
@@ -35457,11 +35430,11 @@
       </c>
       <c r="C36" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A36,'All Upgrades'!$B$2:$B$541,B36,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1207</v>
+        <v>906</v>
       </c>
       <c r="D36" s="23" t="n">
         <f aca="false">C36/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92606060606061</v>
+        <v>2.19636363636364</v>
       </c>
       <c r="E36" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A36,'All Upgrades'!$B$2:$B$541,B36)</f>
@@ -35497,15 +35470,15 @@
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>11250</v>
+        <v>1123</v>
       </c>
       <c r="D38" s="23" t="n">
         <f aca="false">C38/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2</v>
+        <v>0.199644444444444</v>
       </c>
       <c r="E38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35517,15 +35490,15 @@
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A39,'All Upgrades'!$B$2:$B$541,B39,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>12374</v>
+        <v>8663</v>
       </c>
       <c r="D39" s="23" t="n">
         <f aca="false">C39/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19982222222222</v>
+        <v>1.54008888888889</v>
       </c>
       <c r="E39" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A39,'All Upgrades'!$B$2:$B$541,B39)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35537,11 +35510,11 @@
       </c>
       <c r="C40" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A40,'All Upgrades'!$B$2:$B$541,B40,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>13614</v>
+        <v>11571</v>
       </c>
       <c r="D40" s="23" t="n">
         <f aca="false">C40/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.42026666666667</v>
+        <v>2.05706666666667</v>
       </c>
       <c r="E40" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A40,'All Upgrades'!$B$2:$B$541,B40)</f>
@@ -35557,11 +35530,11 @@
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A41,'All Upgrades'!$B$2:$B$541,B41,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>14973</v>
+        <v>11229</v>
       </c>
       <c r="D41" s="23" t="n">
         <f aca="false">C41/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66186666666667</v>
+        <v>1.99626666666667</v>
       </c>
       <c r="E41" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A41,'All Upgrades'!$B$2:$B$541,B41)</f>
@@ -35577,11 +35550,11 @@
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A42,'All Upgrades'!$B$2:$B$541,B42,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>16472</v>
+        <v>12352</v>
       </c>
       <c r="D42" s="23" t="n">
         <f aca="false">C42/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92835555555556</v>
+        <v>2.19591111111111</v>
       </c>
       <c r="E42" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A42,'All Upgrades'!$B$2:$B$541,B42)</f>
@@ -35617,15 +35590,15 @@
       </c>
       <c r="C44" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A44,'All Upgrades'!$B$2:$B$541,B44,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1050</v>
+        <v>105</v>
       </c>
       <c r="D44" s="23" t="n">
         <f aca="false">C44/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="E44" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A44,'All Upgrades'!$B$2:$B$541,B44)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35637,15 +35610,15 @@
       </c>
       <c r="C45" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A45,'All Upgrades'!$B$2:$B$541,B45,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1154</v>
+        <v>810</v>
       </c>
       <c r="D45" s="23" t="n">
         <f aca="false">C45/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.19809523809524</v>
+        <v>1.54285714285714</v>
       </c>
       <c r="E45" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A45,'All Upgrades'!$B$2:$B$541,B45)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35657,11 +35630,11 @@
       </c>
       <c r="C46" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A46,'All Upgrades'!$B$2:$B$541,B46,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1270</v>
+        <v>1079</v>
       </c>
       <c r="D46" s="23" t="n">
         <f aca="false">C46/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.41904761904762</v>
+        <v>2.0552380952381</v>
       </c>
       <c r="E46" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A46,'All Upgrades'!$B$2:$B$541,B46)</f>
@@ -35677,11 +35650,11 @@
       </c>
       <c r="C47" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A47,'All Upgrades'!$B$2:$B$541,B47,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1397</v>
+        <v>1048</v>
       </c>
       <c r="D47" s="23" t="n">
         <f aca="false">C47/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.66095238095238</v>
+        <v>1.99619047619048</v>
       </c>
       <c r="E47" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A47,'All Upgrades'!$B$2:$B$541,B47)</f>
@@ -35697,11 +35670,11 @@
       </c>
       <c r="C48" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A48,'All Upgrades'!$B$2:$B$541,B48,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1536</v>
+        <v>1152</v>
       </c>
       <c r="D48" s="23" t="n">
         <f aca="false">C48/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92571428571429</v>
+        <v>2.19428571428571</v>
       </c>
       <c r="E48" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A48,'All Upgrades'!$B$2:$B$541,B48)</f>
@@ -35737,15 +35710,15 @@
       </c>
       <c r="C50" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A50,'All Upgrades'!$B$2:$B$541,B50,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="D50" s="23" t="n">
         <f aca="false">C50/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2</v>
+        <v>0.117073170731707</v>
       </c>
       <c r="E50" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A50,'All Upgrades'!$B$2:$B$541,B50)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35757,15 +35730,15 @@
       </c>
       <c r="C51" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A51,'All Upgrades'!$B$2:$B$541,B51,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>226</v>
+        <v>15</v>
       </c>
       <c r="D51" s="23" t="n">
         <f aca="false">C51/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.20487804878049</v>
+        <v>0.146341463414634</v>
       </c>
       <c r="E51" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A51,'All Upgrades'!$B$2:$B$541,B51)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35777,11 +35750,11 @@
       </c>
       <c r="C52" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A52,'All Upgrades'!$B$2:$B$541,B52,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>247</v>
+        <v>22</v>
       </c>
       <c r="D52" s="23" t="n">
         <f aca="false">C52/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.40975609756098</v>
+        <v>0.214634146341463</v>
       </c>
       <c r="E52" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A52,'All Upgrades'!$B$2:$B$541,B52)</f>
@@ -35797,11 +35770,11 @@
       </c>
       <c r="C53" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A53,'All Upgrades'!$B$2:$B$541,B53,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="D53" s="23" t="n">
         <f aca="false">C53/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.65365853658537</v>
+        <v>0.273170731707317</v>
       </c>
       <c r="E53" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A53,'All Upgrades'!$B$2:$B$541,B53)</f>
@@ -35817,11 +35790,11 @@
       </c>
       <c r="C54" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A54,'All Upgrades'!$B$2:$B$541,B54,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="D54" s="23" t="n">
         <f aca="false">C54/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.92682926829268</v>
+        <v>0.331707317073171</v>
       </c>
       <c r="E54" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A54,'All Upgrades'!$B$2:$B$541,B54)</f>
@@ -35837,11 +35810,11 @@
       </c>
       <c r="C55" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A55,'All Upgrades'!$B$2:$B$541,B55,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>331</v>
+        <v>40</v>
       </c>
       <c r="D55" s="23" t="n">
         <f aca="false">C55/INDEX(Inputs!$C$15:$C$23,MATCH("hacking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>3.22926829268293</v>
+        <v>0.390243902439024</v>
       </c>
       <c r="E55" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A55,'All Upgrades'!$B$2:$B$541,B55)</f>
@@ -35883,31 +35856,31 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1073</v>
+        <v>1082</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1075</v>
+        <v>1084</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1076</v>
+        <v>1085</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35918,7 +35891,7 @@
         <v>91</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D2" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35952,7 +35925,7 @@
         <v>264</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D3" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35986,7 +35959,7 @@
         <v>368</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36020,7 +35993,7 @@
         <v>454</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36088,7 +36061,7 @@
         <v>118</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36122,7 +36095,7 @@
         <v>278</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36156,7 +36129,7 @@
         <v>379</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36190,7 +36163,7 @@
         <v>465</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36258,7 +36231,7 @@
         <v>144</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36292,7 +36265,7 @@
         <v>292</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36326,7 +36299,7 @@
         <v>390</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36360,7 +36333,7 @@
         <v>476</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36428,7 +36401,7 @@
         <v>170</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36462,7 +36435,7 @@
         <v>306</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36496,7 +36469,7 @@
         <v>401</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36530,7 +36503,7 @@
         <v>487</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36598,7 +36571,7 @@
         <v>196</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36632,7 +36605,7 @@
         <v>320</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36666,7 +36639,7 @@
         <v>411</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36700,7 +36673,7 @@
         <v>497</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36768,7 +36741,7 @@
         <v>222</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36802,7 +36775,7 @@
         <v>334</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36836,7 +36809,7 @@
         <v>422</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36870,7 +36843,7 @@
         <v>508</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36961,16 +36934,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37128,7 +37101,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>90</v>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="1115">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -2086,18 +2086,12 @@
     <t xml:space="preserve">Compression</t>
   </si>
   <si>
-    <t xml:space="preserve">Package passes run faster (on top of Speed), so uploads get fed sooner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 % faster packaging</t>
+    <t xml:space="preserve">More basic resources per decoded cache (stacks with Yield)</t>
   </si>
   <si>
     <t xml:space="preserve">decoding.compression</t>
   </si>
   <si>
-    <t xml:space="preserve">0 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">Field Notes</t>
   </si>
   <si>
@@ -2128,9 +2122,6 @@
     <t xml:space="preserve">0.5 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">20 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 extra intel hacks</t>
   </si>
   <si>
@@ -2152,9 +2143,6 @@
     <t xml:space="preserve">0.75 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">30 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 extra intel hacks</t>
   </si>
   <si>
@@ -2176,9 +2164,6 @@
     <t xml:space="preserve">1 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">40 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 extra intel hacks</t>
   </si>
   <si>
@@ -2200,9 +2185,6 @@
     <t xml:space="preserve">1.25 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">50 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 extra intel hacks</t>
   </si>
   <si>
@@ -2221,9 +2203,6 @@
     <t xml:space="preserve">1.5 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">60 % faster packaging</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 extra intel hacks</t>
   </si>
   <si>
@@ -2263,7 +2242,7 @@
     <t xml:space="preserve">Burst chance, relative (+20% of its own at max)</t>
   </si>
   <si>
-    <t xml:space="preserve">Chance a fill's inputs are not consumed (payloads, mod hacks, access stage payloads; never the access rares); 20% at max</t>
+    <t xml:space="preserve">Chance a fill's inputs are not consumed (payloads and mod hacks); 20% at max</t>
   </si>
   <si>
     <t xml:space="preserve">compiling.recovery</t>
@@ -2452,6 +2431,9 @@
     <t xml:space="preserve">1.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Admin cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">hacking.bandwidth_recovery</t>
   </si>
   <si>
@@ -2473,6 +2455,9 @@
     <t xml:space="preserve">15 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Vice principal cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">hacking.max_bandwidth</t>
   </si>
   <si>
@@ -2509,6 +2494,9 @@
     <t xml:space="preserve">2 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Principal cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">hacking.mod_slots</t>
   </si>
   <si>
@@ -2542,19 +2530,22 @@
     <t xml:space="preserve">10 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">Superintendent cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">hacking.persistent_session</t>
   </si>
   <si>
     <t xml:space="preserve">0 % charge gain</t>
   </si>
   <si>
-    <t xml:space="preserve">MAJOR: Clean Exit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep 50% of banked caches when traced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hacking.clean_exit</t>
+    <t xml:space="preserve">MAJOR: Second Wind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each win in a multi-hack run restores 25% of max anonymity (anonymity carries over between fights)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hacking.second_wind</t>
   </si>
   <si>
     <t xml:space="preserve">+25 dmg, +0.1 heat</t>
@@ -2575,24 +2566,36 @@
     <t xml:space="preserve">2.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Paralegal cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 /s bandwidth regen</t>
   </si>
   <si>
     <t xml:space="preserve">20 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate attorney cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 % of max anonymity per spoof</t>
   </si>
   <si>
     <t xml:space="preserve">3 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Lawyer cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">50 % auto-spoof threshold</t>
   </si>
   <si>
     <t xml:space="preserve">20 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">Partner cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Evasion</t>
   </si>
   <si>
@@ -2617,24 +2620,36 @@
     <t xml:space="preserve">3.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Orderly cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">4 /s bandwidth regen</t>
   </si>
   <si>
     <t xml:space="preserve">25 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Nurse cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">8 % of max anonymity per spoof</t>
   </si>
   <si>
     <t xml:space="preserve">4 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Doctor cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">60 % auto-spoof threshold</t>
   </si>
   <si>
     <t xml:space="preserve">30 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">Chief of medicine cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Recycler</t>
   </si>
   <si>
@@ -2662,24 +2677,36 @@
     <t xml:space="preserve">4.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Loan Officer Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 /s bandwidth regen</t>
   </si>
   <si>
     <t xml:space="preserve">30 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Branch Manager Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">9 % of max anonymity per spoof</t>
   </si>
   <si>
     <t xml:space="preserve">5 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Security Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">70 % auto-spoof threshold</t>
   </si>
   <si>
     <t xml:space="preserve">40 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">Chief Financial Officer Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Siphon</t>
   </si>
   <si>
@@ -2707,24 +2734,36 @@
     <t xml:space="preserve">5.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Cop cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 /s bandwidth regen</t>
   </si>
   <si>
     <t xml:space="preserve">35 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Detective cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">10 % of max anonymity per spoof</t>
   </si>
   <si>
     <t xml:space="preserve">6 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Sergeant cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">80 % auto-spoof threshold</t>
   </si>
   <si>
     <t xml:space="preserve">50 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">Captain cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Dead Man's Switch</t>
   </si>
   <si>
@@ -2752,24 +2791,36 @@
     <t xml:space="preserve">6.5 /s bandwidth regen</t>
   </si>
   <si>
+    <t xml:space="preserve">Analyst Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">7 /s bandwidth regen</t>
   </si>
   <si>
     <t xml:space="preserve">40 max bandwidth</t>
   </si>
   <si>
+    <t xml:space="preserve">Ambassador Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">11 % of max anonymity per spoof</t>
   </si>
   <si>
     <t xml:space="preserve">7 mod slots</t>
   </si>
   <si>
+    <t xml:space="preserve">Vice President Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">90 % auto-spoof threshold</t>
   </si>
   <si>
     <t xml:space="preserve">60 % charge gain</t>
   </si>
   <si>
+    <t xml:space="preserve">President Cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Exploit Kit</t>
   </si>
   <si>
@@ -2962,7 +3013,7 @@
     <t xml:space="preserve">  • At max: SQL attack heat 0.9 - 0.6 System heat reduction = 0.3 net, the same as an attack makes today.</t>
   </si>
   <si>
-    <t xml:space="preserve">  • Capstones: Clean Exit, Evasion, Recycler, Siphon, Dead Man's Switch, Exploit Kit (decided).</t>
+    <t xml:space="preserve">  • Capstones: Second Wind, Evasion, Recycler, Siphon, Dead Man's Switch, Exploit Kit (decided).</t>
   </si>
   <si>
     <t xml:space="preserve">  • Unused alternates: Multi-Thread, Chain Breach, Overkill Carry.</t>
@@ -3109,7 +3160,7 @@
     <t xml:space="preserve">  • Per tier: Speed x3, Efficiency x2 (rare chance, +4% max), Yield (+10% basics), Rare Tracker (+0.25% per dry cache),</t>
   </si>
   <si>
-    <t xml:space="preserve">    Compression (+10% packaged), Field Notes (+1 intel hack), Capstone.</t>
+    <t xml:space="preserve">    Compression (+10% basics per cache), Field Notes (+1 intel hack), Capstone.</t>
   </si>
   <si>
     <t xml:space="preserve">  • Capstones: Overclock, Token Vault (token x2), Index (mod), Forensics (mod), Survey (mod), Clean Room.</t>
@@ -4020,8 +4071,8 @@
         <v>27</v>
       </c>
       <c r="L2" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B2-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D2-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B2-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D2-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -4074,8 +4125,8 @@
         <v>27</v>
       </c>
       <c r="L3" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B3-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D3-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B3-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D3-1)/Inputs!$B$12,0))</f>
+        <v>24</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -4182,8 +4233,8 @@
         <v>27</v>
       </c>
       <c r="L5" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B5-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D5-1)/Inputs!$B$12,0))</f>
-        <v>11</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B5-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D5-1)/Inputs!$B$12,0))</f>
+        <v>32</v>
       </c>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -4236,8 +4287,8 @@
         <v>27</v>
       </c>
       <c r="L6" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B6-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D6-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B6-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D6-1)/Inputs!$B$12,0))</f>
+        <v>37</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -4290,8 +4341,8 @@
         <v>27</v>
       </c>
       <c r="L7" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B7-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D7-1)/Inputs!$B$12,0))</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B7-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D7-1)/Inputs!$B$12,0))</f>
+        <v>42</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -4344,8 +4395,8 @@
         <v>27</v>
       </c>
       <c r="L8" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B8-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D8-1)/Inputs!$B$12,0))</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B8-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D8-1)/Inputs!$B$12,0))</f>
+        <v>49</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -4398,8 +4449,8 @@
         <v>27</v>
       </c>
       <c r="L9" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B9-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D9-1)/Inputs!$B$12,0))</f>
-        <v>19</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B9-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D9-1)/Inputs!$B$12,0))</f>
+        <v>56</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
@@ -4504,8 +4555,8 @@
         <v>27</v>
       </c>
       <c r="L11" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B11-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D11-1)/Inputs!$B$12,0))</f>
-        <v>25</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B11-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D11-1)/Inputs!$B$12,0))</f>
+        <v>74</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>91</v>
@@ -7278,8 +7329,8 @@
         <v>27</v>
       </c>
       <c r="L62" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B62-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D62-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B62-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D62-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -7332,8 +7383,8 @@
         <v>27</v>
       </c>
       <c r="L63" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B63-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D63-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B63-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D63-1)/Inputs!$B$12,0))</f>
+        <v>24</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -7386,8 +7437,8 @@
         <v>27</v>
       </c>
       <c r="L64" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B64-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D64-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B64-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D64-1)/Inputs!$B$12,0))</f>
+        <v>28</v>
       </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
@@ -7440,8 +7491,8 @@
         <v>27</v>
       </c>
       <c r="L65" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B65-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D65-1)/Inputs!$B$12,0))</f>
-        <v>11</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B65-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D65-1)/Inputs!$B$12,0))</f>
+        <v>32</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -7494,8 +7545,8 @@
         <v>27</v>
       </c>
       <c r="L66" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B66-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D66-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B66-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D66-1)/Inputs!$B$12,0))</f>
+        <v>37</v>
       </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
@@ -7548,8 +7599,8 @@
         <v>27</v>
       </c>
       <c r="L67" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B67-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D67-1)/Inputs!$B$12,0))</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B67-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D67-1)/Inputs!$B$12,0))</f>
+        <v>42</v>
       </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
@@ -7602,8 +7653,8 @@
         <v>27</v>
       </c>
       <c r="L68" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B68-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D68-1)/Inputs!$B$12,0))</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B68-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D68-1)/Inputs!$B$12,0))</f>
+        <v>49</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -7656,8 +7707,8 @@
         <v>27</v>
       </c>
       <c r="L69" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B69-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D69-1)/Inputs!$B$12,0))</f>
-        <v>19</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B69-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D69-1)/Inputs!$B$12,0))</f>
+        <v>56</v>
       </c>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
@@ -7710,8 +7761,8 @@
         <v>27</v>
       </c>
       <c r="L70" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B70-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D70-1)/Inputs!$B$12,0))</f>
-        <v>21</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B70-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D70-1)/Inputs!$B$12,0))</f>
+        <v>64</v>
       </c>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
@@ -7762,8 +7813,8 @@
         <v>27</v>
       </c>
       <c r="L71" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B71-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D71-1)/Inputs!$B$12,0))</f>
-        <v>25</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B71-1)*INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D71-1)/Inputs!$B$12,0))</f>
+        <v>74</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>264</v>
@@ -10536,8 +10587,8 @@
         <v>338</v>
       </c>
       <c r="L122" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B122-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D122-1)/Inputs!$B$12,0))</f>
-        <v>4</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B122-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D122-1)/Inputs!$B$12,0))</f>
+        <v>11</v>
       </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
@@ -10590,8 +10641,8 @@
         <v>338</v>
       </c>
       <c r="L123" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B123-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D123-1)/Inputs!$B$12,0))</f>
-        <v>4</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B123-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D123-1)/Inputs!$B$12,0))</f>
+        <v>13</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -10644,8 +10695,8 @@
         <v>338</v>
       </c>
       <c r="L124" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B124-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D124-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B124-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D124-1)/Inputs!$B$12,0))</f>
+        <v>15</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -10698,8 +10749,8 @@
         <v>338</v>
       </c>
       <c r="L125" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B125-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D125-1)/Inputs!$B$12,0))</f>
-        <v>6</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B125-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D125-1)/Inputs!$B$12,0))</f>
+        <v>17</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -10752,8 +10803,8 @@
         <v>338</v>
       </c>
       <c r="L126" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B126-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D126-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B126-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D126-1)/Inputs!$B$12,0))</f>
+        <v>20</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -10806,8 +10857,8 @@
         <v>338</v>
       </c>
       <c r="L127" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B127-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D127-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B127-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D127-1)/Inputs!$B$12,0))</f>
+        <v>23</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -10860,8 +10911,8 @@
         <v>338</v>
       </c>
       <c r="L128" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B128-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D128-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B128-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D128-1)/Inputs!$B$12,0))</f>
+        <v>26</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -10914,8 +10965,8 @@
         <v>338</v>
       </c>
       <c r="L129" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B129-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D129-1)/Inputs!$B$12,0))</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B129-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D129-1)/Inputs!$B$12,0))</f>
+        <v>30</v>
       </c>
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
@@ -10968,8 +11019,8 @@
         <v>338</v>
       </c>
       <c r="L130" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B130-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D130-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B130-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D130-1)/Inputs!$B$12,0))</f>
+        <v>35</v>
       </c>
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
@@ -11020,8 +11071,8 @@
         <v>338</v>
       </c>
       <c r="L131" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B131-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D131-1)/Inputs!$B$12,0))</f>
-        <v>13</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B131-1)*INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/3*Inputs!$B$7*Inputs!$B$6^(D131-1)/Inputs!$B$12,0))</f>
+        <v>40</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>368</v>
@@ -13794,8 +13845,8 @@
         <v>426</v>
       </c>
       <c r="L182" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B182-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D182-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B182-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D182-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
@@ -13848,8 +13899,8 @@
         <v>426</v>
       </c>
       <c r="L183" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B183-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D183-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B183-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D183-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
@@ -13902,8 +13953,8 @@
         <v>426</v>
       </c>
       <c r="L184" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B184-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D184-1)/Inputs!$B$12,0))</f>
-        <v>6</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B184-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D184-1)/Inputs!$B$12,0))</f>
+        <v>18</v>
       </c>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
@@ -13956,8 +14007,8 @@
         <v>426</v>
       </c>
       <c r="L185" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B185-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D185-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B185-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D185-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
@@ -14010,8 +14061,8 @@
         <v>426</v>
       </c>
       <c r="L186" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B186-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D186-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B186-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D186-1)/Inputs!$B$12,0))</f>
+        <v>24</v>
       </c>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
@@ -14064,8 +14115,8 @@
         <v>426</v>
       </c>
       <c r="L187" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B187-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D187-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B187-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D187-1)/Inputs!$B$12,0))</f>
+        <v>28</v>
       </c>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
@@ -14118,8 +14169,8 @@
         <v>426</v>
       </c>
       <c r="L188" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B188-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D188-1)/Inputs!$B$12,0))</f>
-        <v>11</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B188-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D188-1)/Inputs!$B$12,0))</f>
+        <v>32</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -14172,8 +14223,8 @@
         <v>426</v>
       </c>
       <c r="L189" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B189-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D189-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B189-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D189-1)/Inputs!$B$12,0))</f>
+        <v>37</v>
       </c>
       <c r="M189" s="4"/>
       <c r="N189" s="4"/>
@@ -14226,8 +14277,8 @@
         <v>426</v>
       </c>
       <c r="L190" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B190-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D190-1)/Inputs!$B$12,0))</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B190-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D190-1)/Inputs!$B$12,0))</f>
+        <v>42</v>
       </c>
       <c r="M190" s="4"/>
       <c r="N190" s="4"/>
@@ -14278,8 +14329,8 @@
         <v>426</v>
       </c>
       <c r="L191" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B191-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D191-1)/Inputs!$B$12,0))</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B191-1)*INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D191-1)/Inputs!$B$12,0))</f>
+        <v>49</v>
       </c>
       <c r="M191" s="6" t="s">
         <v>454</v>
@@ -17052,8 +17103,8 @@
         <v>512</v>
       </c>
       <c r="L242" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B242-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D242-1)/Inputs!$B$12,0))</f>
-        <v>3</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B242-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D242-1)/Inputs!$B$12,0))</f>
+        <v>8</v>
       </c>
       <c r="M242" s="2"/>
       <c r="N242" s="2"/>
@@ -17106,8 +17157,8 @@
         <v>512</v>
       </c>
       <c r="L243" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B243-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D243-1)/Inputs!$B$12,0))</f>
-        <v>3</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B243-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D243-1)/Inputs!$B$12,0))</f>
+        <v>9</v>
       </c>
       <c r="M243" s="2"/>
       <c r="N243" s="2"/>
@@ -17160,8 +17211,8 @@
         <v>512</v>
       </c>
       <c r="L244" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B244-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D244-1)/Inputs!$B$12,0))</f>
-        <v>3</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B244-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D244-1)/Inputs!$B$12,0))</f>
+        <v>10</v>
       </c>
       <c r="M244" s="2"/>
       <c r="N244" s="2"/>
@@ -17214,8 +17265,8 @@
         <v>512</v>
       </c>
       <c r="L245" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B245-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D245-1)/Inputs!$B$12,0))</f>
-        <v>4</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B245-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D245-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M245" s="2"/>
       <c r="N245" s="2"/>
@@ -17268,8 +17319,8 @@
         <v>512</v>
       </c>
       <c r="L246" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B246-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D246-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B246-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D246-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M246" s="2"/>
       <c r="N246" s="2"/>
@@ -17322,8 +17373,8 @@
         <v>512</v>
       </c>
       <c r="L247" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B247-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D247-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B247-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D247-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M247" s="2"/>
       <c r="N247" s="2"/>
@@ -17376,8 +17427,8 @@
         <v>512</v>
       </c>
       <c r="L248" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B248-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D248-1)/Inputs!$B$12,0))</f>
-        <v>6</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B248-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D248-1)/Inputs!$B$12,0))</f>
+        <v>18</v>
       </c>
       <c r="M248" s="2"/>
       <c r="N248" s="2"/>
@@ -17430,8 +17481,8 @@
         <v>512</v>
       </c>
       <c r="L249" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B249-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D249-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B249-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D249-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
@@ -17484,8 +17535,8 @@
         <v>512</v>
       </c>
       <c r="L250" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B250-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D250-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B250-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D250-1)/Inputs!$B$12,0))</f>
+        <v>24</v>
       </c>
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
@@ -17536,8 +17587,8 @@
         <v>512</v>
       </c>
       <c r="L251" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B251-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D251-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B251-1)*INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D251-1)/Inputs!$B$12,0))</f>
+        <v>27</v>
       </c>
       <c r="M251" s="6" t="s">
         <v>536</v>
@@ -20310,8 +20361,8 @@
         <v>587</v>
       </c>
       <c r="L302" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B302-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D302-1)/Inputs!$B$12,0))</f>
-        <v>4</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B302-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D302-1)/Inputs!$B$12,0))</f>
+        <v>12</v>
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2"/>
@@ -20364,8 +20415,8 @@
         <v>587</v>
       </c>
       <c r="L303" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B303-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D303-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B303-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D303-1)/Inputs!$B$12,0))</f>
+        <v>14</v>
       </c>
       <c r="M303" s="2"/>
       <c r="N303" s="2"/>
@@ -20418,8 +20469,8 @@
         <v>587</v>
       </c>
       <c r="L304" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B304-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D304-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B304-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D304-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M304" s="2"/>
       <c r="N304" s="2"/>
@@ -20472,8 +20523,8 @@
         <v>587</v>
       </c>
       <c r="L305" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B305-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D305-1)/Inputs!$B$12,0))</f>
-        <v>6</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B305-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D305-1)/Inputs!$B$12,0))</f>
+        <v>19</v>
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2"/>
@@ -20526,8 +20577,8 @@
         <v>587</v>
       </c>
       <c r="L306" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B306-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D306-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B306-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D306-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M306" s="2"/>
       <c r="N306" s="2"/>
@@ -20580,8 +20631,8 @@
         <v>587</v>
       </c>
       <c r="L307" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B307-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D307-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B307-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D307-1)/Inputs!$B$12,0))</f>
+        <v>25</v>
       </c>
       <c r="M307" s="2"/>
       <c r="N307" s="2"/>
@@ -20634,8 +20685,8 @@
         <v>587</v>
       </c>
       <c r="L308" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B308-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D308-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B308-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D308-1)/Inputs!$B$12,0))</f>
+        <v>28</v>
       </c>
       <c r="M308" s="2"/>
       <c r="N308" s="2"/>
@@ -20688,8 +20739,8 @@
         <v>587</v>
       </c>
       <c r="L309" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B309-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D309-1)/Inputs!$B$12,0))</f>
-        <v>11</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B309-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D309-1)/Inputs!$B$12,0))</f>
+        <v>32</v>
       </c>
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
@@ -20742,8 +20793,8 @@
         <v>587</v>
       </c>
       <c r="L310" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B310-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D310-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B310-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D310-1)/Inputs!$B$12,0))</f>
+        <v>37</v>
       </c>
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
@@ -20794,8 +20845,8 @@
         <v>587</v>
       </c>
       <c r="L311" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B311-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D311-1)/Inputs!$B$12,0))</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B311-1)*INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D311-1)/Inputs!$B$12,0))</f>
+        <v>43</v>
       </c>
       <c r="M311" s="6" t="s">
         <v>91</v>
@@ -23568,8 +23619,8 @@
         <v>667</v>
       </c>
       <c r="L362" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B362-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D362-1)/Inputs!$B$12,0))</f>
-        <v>55</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B362-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D362-1)/Inputs!$B$12,0))</f>
+        <v>166</v>
       </c>
       <c r="M362" s="2"/>
       <c r="N362" s="2"/>
@@ -23622,8 +23673,8 @@
         <v>667</v>
       </c>
       <c r="L363" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B363-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D363-1)/Inputs!$B$12,0))</f>
-        <v>64</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B363-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D363-1)/Inputs!$B$12,0))</f>
+        <v>191</v>
       </c>
       <c r="M363" s="2"/>
       <c r="N363" s="2"/>
@@ -23676,8 +23727,8 @@
         <v>667</v>
       </c>
       <c r="L364" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B364-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D364-1)/Inputs!$B$12,0))</f>
-        <v>73</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B364-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D364-1)/Inputs!$B$12,0))</f>
+        <v>220</v>
       </c>
       <c r="M364" s="2"/>
       <c r="N364" s="2"/>
@@ -23730,8 +23781,8 @@
         <v>667</v>
       </c>
       <c r="L365" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B365-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D365-1)/Inputs!$B$12,0))</f>
-        <v>84</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B365-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D365-1)/Inputs!$B$12,0))</f>
+        <v>253</v>
       </c>
       <c r="M365" s="2"/>
       <c r="N365" s="2"/>
@@ -23784,8 +23835,8 @@
         <v>667</v>
       </c>
       <c r="L366" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B366-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D366-1)/Inputs!$B$12,0))</f>
-        <v>97</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B366-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D366-1)/Inputs!$B$12,0))</f>
+        <v>291</v>
       </c>
       <c r="M366" s="2"/>
       <c r="N366" s="2"/>
@@ -23838,8 +23889,8 @@
         <v>667</v>
       </c>
       <c r="L367" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B367-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D367-1)/Inputs!$B$12,0))</f>
-        <v>111</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B367-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D367-1)/Inputs!$B$12,0))</f>
+        <v>334</v>
       </c>
       <c r="M367" s="2"/>
       <c r="N367" s="2"/>
@@ -23892,8 +23943,8 @@
         <v>667</v>
       </c>
       <c r="L368" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B368-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D368-1)/Inputs!$B$12,0))</f>
-        <v>128</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B368-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D368-1)/Inputs!$B$12,0))</f>
+        <v>384</v>
       </c>
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
@@ -23940,14 +23991,14 @@
         <v>363</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="K369" s="5" t="s">
         <v>667</v>
       </c>
       <c r="L369" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B369-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D369-1)/Inputs!$B$12,0))</f>
-        <v>147</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B369-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D369-1)/Inputs!$B$12,0))</f>
+        <v>442</v>
       </c>
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
@@ -23956,13 +24007,13 @@
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R369" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S369" s="4" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23985,23 +24036,23 @@
         <v>72</v>
       </c>
       <c r="G370" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H370" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I370" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H370" s="5" t="s">
+      <c r="J370" s="4" t="s">
         <v>690</v>
-      </c>
-      <c r="I370" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="J370" s="4" t="s">
-        <v>692</v>
       </c>
       <c r="K370" s="5" t="s">
         <v>667</v>
       </c>
       <c r="L370" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B370-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D370-1)/Inputs!$B$12,0))</f>
-        <v>169</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B370-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D370-1)/Inputs!$B$12,0))</f>
+        <v>508</v>
       </c>
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
@@ -24010,13 +24061,13 @@
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R370" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S370" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24052,8 +24103,8 @@
         <v>667</v>
       </c>
       <c r="L371" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B371-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D371-1)/Inputs!$B$12,0))</f>
-        <v>195</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B371-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D371-1)/Inputs!$B$12,0))</f>
+        <v>585</v>
       </c>
       <c r="M371" s="6" t="s">
         <v>264</v>
@@ -24066,7 +24117,7 @@
       </c>
       <c r="P371" s="7"/>
       <c r="Q371" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="R371" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24108,7 +24159,7 @@
         <v>267</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L372" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B372-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D372-1)/Inputs!$B$12,0))</f>
@@ -24162,7 +24213,7 @@
         <v>268</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L373" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B373-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D373-1)/Inputs!$B$12,0))</f>
@@ -24216,7 +24267,7 @@
         <v>269</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L374" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B374-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D374-1)/Inputs!$B$12,0))</f>
@@ -24270,7 +24321,7 @@
         <v>621</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L375" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B375-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D375-1)/Inputs!$B$12,0))</f>
@@ -24324,7 +24375,7 @@
         <v>622</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L376" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B376-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D376-1)/Inputs!$B$12,0))</f>
@@ -24375,10 +24426,10 @@
         <v>363</v>
       </c>
       <c r="J377" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L377" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B377-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D377-1)/Inputs!$B$12,0))</f>
@@ -24429,10 +24480,10 @@
         <v>680</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K378" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L378" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B378-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D378-1)/Inputs!$B$12,0))</f>
@@ -24483,10 +24534,10 @@
         <v>363</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="K379" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L379" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B379-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D379-1)/Inputs!$B$12,0))</f>
@@ -24499,13 +24550,13 @@
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R379" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S379" s="4" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24528,19 +24579,19 @@
         <v>72</v>
       </c>
       <c r="G380" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H380" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I380" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H380" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="I380" s="4" t="s">
-        <v>691</v>
-      </c>
       <c r="J380" s="4" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="K380" s="5" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L380" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B380-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D380-1)/Inputs!$B$12,0))</f>
@@ -24553,13 +24604,13 @@
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R380" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S380" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24582,17 +24633,17 @@
         <v>87</v>
       </c>
       <c r="G381" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="I381" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="L381" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B381-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D381-1)/Inputs!$B$12,0))</f>
@@ -24609,7 +24660,7 @@
       </c>
       <c r="P381" s="7"/>
       <c r="Q381" s="6" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="R381" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24651,7 +24702,7 @@
         <v>281</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L382" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B382-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D382-1)/Inputs!$B$12,0))</f>
@@ -24705,7 +24756,7 @@
         <v>282</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L383" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B383-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D383-1)/Inputs!$B$12,0))</f>
@@ -24759,7 +24810,7 @@
         <v>283</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L384" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B384-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D384-1)/Inputs!$B$12,0))</f>
@@ -24813,7 +24864,7 @@
         <v>630</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L385" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B385-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D385-1)/Inputs!$B$12,0))</f>
@@ -24867,7 +24918,7 @@
         <v>631</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L386" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B386-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D386-1)/Inputs!$B$12,0))</f>
@@ -24918,10 +24969,10 @@
         <v>363</v>
       </c>
       <c r="J387" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L387" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B387-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D387-1)/Inputs!$B$12,0))</f>
@@ -24940,7 +24991,7 @@
         <v>0.1</v>
       </c>
       <c r="S387" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24972,10 +25023,10 @@
         <v>680</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="K388" s="5" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L388" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B388-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D388-1)/Inputs!$B$12,0))</f>
@@ -24994,7 +25045,7 @@
         <v>0.0025</v>
       </c>
       <c r="S388" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25026,10 +25077,10 @@
         <v>363</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="K389" s="5" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L389" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B389-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D389-1)/Inputs!$B$12,0))</f>
@@ -25042,13 +25093,13 @@
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R389" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S389" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25071,19 +25122,19 @@
         <v>72</v>
       </c>
       <c r="G390" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H390" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I390" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H390" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="I390" s="4" t="s">
-        <v>691</v>
-      </c>
       <c r="J390" s="4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="K390" s="5" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L390" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B390-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D390-1)/Inputs!$B$12,0))</f>
@@ -25096,13 +25147,13 @@
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R390" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S390" s="4" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25125,17 +25176,17 @@
         <v>87</v>
       </c>
       <c r="G391" s="6" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="I391" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="L391" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B391-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D391-1)/Inputs!$B$12,0))</f>
@@ -25152,7 +25203,7 @@
       </c>
       <c r="P391" s="7"/>
       <c r="Q391" s="6" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="R391" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25194,7 +25245,7 @@
         <v>295</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L392" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B392-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D392-1)/Inputs!$B$12,0))</f>
@@ -25248,7 +25299,7 @@
         <v>296</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L393" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B393-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D393-1)/Inputs!$B$12,0))</f>
@@ -25302,7 +25353,7 @@
         <v>297</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L394" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B394-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D394-1)/Inputs!$B$12,0))</f>
@@ -25356,7 +25407,7 @@
         <v>639</v>
       </c>
       <c r="K395" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L395" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B395-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D395-1)/Inputs!$B$12,0))</f>
@@ -25410,7 +25461,7 @@
         <v>640</v>
       </c>
       <c r="K396" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L396" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B396-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D396-1)/Inputs!$B$12,0))</f>
@@ -25461,10 +25512,10 @@
         <v>363</v>
       </c>
       <c r="J397" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="K397" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L397" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B397-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D397-1)/Inputs!$B$12,0))</f>
@@ -25483,7 +25534,7 @@
         <v>0.1</v>
       </c>
       <c r="S397" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25515,10 +25566,10 @@
         <v>680</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="K398" s="5" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L398" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B398-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D398-1)/Inputs!$B$12,0))</f>
@@ -25537,7 +25588,7 @@
         <v>0.0025</v>
       </c>
       <c r="S398" s="4" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25569,10 +25620,10 @@
         <v>363</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="K399" s="5" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L399" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B399-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D399-1)/Inputs!$B$12,0))</f>
@@ -25585,13 +25636,13 @@
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R399" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S399" s="4" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25614,19 +25665,19 @@
         <v>72</v>
       </c>
       <c r="G400" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H400" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I400" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H400" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="I400" s="4" t="s">
-        <v>691</v>
-      </c>
       <c r="J400" s="4" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="K400" s="5" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L400" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B400-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D400-1)/Inputs!$B$12,0))</f>
@@ -25639,13 +25690,13 @@
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R400" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S400" s="4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25668,17 +25719,17 @@
         <v>87</v>
       </c>
       <c r="G401" s="6" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="I401" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L401" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B401-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D401-1)/Inputs!$B$12,0))</f>
@@ -25695,7 +25746,7 @@
       </c>
       <c r="P401" s="7"/>
       <c r="Q401" s="6" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="R401" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25737,7 +25788,7 @@
         <v>309</v>
       </c>
       <c r="K402" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L402" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B402-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D402-1)/Inputs!$B$12,0))</f>
@@ -25791,7 +25842,7 @@
         <v>310</v>
       </c>
       <c r="K403" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L403" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B403-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D403-1)/Inputs!$B$12,0))</f>
@@ -25845,7 +25896,7 @@
         <v>311</v>
       </c>
       <c r="K404" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L404" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B404-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D404-1)/Inputs!$B$12,0))</f>
@@ -25899,7 +25950,7 @@
         <v>648</v>
       </c>
       <c r="K405" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L405" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B405-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D405-1)/Inputs!$B$12,0))</f>
@@ -25953,7 +26004,7 @@
         <v>649</v>
       </c>
       <c r="K406" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L406" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B406-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D406-1)/Inputs!$B$12,0))</f>
@@ -26004,10 +26055,10 @@
         <v>363</v>
       </c>
       <c r="J407" s="2" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="K407" s="3" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L407" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B407-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D407-1)/Inputs!$B$12,0))</f>
@@ -26026,7 +26077,7 @@
         <v>0.1</v>
       </c>
       <c r="S407" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26058,10 +26109,10 @@
         <v>680</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="K408" s="5" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L408" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B408-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D408-1)/Inputs!$B$12,0))</f>
@@ -26080,7 +26131,7 @@
         <v>0.0025</v>
       </c>
       <c r="S408" s="4" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26112,10 +26163,10 @@
         <v>363</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="K409" s="5" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L409" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B409-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D409-1)/Inputs!$B$12,0))</f>
@@ -26128,13 +26179,13 @@
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R409" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S409" s="4" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26157,19 +26208,19 @@
         <v>72</v>
       </c>
       <c r="G410" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H410" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I410" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H410" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="I410" s="4" t="s">
-        <v>691</v>
-      </c>
       <c r="J410" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="K410" s="5" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L410" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B410-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D410-1)/Inputs!$B$12,0))</f>
@@ -26182,13 +26233,13 @@
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R410" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S410" s="4" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26214,14 +26265,14 @@
         <v>318</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="I411" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="L411" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B411-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D411-1)/Inputs!$B$12,0))</f>
@@ -26238,7 +26289,7 @@
       </c>
       <c r="P411" s="7"/>
       <c r="Q411" s="6" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="R411" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26280,7 +26331,7 @@
         <v>323</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L412" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B412-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D412-1)/Inputs!$B$12,0))</f>
@@ -26334,7 +26385,7 @@
         <v>324</v>
       </c>
       <c r="K413" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L413" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B413-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D413-1)/Inputs!$B$12,0))</f>
@@ -26388,7 +26439,7 @@
         <v>325</v>
       </c>
       <c r="K414" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L414" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B414-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D414-1)/Inputs!$B$12,0))</f>
@@ -26442,7 +26493,7 @@
         <v>656</v>
       </c>
       <c r="K415" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L415" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B415-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D415-1)/Inputs!$B$12,0))</f>
@@ -26496,7 +26547,7 @@
         <v>657</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L416" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B416-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D416-1)/Inputs!$B$12,0))</f>
@@ -26547,10 +26598,10 @@
         <v>363</v>
       </c>
       <c r="J417" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="K417" s="3" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L417" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B417-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D417-1)/Inputs!$B$12,0))</f>
@@ -26569,7 +26620,7 @@
         <v>0.1</v>
       </c>
       <c r="S417" s="2" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26601,10 +26652,10 @@
         <v>680</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="K418" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L418" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B418-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D418-1)/Inputs!$B$12,0))</f>
@@ -26623,7 +26674,7 @@
         <v>0.0025</v>
       </c>
       <c r="S418" s="4" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26655,10 +26706,10 @@
         <v>363</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="K419" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L419" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B419-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D419-1)/Inputs!$B$12,0))</f>
@@ -26671,13 +26722,13 @@
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="R419" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S419" s="4" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26700,19 +26751,19 @@
         <v>72</v>
       </c>
       <c r="G420" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="H420" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="I420" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H420" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="I420" s="4" t="s">
-        <v>691</v>
-      </c>
       <c r="J420" s="4" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="K420" s="5" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L420" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B420-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D420-1)/Inputs!$B$12,0))</f>
@@ -26725,13 +26776,13 @@
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="R420" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S420" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26754,17 +26805,17 @@
         <v>87</v>
       </c>
       <c r="G421" s="6" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="I421" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J421" s="6"/>
       <c r="K421" s="7" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="L421" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B421-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D421-1)/Inputs!$B$12,0))</f>
@@ -26781,7 +26832,7 @@
       </c>
       <c r="P421" s="7"/>
       <c r="Q421" s="6" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="R421" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26793,7 +26844,7 @@
     </row>
     <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>1</v>
@@ -26814,7 +26865,7 @@
         <v>225</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I422" s="2" t="s">
         <v>227</v>
@@ -26823,20 +26874,20 @@
         <v>228</v>
       </c>
       <c r="K422" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L422" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0))</f>
-        <v>5</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0))</f>
+        <v>16</v>
       </c>
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
       <c r="O422" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P422" s="3"/>
       <c r="Q422" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R422" s="2" t="n">
         <v>0.1667</v>
@@ -26847,7 +26898,7 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>1</v>
@@ -26868,7 +26919,7 @@
         <v>225</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I423" s="2" t="s">
         <v>227</v>
@@ -26877,20 +26928,20 @@
         <v>232</v>
       </c>
       <c r="K423" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L423" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0))</f>
-        <v>6</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0))</f>
+        <v>18</v>
       </c>
       <c r="M423" s="2"/>
       <c r="N423" s="2"/>
       <c r="O423" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P423" s="3"/>
       <c r="Q423" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R423" s="2" t="n">
         <v>0.1667</v>
@@ -26901,7 +26952,7 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>1</v>
@@ -26922,7 +26973,7 @@
         <v>225</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I424" s="2" t="s">
         <v>227</v>
@@ -26931,20 +26982,20 @@
         <v>233</v>
       </c>
       <c r="K424" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L424" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0))</f>
-        <v>7</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0))</f>
+        <v>21</v>
       </c>
       <c r="M424" s="2"/>
       <c r="N424" s="2"/>
       <c r="O424" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P424" s="3"/>
       <c r="Q424" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R424" s="2" t="n">
         <v>0.1667</v>
@@ -26955,7 +27006,7 @@
     </row>
     <row r="425" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>1</v>
@@ -26976,7 +27027,7 @@
         <v>234</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I425" s="2" t="s">
         <v>592</v>
@@ -26985,20 +27036,20 @@
         <v>593</v>
       </c>
       <c r="K425" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L425" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0))</f>
-        <v>8</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0))</f>
+        <v>24</v>
       </c>
       <c r="M425" s="2"/>
       <c r="N425" s="2"/>
       <c r="O425" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P425" s="3"/>
       <c r="Q425" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R425" s="2" t="n">
         <v>0.016667</v>
@@ -27009,7 +27060,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>1</v>
@@ -27030,7 +27081,7 @@
         <v>234</v>
       </c>
       <c r="H426" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I426" s="2" t="s">
         <v>592</v>
@@ -27039,20 +27090,20 @@
         <v>597</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L426" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0))</f>
-        <v>9</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0))</f>
+        <v>27</v>
       </c>
       <c r="M426" s="2"/>
       <c r="N426" s="2"/>
       <c r="O426" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P426" s="3"/>
       <c r="Q426" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R426" s="2" t="n">
         <v>0.016667</v>
@@ -27061,9 +27112,9 @@
         <v>593</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>1</v>
@@ -27084,7 +27135,7 @@
         <v>436</v>
       </c>
       <c r="H427" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I427" s="2" t="s">
         <v>343</v>
@@ -27093,20 +27144,20 @@
         <v>522</v>
       </c>
       <c r="K427" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L427" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0))</f>
-        <v>10</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0))</f>
+        <v>31</v>
       </c>
       <c r="M427" s="2"/>
       <c r="N427" s="2"/>
       <c r="O427" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P427" s="3"/>
       <c r="Q427" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R427" s="2" t="n">
         <v>0.016667</v>
@@ -27117,7 +27168,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>1</v>
@@ -27147,20 +27198,20 @@
         <v>526</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L428" s="2" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0))</f>
-        <v>12</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0))</f>
+        <v>36</v>
       </c>
       <c r="M428" s="2"/>
       <c r="N428" s="2"/>
       <c r="O428" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P428" s="3"/>
       <c r="Q428" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R428" s="2" t="n">
         <v>0.016667</v>
@@ -27171,7 +27222,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B429" s="4" t="n">
         <v>1</v>
@@ -27189,43 +27240,43 @@
         <v>72</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H429" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="K429" s="5" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L429" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0))</f>
-        <v>14</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0))</f>
+        <v>41</v>
       </c>
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
       <c r="O429" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P429" s="5"/>
       <c r="Q429" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R429" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S429" s="4" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B430" s="4" t="n">
         <v>1</v>
@@ -27243,43 +27294,43 @@
         <v>72</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H430" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I430" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="K430" s="5" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L430" s="4" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0))</f>
-        <v>16</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0))</f>
+        <v>47</v>
       </c>
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
       <c r="O430" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P430" s="5"/>
       <c r="Q430" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R430" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S430" s="4" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B431" s="6" t="n">
         <v>1</v>
@@ -27300,18 +27351,18 @@
         <v>262</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="I431" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J431" s="6"/>
       <c r="K431" s="7" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="L431" s="6" t="n">
-        <f aca="false">MAX(1,ROUND(0.1*Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12,0))</f>
-        <v>18</v>
+        <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12,0))</f>
+        <v>55</v>
       </c>
       <c r="M431" s="6" t="s">
         <v>368</v>
@@ -27320,11 +27371,11 @@
         <v>1</v>
       </c>
       <c r="O431" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P431" s="7"/>
       <c r="Q431" s="6" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="R431" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27336,7 +27387,7 @@
     </row>
     <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>2</v>
@@ -27357,7 +27408,7 @@
         <v>225</v>
       </c>
       <c r="H432" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I432" s="2" t="s">
         <v>266</v>
@@ -27366,7 +27417,7 @@
         <v>267</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L432" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B432-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D432-1)/Inputs!$B$12,0))</f>
@@ -27375,11 +27426,11 @@
       <c r="M432" s="2"/>
       <c r="N432" s="2"/>
       <c r="O432" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P432" s="3"/>
       <c r="Q432" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R432" s="2" t="n">
         <v>0.25</v>
@@ -27390,7 +27441,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>2</v>
@@ -27411,7 +27462,7 @@
         <v>225</v>
       </c>
       <c r="H433" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I433" s="2" t="s">
         <v>266</v>
@@ -27420,7 +27471,7 @@
         <v>268</v>
       </c>
       <c r="K433" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L433" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B433-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D433-1)/Inputs!$B$12,0))</f>
@@ -27429,11 +27480,11 @@
       <c r="M433" s="2"/>
       <c r="N433" s="2"/>
       <c r="O433" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P433" s="3"/>
       <c r="Q433" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R433" s="2" t="n">
         <v>0.25</v>
@@ -27444,7 +27495,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>2</v>
@@ -27465,7 +27516,7 @@
         <v>225</v>
       </c>
       <c r="H434" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I434" s="2" t="s">
         <v>266</v>
@@ -27474,7 +27525,7 @@
         <v>269</v>
       </c>
       <c r="K434" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L434" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B434-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D434-1)/Inputs!$B$12,0))</f>
@@ -27483,11 +27534,11 @@
       <c r="M434" s="2"/>
       <c r="N434" s="2"/>
       <c r="O434" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P434" s="3"/>
       <c r="Q434" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R434" s="2" t="n">
         <v>0.25</v>
@@ -27498,7 +27549,7 @@
     </row>
     <row r="435" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>2</v>
@@ -27519,7 +27570,7 @@
         <v>234</v>
       </c>
       <c r="H435" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I435" s="2" t="s">
         <v>592</v>
@@ -27528,7 +27579,7 @@
         <v>621</v>
       </c>
       <c r="K435" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L435" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B435-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D435-1)/Inputs!$B$12,0))</f>
@@ -27537,11 +27588,11 @@
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
       <c r="O435" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P435" s="3"/>
       <c r="Q435" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R435" s="2" t="n">
         <v>0.016667</v>
@@ -27552,7 +27603,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>2</v>
@@ -27573,7 +27624,7 @@
         <v>234</v>
       </c>
       <c r="H436" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I436" s="2" t="s">
         <v>592</v>
@@ -27582,7 +27633,7 @@
         <v>622</v>
       </c>
       <c r="K436" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L436" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B436-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D436-1)/Inputs!$B$12,0))</f>
@@ -27591,11 +27642,11 @@
       <c r="M436" s="2"/>
       <c r="N436" s="2"/>
       <c r="O436" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P436" s="3"/>
       <c r="Q436" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R436" s="2" t="n">
         <v>0.016667</v>
@@ -27604,9 +27655,9 @@
         <v>621</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>2</v>
@@ -27627,7 +27678,7 @@
         <v>436</v>
       </c>
       <c r="H437" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I437" s="2" t="s">
         <v>343</v>
@@ -27636,7 +27687,7 @@
         <v>541</v>
       </c>
       <c r="K437" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L437" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B437-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D437-1)/Inputs!$B$12,0))</f>
@@ -27645,11 +27696,11 @@
       <c r="M437" s="2"/>
       <c r="N437" s="2"/>
       <c r="O437" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P437" s="3"/>
       <c r="Q437" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R437" s="2" t="n">
         <v>0.016667</v>
@@ -27660,7 +27711,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>2</v>
@@ -27690,7 +27741,7 @@
         <v>542</v>
       </c>
       <c r="K438" s="3" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L438" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B438-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D438-1)/Inputs!$B$12,0))</f>
@@ -27699,11 +27750,11 @@
       <c r="M438" s="2"/>
       <c r="N438" s="2"/>
       <c r="O438" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P438" s="3"/>
       <c r="Q438" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R438" s="2" t="n">
         <v>0.016667</v>
@@ -27714,7 +27765,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B439" s="4" t="n">
         <v>2</v>
@@ -27732,19 +27783,19 @@
         <v>72</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H439" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I439" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="K439" s="5" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L439" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B439-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D439-1)/Inputs!$B$12,0))</f>
@@ -27753,22 +27804,22 @@
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
       <c r="O439" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P439" s="5"/>
       <c r="Q439" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R439" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S439" s="4" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B440" s="4" t="n">
         <v>2</v>
@@ -27786,19 +27837,19 @@
         <v>72</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H440" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I440" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
       <c r="K440" s="5" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L440" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B440-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D440-1)/Inputs!$B$12,0))</f>
@@ -27807,22 +27858,22 @@
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
       <c r="O440" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P440" s="5"/>
       <c r="Q440" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R440" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S440" s="4" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B441" s="6" t="n">
         <v>2</v>
@@ -27840,17 +27891,17 @@
         <v>87</v>
       </c>
       <c r="G441" s="6" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="I441" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J441" s="6"/>
       <c r="K441" s="7" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="L441" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B441-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D441-1)/Inputs!$B$12,0))</f>
@@ -27863,11 +27914,11 @@
         <v>1</v>
       </c>
       <c r="O441" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P441" s="7"/>
       <c r="Q441" s="6" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="R441" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27879,7 +27930,7 @@
     </row>
     <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B442" s="2" t="n">
         <v>3</v>
@@ -27900,7 +27951,7 @@
         <v>225</v>
       </c>
       <c r="H442" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I442" s="2" t="s">
         <v>280</v>
@@ -27909,7 +27960,7 @@
         <v>281</v>
       </c>
       <c r="K442" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L442" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B442-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D442-1)/Inputs!$B$12,0))</f>
@@ -27918,11 +27969,11 @@
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
       <c r="O442" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P442" s="3"/>
       <c r="Q442" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R442" s="2" t="n">
         <v>0.375</v>
@@ -27933,7 +27984,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B443" s="2" t="n">
         <v>3</v>
@@ -27954,7 +28005,7 @@
         <v>225</v>
       </c>
       <c r="H443" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I443" s="2" t="s">
         <v>280</v>
@@ -27963,7 +28014,7 @@
         <v>282</v>
       </c>
       <c r="K443" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L443" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B443-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D443-1)/Inputs!$B$12,0))</f>
@@ -27972,11 +28023,11 @@
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
       <c r="O443" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P443" s="3"/>
       <c r="Q443" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R443" s="2" t="n">
         <v>0.375</v>
@@ -27987,7 +28038,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B444" s="2" t="n">
         <v>3</v>
@@ -28008,7 +28059,7 @@
         <v>225</v>
       </c>
       <c r="H444" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I444" s="2" t="s">
         <v>280</v>
@@ -28017,7 +28068,7 @@
         <v>283</v>
       </c>
       <c r="K444" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L444" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B444-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D444-1)/Inputs!$B$12,0))</f>
@@ -28026,11 +28077,11 @@
       <c r="M444" s="2"/>
       <c r="N444" s="2"/>
       <c r="O444" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P444" s="3"/>
       <c r="Q444" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R444" s="2" t="n">
         <v>0.375</v>
@@ -28041,7 +28092,7 @@
     </row>
     <row r="445" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B445" s="2" t="n">
         <v>3</v>
@@ -28062,7 +28113,7 @@
         <v>234</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I445" s="2" t="s">
         <v>592</v>
@@ -28071,7 +28122,7 @@
         <v>630</v>
       </c>
       <c r="K445" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L445" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B445-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D445-1)/Inputs!$B$12,0))</f>
@@ -28080,11 +28131,11 @@
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
       <c r="O445" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P445" s="3"/>
       <c r="Q445" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R445" s="2" t="n">
         <v>0.016667</v>
@@ -28095,7 +28146,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B446" s="2" t="n">
         <v>3</v>
@@ -28116,7 +28167,7 @@
         <v>234</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I446" s="2" t="s">
         <v>592</v>
@@ -28125,7 +28176,7 @@
         <v>631</v>
       </c>
       <c r="K446" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L446" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B446-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D446-1)/Inputs!$B$12,0))</f>
@@ -28134,11 +28185,11 @@
       <c r="M446" s="2"/>
       <c r="N446" s="2"/>
       <c r="O446" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P446" s="3"/>
       <c r="Q446" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R446" s="2" t="n">
         <v>0.016667</v>
@@ -28147,9 +28198,9 @@
         <v>630</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B447" s="2" t="n">
         <v>3</v>
@@ -28170,7 +28221,7 @@
         <v>436</v>
       </c>
       <c r="H447" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I447" s="2" t="s">
         <v>343</v>
@@ -28179,7 +28230,7 @@
         <v>550</v>
       </c>
       <c r="K447" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L447" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B447-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D447-1)/Inputs!$B$12,0))</f>
@@ -28188,11 +28239,11 @@
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
       <c r="O447" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P447" s="3"/>
       <c r="Q447" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R447" s="2" t="n">
         <v>0.016667</v>
@@ -28203,7 +28254,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B448" s="2" t="n">
         <v>3</v>
@@ -28233,7 +28284,7 @@
         <v>551</v>
       </c>
       <c r="K448" s="3" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L448" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B448-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D448-1)/Inputs!$B$12,0))</f>
@@ -28242,11 +28293,11 @@
       <c r="M448" s="2"/>
       <c r="N448" s="2"/>
       <c r="O448" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P448" s="3"/>
       <c r="Q448" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R448" s="2" t="n">
         <v>0.016667</v>
@@ -28257,7 +28308,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B449" s="4" t="n">
         <v>3</v>
@@ -28275,19 +28326,19 @@
         <v>72</v>
       </c>
       <c r="G449" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H449" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I449" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="K449" s="5" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L449" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B449-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D449-1)/Inputs!$B$12,0))</f>
@@ -28296,22 +28347,22 @@
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
       <c r="O449" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P449" s="5"/>
       <c r="Q449" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R449" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S449" s="4" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B450" s="4" t="n">
         <v>3</v>
@@ -28329,19 +28380,19 @@
         <v>72</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H450" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I450" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="K450" s="5" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L450" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B450-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D450-1)/Inputs!$B$12,0))</f>
@@ -28350,22 +28401,22 @@
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
       <c r="O450" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P450" s="5"/>
       <c r="Q450" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R450" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S450" s="4" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B451" s="6" t="n">
         <v>3</v>
@@ -28383,17 +28434,17 @@
         <v>87</v>
       </c>
       <c r="G451" s="6" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="H451" s="7" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="I451" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J451" s="6"/>
       <c r="K451" s="7" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
       <c r="L451" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B451-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D451-1)/Inputs!$B$12,0))</f>
@@ -28406,11 +28457,11 @@
         <v>2</v>
       </c>
       <c r="O451" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P451" s="7"/>
       <c r="Q451" s="6" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="R451" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28422,7 +28473,7 @@
     </row>
     <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B452" s="2" t="n">
         <v>4</v>
@@ -28443,7 +28494,7 @@
         <v>225</v>
       </c>
       <c r="H452" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I452" s="2" t="s">
         <v>294</v>
@@ -28452,7 +28503,7 @@
         <v>295</v>
       </c>
       <c r="K452" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L452" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B452-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D452-1)/Inputs!$B$12,0))</f>
@@ -28461,11 +28512,11 @@
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
       <c r="O452" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P452" s="3"/>
       <c r="Q452" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R452" s="2" t="n">
         <v>0.5625</v>
@@ -28476,7 +28527,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B453" s="2" t="n">
         <v>4</v>
@@ -28497,7 +28548,7 @@
         <v>225</v>
       </c>
       <c r="H453" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I453" s="2" t="s">
         <v>294</v>
@@ -28506,7 +28557,7 @@
         <v>296</v>
       </c>
       <c r="K453" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L453" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B453-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D453-1)/Inputs!$B$12,0))</f>
@@ -28515,11 +28566,11 @@
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
       <c r="O453" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P453" s="3"/>
       <c r="Q453" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R453" s="2" t="n">
         <v>0.5625</v>
@@ -28530,7 +28581,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B454" s="2" t="n">
         <v>4</v>
@@ -28551,7 +28602,7 @@
         <v>225</v>
       </c>
       <c r="H454" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I454" s="2" t="s">
         <v>294</v>
@@ -28560,7 +28611,7 @@
         <v>297</v>
       </c>
       <c r="K454" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L454" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B454-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D454-1)/Inputs!$B$12,0))</f>
@@ -28569,11 +28620,11 @@
       <c r="M454" s="2"/>
       <c r="N454" s="2"/>
       <c r="O454" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P454" s="3"/>
       <c r="Q454" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R454" s="2" t="n">
         <v>0.5625</v>
@@ -28584,7 +28635,7 @@
     </row>
     <row r="455" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B455" s="2" t="n">
         <v>4</v>
@@ -28605,7 +28656,7 @@
         <v>234</v>
       </c>
       <c r="H455" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I455" s="2" t="s">
         <v>592</v>
@@ -28614,7 +28665,7 @@
         <v>639</v>
       </c>
       <c r="K455" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L455" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B455-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D455-1)/Inputs!$B$12,0))</f>
@@ -28623,11 +28674,11 @@
       <c r="M455" s="2"/>
       <c r="N455" s="2"/>
       <c r="O455" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P455" s="3"/>
       <c r="Q455" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R455" s="2" t="n">
         <v>0.016667</v>
@@ -28638,7 +28689,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B456" s="2" t="n">
         <v>4</v>
@@ -28659,7 +28710,7 @@
         <v>234</v>
       </c>
       <c r="H456" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I456" s="2" t="s">
         <v>592</v>
@@ -28668,7 +28719,7 @@
         <v>640</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L456" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B456-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D456-1)/Inputs!$B$12,0))</f>
@@ -28677,11 +28728,11 @@
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
       <c r="O456" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P456" s="3"/>
       <c r="Q456" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R456" s="2" t="n">
         <v>0.016667</v>
@@ -28690,9 +28741,9 @@
         <v>639</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B457" s="2" t="n">
         <v>4</v>
@@ -28713,7 +28764,7 @@
         <v>436</v>
       </c>
       <c r="H457" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I457" s="2" t="s">
         <v>343</v>
@@ -28722,7 +28773,7 @@
         <v>560</v>
       </c>
       <c r="K457" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L457" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B457-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D457-1)/Inputs!$B$12,0))</f>
@@ -28731,11 +28782,11 @@
       <c r="M457" s="2"/>
       <c r="N457" s="2"/>
       <c r="O457" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P457" s="3"/>
       <c r="Q457" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R457" s="2" t="n">
         <v>0.016667</v>
@@ -28746,7 +28797,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B458" s="2" t="n">
         <v>4</v>
@@ -28776,7 +28827,7 @@
         <v>561</v>
       </c>
       <c r="K458" s="3" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L458" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B458-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D458-1)/Inputs!$B$12,0))</f>
@@ -28785,11 +28836,11 @@
       <c r="M458" s="2"/>
       <c r="N458" s="2"/>
       <c r="O458" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P458" s="3"/>
       <c r="Q458" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R458" s="2" t="n">
         <v>0.016667</v>
@@ -28800,7 +28851,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B459" s="4" t="n">
         <v>4</v>
@@ -28818,19 +28869,19 @@
         <v>72</v>
       </c>
       <c r="G459" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H459" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I459" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="K459" s="5" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L459" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B459-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D459-1)/Inputs!$B$12,0))</f>
@@ -28839,22 +28890,22 @@
       <c r="M459" s="4"/>
       <c r="N459" s="4"/>
       <c r="O459" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P459" s="5"/>
       <c r="Q459" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R459" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S459" s="4" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B460" s="4" t="n">
         <v>4</v>
@@ -28872,19 +28923,19 @@
         <v>72</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H460" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I460" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="K460" s="5" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L460" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B460-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D460-1)/Inputs!$B$12,0))</f>
@@ -28893,22 +28944,22 @@
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
       <c r="O460" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P460" s="5"/>
       <c r="Q460" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R460" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S460" s="4" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B461" s="6" t="n">
         <v>4</v>
@@ -28926,17 +28977,17 @@
         <v>87</v>
       </c>
       <c r="G461" s="6" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="H461" s="7" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="I461" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J461" s="6"/>
       <c r="K461" s="7" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="L461" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B461-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D461-1)/Inputs!$B$12,0))</f>
@@ -28949,11 +29000,11 @@
         <v>2</v>
       </c>
       <c r="O461" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P461" s="7"/>
       <c r="Q461" s="6" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="R461" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28965,7 +29016,7 @@
     </row>
     <row r="462" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B462" s="2" t="n">
         <v>5</v>
@@ -28986,7 +29037,7 @@
         <v>225</v>
       </c>
       <c r="H462" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I462" s="2" t="s">
         <v>308</v>
@@ -28995,7 +29046,7 @@
         <v>309</v>
       </c>
       <c r="K462" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L462" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B462-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D462-1)/Inputs!$B$12,0))</f>
@@ -29004,11 +29055,11 @@
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
       <c r="O462" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P462" s="3"/>
       <c r="Q462" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R462" s="2" t="n">
         <v>0.8438</v>
@@ -29019,7 +29070,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B463" s="2" t="n">
         <v>5</v>
@@ -29040,7 +29091,7 @@
         <v>225</v>
       </c>
       <c r="H463" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I463" s="2" t="s">
         <v>308</v>
@@ -29049,7 +29100,7 @@
         <v>310</v>
       </c>
       <c r="K463" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L463" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B463-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D463-1)/Inputs!$B$12,0))</f>
@@ -29058,11 +29109,11 @@
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
       <c r="O463" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P463" s="3"/>
       <c r="Q463" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R463" s="2" t="n">
         <v>0.8438</v>
@@ -29073,7 +29124,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B464" s="2" t="n">
         <v>5</v>
@@ -29094,7 +29145,7 @@
         <v>225</v>
       </c>
       <c r="H464" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I464" s="2" t="s">
         <v>308</v>
@@ -29103,7 +29154,7 @@
         <v>311</v>
       </c>
       <c r="K464" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L464" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B464-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D464-1)/Inputs!$B$12,0))</f>
@@ -29112,11 +29163,11 @@
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
       <c r="O464" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P464" s="3"/>
       <c r="Q464" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R464" s="2" t="n">
         <v>0.8438</v>
@@ -29127,7 +29178,7 @@
     </row>
     <row r="465" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B465" s="2" t="n">
         <v>5</v>
@@ -29148,7 +29199,7 @@
         <v>234</v>
       </c>
       <c r="H465" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I465" s="2" t="s">
         <v>592</v>
@@ -29157,7 +29208,7 @@
         <v>648</v>
       </c>
       <c r="K465" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L465" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B465-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D465-1)/Inputs!$B$12,0))</f>
@@ -29166,11 +29217,11 @@
       <c r="M465" s="2"/>
       <c r="N465" s="2"/>
       <c r="O465" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P465" s="3"/>
       <c r="Q465" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R465" s="2" t="n">
         <v>0.016667</v>
@@ -29181,7 +29232,7 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B466" s="2" t="n">
         <v>5</v>
@@ -29202,7 +29253,7 @@
         <v>234</v>
       </c>
       <c r="H466" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I466" s="2" t="s">
         <v>592</v>
@@ -29211,7 +29262,7 @@
         <v>649</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L466" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B466-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D466-1)/Inputs!$B$12,0))</f>
@@ -29220,11 +29271,11 @@
       <c r="M466" s="2"/>
       <c r="N466" s="2"/>
       <c r="O466" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P466" s="3"/>
       <c r="Q466" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R466" s="2" t="n">
         <v>0.016667</v>
@@ -29233,9 +29284,9 @@
         <v>648</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B467" s="2" t="n">
         <v>5</v>
@@ -29256,7 +29307,7 @@
         <v>436</v>
       </c>
       <c r="H467" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I467" s="2" t="s">
         <v>343</v>
@@ -29265,7 +29316,7 @@
         <v>569</v>
       </c>
       <c r="K467" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L467" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B467-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D467-1)/Inputs!$B$12,0))</f>
@@ -29274,11 +29325,11 @@
       <c r="M467" s="2"/>
       <c r="N467" s="2"/>
       <c r="O467" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P467" s="3"/>
       <c r="Q467" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R467" s="2" t="n">
         <v>0.016667</v>
@@ -29289,7 +29340,7 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B468" s="2" t="n">
         <v>5</v>
@@ -29319,7 +29370,7 @@
         <v>570</v>
       </c>
       <c r="K468" s="3" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L468" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B468-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D468-1)/Inputs!$B$12,0))</f>
@@ -29328,11 +29379,11 @@
       <c r="M468" s="2"/>
       <c r="N468" s="2"/>
       <c r="O468" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P468" s="3"/>
       <c r="Q468" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R468" s="2" t="n">
         <v>0.016667</v>
@@ -29343,7 +29394,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B469" s="4" t="n">
         <v>5</v>
@@ -29361,19 +29412,19 @@
         <v>72</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H469" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="K469" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L469" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B469-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D469-1)/Inputs!$B$12,0))</f>
@@ -29382,22 +29433,22 @@
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
       <c r="O469" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P469" s="5"/>
       <c r="Q469" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R469" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S469" s="4" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B470" s="4" t="n">
         <v>5</v>
@@ -29415,19 +29466,19 @@
         <v>72</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H470" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I470" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="K470" s="5" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L470" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B470-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D470-1)/Inputs!$B$12,0))</f>
@@ -29436,22 +29487,22 @@
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
       <c r="O470" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P470" s="5"/>
       <c r="Q470" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R470" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S470" s="4" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B471" s="6" t="n">
         <v>5</v>
@@ -29472,14 +29523,14 @@
         <v>318</v>
       </c>
       <c r="H471" s="7" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="I471" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J471" s="6"/>
       <c r="K471" s="7" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="L471" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B471-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D471-1)/Inputs!$B$12,0))</f>
@@ -29492,11 +29543,11 @@
         <v>2</v>
       </c>
       <c r="O471" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P471" s="7"/>
       <c r="Q471" s="6" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="R471" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -29508,7 +29559,7 @@
     </row>
     <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B472" s="2" t="n">
         <v>6</v>
@@ -29529,7 +29580,7 @@
         <v>225</v>
       </c>
       <c r="H472" s="3" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I472" s="2" t="s">
         <v>322</v>
@@ -29538,7 +29589,7 @@
         <v>323</v>
       </c>
       <c r="K472" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L472" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B472-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D472-1)/Inputs!$B$12,0))</f>
@@ -29547,11 +29598,11 @@
       <c r="M472" s="2"/>
       <c r="N472" s="2"/>
       <c r="O472" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P472" s="3"/>
       <c r="Q472" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R472" s="2" t="n">
         <v>1.2656</v>
@@ -29562,7 +29613,7 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B473" s="2" t="n">
         <v>6</v>
@@ -29583,7 +29634,7 @@
         <v>225</v>
       </c>
       <c r="H473" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I473" s="2" t="s">
         <v>322</v>
@@ -29592,7 +29643,7 @@
         <v>324</v>
       </c>
       <c r="K473" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L473" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B473-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D473-1)/Inputs!$B$12,0))</f>
@@ -29601,11 +29652,11 @@
       <c r="M473" s="2"/>
       <c r="N473" s="2"/>
       <c r="O473" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P473" s="3"/>
       <c r="Q473" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R473" s="2" t="n">
         <v>1.2656</v>
@@ -29616,7 +29667,7 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B474" s="2" t="n">
         <v>6</v>
@@ -29637,7 +29688,7 @@
         <v>225</v>
       </c>
       <c r="H474" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I474" s="2" t="s">
         <v>322</v>
@@ -29646,7 +29697,7 @@
         <v>325</v>
       </c>
       <c r="K474" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L474" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B474-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D474-1)/Inputs!$B$12,0))</f>
@@ -29655,11 +29706,11 @@
       <c r="M474" s="2"/>
       <c r="N474" s="2"/>
       <c r="O474" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P474" s="3"/>
       <c r="Q474" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="R474" s="2" t="n">
         <v>1.2656</v>
@@ -29670,7 +29721,7 @@
     </row>
     <row r="475" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B475" s="2" t="n">
         <v>6</v>
@@ -29691,7 +29742,7 @@
         <v>234</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I475" s="2" t="s">
         <v>592</v>
@@ -29700,7 +29751,7 @@
         <v>656</v>
       </c>
       <c r="K475" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L475" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B475-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D475-1)/Inputs!$B$12,0))</f>
@@ -29709,11 +29760,11 @@
       <c r="M475" s="2"/>
       <c r="N475" s="2"/>
       <c r="O475" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P475" s="3"/>
       <c r="Q475" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R475" s="2" t="n">
         <v>0.016667</v>
@@ -29724,7 +29775,7 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B476" s="2" t="n">
         <v>6</v>
@@ -29745,7 +29796,7 @@
         <v>234</v>
       </c>
       <c r="H476" s="3" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I476" s="2" t="s">
         <v>592</v>
@@ -29754,7 +29805,7 @@
         <v>657</v>
       </c>
       <c r="K476" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L476" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B476-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D476-1)/Inputs!$B$12,0))</f>
@@ -29763,11 +29814,11 @@
       <c r="M476" s="2"/>
       <c r="N476" s="2"/>
       <c r="O476" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P476" s="3"/>
       <c r="Q476" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R476" s="2" t="n">
         <v>0.016667</v>
@@ -29776,9 +29827,9 @@
         <v>656</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B477" s="2" t="n">
         <v>6</v>
@@ -29799,7 +29850,7 @@
         <v>436</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I477" s="2" t="s">
         <v>343</v>
@@ -29808,7 +29859,7 @@
         <v>578</v>
       </c>
       <c r="K477" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L477" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B477-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D477-1)/Inputs!$B$12,0))</f>
@@ -29817,11 +29868,11 @@
       <c r="M477" s="2"/>
       <c r="N477" s="2"/>
       <c r="O477" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P477" s="3"/>
       <c r="Q477" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R477" s="2" t="n">
         <v>0.016667</v>
@@ -29832,7 +29883,7 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B478" s="2" t="n">
         <v>6</v>
@@ -29862,7 +29913,7 @@
         <v>579</v>
       </c>
       <c r="K478" s="3" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L478" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B478-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D478-1)/Inputs!$B$12,0))</f>
@@ -29871,11 +29922,11 @@
       <c r="M478" s="2"/>
       <c r="N478" s="2"/>
       <c r="O478" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P478" s="3"/>
       <c r="Q478" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="R478" s="2" t="n">
         <v>0.016667</v>
@@ -29886,7 +29937,7 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B479" s="4" t="n">
         <v>6</v>
@@ -29904,19 +29955,19 @@
         <v>72</v>
       </c>
       <c r="G479" s="4" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="H479" s="5" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I479" s="4" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="K479" s="5" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L479" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B479-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D479-1)/Inputs!$B$12,0))</f>
@@ -29925,22 +29976,22 @@
       <c r="M479" s="4"/>
       <c r="N479" s="4"/>
       <c r="O479" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P479" s="5"/>
       <c r="Q479" s="4" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="R479" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S479" s="4" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="4" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B480" s="4" t="n">
         <v>6</v>
@@ -29958,19 +30009,19 @@
         <v>72</v>
       </c>
       <c r="G480" s="4" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="H480" s="5" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="I480" s="4" t="s">
         <v>605</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="K480" s="5" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L480" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B480-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D480-1)/Inputs!$B$12,0))</f>
@@ -29979,22 +30030,22 @@
       <c r="M480" s="4"/>
       <c r="N480" s="4"/>
       <c r="O480" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P480" s="5"/>
       <c r="Q480" s="4" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R480" s="4" t="n">
         <v>0.05</v>
       </c>
       <c r="S480" s="4" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="6" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B481" s="6" t="n">
         <v>6</v>
@@ -30012,17 +30063,17 @@
         <v>87</v>
       </c>
       <c r="G481" s="6" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="I481" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J481" s="6"/>
       <c r="K481" s="7" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="L481" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B481-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D481-1)/Inputs!$B$12,0))</f>
@@ -30035,11 +30086,11 @@
         <v>2</v>
       </c>
       <c r="O481" s="6" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="P481" s="7"/>
       <c r="Q481" s="6" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="R481" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -30051,7 +30102,7 @@
     </row>
     <row r="482" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B482" s="2" t="n">
         <v>1</v>
@@ -30069,19 +30120,19 @@
         <v>22</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H482" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I482" s="2" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="J482" s="2" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="K482" s="3" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="L482" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D482-1)/Inputs!$B$12,0))</f>
@@ -30090,22 +30141,22 @@
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
       <c r="O482" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P482" s="3"/>
       <c r="Q482" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R482" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S482" s="2" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>1</v>
@@ -30123,19 +30174,19 @@
         <v>22</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H483" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I483" s="2" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="J483" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="K483" s="3" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="L483" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D483-1)/Inputs!$B$12,0))</f>
@@ -30144,22 +30195,22 @@
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
       <c r="O483" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P483" s="3"/>
       <c r="Q483" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R483" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S483" s="2" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>1</v>
@@ -30177,19 +30228,19 @@
         <v>22</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H484" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I484" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J484" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="L484" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D484-1)/Inputs!$B$12,0))</f>
@@ -30198,22 +30249,22 @@
       <c r="M484" s="2"/>
       <c r="N484" s="2"/>
       <c r="O484" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P484" s="3"/>
       <c r="Q484" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R484" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S484" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B485" s="2" t="n">
         <v>1</v>
@@ -30231,19 +30282,19 @@
         <v>22</v>
       </c>
       <c r="G485" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="H485" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="I485" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="J485" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="H485" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="I485" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="J485" s="2" t="s">
-        <v>809</v>
-      </c>
       <c r="K485" s="3" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="L485" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D485-1)/Inputs!$B$12,0))</f>
@@ -30252,22 +30303,22 @@
       <c r="M485" s="2"/>
       <c r="N485" s="2"/>
       <c r="O485" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P485" s="3"/>
       <c r="Q485" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R485" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S485" s="2" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B486" s="2" t="n">
         <v>1</v>
@@ -30285,19 +30336,19 @@
         <v>22</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H486" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I486" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J486" s="2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="K486" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="L486" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D486-1)/Inputs!$B$12,0))</f>
@@ -30306,22 +30357,22 @@
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
       <c r="O486" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P486" s="3"/>
       <c r="Q486" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R486" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S486" s="2" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B487" s="2" t="n">
         <v>1</v>
@@ -30339,19 +30390,19 @@
         <v>22</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H487" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I487" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J487" s="2" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="K487" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="L487" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D487-1)/Inputs!$B$12,0))</f>
@@ -30360,22 +30411,22 @@
       <c r="M487" s="2"/>
       <c r="N487" s="2"/>
       <c r="O487" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P487" s="3"/>
       <c r="Q487" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R487" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S487" s="2" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B488" s="4" t="n">
         <v>1</v>
@@ -30393,19 +30444,19 @@
         <v>72</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H488" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I488" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="K488" s="5" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="L488" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D488-1)/Inputs!$B$12,0))</f>
@@ -30414,22 +30465,22 @@
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
       <c r="O488" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P488" s="5"/>
       <c r="Q488" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R488" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S488" s="4" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B489" s="4" t="n">
         <v>1</v>
@@ -30447,19 +30498,19 @@
         <v>72</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H489" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I489" s="4" t="s">
         <v>363</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="K489" s="5" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="L489" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D489-1)/Inputs!$B$12,0))</f>
@@ -30468,22 +30519,22 @@
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
       <c r="O489" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P489" s="5"/>
       <c r="Q489" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R489" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S489" s="4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B490" s="4" t="n">
         <v>1</v>
@@ -30501,19 +30552,19 @@
         <v>72</v>
       </c>
       <c r="G490" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="H490" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="I490" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="J490" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="K490" s="5" t="s">
         <v>833</v>
-      </c>
-      <c r="H490" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="I490" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="J490" s="4" t="s">
-        <v>836</v>
-      </c>
-      <c r="K490" s="5" t="s">
-        <v>793</v>
       </c>
       <c r="L490" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D490-1)/Inputs!$B$12,0))</f>
@@ -30522,22 +30573,22 @@
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
       <c r="O490" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P490" s="5"/>
       <c r="Q490" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R490" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S490" s="4" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="491" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B491" s="6" t="n">
         <v>1</v>
@@ -30555,17 +30606,17 @@
         <v>87</v>
       </c>
       <c r="G491" s="6" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="H491" s="7" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="I491" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J491" s="6"/>
       <c r="K491" s="7" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="L491" s="6" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D491-1)/Inputs!$B$12,0))</f>
@@ -30578,11 +30629,11 @@
         <v>1</v>
       </c>
       <c r="O491" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P491" s="7"/>
       <c r="Q491" s="6" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="R491" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -30594,7 +30645,7 @@
     </row>
     <row r="492" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B492" s="2" t="n">
         <v>2</v>
@@ -30612,19 +30663,19 @@
         <v>22</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H492" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I492" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="J492" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="K492" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L492" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D492-1)/Inputs!$B$12,0))</f>
@@ -30633,22 +30684,22 @@
       <c r="M492" s="2"/>
       <c r="N492" s="2"/>
       <c r="O492" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P492" s="3"/>
       <c r="Q492" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R492" s="2" t="n">
         <v>25</v>
       </c>
       <c r="S492" s="2" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B493" s="2" t="n">
         <v>2</v>
@@ -30666,19 +30717,19 @@
         <v>22</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H493" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I493" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="J493" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="K493" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="L493" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D493-1)/Inputs!$B$12,0))</f>
@@ -30687,22 +30738,22 @@
       <c r="M493" s="2"/>
       <c r="N493" s="2"/>
       <c r="O493" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P493" s="3"/>
       <c r="Q493" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R493" s="2" t="n">
         <v>3</v>
       </c>
       <c r="S493" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>2</v>
@@ -30720,19 +30771,19 @@
         <v>22</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I494" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J494" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="K494" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L494" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D494-1)/Inputs!$B$12,0))</f>
@@ -30741,22 +30792,22 @@
       <c r="M494" s="2"/>
       <c r="N494" s="2"/>
       <c r="O494" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P494" s="3"/>
       <c r="Q494" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R494" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S494" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>2</v>
@@ -30774,19 +30825,19 @@
         <v>22</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I495" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="K495" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L495" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D495-1)/Inputs!$B$12,0))</f>
@@ -30795,22 +30846,22 @@
       <c r="M495" s="2"/>
       <c r="N495" s="2"/>
       <c r="O495" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P495" s="3"/>
       <c r="Q495" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R495" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S495" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B496" s="2" t="n">
         <v>2</v>
@@ -30828,19 +30879,19 @@
         <v>22</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I496" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J496" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="K496" s="3" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="L496" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D496-1)/Inputs!$B$12,0))</f>
@@ -30849,22 +30900,22 @@
       <c r="M496" s="2"/>
       <c r="N496" s="2"/>
       <c r="O496" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P496" s="3"/>
       <c r="Q496" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R496" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S496" s="2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B497" s="2" t="n">
         <v>2</v>
@@ -30882,19 +30933,19 @@
         <v>22</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I497" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="K497" s="3" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="L497" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D497-1)/Inputs!$B$12,0))</f>
@@ -30903,22 +30954,22 @@
       <c r="M497" s="2"/>
       <c r="N497" s="2"/>
       <c r="O497" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P497" s="3"/>
       <c r="Q497" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R497" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S497" s="2" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B498" s="4" t="n">
         <v>2</v>
@@ -30936,19 +30987,19 @@
         <v>72</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H498" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I498" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J498" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="K498" s="5" t="s">
         <v>851</v>
-      </c>
-      <c r="K498" s="5" t="s">
-        <v>844</v>
       </c>
       <c r="L498" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D498-1)/Inputs!$B$12,0))</f>
@@ -30957,22 +31008,22 @@
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
       <c r="O498" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P498" s="5"/>
       <c r="Q498" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R498" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S498" s="4" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B499" s="4" t="n">
         <v>2</v>
@@ -30990,10 +31041,10 @@
         <v>72</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H499" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I499" s="4" t="s">
         <v>363</v>
@@ -31002,7 +31053,7 @@
         <v>852</v>
       </c>
       <c r="K499" s="5" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="L499" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D499-1)/Inputs!$B$12,0))</f>
@@ -31011,22 +31062,22 @@
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
       <c r="O499" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P499" s="5"/>
       <c r="Q499" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R499" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S499" s="4" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B500" s="4" t="n">
         <v>2</v>
@@ -31044,19 +31095,19 @@
         <v>72</v>
       </c>
       <c r="G500" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H500" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I500" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J500" s="4" t="s">
         <v>853</v>
       </c>
       <c r="K500" s="5" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="L500" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D500-1)/Inputs!$B$12,0))</f>
@@ -31065,22 +31116,22 @@
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
       <c r="O500" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P500" s="5"/>
       <c r="Q500" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R500" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S500" s="4" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B501" s="6" t="n">
         <v>2</v>
@@ -31098,17 +31149,17 @@
         <v>87</v>
       </c>
       <c r="G501" s="6" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H501" s="7" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="I501" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="7" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="L501" s="6" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D501-1)/Inputs!$B$12,0))</f>
@@ -31121,11 +31172,11 @@
         <v>1</v>
       </c>
       <c r="O501" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P501" s="7"/>
       <c r="Q501" s="6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="R501" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31137,7 +31188,7 @@
     </row>
     <row r="502" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B502" s="2" t="n">
         <v>3</v>
@@ -31155,19 +31206,19 @@
         <v>22</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K502" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="L502" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D502-1)/Inputs!$B$12,0))</f>
@@ -31176,22 +31227,22 @@
       <c r="M502" s="2"/>
       <c r="N502" s="2"/>
       <c r="O502" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P502" s="3"/>
       <c r="Q502" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R502" s="2" t="n">
         <v>38</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B503" s="2" t="n">
         <v>3</v>
@@ -31209,19 +31260,19 @@
         <v>22</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I503" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J503" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="K503" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="K503" s="3" t="s">
-        <v>859</v>
       </c>
       <c r="L503" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D503-1)/Inputs!$B$12,0))</f>
@@ -31230,22 +31281,22 @@
       <c r="M503" s="2"/>
       <c r="N503" s="2"/>
       <c r="O503" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P503" s="3"/>
       <c r="Q503" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R503" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S503" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B504" s="2" t="n">
         <v>3</v>
@@ -31263,19 +31314,19 @@
         <v>22</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="K504" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="L504" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D504-1)/Inputs!$B$12,0))</f>
@@ -31284,22 +31335,22 @@
       <c r="M504" s="2"/>
       <c r="N504" s="2"/>
       <c r="O504" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P504" s="3"/>
       <c r="Q504" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R504" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S504" s="2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B505" s="2" t="n">
         <v>3</v>
@@ -31317,19 +31368,19 @@
         <v>22</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I505" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="K505" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="L505" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D505-1)/Inputs!$B$12,0))</f>
@@ -31338,22 +31389,22 @@
       <c r="M505" s="2"/>
       <c r="N505" s="2"/>
       <c r="O505" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P505" s="3"/>
       <c r="Q505" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R505" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S505" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B506" s="2" t="n">
         <v>3</v>
@@ -31371,19 +31422,19 @@
         <v>22</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I506" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="L506" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D506-1)/Inputs!$B$12,0))</f>
@@ -31392,22 +31443,22 @@
       <c r="M506" s="2"/>
       <c r="N506" s="2"/>
       <c r="O506" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P506" s="3"/>
       <c r="Q506" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R506" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S506" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B507" s="2" t="n">
         <v>3</v>
@@ -31425,19 +31476,19 @@
         <v>22</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I507" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="K507" s="3" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="L507" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D507-1)/Inputs!$B$12,0))</f>
@@ -31446,22 +31497,22 @@
       <c r="M507" s="2"/>
       <c r="N507" s="2"/>
       <c r="O507" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P507" s="3"/>
       <c r="Q507" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R507" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S507" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B508" s="4" t="n">
         <v>3</v>
@@ -31479,19 +31530,19 @@
         <v>72</v>
       </c>
       <c r="G508" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H508" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I508" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="K508" s="5" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="L508" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D508-1)/Inputs!$B$12,0))</f>
@@ -31500,22 +31551,22 @@
       <c r="M508" s="4"/>
       <c r="N508" s="4"/>
       <c r="O508" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P508" s="5"/>
       <c r="Q508" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R508" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S508" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B509" s="4" t="n">
         <v>3</v>
@@ -31533,19 +31584,19 @@
         <v>72</v>
       </c>
       <c r="G509" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H509" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I509" s="4" t="s">
         <v>363</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="K509" s="5" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="L509" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D509-1)/Inputs!$B$12,0))</f>
@@ -31554,11 +31605,11 @@
       <c r="M509" s="4"/>
       <c r="N509" s="4"/>
       <c r="O509" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P509" s="5"/>
       <c r="Q509" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R509" s="4" t="n">
         <v>0.1</v>
@@ -31569,7 +31620,7 @@
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B510" s="4" t="n">
         <v>3</v>
@@ -31587,19 +31638,19 @@
         <v>72</v>
       </c>
       <c r="G510" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I510" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="K510" s="5" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="L510" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D510-1)/Inputs!$B$12,0))</f>
@@ -31608,11 +31659,11 @@
       <c r="M510" s="4"/>
       <c r="N510" s="4"/>
       <c r="O510" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P510" s="5"/>
       <c r="Q510" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R510" s="4" t="n">
         <v>0.1</v>
@@ -31623,7 +31674,7 @@
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B511" s="6" t="n">
         <v>3</v>
@@ -31641,17 +31692,17 @@
         <v>87</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="H511" s="7" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J511" s="6"/>
       <c r="K511" s="7" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="L511" s="6" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D511-1)/Inputs!$B$12,0))</f>
@@ -31664,11 +31715,11 @@
         <v>2</v>
       </c>
       <c r="O511" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P511" s="7"/>
       <c r="Q511" s="6" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="R511" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31680,7 +31731,7 @@
     </row>
     <row r="512" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B512" s="2" t="n">
         <v>4</v>
@@ -31698,19 +31749,19 @@
         <v>22</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H512" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="K512" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="L512" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D512-1)/Inputs!$B$12,0))</f>
@@ -31719,22 +31770,22 @@
       <c r="M512" s="2"/>
       <c r="N512" s="2"/>
       <c r="O512" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P512" s="3"/>
       <c r="Q512" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R512" s="2" t="n">
         <v>50</v>
       </c>
       <c r="S512" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B513" s="2" t="n">
         <v>4</v>
@@ -31752,19 +31803,19 @@
         <v>22</v>
       </c>
       <c r="G513" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H513" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I513" s="2" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="J513" s="2" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="K513" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="L513" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D513-1)/Inputs!$B$12,0))</f>
@@ -31773,22 +31824,22 @@
       <c r="M513" s="2"/>
       <c r="N513" s="2"/>
       <c r="O513" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P513" s="3"/>
       <c r="Q513" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R513" s="2" t="n">
         <v>6</v>
       </c>
       <c r="S513" s="2" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B514" s="2" t="n">
         <v>4</v>
@@ -31806,19 +31857,19 @@
         <v>22</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H514" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="K514" s="3" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="L514" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D514-1)/Inputs!$B$12,0))</f>
@@ -31827,22 +31878,22 @@
       <c r="M514" s="2"/>
       <c r="N514" s="2"/>
       <c r="O514" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P514" s="3"/>
       <c r="Q514" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R514" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S514" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B515" s="2" t="n">
         <v>4</v>
@@ -31860,19 +31911,19 @@
         <v>22</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H515" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I515" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="K515" s="3" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="L515" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D515-1)/Inputs!$B$12,0))</f>
@@ -31881,22 +31932,22 @@
       <c r="M515" s="2"/>
       <c r="N515" s="2"/>
       <c r="O515" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P515" s="3"/>
       <c r="Q515" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R515" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S515" s="2" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>4</v>
@@ -31914,19 +31965,19 @@
         <v>22</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H516" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I516" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J516" s="2" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
       <c r="K516" s="3" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="L516" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D516-1)/Inputs!$B$12,0))</f>
@@ -31935,22 +31986,22 @@
       <c r="M516" s="2"/>
       <c r="N516" s="2"/>
       <c r="O516" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P516" s="3"/>
       <c r="Q516" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R516" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S516" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>4</v>
@@ -31968,19 +32019,19 @@
         <v>22</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H517" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I517" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="K517" s="3" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="L517" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D517-1)/Inputs!$B$12,0))</f>
@@ -31989,22 +32040,22 @@
       <c r="M517" s="2"/>
       <c r="N517" s="2"/>
       <c r="O517" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P517" s="3"/>
       <c r="Q517" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R517" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S517" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B518" s="4" t="n">
         <v>4</v>
@@ -32022,19 +32073,19 @@
         <v>72</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H518" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I518" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
       <c r="K518" s="5" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="L518" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D518-1)/Inputs!$B$12,0))</f>
@@ -32043,22 +32094,22 @@
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
       <c r="O518" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P518" s="5"/>
       <c r="Q518" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R518" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S518" s="4" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B519" s="4" t="n">
         <v>4</v>
@@ -32076,19 +32127,19 @@
         <v>72</v>
       </c>
       <c r="G519" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H519" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I519" s="4" t="s">
         <v>363</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="K519" s="5" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="L519" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D519-1)/Inputs!$B$12,0))</f>
@@ -32097,22 +32148,22 @@
       <c r="M519" s="4"/>
       <c r="N519" s="4"/>
       <c r="O519" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P519" s="5"/>
       <c r="Q519" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R519" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S519" s="4" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B520" s="4" t="n">
         <v>4</v>
@@ -32130,19 +32181,19 @@
         <v>72</v>
       </c>
       <c r="G520" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H520" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I520" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="K520" s="5" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="L520" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D520-1)/Inputs!$B$12,0))</f>
@@ -32151,22 +32202,22 @@
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
       <c r="O520" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P520" s="5"/>
       <c r="Q520" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R520" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S520" s="4" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B521" s="6" t="n">
         <v>4</v>
@@ -32184,17 +32235,17 @@
         <v>87</v>
       </c>
       <c r="G521" s="6" t="s">
-        <v>883</v>
+        <v>892</v>
       </c>
       <c r="H521" s="7" t="s">
-        <v>884</v>
+        <v>893</v>
       </c>
       <c r="I521" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J521" s="6"/>
       <c r="K521" s="7" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="L521" s="6" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D521-1)/Inputs!$B$12,0))</f>
@@ -32207,11 +32258,11 @@
         <v>2</v>
       </c>
       <c r="O521" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P521" s="7"/>
       <c r="Q521" s="6" t="s">
-        <v>885</v>
+        <v>894</v>
       </c>
       <c r="R521" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32223,7 +32274,7 @@
     </row>
     <row r="522" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B522" s="2" t="n">
         <v>5</v>
@@ -32241,19 +32292,19 @@
         <v>22</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H522" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>886</v>
+        <v>895</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
       <c r="K522" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="L522" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D522-1)/Inputs!$B$12,0))</f>
@@ -32262,22 +32313,22 @@
       <c r="M522" s="2"/>
       <c r="N522" s="2"/>
       <c r="O522" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P522" s="3"/>
       <c r="Q522" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R522" s="2" t="n">
         <v>62</v>
       </c>
       <c r="S522" s="2" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B523" s="2" t="n">
         <v>5</v>
@@ -32295,19 +32346,19 @@
         <v>22</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H523" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="K523" s="3" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="L523" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D523-1)/Inputs!$B$12,0))</f>
@@ -32316,22 +32367,22 @@
       <c r="M523" s="2"/>
       <c r="N523" s="2"/>
       <c r="O523" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P523" s="3"/>
       <c r="Q523" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R523" s="2" t="n">
         <v>7</v>
       </c>
       <c r="S523" s="2" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B524" s="2" t="n">
         <v>5</v>
@@ -32349,19 +32400,19 @@
         <v>22</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H524" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I524" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
       <c r="K524" s="3" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="L524" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D524-1)/Inputs!$B$12,0))</f>
@@ -32370,22 +32421,22 @@
       <c r="M524" s="2"/>
       <c r="N524" s="2"/>
       <c r="O524" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P524" s="3"/>
       <c r="Q524" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R524" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B525" s="2" t="n">
         <v>5</v>
@@ -32403,19 +32454,19 @@
         <v>22</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H525" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="L525" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D525-1)/Inputs!$B$12,0))</f>
@@ -32424,22 +32475,22 @@
       <c r="M525" s="2"/>
       <c r="N525" s="2"/>
       <c r="O525" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P525" s="3"/>
       <c r="Q525" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R525" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S525" s="2" t="s">
-        <v>891</v>
+        <v>900</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B526" s="2" t="n">
         <v>5</v>
@@ -32457,19 +32508,19 @@
         <v>22</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H526" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I526" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
       <c r="K526" s="3" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="L526" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D526-1)/Inputs!$B$12,0))</f>
@@ -32478,22 +32529,22 @@
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
       <c r="O526" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P526" s="3"/>
       <c r="Q526" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R526" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S526" s="2" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>5</v>
@@ -32511,19 +32562,19 @@
         <v>22</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H527" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I527" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="K527" s="3" t="s">
-        <v>888</v>
+        <v>904</v>
       </c>
       <c r="L527" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D527-1)/Inputs!$B$12,0))</f>
@@ -32532,22 +32583,22 @@
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
       <c r="O527" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P527" s="3"/>
       <c r="Q527" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R527" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S527" s="2" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B528" s="4" t="n">
         <v>5</v>
@@ -32565,19 +32616,19 @@
         <v>72</v>
       </c>
       <c r="G528" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H528" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I528" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="K528" s="5" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="L528" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D528-1)/Inputs!$B$12,0))</f>
@@ -32586,22 +32637,22 @@
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
       <c r="O528" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P528" s="5"/>
       <c r="Q528" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R528" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S528" s="4" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B529" s="4" t="n">
         <v>5</v>
@@ -32619,19 +32670,19 @@
         <v>72</v>
       </c>
       <c r="G529" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H529" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I529" s="4" t="s">
         <v>363</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="K529" s="5" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="L529" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D529-1)/Inputs!$B$12,0))</f>
@@ -32640,22 +32691,22 @@
       <c r="M529" s="4"/>
       <c r="N529" s="4"/>
       <c r="O529" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P529" s="5"/>
       <c r="Q529" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R529" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S529" s="4" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B530" s="4" t="n">
         <v>5</v>
@@ -32673,19 +32724,19 @@
         <v>72</v>
       </c>
       <c r="G530" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H530" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I530" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="K530" s="5" t="s">
-        <v>888</v>
+        <v>910</v>
       </c>
       <c r="L530" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D530-1)/Inputs!$B$12,0))</f>
@@ -32694,22 +32745,22 @@
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
       <c r="O530" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P530" s="5"/>
       <c r="Q530" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R530" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S530" s="4" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B531" s="6" t="n">
         <v>5</v>
@@ -32727,17 +32778,17 @@
         <v>87</v>
       </c>
       <c r="G531" s="6" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="H531" s="7" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="I531" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J531" s="6"/>
       <c r="K531" s="7" t="s">
-        <v>888</v>
+        <v>910</v>
       </c>
       <c r="L531" s="6" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D531-1)/Inputs!$B$12,0))</f>
@@ -32750,11 +32801,11 @@
         <v>2</v>
       </c>
       <c r="O531" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P531" s="7"/>
       <c r="Q531" s="6" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="R531" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32766,7 +32817,7 @@
     </row>
     <row r="532" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B532" s="2" t="n">
         <v>6</v>
@@ -32784,19 +32835,19 @@
         <v>22</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="H532" s="3" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
       <c r="K532" s="3" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="L532" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D532-1)/Inputs!$B$12,0))</f>
@@ -32805,22 +32856,22 @@
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
       <c r="O532" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P532" s="3"/>
       <c r="Q532" s="2" t="s">
-        <v>795</v>
+        <v>788</v>
       </c>
       <c r="R532" s="2" t="n">
         <v>100</v>
       </c>
       <c r="S532" s="2" t="s">
-        <v>887</v>
+        <v>896</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B533" s="2" t="n">
         <v>6</v>
@@ -32838,19 +32889,19 @@
         <v>22</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H533" s="3" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="K533" s="3" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="L533" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D533-1)/Inputs!$B$12,0))</f>
@@ -32859,22 +32910,22 @@
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
       <c r="O533" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P533" s="3"/>
       <c r="Q533" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="R533" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S533" s="2" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B534" s="2" t="n">
         <v>6</v>
@@ -32892,19 +32943,19 @@
         <v>22</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H534" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I534" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="K534" s="3" t="s">
-        <v>903</v>
+        <v>920</v>
       </c>
       <c r="L534" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D534-1)/Inputs!$B$12,0))</f>
@@ -32913,22 +32964,22 @@
       <c r="M534" s="2"/>
       <c r="N534" s="2"/>
       <c r="O534" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P534" s="3"/>
       <c r="Q534" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R534" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S534" s="2" t="s">
-        <v>892</v>
+        <v>902</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B535" s="2" t="n">
         <v>6</v>
@@ -32946,19 +32997,19 @@
         <v>22</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
       <c r="K535" s="3" t="s">
-        <v>903</v>
+        <v>920</v>
       </c>
       <c r="L535" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D535-1)/Inputs!$B$12,0))</f>
@@ -32967,22 +33018,22 @@
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
       <c r="O535" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P535" s="3"/>
       <c r="Q535" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="R535" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S535" s="2" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B536" s="2" t="n">
         <v>6</v>
@@ -33000,19 +33051,19 @@
         <v>22</v>
       </c>
       <c r="G536" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="H536" s="3" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="I536" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="J536" s="2" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="K536" s="3" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="L536" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D536-1)/Inputs!$B$12,0))</f>
@@ -33021,22 +33072,22 @@
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
       <c r="O536" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P536" s="3"/>
       <c r="Q536" s="2" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="R536" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S536" s="2" t="s">
-        <v>893</v>
+        <v>903</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>6</v>
@@ -33054,19 +33105,19 @@
         <v>22</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="H537" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="I537" s="2" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="K537" s="3" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="L537" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D537-1)/Inputs!$B$12,0))</f>
@@ -33075,22 +33126,22 @@
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
       <c r="O537" s="2" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P537" s="3"/>
       <c r="Q537" s="2" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="R537" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S537" s="2" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B538" s="4" t="n">
         <v>6</v>
@@ -33108,19 +33159,19 @@
         <v>72</v>
       </c>
       <c r="G538" s="4" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="H538" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="I538" s="4" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="J538" s="4" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="K538" s="5" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="L538" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D538-1)/Inputs!$B$12,0))</f>
@@ -33129,22 +33180,22 @@
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
       <c r="O538" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P538" s="5"/>
       <c r="Q538" s="4" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R538" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S538" s="4" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B539" s="4" t="n">
         <v>6</v>
@@ -33162,19 +33213,19 @@
         <v>72</v>
       </c>
       <c r="G539" s="4" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="H539" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="I539" s="4" t="s">
         <v>363</v>
       </c>
       <c r="J539" s="4" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="K539" s="5" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="L539" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D539-1)/Inputs!$B$12,0))</f>
@@ -33183,22 +33234,22 @@
       <c r="M539" s="4"/>
       <c r="N539" s="4"/>
       <c r="O539" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P539" s="5"/>
       <c r="Q539" s="4" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="R539" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S539" s="4" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B540" s="4" t="n">
         <v>6</v>
@@ -33216,19 +33267,19 @@
         <v>72</v>
       </c>
       <c r="G540" s="4" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="H540" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="I540" s="4" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="J540" s="4" t="s">
-        <v>912</v>
+        <v>928</v>
       </c>
       <c r="K540" s="5" t="s">
-        <v>903</v>
+        <v>929</v>
       </c>
       <c r="L540" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D540-1)/Inputs!$B$12,0))</f>
@@ -33237,22 +33288,22 @@
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
       <c r="O540" s="4" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P540" s="5"/>
       <c r="Q540" s="4" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="R540" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S540" s="4" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="6" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B541" s="6" t="n">
         <v>6</v>
@@ -33270,17 +33321,17 @@
         <v>87</v>
       </c>
       <c r="G541" s="6" t="s">
-        <v>913</v>
+        <v>930</v>
       </c>
       <c r="H541" s="7" t="s">
-        <v>914</v>
+        <v>931</v>
       </c>
       <c r="I541" s="6" t="s">
         <v>90</v>
       </c>
       <c r="J541" s="6"/>
       <c r="K541" s="7" t="s">
-        <v>903</v>
+        <v>929</v>
       </c>
       <c r="L541" s="6" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D541-1)/Inputs!$B$12,0))</f>
@@ -33293,11 +33344,11 @@
         <v>2</v>
       </c>
       <c r="O541" s="6" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="P541" s="7"/>
       <c r="Q541" s="6" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
       <c r="R541" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -33336,12 +33387,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>916</v>
+        <v>933</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>917</v>
+        <v>934</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>2</v>
@@ -33349,7 +33400,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>918</v>
+        <v>935</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.1</v>
@@ -33357,7 +33408,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>919</v>
+        <v>936</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1.15</v>
@@ -33365,7 +33416,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>920</v>
+        <v>937</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1.25</v>
@@ -33373,7 +33424,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>921</v>
+        <v>938</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2</v>
@@ -33381,7 +33432,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>922</v>
+        <v>939</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>10</v>
@@ -33389,7 +33440,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>923</v>
+        <v>940</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1.5</v>
@@ -33397,7 +33448,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>924</v>
+        <v>941</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">(B6^10-1)/(B6-1)</f>
@@ -33409,13 +33460,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>925</v>
+        <v>942</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>926</v>
+        <v>943</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>927</v>
+        <v>944</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33423,13 +33474,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>928</v>
+        <v>945</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>570</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>929</v>
+        <v>946</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33437,13 +33488,13 @@
         <v>339</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>930</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>931</v>
+        <v>948</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33451,13 +33502,13 @@
         <v>427</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>932</v>
+        <v>949</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>933</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33465,13 +33516,13 @@
         <v>513</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>934</v>
+        <v>951</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>210</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33479,13 +33530,13 @@
         <v>588</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>936</v>
+        <v>953</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>330</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>937</v>
+        <v>954</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33493,41 +33544,41 @@
         <v>668</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>939</v>
+        <v>956</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>940</v>
+        <v>957</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>420</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>941</v>
+        <v>958</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>942</v>
+        <v>959</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>82</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>943</v>
+        <v>960</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33535,28 +33586,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>944</v>
+        <v>961</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>945</v>
+        <v>962</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>946</v>
+        <v>963</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>947</v>
+        <v>964</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>948</v>
+        <v>965</v>
       </c>
     </row>
   </sheetData>
@@ -33583,7 +33634,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>949</v>
+        <v>966</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33591,22 +33642,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>950</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>951</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>952</v>
+        <v>969</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>953</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33614,22 +33665,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>954</v>
+        <v>971</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>955</v>
+        <v>972</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>956</v>
+        <v>973</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>957</v>
+        <v>974</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33637,17 +33688,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>958</v>
+        <v>975</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>959</v>
+        <v>976</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>960</v>
+        <v>977</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33655,22 +33706,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>961</v>
+        <v>978</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>962</v>
+        <v>979</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>963</v>
+        <v>980</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>964</v>
+        <v>981</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33678,22 +33729,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>965</v>
+        <v>982</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>966</v>
+        <v>983</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>967</v>
+        <v>984</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>968</v>
+        <v>985</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33701,22 +33752,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>969</v>
+        <v>986</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>970</v>
+        <v>987</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>971</v>
+        <v>988</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>972</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33724,37 +33775,37 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>973</v>
+        <v>990</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>974</v>
+        <v>991</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>975</v>
+        <v>992</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>976</v>
+        <v>993</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>977</v>
+        <v>994</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>978</v>
+        <v>995</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>979</v>
+        <v>996</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33762,42 +33813,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>980</v>
+        <v>997</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>981</v>
+        <v>998</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>982</v>
+        <v>999</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>983</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>984</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>985</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>986</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>987</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33805,32 +33856,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>988</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>989</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>990</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>993</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33838,32 +33889,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>995</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>996</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>997</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>998</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>999</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33871,27 +33922,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>1000</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>1001</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1002</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>1003</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1004</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33899,32 +33950,32 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1005</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1006</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1007</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1008</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1009</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1010</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33932,22 +33983,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1011</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1012</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1013</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1014</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33955,47 +34006,47 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1015</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1016</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1017</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1018</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1019</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1020</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1021</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1022</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1023</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34003,22 +34054,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1024</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1025</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1026</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34026,22 +34077,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1028</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1029</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1030</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1031</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34049,42 +34100,42 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1032</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1033</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1035</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1036</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1037</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1038</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1039</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34092,42 +34143,42 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1040</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1041</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1042</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1043</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1044</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1045</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1046</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1047</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34135,17 +34186,17 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
-        <v>1048</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1049</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1050</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -34173,12 +34224,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1051</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1052</v>
+        <v>1069</v>
       </c>
       <c r="B3" s="17" t="n">
         <v>100</v>
@@ -34186,7 +34237,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1053</v>
+        <v>1070</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>5</v>
@@ -34194,7 +34245,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1054</v>
+        <v>1071</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>100</v>
@@ -34205,25 +34256,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1056</v>
+        <v>1073</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1057</v>
+        <v>1074</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1058</v>
+        <v>1075</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>1059</v>
+        <v>1076</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1060</v>
+        <v>1077</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>1059</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34408,7 +34459,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1061</v>
+        <v>1078</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>99</v>
@@ -34438,27 +34489,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1062</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1063</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1064</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1065</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>1066</v>
+        <v>1083</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>0.05</v>
@@ -34466,7 +34517,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>1067</v>
+        <v>1084</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>0.01</v>
@@ -34474,7 +34525,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>1068</v>
+        <v>1085</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>12.5</v>
@@ -34482,7 +34533,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>1069</v>
+        <v>1086</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>6.25</v>
@@ -34493,22 +34544,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>1070</v>
+        <v>1087</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>1071</v>
+        <v>1088</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>1056</v>
+        <v>1073</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>1072</v>
+        <v>1089</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>1073</v>
+        <v>1090</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1074</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34687,12 +34738,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1075</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1076</v>
+        <v>1093</v>
       </c>
     </row>
   </sheetData>
@@ -34729,16 +34780,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1077</v>
+        <v>1094</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1078</v>
+        <v>1095</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1079</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34750,11 +34801,11 @@
       </c>
       <c r="C2" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A2,'All Upgrades'!$B$2:$B$541,B2,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>112</v>
+        <v>335</v>
       </c>
       <c r="D2" s="23" t="n">
         <f aca="false">C2/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.15719298245614</v>
+        <v>0.470175438596491</v>
       </c>
       <c r="E2" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A2,'All Upgrades'!$B$2:$B$541,B2)</f>
@@ -34870,11 +34921,11 @@
       </c>
       <c r="C8" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A8,'All Upgrades'!$B$2:$B$541,B8,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>142</v>
+        <v>427</v>
       </c>
       <c r="D8" s="23" t="n">
         <f aca="false">C8/INDEX(Inputs!$C$15:$C$23,MATCH("mining",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.199298245614035</v>
+        <v>0.599298245614035</v>
       </c>
       <c r="E8" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A8,'All Upgrades'!$B$2:$B$541,B8)</f>
@@ -34990,11 +35041,11 @@
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A14,'All Upgrades'!$B$2:$B$541,B14,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="D14" s="23" t="n">
         <f aca="false">C14*3/INDEX(Inputs!$C$15:$C$23,MATCH("parsing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.201290322580645</v>
+        <v>0.593548387096774</v>
       </c>
       <c r="E14" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A14,'All Upgrades'!$B$2:$B$541,B14)</f>
@@ -35110,11 +35161,11 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A20,'All Upgrades'!$B$2:$B$541,B20,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>93</v>
+        <v>281</v>
       </c>
       <c r="D20" s="23" t="n">
         <f aca="false">C20/INDEX(Inputs!$C$15:$C$23,MATCH("cracking",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.1984</v>
+        <v>0.599466666666667</v>
       </c>
       <c r="E20" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A20,'All Upgrades'!$B$2:$B$541,B20)</f>
@@ -35230,11 +35281,11 @@
       </c>
       <c r="C26" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A26,'All Upgrades'!$B$2:$B$541,B26,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>53</v>
+        <v>159</v>
       </c>
       <c r="D26" s="23" t="n">
         <f aca="false">C26/INDEX(Inputs!$C$15:$C$23,MATCH("matching",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.201904761904762</v>
+        <v>0.605714285714286</v>
       </c>
       <c r="E26" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A26,'All Upgrades'!$B$2:$B$541,B26)</f>
@@ -35350,11 +35401,11 @@
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A32,'All Upgrades'!$B$2:$B$541,B32,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>81</v>
+        <v>247</v>
       </c>
       <c r="D32" s="23" t="n">
         <f aca="false">C32/INDEX(Inputs!$C$15:$C$23,MATCH("phishing",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.196363636363636</v>
+        <v>0.598787878787879</v>
       </c>
       <c r="E32" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A32,'All Upgrades'!$B$2:$B$541,B32)</f>
@@ -35470,11 +35521,11 @@
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>1123</v>
+        <v>3374</v>
       </c>
       <c r="D38" s="23" t="n">
         <f aca="false">C38/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.199644444444444</v>
+        <v>0.599822222222222</v>
       </c>
       <c r="E38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38)</f>
@@ -35583,18 +35634,18 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="C44" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A44,'All Upgrades'!$B$2:$B$541,B44,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>105</v>
+        <v>316</v>
       </c>
       <c r="D44" s="23" t="n">
         <f aca="false">C44/INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.2</v>
+        <v>0.601904761904762</v>
       </c>
       <c r="E44" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A44,'All Upgrades'!$B$2:$B$541,B44)</f>
@@ -35603,7 +35654,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>2</v>
@@ -35623,7 +35674,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>3</v>
@@ -35643,7 +35694,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>4</v>
@@ -35663,7 +35714,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>5</v>
@@ -35683,7 +35734,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>6</v>
@@ -35703,7 +35754,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>1</v>
@@ -35723,7 +35774,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>2</v>
@@ -35743,7 +35794,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>3</v>
@@ -35763,7 +35814,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>4</v>
@@ -35783,7 +35834,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>5</v>
@@ -35803,7 +35854,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>6</v>
@@ -35856,31 +35907,31 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1080</v>
+        <v>1097</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1081</v>
+        <v>1098</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1082</v>
+        <v>1099</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1083</v>
+        <v>1100</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1084</v>
+        <v>1101</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1085</v>
+        <v>1102</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1086</v>
+        <v>1103</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1087</v>
+        <v>1104</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>1088</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35891,7 +35942,7 @@
         <v>91</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D2" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35925,7 +35976,7 @@
         <v>264</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D3" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35959,7 +36010,7 @@
         <v>368</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35993,7 +36044,7 @@
         <v>454</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36061,7 +36112,7 @@
         <v>118</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36095,7 +36146,7 @@
         <v>278</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36129,7 +36180,7 @@
         <v>379</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36163,7 +36214,7 @@
         <v>465</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36231,7 +36282,7 @@
         <v>144</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36265,7 +36316,7 @@
         <v>292</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36299,7 +36350,7 @@
         <v>390</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36333,7 +36384,7 @@
         <v>476</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36401,7 +36452,7 @@
         <v>170</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36435,7 +36486,7 @@
         <v>306</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36469,7 +36520,7 @@
         <v>401</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36503,7 +36554,7 @@
         <v>487</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36571,7 +36622,7 @@
         <v>196</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36605,7 +36656,7 @@
         <v>320</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36639,7 +36690,7 @@
         <v>411</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36673,7 +36724,7 @@
         <v>497</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36741,7 +36792,7 @@
         <v>222</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1089</v>
+        <v>1106</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36775,7 +36826,7 @@
         <v>334</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1090</v>
+        <v>1107</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36809,7 +36860,7 @@
         <v>422</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36843,7 +36894,7 @@
         <v>508</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1092</v>
+        <v>1109</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36934,16 +36985,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1093</v>
+        <v>1110</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1094</v>
+        <v>1111</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1095</v>
+        <v>1112</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1096</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37067,7 +37118,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>10</v>
@@ -37084,7 +37135,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>10</v>
@@ -37101,7 +37152,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>1097</v>
+        <v>1114</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>90</v>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -109,7 +109,7 @@
     <t xml:space="preserve">+0.3 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4 C/s cooling</t>
+    <t xml:space="preserve">0.5 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Logs</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">system.cooling_amount</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1 C/s cooling</t>
+    <t xml:space="preserve">0.2 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">v0.2</t>
@@ -250,22 +250,22 @@
     <t xml:space="preserve">Pointed</t>
   </si>
   <si>
-    <t xml:space="preserve">Thermal Paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overheat clears sooner: the clear temp rises toward the 95 C trigger (today: clears at 80 C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+2 C clear temp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82 C overheat clears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">system.thermal_paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80 C overheat clears</t>
+    <t xml:space="preserve">VM Snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chance a VM token isn't used up when a VM starts or renews (5% at Tier 1, +3% per tier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5% / +3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 % chance to keep the VM token</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system.vm_snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v0.9</t>
@@ -322,7 +322,7 @@
     <t xml:space="preserve">+0.35 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">0.75 C/s cooling</t>
+    <t xml:space="preserve">0.85 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Archives</t>
@@ -367,7 +367,7 @@
     <t xml:space="preserve">v1.8</t>
   </si>
   <si>
-    <t xml:space="preserve">84 C overheat clears</t>
+    <t xml:space="preserve">8 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v1.9</t>
@@ -400,7 +400,7 @@
     <t xml:space="preserve">+0.55 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3 C/s cooling</t>
+    <t xml:space="preserve">1.4 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Metadata</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">v2.8</t>
   </si>
   <si>
-    <t xml:space="preserve">86 C overheat clears</t>
+    <t xml:space="preserve">11 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v2.9</t>
@@ -478,7 +478,7 @@
     <t xml:space="preserve">+0.7 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">2 C/s cooling</t>
+    <t xml:space="preserve">2.1 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Cookies</t>
@@ -523,7 +523,7 @@
     <t xml:space="preserve">v3.8</t>
   </si>
   <si>
-    <t xml:space="preserve">88 C overheat clears</t>
+    <t xml:space="preserve">14 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v3.9</t>
@@ -556,7 +556,7 @@
     <t xml:space="preserve">+1.05 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05 C/s cooling</t>
+    <t xml:space="preserve">3.15 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Repositories</t>
@@ -601,7 +601,7 @@
     <t xml:space="preserve">v4.8</t>
   </si>
   <si>
-    <t xml:space="preserve">90 C overheat clears</t>
+    <t xml:space="preserve">17 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v4.9</t>
@@ -634,7 +634,7 @@
     <t xml:space="preserve">+1.55 C/s</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6 C/s cooling</t>
+    <t xml:space="preserve">4.7 C/s cooling</t>
   </si>
   <si>
     <t xml:space="preserve">Databases</t>
@@ -679,7 +679,7 @@
     <t xml:space="preserve">v5.8</t>
   </si>
   <si>
-    <t xml:space="preserve">92 C overheat clears</t>
+    <t xml:space="preserve">20 % chance to keep the VM token</t>
   </si>
   <si>
     <t xml:space="preserve">v5.9</t>
@@ -4462,7 +4462,7 @@
         <v>77</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="S9" s="4" t="s">
         <v>78</v>
@@ -5005,7 +5005,7 @@
         <v>77</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="S19" s="4" t="s">
         <v>76</v>
@@ -5548,7 +5548,7 @@
         <v>77</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="S29" s="4" t="s">
         <v>112</v>
@@ -6091,7 +6091,7 @@
         <v>77</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="S39" s="4" t="s">
         <v>138</v>
@@ -6634,7 +6634,7 @@
         <v>77</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="S49" s="4" t="s">
         <v>164</v>
@@ -7177,7 +7177,7 @@
         <v>77</v>
       </c>
       <c r="R59" s="4" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="S59" s="4" t="s">
         <v>190</v>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -2179,7 +2179,7 @@
     <t xml:space="preserve">MAJOR: Forensics</t>
   </si>
   <si>
-    <t xml:space="preserve">MODIFIER 'forensics': -40% speed; one-time item find chance x2, VM token chance x2, heat x2</t>
+    <t xml:space="preserve">MODIFIER 'forensics': -40% speed; Exploit find chance x2, VM token chance x2, heat x2</t>
   </si>
   <si>
     <t xml:space="preserve">decoding.forensics</t>
@@ -2833,7 +2833,7 @@
     <t xml:space="preserve">MAJOR: Exploit Kit</t>
   </si>
   <si>
-    <t xml:space="preserve">50% chance a one-time item is not consumed</t>
+    <t xml:space="preserve">50% chance an Exploit is not consumed</t>
   </si>
   <si>
     <t xml:space="preserve">hacking.exploit_kit</t>
@@ -25708,7 +25708,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="6" t="s">
         <v>669</v>
       </c>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1126">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -2005,13 +2005,22 @@
     <t xml:space="preserve">0 % added per dry cache</t>
   </si>
   <si>
-    <t xml:space="preserve">Compression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More basic resources per decoded cache (stacks with Yield)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decoding.compression</t>
+    <t xml:space="preserve">Salvage Sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each cache has a chance to also drop an Exploit or Hacking Mod of its tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 % sweep chance per cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decoding.salvage_sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 % sweep chance per cache</t>
   </si>
   <si>
     <t xml:space="preserve">Field Notes</t>
@@ -2041,6 +2050,9 @@
     <t xml:space="preserve">0.5 % added per dry cache</t>
   </si>
   <si>
+    <t xml:space="preserve">4 % sweep chance per cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 extra intel hacks</t>
   </si>
   <si>
@@ -2062,6 +2074,9 @@
     <t xml:space="preserve">0.75 % added per dry cache</t>
   </si>
   <si>
+    <t xml:space="preserve">6 % sweep chance per cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 extra intel hacks</t>
   </si>
   <si>
@@ -2083,6 +2098,9 @@
     <t xml:space="preserve">1 % added per dry cache</t>
   </si>
   <si>
+    <t xml:space="preserve">8 % sweep chance per cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">4 extra intel hacks</t>
   </si>
   <si>
@@ -2104,6 +2122,9 @@
     <t xml:space="preserve">1.25 % added per dry cache</t>
   </si>
   <si>
+    <t xml:space="preserve">10 % sweep chance per cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 extra intel hacks</t>
   </si>
   <si>
@@ -2122,6 +2143,9 @@
     <t xml:space="preserve">1.5 % added per dry cache</t>
   </si>
   <si>
+    <t xml:space="preserve">12 % sweep chance per cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">6 extra intel hacks</t>
   </si>
   <si>
@@ -3079,7 +3103,7 @@
     <t xml:space="preserve">  • Per tier: Speed x3, Efficiency x2 (rare chance, +4% max), Yield (+10% basics), Rare Tracker (+0.25% per dry cache),</t>
   </si>
   <si>
-    <t xml:space="preserve">    Compression (+10% basics per cache), Field Notes (+1 intel hack), Capstone.</t>
+    <t xml:space="preserve">    Salvage Sweep (+2% chance per cache at an extra Exploit or Hacking Mod), Field Notes (+1 intel hack), Capstone.</t>
   </si>
   <si>
     <t xml:space="preserve">  • Capstones: Overclock, Token Vault (token x2), Index (mod), Forensics (mod), Survey (mod), Clean Room.</t>
@@ -23853,10 +23877,10 @@
         <v>659</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="K369" s="5" t="s">
         <v>641</v>
@@ -23872,13 +23896,13 @@
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R369" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S369" s="4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23901,16 +23925,16 @@
         <v>55</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H370" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I370" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="K370" s="5" t="s">
         <v>641</v>
@@ -23926,13 +23950,13 @@
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R370" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S370" s="4" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23978,7 +24002,7 @@
       </c>
       <c r="P371" s="7"/>
       <c r="Q371" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="R371" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24020,7 +24044,7 @@
         <v>264</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L372" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B372-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D372-1)/Inputs!$B$12,0))</f>
@@ -24074,7 +24098,7 @@
         <v>265</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L373" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B373-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D373-1)/Inputs!$B$12,0))</f>
@@ -24128,7 +24152,7 @@
         <v>266</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L374" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B374-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D374-1)/Inputs!$B$12,0))</f>
@@ -24182,7 +24206,7 @@
         <v>595</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L375" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B375-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D375-1)/Inputs!$B$12,0))</f>
@@ -24236,7 +24260,7 @@
         <v>596</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L376" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B376-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D376-1)/Inputs!$B$12,0))</f>
@@ -24287,10 +24311,10 @@
         <v>355</v>
       </c>
       <c r="J377" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L377" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B377-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D377-1)/Inputs!$B$12,0))</f>
@@ -24341,10 +24365,10 @@
         <v>654</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="K378" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L378" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B378-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D378-1)/Inputs!$B$12,0))</f>
@@ -24392,13 +24416,13 @@
         <v>659</v>
       </c>
       <c r="I379" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="K379" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L379" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B379-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D379-1)/Inputs!$B$12,0))</f>
@@ -24411,13 +24435,13 @@
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R379" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S379" s="4" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24440,19 +24464,19 @@
         <v>55</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H380" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I380" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J380" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="K380" s="5" t="s">
         <v>670</v>
-      </c>
-      <c r="K380" s="5" t="s">
-        <v>667</v>
       </c>
       <c r="L380" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B380-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D380-1)/Inputs!$B$12,0))</f>
@@ -24465,13 +24489,13 @@
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R380" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S380" s="4" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24494,17 +24518,17 @@
         <v>91</v>
       </c>
       <c r="G381" s="6" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="I381" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="L381" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B381-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D381-1)/Inputs!$B$12*3.66,0))</f>
@@ -24517,7 +24541,7 @@
       </c>
       <c r="P381" s="7"/>
       <c r="Q381" s="6" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="R381" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24559,7 +24583,7 @@
         <v>277</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L382" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B382-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D382-1)/Inputs!$B$12,0))</f>
@@ -24613,7 +24637,7 @@
         <v>278</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L383" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B383-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D383-1)/Inputs!$B$12,0))</f>
@@ -24667,7 +24691,7 @@
         <v>279</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L384" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B384-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D384-1)/Inputs!$B$12,0))</f>
@@ -24721,7 +24745,7 @@
         <v>604</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L385" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B385-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D385-1)/Inputs!$B$12,0))</f>
@@ -24775,7 +24799,7 @@
         <v>605</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L386" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B386-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D386-1)/Inputs!$B$12,0))</f>
@@ -24826,10 +24850,10 @@
         <v>355</v>
       </c>
       <c r="J387" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L387" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B387-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D387-1)/Inputs!$B$12,0))</f>
@@ -24848,7 +24872,7 @@
         <v>0.1</v>
       </c>
       <c r="S387" s="2" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24880,10 +24904,10 @@
         <v>654</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="K388" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L388" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B388-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D388-1)/Inputs!$B$12,0))</f>
@@ -24902,7 +24926,7 @@
         <v>0.0025</v>
       </c>
       <c r="S388" s="4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24931,13 +24955,13 @@
         <v>659</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="K389" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L389" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B389-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D389-1)/Inputs!$B$12,0))</f>
@@ -24950,13 +24974,13 @@
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R389" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S389" s="4" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24979,19 +25003,19 @@
         <v>55</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H390" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I390" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="K390" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L390" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B390-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D390-1)/Inputs!$B$12,0))</f>
@@ -25004,13 +25028,13 @@
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R390" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S390" s="4" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25033,17 +25057,17 @@
         <v>91</v>
       </c>
       <c r="G391" s="6" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="I391" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="L391" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B391-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D391-1)/Inputs!$B$12*3.66,0))</f>
@@ -25056,7 +25080,7 @@
       </c>
       <c r="P391" s="7"/>
       <c r="Q391" s="6" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="R391" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25098,7 +25122,7 @@
         <v>290</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L392" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B392-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D392-1)/Inputs!$B$12,0))</f>
@@ -25152,7 +25176,7 @@
         <v>291</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L393" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B393-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D393-1)/Inputs!$B$12,0))</f>
@@ -25206,7 +25230,7 @@
         <v>292</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L394" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B394-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D394-1)/Inputs!$B$12,0))</f>
@@ -25260,7 +25284,7 @@
         <v>613</v>
       </c>
       <c r="K395" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L395" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B395-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D395-1)/Inputs!$B$12,0))</f>
@@ -25314,7 +25338,7 @@
         <v>614</v>
       </c>
       <c r="K396" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L396" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B396-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D396-1)/Inputs!$B$12,0))</f>
@@ -25365,10 +25389,10 @@
         <v>355</v>
       </c>
       <c r="J397" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="K397" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L397" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B397-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D397-1)/Inputs!$B$12,0))</f>
@@ -25387,7 +25411,7 @@
         <v>0.1</v>
       </c>
       <c r="S397" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25419,10 +25443,10 @@
         <v>654</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="K398" s="5" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L398" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B398-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D398-1)/Inputs!$B$12,0))</f>
@@ -25441,7 +25465,7 @@
         <v>0.0025</v>
       </c>
       <c r="S398" s="4" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25470,13 +25494,13 @@
         <v>659</v>
       </c>
       <c r="I399" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="K399" s="5" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L399" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B399-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D399-1)/Inputs!$B$12,0))</f>
@@ -25489,13 +25513,13 @@
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R399" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S399" s="4" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25518,19 +25542,19 @@
         <v>55</v>
       </c>
       <c r="G400" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H400" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I400" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="K400" s="5" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L400" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B400-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D400-1)/Inputs!$B$12,0))</f>
@@ -25543,13 +25567,13 @@
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R400" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S400" s="4" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25572,17 +25596,17 @@
         <v>91</v>
       </c>
       <c r="G401" s="6" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="I401" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="L401" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B401-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D401-1)/Inputs!$B$12*3.66,0))</f>
@@ -25595,7 +25619,7 @@
       </c>
       <c r="P401" s="7"/>
       <c r="Q401" s="6" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="R401" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25637,7 +25661,7 @@
         <v>303</v>
       </c>
       <c r="K402" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L402" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B402-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D402-1)/Inputs!$B$12,0))</f>
@@ -25691,7 +25715,7 @@
         <v>304</v>
       </c>
       <c r="K403" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L403" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B403-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D403-1)/Inputs!$B$12,0))</f>
@@ -25745,7 +25769,7 @@
         <v>305</v>
       </c>
       <c r="K404" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L404" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B404-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D404-1)/Inputs!$B$12,0))</f>
@@ -25799,7 +25823,7 @@
         <v>622</v>
       </c>
       <c r="K405" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L405" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B405-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D405-1)/Inputs!$B$12,0))</f>
@@ -25853,7 +25877,7 @@
         <v>623</v>
       </c>
       <c r="K406" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L406" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B406-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D406-1)/Inputs!$B$12,0))</f>
@@ -25904,10 +25928,10 @@
         <v>355</v>
       </c>
       <c r="J407" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="K407" s="3" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L407" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B407-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D407-1)/Inputs!$B$12,0))</f>
@@ -25926,7 +25950,7 @@
         <v>0.1</v>
       </c>
       <c r="S407" s="2" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25958,10 +25982,10 @@
         <v>654</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="K408" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L408" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B408-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D408-1)/Inputs!$B$12,0))</f>
@@ -25980,7 +26004,7 @@
         <v>0.0025</v>
       </c>
       <c r="S408" s="4" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26009,13 +26033,13 @@
         <v>659</v>
       </c>
       <c r="I409" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="K409" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L409" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B409-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D409-1)/Inputs!$B$12,0))</f>
@@ -26028,13 +26052,13 @@
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R409" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S409" s="4" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26057,19 +26081,19 @@
         <v>55</v>
       </c>
       <c r="G410" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H410" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I410" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="K410" s="5" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L410" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B410-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D410-1)/Inputs!$B$12,0))</f>
@@ -26082,13 +26106,13 @@
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R410" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S410" s="4" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26114,14 +26138,14 @@
         <v>312</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="I411" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="L411" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B411-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D411-1)/Inputs!$B$12*3.66,0))</f>
@@ -26134,7 +26158,7 @@
       </c>
       <c r="P411" s="7"/>
       <c r="Q411" s="6" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="R411" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26176,7 +26200,7 @@
         <v>316</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L412" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B412-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D412-1)/Inputs!$B$12,0))</f>
@@ -26230,7 +26254,7 @@
         <v>317</v>
       </c>
       <c r="K413" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L413" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B413-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D413-1)/Inputs!$B$12,0))</f>
@@ -26284,7 +26308,7 @@
         <v>318</v>
       </c>
       <c r="K414" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L414" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B414-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D414-1)/Inputs!$B$12,0))</f>
@@ -26338,7 +26362,7 @@
         <v>630</v>
       </c>
       <c r="K415" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L415" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B415-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D415-1)/Inputs!$B$12,0))</f>
@@ -26392,7 +26416,7 @@
         <v>631</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L416" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B416-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D416-1)/Inputs!$B$12,0))</f>
@@ -26443,10 +26467,10 @@
         <v>355</v>
       </c>
       <c r="J417" s="2" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="K417" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L417" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B417-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D417-1)/Inputs!$B$12,0))</f>
@@ -26465,7 +26489,7 @@
         <v>0.1</v>
       </c>
       <c r="S417" s="2" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26497,10 +26521,10 @@
         <v>654</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="K418" s="5" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L418" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B418-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D418-1)/Inputs!$B$12,0))</f>
@@ -26519,7 +26543,7 @@
         <v>0.0025</v>
       </c>
       <c r="S418" s="4" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26548,13 +26572,13 @@
         <v>659</v>
       </c>
       <c r="I419" s="4" t="s">
-        <v>355</v>
+        <v>660</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="K419" s="5" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L419" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B419-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D419-1)/Inputs!$B$12,0))</f>
@@ -26567,13 +26591,13 @@
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="R419" s="4" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="S419" s="4" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26596,19 +26620,19 @@
         <v>55</v>
       </c>
       <c r="G420" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H420" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="K420" s="5" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L420" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B420-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D420-1)/Inputs!$B$12,0))</f>
@@ -26621,13 +26645,13 @@
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="R420" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S420" s="4" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26650,17 +26674,17 @@
         <v>91</v>
       </c>
       <c r="G421" s="6" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="I421" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J421" s="6"/>
       <c r="K421" s="7" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="L421" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B421-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D421-1)/Inputs!$B$12*3.66,0))</f>
@@ -26673,7 +26697,7 @@
       </c>
       <c r="P421" s="7"/>
       <c r="Q421" s="6" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="R421" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26685,7 +26709,7 @@
     </row>
     <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>1</v>
@@ -26706,7 +26730,7 @@
         <v>223</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I422" s="2" t="s">
         <v>225</v>
@@ -26715,7 +26739,7 @@
         <v>226</v>
       </c>
       <c r="K422" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L422" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0))</f>
@@ -26724,11 +26748,11 @@
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
       <c r="O422" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P422" s="3"/>
       <c r="Q422" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R422" s="2" t="n">
         <v>0.1667</v>
@@ -26739,7 +26763,7 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>1</v>
@@ -26760,7 +26784,7 @@
         <v>223</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I423" s="2" t="s">
         <v>225</v>
@@ -26769,7 +26793,7 @@
         <v>230</v>
       </c>
       <c r="K423" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L423" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0))</f>
@@ -26778,11 +26802,11 @@
       <c r="M423" s="2"/>
       <c r="N423" s="2"/>
       <c r="O423" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P423" s="3"/>
       <c r="Q423" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R423" s="2" t="n">
         <v>0.1667</v>
@@ -26793,7 +26817,7 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>1</v>
@@ -26814,7 +26838,7 @@
         <v>223</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I424" s="2" t="s">
         <v>225</v>
@@ -26823,7 +26847,7 @@
         <v>231</v>
       </c>
       <c r="K424" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L424" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0))</f>
@@ -26832,11 +26856,11 @@
       <c r="M424" s="2"/>
       <c r="N424" s="2"/>
       <c r="O424" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P424" s="3"/>
       <c r="Q424" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R424" s="2" t="n">
         <v>0.1667</v>
@@ -26847,7 +26871,7 @@
     </row>
     <row r="425" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>1</v>
@@ -26868,7 +26892,7 @@
         <v>232</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I425" s="2" t="s">
         <v>566</v>
@@ -26877,7 +26901,7 @@
         <v>567</v>
       </c>
       <c r="K425" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L425" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0))</f>
@@ -26886,11 +26910,11 @@
       <c r="M425" s="2"/>
       <c r="N425" s="2"/>
       <c r="O425" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P425" s="3"/>
       <c r="Q425" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R425" s="2" t="n">
         <v>0.016667</v>
@@ -26901,7 +26925,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>1</v>
@@ -26922,7 +26946,7 @@
         <v>232</v>
       </c>
       <c r="H426" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I426" s="2" t="s">
         <v>566</v>
@@ -26931,7 +26955,7 @@
         <v>571</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L426" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0))</f>
@@ -26940,11 +26964,11 @@
       <c r="M426" s="2"/>
       <c r="N426" s="2"/>
       <c r="O426" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P426" s="3"/>
       <c r="Q426" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R426" s="2" t="n">
         <v>0.016667</v>
@@ -26955,7 +26979,7 @@
     </row>
     <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>1</v>
@@ -26976,7 +27000,7 @@
         <v>422</v>
       </c>
       <c r="H427" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I427" s="2" t="s">
         <v>335</v>
@@ -26985,7 +27009,7 @@
         <v>502</v>
       </c>
       <c r="K427" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L427" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0))</f>
@@ -26994,11 +27018,11 @@
       <c r="M427" s="2"/>
       <c r="N427" s="2"/>
       <c r="O427" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P427" s="3"/>
       <c r="Q427" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R427" s="2" t="n">
         <v>0.016667</v>
@@ -27009,7 +27033,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>1</v>
@@ -27039,7 +27063,7 @@
         <v>506</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L428" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0))</f>
@@ -27048,11 +27072,11 @@
       <c r="M428" s="2"/>
       <c r="N428" s="2"/>
       <c r="O428" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P428" s="3"/>
       <c r="Q428" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R428" s="2" t="n">
         <v>0.016667</v>
@@ -27063,7 +27087,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B429" s="4" t="n">
         <v>1</v>
@@ -27081,19 +27105,19 @@
         <v>55</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H429" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="K429" s="5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L429" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0))</f>
@@ -27102,22 +27126,22 @@
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
       <c r="O429" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P429" s="5"/>
       <c r="Q429" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R429" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S429" s="4" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B430" s="4" t="n">
         <v>1</v>
@@ -27135,19 +27159,19 @@
         <v>55</v>
       </c>
       <c r="G430" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H430" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I430" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="K430" s="5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L430" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0))</f>
@@ -27156,22 +27180,22 @@
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
       <c r="O430" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P430" s="5"/>
       <c r="Q430" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R430" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S430" s="4" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B431" s="6" t="n">
         <v>1</v>
@@ -27192,14 +27216,14 @@
         <v>260</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="I431" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J431" s="6"/>
       <c r="K431" s="7" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="L431" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12*3.66,0))</f>
@@ -27208,11 +27232,11 @@
       <c r="M431" s="6"/>
       <c r="N431" s="6"/>
       <c r="O431" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P431" s="7"/>
       <c r="Q431" s="6" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="R431" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27224,7 +27248,7 @@
     </row>
     <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>2</v>
@@ -27245,7 +27269,7 @@
         <v>223</v>
       </c>
       <c r="H432" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I432" s="2" t="s">
         <v>263</v>
@@ -27254,7 +27278,7 @@
         <v>264</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L432" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B432-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D432-1)/Inputs!$B$12,0))</f>
@@ -27263,11 +27287,11 @@
       <c r="M432" s="2"/>
       <c r="N432" s="2"/>
       <c r="O432" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P432" s="3"/>
       <c r="Q432" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R432" s="2" t="n">
         <v>0.25</v>
@@ -27278,7 +27302,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>2</v>
@@ -27299,7 +27323,7 @@
         <v>223</v>
       </c>
       <c r="H433" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I433" s="2" t="s">
         <v>263</v>
@@ -27308,7 +27332,7 @@
         <v>265</v>
       </c>
       <c r="K433" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L433" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B433-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D433-1)/Inputs!$B$12,0))</f>
@@ -27317,11 +27341,11 @@
       <c r="M433" s="2"/>
       <c r="N433" s="2"/>
       <c r="O433" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P433" s="3"/>
       <c r="Q433" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R433" s="2" t="n">
         <v>0.25</v>
@@ -27332,7 +27356,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>2</v>
@@ -27353,7 +27377,7 @@
         <v>223</v>
       </c>
       <c r="H434" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I434" s="2" t="s">
         <v>263</v>
@@ -27362,7 +27386,7 @@
         <v>266</v>
       </c>
       <c r="K434" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L434" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B434-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D434-1)/Inputs!$B$12,0))</f>
@@ -27371,11 +27395,11 @@
       <c r="M434" s="2"/>
       <c r="N434" s="2"/>
       <c r="O434" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P434" s="3"/>
       <c r="Q434" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R434" s="2" t="n">
         <v>0.25</v>
@@ -27386,7 +27410,7 @@
     </row>
     <row r="435" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>2</v>
@@ -27407,7 +27431,7 @@
         <v>232</v>
       </c>
       <c r="H435" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I435" s="2" t="s">
         <v>566</v>
@@ -27416,7 +27440,7 @@
         <v>595</v>
       </c>
       <c r="K435" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L435" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B435-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D435-1)/Inputs!$B$12,0))</f>
@@ -27425,11 +27449,11 @@
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
       <c r="O435" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P435" s="3"/>
       <c r="Q435" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R435" s="2" t="n">
         <v>0.016667</v>
@@ -27440,7 +27464,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>2</v>
@@ -27461,7 +27485,7 @@
         <v>232</v>
       </c>
       <c r="H436" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I436" s="2" t="s">
         <v>566</v>
@@ -27470,7 +27494,7 @@
         <v>596</v>
       </c>
       <c r="K436" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L436" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B436-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D436-1)/Inputs!$B$12,0))</f>
@@ -27479,11 +27503,11 @@
       <c r="M436" s="2"/>
       <c r="N436" s="2"/>
       <c r="O436" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P436" s="3"/>
       <c r="Q436" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R436" s="2" t="n">
         <v>0.016667</v>
@@ -27494,7 +27518,7 @@
     </row>
     <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>2</v>
@@ -27515,7 +27539,7 @@
         <v>422</v>
       </c>
       <c r="H437" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I437" s="2" t="s">
         <v>335</v>
@@ -27524,7 +27548,7 @@
         <v>520</v>
       </c>
       <c r="K437" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L437" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B437-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D437-1)/Inputs!$B$12,0))</f>
@@ -27533,11 +27557,11 @@
       <c r="M437" s="2"/>
       <c r="N437" s="2"/>
       <c r="O437" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P437" s="3"/>
       <c r="Q437" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R437" s="2" t="n">
         <v>0.016667</v>
@@ -27548,7 +27572,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>2</v>
@@ -27578,7 +27602,7 @@
         <v>521</v>
       </c>
       <c r="K438" s="3" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L438" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B438-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D438-1)/Inputs!$B$12,0))</f>
@@ -27587,11 +27611,11 @@
       <c r="M438" s="2"/>
       <c r="N438" s="2"/>
       <c r="O438" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P438" s="3"/>
       <c r="Q438" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R438" s="2" t="n">
         <v>0.016667</v>
@@ -27602,7 +27626,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B439" s="4" t="n">
         <v>2</v>
@@ -27620,19 +27644,19 @@
         <v>55</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H439" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I439" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="K439" s="5" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L439" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B439-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D439-1)/Inputs!$B$12,0))</f>
@@ -27641,22 +27665,22 @@
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
       <c r="O439" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P439" s="5"/>
       <c r="Q439" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R439" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S439" s="4" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B440" s="4" t="n">
         <v>2</v>
@@ -27674,19 +27698,19 @@
         <v>55</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H440" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I440" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="K440" s="5" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L440" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B440-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D440-1)/Inputs!$B$12,0))</f>
@@ -27695,22 +27719,22 @@
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
       <c r="O440" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P440" s="5"/>
       <c r="Q440" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R440" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S440" s="4" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B441" s="6" t="n">
         <v>2</v>
@@ -27728,17 +27752,17 @@
         <v>91</v>
       </c>
       <c r="G441" s="6" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="I441" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J441" s="6"/>
       <c r="K441" s="7" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="L441" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B441-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D441-1)/Inputs!$B$12*3.66,0))</f>
@@ -27747,11 +27771,11 @@
       <c r="M441" s="6"/>
       <c r="N441" s="6"/>
       <c r="O441" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P441" s="7"/>
       <c r="Q441" s="6" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="R441" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27763,7 +27787,7 @@
     </row>
     <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B442" s="2" t="n">
         <v>3</v>
@@ -27784,7 +27808,7 @@
         <v>223</v>
       </c>
       <c r="H442" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I442" s="2" t="s">
         <v>276</v>
@@ -27793,7 +27817,7 @@
         <v>277</v>
       </c>
       <c r="K442" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L442" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B442-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D442-1)/Inputs!$B$12,0))</f>
@@ -27802,11 +27826,11 @@
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
       <c r="O442" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P442" s="3"/>
       <c r="Q442" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R442" s="2" t="n">
         <v>0.375</v>
@@ -27817,7 +27841,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B443" s="2" t="n">
         <v>3</v>
@@ -27838,7 +27862,7 @@
         <v>223</v>
       </c>
       <c r="H443" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I443" s="2" t="s">
         <v>276</v>
@@ -27847,7 +27871,7 @@
         <v>278</v>
       </c>
       <c r="K443" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L443" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B443-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D443-1)/Inputs!$B$12,0))</f>
@@ -27856,11 +27880,11 @@
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
       <c r="O443" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P443" s="3"/>
       <c r="Q443" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R443" s="2" t="n">
         <v>0.375</v>
@@ -27871,7 +27895,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B444" s="2" t="n">
         <v>3</v>
@@ -27892,7 +27916,7 @@
         <v>223</v>
       </c>
       <c r="H444" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I444" s="2" t="s">
         <v>276</v>
@@ -27901,7 +27925,7 @@
         <v>279</v>
       </c>
       <c r="K444" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L444" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B444-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D444-1)/Inputs!$B$12,0))</f>
@@ -27910,11 +27934,11 @@
       <c r="M444" s="2"/>
       <c r="N444" s="2"/>
       <c r="O444" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P444" s="3"/>
       <c r="Q444" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R444" s="2" t="n">
         <v>0.375</v>
@@ -27925,7 +27949,7 @@
     </row>
     <row r="445" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B445" s="2" t="n">
         <v>3</v>
@@ -27946,7 +27970,7 @@
         <v>232</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I445" s="2" t="s">
         <v>566</v>
@@ -27955,7 +27979,7 @@
         <v>604</v>
       </c>
       <c r="K445" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L445" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B445-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D445-1)/Inputs!$B$12,0))</f>
@@ -27964,11 +27988,11 @@
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
       <c r="O445" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P445" s="3"/>
       <c r="Q445" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R445" s="2" t="n">
         <v>0.016667</v>
@@ -27979,7 +28003,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B446" s="2" t="n">
         <v>3</v>
@@ -28000,7 +28024,7 @@
         <v>232</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I446" s="2" t="s">
         <v>566</v>
@@ -28009,7 +28033,7 @@
         <v>605</v>
       </c>
       <c r="K446" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L446" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B446-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D446-1)/Inputs!$B$12,0))</f>
@@ -28018,11 +28042,11 @@
       <c r="M446" s="2"/>
       <c r="N446" s="2"/>
       <c r="O446" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P446" s="3"/>
       <c r="Q446" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R446" s="2" t="n">
         <v>0.016667</v>
@@ -28033,7 +28057,7 @@
     </row>
     <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B447" s="2" t="n">
         <v>3</v>
@@ -28054,7 +28078,7 @@
         <v>422</v>
       </c>
       <c r="H447" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I447" s="2" t="s">
         <v>335</v>
@@ -28063,7 +28087,7 @@
         <v>528</v>
       </c>
       <c r="K447" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L447" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B447-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D447-1)/Inputs!$B$12,0))</f>
@@ -28072,11 +28096,11 @@
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
       <c r="O447" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P447" s="3"/>
       <c r="Q447" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R447" s="2" t="n">
         <v>0.016667</v>
@@ -28087,7 +28111,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B448" s="2" t="n">
         <v>3</v>
@@ -28117,7 +28141,7 @@
         <v>529</v>
       </c>
       <c r="K448" s="3" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L448" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B448-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D448-1)/Inputs!$B$12,0))</f>
@@ -28126,11 +28150,11 @@
       <c r="M448" s="2"/>
       <c r="N448" s="2"/>
       <c r="O448" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P448" s="3"/>
       <c r="Q448" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R448" s="2" t="n">
         <v>0.016667</v>
@@ -28141,7 +28165,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B449" s="4" t="n">
         <v>3</v>
@@ -28159,19 +28183,19 @@
         <v>55</v>
       </c>
       <c r="G449" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H449" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I449" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="K449" s="5" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L449" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B449-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D449-1)/Inputs!$B$12,0))</f>
@@ -28180,22 +28204,22 @@
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
       <c r="O449" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P449" s="5"/>
       <c r="Q449" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R449" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S449" s="4" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B450" s="4" t="n">
         <v>3</v>
@@ -28213,19 +28237,19 @@
         <v>55</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H450" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I450" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="K450" s="5" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L450" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B450-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D450-1)/Inputs!$B$12,0))</f>
@@ -28234,22 +28258,22 @@
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
       <c r="O450" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P450" s="5"/>
       <c r="Q450" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R450" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S450" s="4" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B451" s="6" t="n">
         <v>3</v>
@@ -28267,17 +28291,17 @@
         <v>91</v>
       </c>
       <c r="G451" s="6" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="H451" s="7" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="I451" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J451" s="6"/>
       <c r="K451" s="7" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="L451" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B451-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D451-1)/Inputs!$B$12*3.66,0))</f>
@@ -28286,11 +28310,11 @@
       <c r="M451" s="6"/>
       <c r="N451" s="6"/>
       <c r="O451" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P451" s="7"/>
       <c r="Q451" s="6" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="R451" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28302,7 +28326,7 @@
     </row>
     <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B452" s="2" t="n">
         <v>4</v>
@@ -28323,7 +28347,7 @@
         <v>223</v>
       </c>
       <c r="H452" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I452" s="2" t="s">
         <v>289</v>
@@ -28332,7 +28356,7 @@
         <v>290</v>
       </c>
       <c r="K452" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L452" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B452-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D452-1)/Inputs!$B$12,0))</f>
@@ -28341,11 +28365,11 @@
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
       <c r="O452" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P452" s="3"/>
       <c r="Q452" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R452" s="2" t="n">
         <v>0.5625</v>
@@ -28356,7 +28380,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B453" s="2" t="n">
         <v>4</v>
@@ -28377,7 +28401,7 @@
         <v>223</v>
       </c>
       <c r="H453" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I453" s="2" t="s">
         <v>289</v>
@@ -28386,7 +28410,7 @@
         <v>291</v>
       </c>
       <c r="K453" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L453" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B453-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D453-1)/Inputs!$B$12,0))</f>
@@ -28395,11 +28419,11 @@
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
       <c r="O453" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P453" s="3"/>
       <c r="Q453" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R453" s="2" t="n">
         <v>0.5625</v>
@@ -28410,7 +28434,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B454" s="2" t="n">
         <v>4</v>
@@ -28431,7 +28455,7 @@
         <v>223</v>
       </c>
       <c r="H454" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I454" s="2" t="s">
         <v>289</v>
@@ -28440,7 +28464,7 @@
         <v>292</v>
       </c>
       <c r="K454" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L454" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B454-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D454-1)/Inputs!$B$12,0))</f>
@@ -28449,11 +28473,11 @@
       <c r="M454" s="2"/>
       <c r="N454" s="2"/>
       <c r="O454" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P454" s="3"/>
       <c r="Q454" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R454" s="2" t="n">
         <v>0.5625</v>
@@ -28464,7 +28488,7 @@
     </row>
     <row r="455" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B455" s="2" t="n">
         <v>4</v>
@@ -28485,7 +28509,7 @@
         <v>232</v>
       </c>
       <c r="H455" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I455" s="2" t="s">
         <v>566</v>
@@ -28494,7 +28518,7 @@
         <v>613</v>
       </c>
       <c r="K455" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L455" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B455-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D455-1)/Inputs!$B$12,0))</f>
@@ -28503,11 +28527,11 @@
       <c r="M455" s="2"/>
       <c r="N455" s="2"/>
       <c r="O455" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P455" s="3"/>
       <c r="Q455" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R455" s="2" t="n">
         <v>0.016667</v>
@@ -28518,7 +28542,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B456" s="2" t="n">
         <v>4</v>
@@ -28539,7 +28563,7 @@
         <v>232</v>
       </c>
       <c r="H456" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I456" s="2" t="s">
         <v>566</v>
@@ -28548,7 +28572,7 @@
         <v>614</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L456" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B456-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D456-1)/Inputs!$B$12,0))</f>
@@ -28557,11 +28581,11 @@
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
       <c r="O456" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P456" s="3"/>
       <c r="Q456" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R456" s="2" t="n">
         <v>0.016667</v>
@@ -28572,7 +28596,7 @@
     </row>
     <row r="457" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B457" s="2" t="n">
         <v>4</v>
@@ -28593,7 +28617,7 @@
         <v>422</v>
       </c>
       <c r="H457" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I457" s="2" t="s">
         <v>335</v>
@@ -28602,7 +28626,7 @@
         <v>537</v>
       </c>
       <c r="K457" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L457" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B457-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D457-1)/Inputs!$B$12,0))</f>
@@ -28611,11 +28635,11 @@
       <c r="M457" s="2"/>
       <c r="N457" s="2"/>
       <c r="O457" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P457" s="3"/>
       <c r="Q457" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R457" s="2" t="n">
         <v>0.016667</v>
@@ -28626,7 +28650,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B458" s="2" t="n">
         <v>4</v>
@@ -28656,7 +28680,7 @@
         <v>538</v>
       </c>
       <c r="K458" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L458" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B458-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D458-1)/Inputs!$B$12,0))</f>
@@ -28665,11 +28689,11 @@
       <c r="M458" s="2"/>
       <c r="N458" s="2"/>
       <c r="O458" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P458" s="3"/>
       <c r="Q458" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R458" s="2" t="n">
         <v>0.016667</v>
@@ -28680,7 +28704,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B459" s="4" t="n">
         <v>4</v>
@@ -28698,19 +28722,19 @@
         <v>55</v>
       </c>
       <c r="G459" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H459" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I459" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="K459" s="5" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L459" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B459-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D459-1)/Inputs!$B$12,0))</f>
@@ -28719,22 +28743,22 @@
       <c r="M459" s="4"/>
       <c r="N459" s="4"/>
       <c r="O459" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P459" s="5"/>
       <c r="Q459" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R459" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S459" s="4" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B460" s="4" t="n">
         <v>4</v>
@@ -28752,19 +28776,19 @@
         <v>55</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H460" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I460" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="K460" s="5" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L460" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B460-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D460-1)/Inputs!$B$12,0))</f>
@@ -28773,22 +28797,22 @@
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
       <c r="O460" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P460" s="5"/>
       <c r="Q460" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R460" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S460" s="4" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B461" s="6" t="n">
         <v>4</v>
@@ -28806,17 +28830,17 @@
         <v>91</v>
       </c>
       <c r="G461" s="6" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="H461" s="7" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="I461" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J461" s="6"/>
       <c r="K461" s="7" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="L461" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B461-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D461-1)/Inputs!$B$12*3.66,0))</f>
@@ -28825,11 +28849,11 @@
       <c r="M461" s="6"/>
       <c r="N461" s="6"/>
       <c r="O461" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P461" s="7"/>
       <c r="Q461" s="6" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="R461" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28841,7 +28865,7 @@
     </row>
     <row r="462" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B462" s="2" t="n">
         <v>5</v>
@@ -28862,7 +28886,7 @@
         <v>223</v>
       </c>
       <c r="H462" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I462" s="2" t="s">
         <v>302</v>
@@ -28871,7 +28895,7 @@
         <v>303</v>
       </c>
       <c r="K462" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L462" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B462-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D462-1)/Inputs!$B$12,0))</f>
@@ -28880,11 +28904,11 @@
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
       <c r="O462" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P462" s="3"/>
       <c r="Q462" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R462" s="2" t="n">
         <v>0.8438</v>
@@ -28895,7 +28919,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B463" s="2" t="n">
         <v>5</v>
@@ -28916,7 +28940,7 @@
         <v>223</v>
       </c>
       <c r="H463" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I463" s="2" t="s">
         <v>302</v>
@@ -28925,7 +28949,7 @@
         <v>304</v>
       </c>
       <c r="K463" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L463" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B463-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D463-1)/Inputs!$B$12,0))</f>
@@ -28934,11 +28958,11 @@
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
       <c r="O463" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P463" s="3"/>
       <c r="Q463" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R463" s="2" t="n">
         <v>0.8438</v>
@@ -28949,7 +28973,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B464" s="2" t="n">
         <v>5</v>
@@ -28970,7 +28994,7 @@
         <v>223</v>
       </c>
       <c r="H464" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I464" s="2" t="s">
         <v>302</v>
@@ -28979,7 +29003,7 @@
         <v>305</v>
       </c>
       <c r="K464" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L464" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B464-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D464-1)/Inputs!$B$12,0))</f>
@@ -28988,11 +29012,11 @@
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
       <c r="O464" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P464" s="3"/>
       <c r="Q464" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R464" s="2" t="n">
         <v>0.8438</v>
@@ -29003,7 +29027,7 @@
     </row>
     <row r="465" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B465" s="2" t="n">
         <v>5</v>
@@ -29024,7 +29048,7 @@
         <v>232</v>
       </c>
       <c r="H465" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I465" s="2" t="s">
         <v>566</v>
@@ -29033,7 +29057,7 @@
         <v>622</v>
       </c>
       <c r="K465" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L465" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B465-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D465-1)/Inputs!$B$12,0))</f>
@@ -29042,11 +29066,11 @@
       <c r="M465" s="2"/>
       <c r="N465" s="2"/>
       <c r="O465" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P465" s="3"/>
       <c r="Q465" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R465" s="2" t="n">
         <v>0.016667</v>
@@ -29057,7 +29081,7 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B466" s="2" t="n">
         <v>5</v>
@@ -29078,7 +29102,7 @@
         <v>232</v>
       </c>
       <c r="H466" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I466" s="2" t="s">
         <v>566</v>
@@ -29087,7 +29111,7 @@
         <v>623</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L466" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B466-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D466-1)/Inputs!$B$12,0))</f>
@@ -29096,11 +29120,11 @@
       <c r="M466" s="2"/>
       <c r="N466" s="2"/>
       <c r="O466" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P466" s="3"/>
       <c r="Q466" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R466" s="2" t="n">
         <v>0.016667</v>
@@ -29111,7 +29135,7 @@
     </row>
     <row r="467" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B467" s="2" t="n">
         <v>5</v>
@@ -29132,7 +29156,7 @@
         <v>422</v>
       </c>
       <c r="H467" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I467" s="2" t="s">
         <v>335</v>
@@ -29141,7 +29165,7 @@
         <v>545</v>
       </c>
       <c r="K467" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L467" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B467-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D467-1)/Inputs!$B$12,0))</f>
@@ -29150,11 +29174,11 @@
       <c r="M467" s="2"/>
       <c r="N467" s="2"/>
       <c r="O467" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P467" s="3"/>
       <c r="Q467" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R467" s="2" t="n">
         <v>0.016667</v>
@@ -29165,7 +29189,7 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B468" s="2" t="n">
         <v>5</v>
@@ -29195,7 +29219,7 @@
         <v>546</v>
       </c>
       <c r="K468" s="3" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L468" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B468-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D468-1)/Inputs!$B$12,0))</f>
@@ -29204,11 +29228,11 @@
       <c r="M468" s="2"/>
       <c r="N468" s="2"/>
       <c r="O468" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P468" s="3"/>
       <c r="Q468" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R468" s="2" t="n">
         <v>0.016667</v>
@@ -29219,7 +29243,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B469" s="4" t="n">
         <v>5</v>
@@ -29237,19 +29261,19 @@
         <v>55</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H469" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="K469" s="5" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L469" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B469-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D469-1)/Inputs!$B$12,0))</f>
@@ -29258,22 +29282,22 @@
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
       <c r="O469" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P469" s="5"/>
       <c r="Q469" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R469" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S469" s="4" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B470" s="4" t="n">
         <v>5</v>
@@ -29291,19 +29315,19 @@
         <v>55</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H470" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I470" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="K470" s="5" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L470" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B470-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D470-1)/Inputs!$B$12,0))</f>
@@ -29312,22 +29336,22 @@
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
       <c r="O470" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P470" s="5"/>
       <c r="Q470" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R470" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S470" s="4" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B471" s="6" t="n">
         <v>5</v>
@@ -29348,14 +29372,14 @@
         <v>312</v>
       </c>
       <c r="H471" s="7" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="I471" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J471" s="6"/>
       <c r="K471" s="7" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="L471" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B471-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D471-1)/Inputs!$B$12*3.66,0))</f>
@@ -29364,11 +29388,11 @@
       <c r="M471" s="6"/>
       <c r="N471" s="6"/>
       <c r="O471" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P471" s="7"/>
       <c r="Q471" s="6" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="R471" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -29380,7 +29404,7 @@
     </row>
     <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B472" s="2" t="n">
         <v>6</v>
@@ -29401,7 +29425,7 @@
         <v>223</v>
       </c>
       <c r="H472" s="3" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I472" s="2" t="s">
         <v>315</v>
@@ -29410,7 +29434,7 @@
         <v>316</v>
       </c>
       <c r="K472" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L472" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B472-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D472-1)/Inputs!$B$12,0))</f>
@@ -29419,11 +29443,11 @@
       <c r="M472" s="2"/>
       <c r="N472" s="2"/>
       <c r="O472" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P472" s="3"/>
       <c r="Q472" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R472" s="2" t="n">
         <v>1.2656</v>
@@ -29434,7 +29458,7 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B473" s="2" t="n">
         <v>6</v>
@@ -29455,7 +29479,7 @@
         <v>223</v>
       </c>
       <c r="H473" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I473" s="2" t="s">
         <v>315</v>
@@ -29464,7 +29488,7 @@
         <v>317</v>
       </c>
       <c r="K473" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L473" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B473-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D473-1)/Inputs!$B$12,0))</f>
@@ -29473,11 +29497,11 @@
       <c r="M473" s="2"/>
       <c r="N473" s="2"/>
       <c r="O473" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P473" s="3"/>
       <c r="Q473" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R473" s="2" t="n">
         <v>1.2656</v>
@@ -29488,7 +29512,7 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B474" s="2" t="n">
         <v>6</v>
@@ -29509,7 +29533,7 @@
         <v>223</v>
       </c>
       <c r="H474" s="3" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="I474" s="2" t="s">
         <v>315</v>
@@ -29518,7 +29542,7 @@
         <v>318</v>
       </c>
       <c r="K474" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L474" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B474-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D474-1)/Inputs!$B$12,0))</f>
@@ -29527,11 +29551,11 @@
       <c r="M474" s="2"/>
       <c r="N474" s="2"/>
       <c r="O474" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P474" s="3"/>
       <c r="Q474" s="2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="R474" s="2" t="n">
         <v>1.2656</v>
@@ -29542,7 +29566,7 @@
     </row>
     <row r="475" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B475" s="2" t="n">
         <v>6</v>
@@ -29563,7 +29587,7 @@
         <v>232</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="I475" s="2" t="s">
         <v>566</v>
@@ -29572,7 +29596,7 @@
         <v>630</v>
       </c>
       <c r="K475" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L475" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B475-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D475-1)/Inputs!$B$12,0))</f>
@@ -29581,11 +29605,11 @@
       <c r="M475" s="2"/>
       <c r="N475" s="2"/>
       <c r="O475" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P475" s="3"/>
       <c r="Q475" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R475" s="2" t="n">
         <v>0.016667</v>
@@ -29596,7 +29620,7 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B476" s="2" t="n">
         <v>6</v>
@@ -29617,7 +29641,7 @@
         <v>232</v>
       </c>
       <c r="H476" s="3" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I476" s="2" t="s">
         <v>566</v>
@@ -29626,7 +29650,7 @@
         <v>631</v>
       </c>
       <c r="K476" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L476" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B476-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D476-1)/Inputs!$B$12,0))</f>
@@ -29635,11 +29659,11 @@
       <c r="M476" s="2"/>
       <c r="N476" s="2"/>
       <c r="O476" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P476" s="3"/>
       <c r="Q476" s="2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="R476" s="2" t="n">
         <v>0.016667</v>
@@ -29650,7 +29674,7 @@
     </row>
     <row r="477" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B477" s="2" t="n">
         <v>6</v>
@@ -29671,7 +29695,7 @@
         <v>422</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I477" s="2" t="s">
         <v>335</v>
@@ -29680,7 +29704,7 @@
         <v>553</v>
       </c>
       <c r="K477" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L477" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B477-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D477-1)/Inputs!$B$12,0))</f>
@@ -29689,11 +29713,11 @@
       <c r="M477" s="2"/>
       <c r="N477" s="2"/>
       <c r="O477" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P477" s="3"/>
       <c r="Q477" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R477" s="2" t="n">
         <v>0.016667</v>
@@ -29704,7 +29728,7 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B478" s="2" t="n">
         <v>6</v>
@@ -29734,7 +29758,7 @@
         <v>554</v>
       </c>
       <c r="K478" s="3" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L478" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B478-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D478-1)/Inputs!$B$12,0))</f>
@@ -29743,11 +29767,11 @@
       <c r="M478" s="2"/>
       <c r="N478" s="2"/>
       <c r="O478" s="2" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P478" s="3"/>
       <c r="Q478" s="2" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="R478" s="2" t="n">
         <v>0.016667</v>
@@ -29758,7 +29782,7 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B479" s="4" t="n">
         <v>6</v>
@@ -29776,19 +29800,19 @@
         <v>55</v>
       </c>
       <c r="G479" s="4" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="H479" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="I479" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="K479" s="5" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L479" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B479-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D479-1)/Inputs!$B$12,0))</f>
@@ -29797,22 +29821,22 @@
       <c r="M479" s="4"/>
       <c r="N479" s="4"/>
       <c r="O479" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P479" s="5"/>
       <c r="Q479" s="4" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="R479" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S479" s="4" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="4" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B480" s="4" t="n">
         <v>6</v>
@@ -29830,19 +29854,19 @@
         <v>55</v>
       </c>
       <c r="G480" s="4" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="H480" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="I480" s="4" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="K480" s="5" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L480" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B480-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D480-1)/Inputs!$B$12,0))</f>
@@ -29851,22 +29875,22 @@
       <c r="M480" s="4"/>
       <c r="N480" s="4"/>
       <c r="O480" s="4" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P480" s="5"/>
       <c r="Q480" s="4" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="R480" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S480" s="4" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="6" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B481" s="6" t="n">
         <v>6</v>
@@ -29884,17 +29908,17 @@
         <v>91</v>
       </c>
       <c r="G481" s="6" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="I481" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J481" s="6"/>
       <c r="K481" s="7" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="L481" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B481-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D481-1)/Inputs!$B$12*3.66,0))</f>
@@ -29903,11 +29927,11 @@
       <c r="M481" s="6"/>
       <c r="N481" s="6"/>
       <c r="O481" s="6" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="P481" s="7"/>
       <c r="Q481" s="6" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="R481" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -29919,7 +29943,7 @@
     </row>
     <row r="482" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B482" s="2" t="n">
         <v>1</v>
@@ -29937,19 +29961,19 @@
         <v>22</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H482" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I482" s="2" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="J482" s="2" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="K482" s="3" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="L482" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D482-1)/Inputs!$B$12,0))</f>
@@ -29958,22 +29982,22 @@
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
       <c r="O482" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P482" s="3"/>
       <c r="Q482" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R482" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S482" s="2" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>1</v>
@@ -29991,19 +30015,19 @@
         <v>22</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H483" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I483" s="2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="J483" s="2" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="K483" s="3" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="L483" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D483-1)/Inputs!$B$12,0))</f>
@@ -30012,22 +30036,22 @@
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
       <c r="O483" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P483" s="3"/>
       <c r="Q483" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R483" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S483" s="2" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>1</v>
@@ -30045,19 +30069,19 @@
         <v>22</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H484" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I484" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J484" s="2" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="L484" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D484-1)/Inputs!$B$12,0))</f>
@@ -30066,22 +30090,22 @@
       <c r="M484" s="2"/>
       <c r="N484" s="2"/>
       <c r="O484" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P484" s="3"/>
       <c r="Q484" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R484" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S484" s="2" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B485" s="2" t="n">
         <v>1</v>
@@ -30099,19 +30123,19 @@
         <v>22</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H485" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I485" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J485" s="2" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="K485" s="3" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="L485" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D485-1)/Inputs!$B$12,0))</f>
@@ -30120,22 +30144,22 @@
       <c r="M485" s="2"/>
       <c r="N485" s="2"/>
       <c r="O485" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P485" s="3"/>
       <c r="Q485" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R485" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S485" s="2" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B486" s="2" t="n">
         <v>1</v>
@@ -30153,19 +30177,19 @@
         <v>22</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H486" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I486" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J486" s="2" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="K486" s="3" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="L486" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D486-1)/Inputs!$B$12,0))</f>
@@ -30174,22 +30198,22 @@
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
       <c r="O486" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P486" s="3"/>
       <c r="Q486" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R486" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S486" s="2" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B487" s="2" t="n">
         <v>1</v>
@@ -30207,19 +30231,19 @@
         <v>22</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H487" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I487" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J487" s="2" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="K487" s="3" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="L487" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D487-1)/Inputs!$B$12,0))</f>
@@ -30228,22 +30252,22 @@
       <c r="M487" s="2"/>
       <c r="N487" s="2"/>
       <c r="O487" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P487" s="3"/>
       <c r="Q487" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R487" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S487" s="2" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B488" s="4" t="n">
         <v>1</v>
@@ -30261,19 +30285,19 @@
         <v>55</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H488" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I488" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="K488" s="5" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="L488" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D488-1)/Inputs!$B$12,0))</f>
@@ -30282,22 +30306,22 @@
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
       <c r="O488" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P488" s="5"/>
       <c r="Q488" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R488" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S488" s="4" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B489" s="4" t="n">
         <v>1</v>
@@ -30315,19 +30339,19 @@
         <v>55</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H489" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I489" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="K489" s="5" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="L489" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D489-1)/Inputs!$B$12,0))</f>
@@ -30336,22 +30360,22 @@
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
       <c r="O489" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P489" s="5"/>
       <c r="Q489" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R489" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S489" s="4" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B490" s="4" t="n">
         <v>1</v>
@@ -30369,19 +30393,19 @@
         <v>55</v>
       </c>
       <c r="G490" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H490" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I490" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="K490" s="5" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="L490" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D490-1)/Inputs!$B$12,0))</f>
@@ -30390,22 +30414,22 @@
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
       <c r="O490" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P490" s="5"/>
       <c r="Q490" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R490" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S490" s="4" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B491" s="6" t="n">
         <v>1</v>
@@ -30423,17 +30447,17 @@
         <v>91</v>
       </c>
       <c r="G491" s="6" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="H491" s="7" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="I491" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J491" s="6"/>
       <c r="K491" s="7" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="L491" s="6" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D491-1)/Inputs!$B$12*3.66,0))</f>
@@ -30442,11 +30466,11 @@
       <c r="M491" s="6"/>
       <c r="N491" s="6"/>
       <c r="O491" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P491" s="7"/>
       <c r="Q491" s="6" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="R491" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -30458,7 +30482,7 @@
     </row>
     <row r="492" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B492" s="2" t="n">
         <v>2</v>
@@ -30476,19 +30500,19 @@
         <v>22</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H492" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I492" s="2" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="J492" s="2" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="K492" s="3" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="L492" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D492-1)/Inputs!$B$12,0))</f>
@@ -30497,22 +30521,22 @@
       <c r="M492" s="2"/>
       <c r="N492" s="2"/>
       <c r="O492" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P492" s="3"/>
       <c r="Q492" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R492" s="2" t="n">
         <v>25</v>
       </c>
       <c r="S492" s="2" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B493" s="2" t="n">
         <v>2</v>
@@ -30530,19 +30554,19 @@
         <v>22</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H493" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I493" s="2" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="J493" s="2" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="K493" s="3" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="L493" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D493-1)/Inputs!$B$12,0))</f>
@@ -30551,22 +30575,22 @@
       <c r="M493" s="2"/>
       <c r="N493" s="2"/>
       <c r="O493" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P493" s="3"/>
       <c r="Q493" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R493" s="2" t="n">
         <v>3</v>
       </c>
       <c r="S493" s="2" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>2</v>
@@ -30584,19 +30608,19 @@
         <v>22</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I494" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J494" s="2" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="K494" s="3" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="L494" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D494-1)/Inputs!$B$12,0))</f>
@@ -30605,22 +30629,22 @@
       <c r="M494" s="2"/>
       <c r="N494" s="2"/>
       <c r="O494" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P494" s="3"/>
       <c r="Q494" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R494" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S494" s="2" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>2</v>
@@ -30638,19 +30662,19 @@
         <v>22</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I495" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="K495" s="3" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="L495" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D495-1)/Inputs!$B$12,0))</f>
@@ -30659,22 +30683,22 @@
       <c r="M495" s="2"/>
       <c r="N495" s="2"/>
       <c r="O495" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P495" s="3"/>
       <c r="Q495" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R495" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S495" s="2" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B496" s="2" t="n">
         <v>2</v>
@@ -30692,19 +30716,19 @@
         <v>22</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I496" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J496" s="2" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="K496" s="3" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="L496" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D496-1)/Inputs!$B$12,0))</f>
@@ -30713,22 +30737,22 @@
       <c r="M496" s="2"/>
       <c r="N496" s="2"/>
       <c r="O496" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P496" s="3"/>
       <c r="Q496" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R496" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S496" s="2" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B497" s="2" t="n">
         <v>2</v>
@@ -30746,19 +30770,19 @@
         <v>22</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I497" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="K497" s="3" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="L497" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D497-1)/Inputs!$B$12,0))</f>
@@ -30767,22 +30791,22 @@
       <c r="M497" s="2"/>
       <c r="N497" s="2"/>
       <c r="O497" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P497" s="3"/>
       <c r="Q497" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R497" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S497" s="2" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B498" s="4" t="n">
         <v>2</v>
@@ -30800,19 +30824,19 @@
         <v>55</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H498" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I498" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J498" s="4" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="K498" s="5" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="L498" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D498-1)/Inputs!$B$12,0))</f>
@@ -30821,22 +30845,22 @@
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
       <c r="O498" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P498" s="5"/>
       <c r="Q498" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R498" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S498" s="4" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B499" s="4" t="n">
         <v>2</v>
@@ -30854,19 +30878,19 @@
         <v>55</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H499" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I499" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="K499" s="5" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="L499" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D499-1)/Inputs!$B$12,0))</f>
@@ -30875,22 +30899,22 @@
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
       <c r="O499" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P499" s="5"/>
       <c r="Q499" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R499" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S499" s="4" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B500" s="4" t="n">
         <v>2</v>
@@ -30908,19 +30932,19 @@
         <v>55</v>
       </c>
       <c r="G500" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H500" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I500" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J500" s="4" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="K500" s="5" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="L500" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D500-1)/Inputs!$B$12,0))</f>
@@ -30929,22 +30953,22 @@
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
       <c r="O500" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P500" s="5"/>
       <c r="Q500" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R500" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S500" s="4" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B501" s="6" t="n">
         <v>2</v>
@@ -30962,17 +30986,17 @@
         <v>91</v>
       </c>
       <c r="G501" s="6" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="H501" s="7" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="I501" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="7" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="L501" s="6" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D501-1)/Inputs!$B$12*3.66,0))</f>
@@ -30981,11 +31005,11 @@
       <c r="M501" s="6"/>
       <c r="N501" s="6"/>
       <c r="O501" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P501" s="7"/>
       <c r="Q501" s="6" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="R501" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -30997,7 +31021,7 @@
     </row>
     <row r="502" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B502" s="2" t="n">
         <v>3</v>
@@ -31015,19 +31039,19 @@
         <v>22</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="K502" s="3" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="L502" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D502-1)/Inputs!$B$12,0))</f>
@@ -31036,22 +31060,22 @@
       <c r="M502" s="2"/>
       <c r="N502" s="2"/>
       <c r="O502" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P502" s="3"/>
       <c r="Q502" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R502" s="2" t="n">
         <v>38</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B503" s="2" t="n">
         <v>3</v>
@@ -31069,19 +31093,19 @@
         <v>22</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I503" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="K503" s="3" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="L503" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D503-1)/Inputs!$B$12,0))</f>
@@ -31090,22 +31114,22 @@
       <c r="M503" s="2"/>
       <c r="N503" s="2"/>
       <c r="O503" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P503" s="3"/>
       <c r="Q503" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R503" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S503" s="2" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B504" s="2" t="n">
         <v>3</v>
@@ -31123,19 +31147,19 @@
         <v>22</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="K504" s="3" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="L504" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D504-1)/Inputs!$B$12,0))</f>
@@ -31144,22 +31168,22 @@
       <c r="M504" s="2"/>
       <c r="N504" s="2"/>
       <c r="O504" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P504" s="3"/>
       <c r="Q504" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R504" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S504" s="2" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B505" s="2" t="n">
         <v>3</v>
@@ -31177,19 +31201,19 @@
         <v>22</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I505" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="K505" s="3" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="L505" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D505-1)/Inputs!$B$12,0))</f>
@@ -31198,22 +31222,22 @@
       <c r="M505" s="2"/>
       <c r="N505" s="2"/>
       <c r="O505" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P505" s="3"/>
       <c r="Q505" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R505" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S505" s="2" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B506" s="2" t="n">
         <v>3</v>
@@ -31231,19 +31255,19 @@
         <v>22</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I506" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="L506" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D506-1)/Inputs!$B$12,0))</f>
@@ -31252,22 +31276,22 @@
       <c r="M506" s="2"/>
       <c r="N506" s="2"/>
       <c r="O506" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P506" s="3"/>
       <c r="Q506" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R506" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S506" s="2" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B507" s="2" t="n">
         <v>3</v>
@@ -31285,19 +31309,19 @@
         <v>22</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I507" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="K507" s="3" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="L507" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D507-1)/Inputs!$B$12,0))</f>
@@ -31306,22 +31330,22 @@
       <c r="M507" s="2"/>
       <c r="N507" s="2"/>
       <c r="O507" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P507" s="3"/>
       <c r="Q507" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R507" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S507" s="2" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B508" s="4" t="n">
         <v>3</v>
@@ -31339,19 +31363,19 @@
         <v>55</v>
       </c>
       <c r="G508" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H508" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I508" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="K508" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="L508" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D508-1)/Inputs!$B$12,0))</f>
@@ -31360,22 +31384,22 @@
       <c r="M508" s="4"/>
       <c r="N508" s="4"/>
       <c r="O508" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P508" s="5"/>
       <c r="Q508" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R508" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S508" s="4" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B509" s="4" t="n">
         <v>3</v>
@@ -31393,19 +31417,19 @@
         <v>55</v>
       </c>
       <c r="G509" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H509" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I509" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="K509" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="L509" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D509-1)/Inputs!$B$12,0))</f>
@@ -31414,22 +31438,22 @@
       <c r="M509" s="4"/>
       <c r="N509" s="4"/>
       <c r="O509" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P509" s="5"/>
       <c r="Q509" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R509" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S509" s="4" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B510" s="4" t="n">
         <v>3</v>
@@ -31447,19 +31471,19 @@
         <v>55</v>
       </c>
       <c r="G510" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I510" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="K510" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="L510" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D510-1)/Inputs!$B$12,0))</f>
@@ -31468,22 +31492,22 @@
       <c r="M510" s="4"/>
       <c r="N510" s="4"/>
       <c r="O510" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P510" s="5"/>
       <c r="Q510" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R510" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S510" s="4" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B511" s="6" t="n">
         <v>3</v>
@@ -31501,17 +31525,17 @@
         <v>91</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="H511" s="7" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J511" s="6"/>
       <c r="K511" s="7" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="L511" s="6" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D511-1)/Inputs!$B$12*3.66,0))</f>
@@ -31520,11 +31544,11 @@
       <c r="M511" s="6"/>
       <c r="N511" s="6"/>
       <c r="O511" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P511" s="7"/>
       <c r="Q511" s="6" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="R511" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31536,7 +31560,7 @@
     </row>
     <row r="512" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B512" s="2" t="n">
         <v>4</v>
@@ -31554,19 +31578,19 @@
         <v>22</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H512" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="K512" s="3" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="L512" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D512-1)/Inputs!$B$12,0))</f>
@@ -31575,22 +31599,22 @@
       <c r="M512" s="2"/>
       <c r="N512" s="2"/>
       <c r="O512" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P512" s="3"/>
       <c r="Q512" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R512" s="2" t="n">
         <v>50</v>
       </c>
       <c r="S512" s="2" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B513" s="2" t="n">
         <v>4</v>
@@ -31608,19 +31632,19 @@
         <v>22</v>
       </c>
       <c r="G513" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H513" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I513" s="2" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="J513" s="2" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="K513" s="3" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="L513" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D513-1)/Inputs!$B$12,0))</f>
@@ -31629,22 +31653,22 @@
       <c r="M513" s="2"/>
       <c r="N513" s="2"/>
       <c r="O513" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P513" s="3"/>
       <c r="Q513" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R513" s="2" t="n">
         <v>6</v>
       </c>
       <c r="S513" s="2" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B514" s="2" t="n">
         <v>4</v>
@@ -31662,19 +31686,19 @@
         <v>22</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H514" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="K514" s="3" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="L514" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D514-1)/Inputs!$B$12,0))</f>
@@ -31683,22 +31707,22 @@
       <c r="M514" s="2"/>
       <c r="N514" s="2"/>
       <c r="O514" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P514" s="3"/>
       <c r="Q514" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R514" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S514" s="2" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B515" s="2" t="n">
         <v>4</v>
@@ -31716,19 +31740,19 @@
         <v>22</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H515" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I515" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="K515" s="3" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="L515" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D515-1)/Inputs!$B$12,0))</f>
@@ -31737,22 +31761,22 @@
       <c r="M515" s="2"/>
       <c r="N515" s="2"/>
       <c r="O515" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P515" s="3"/>
       <c r="Q515" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R515" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S515" s="2" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>4</v>
@@ -31770,19 +31794,19 @@
         <v>22</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H516" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I516" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J516" s="2" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="K516" s="3" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="L516" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D516-1)/Inputs!$B$12,0))</f>
@@ -31791,22 +31815,22 @@
       <c r="M516" s="2"/>
       <c r="N516" s="2"/>
       <c r="O516" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P516" s="3"/>
       <c r="Q516" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R516" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S516" s="2" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>4</v>
@@ -31824,19 +31848,19 @@
         <v>22</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H517" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I517" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="K517" s="3" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="L517" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D517-1)/Inputs!$B$12,0))</f>
@@ -31845,22 +31869,22 @@
       <c r="M517" s="2"/>
       <c r="N517" s="2"/>
       <c r="O517" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P517" s="3"/>
       <c r="Q517" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R517" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S517" s="2" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B518" s="4" t="n">
         <v>4</v>
@@ -31878,19 +31902,19 @@
         <v>55</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H518" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I518" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="K518" s="5" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L518" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D518-1)/Inputs!$B$12,0))</f>
@@ -31899,22 +31923,22 @@
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
       <c r="O518" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P518" s="5"/>
       <c r="Q518" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R518" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S518" s="4" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B519" s="4" t="n">
         <v>4</v>
@@ -31932,19 +31956,19 @@
         <v>55</v>
       </c>
       <c r="G519" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H519" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I519" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="K519" s="5" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L519" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D519-1)/Inputs!$B$12,0))</f>
@@ -31953,22 +31977,22 @@
       <c r="M519" s="4"/>
       <c r="N519" s="4"/>
       <c r="O519" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P519" s="5"/>
       <c r="Q519" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R519" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S519" s="4" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B520" s="4" t="n">
         <v>4</v>
@@ -31986,19 +32010,19 @@
         <v>55</v>
       </c>
       <c r="G520" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H520" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I520" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="K520" s="5" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="L520" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D520-1)/Inputs!$B$12,0))</f>
@@ -32007,22 +32031,22 @@
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
       <c r="O520" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P520" s="5"/>
       <c r="Q520" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R520" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S520" s="4" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B521" s="6" t="n">
         <v>4</v>
@@ -32040,17 +32064,17 @@
         <v>91</v>
       </c>
       <c r="G521" s="6" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="H521" s="7" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="I521" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J521" s="6"/>
       <c r="K521" s="7" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="L521" s="6" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D521-1)/Inputs!$B$12*3.66,0))</f>
@@ -32059,11 +32083,11 @@
       <c r="M521" s="6"/>
       <c r="N521" s="6"/>
       <c r="O521" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P521" s="7"/>
       <c r="Q521" s="6" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="R521" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32075,7 +32099,7 @@
     </row>
     <row r="522" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B522" s="2" t="n">
         <v>5</v>
@@ -32093,19 +32117,19 @@
         <v>22</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H522" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="K522" s="3" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="L522" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D522-1)/Inputs!$B$12,0))</f>
@@ -32114,22 +32138,22 @@
       <c r="M522" s="2"/>
       <c r="N522" s="2"/>
       <c r="O522" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P522" s="3"/>
       <c r="Q522" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R522" s="2" t="n">
         <v>62</v>
       </c>
       <c r="S522" s="2" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B523" s="2" t="n">
         <v>5</v>
@@ -32147,19 +32171,19 @@
         <v>22</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H523" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="K523" s="3" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="L523" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D523-1)/Inputs!$B$12,0))</f>
@@ -32168,22 +32192,22 @@
       <c r="M523" s="2"/>
       <c r="N523" s="2"/>
       <c r="O523" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P523" s="3"/>
       <c r="Q523" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R523" s="2" t="n">
         <v>7</v>
       </c>
       <c r="S523" s="2" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B524" s="2" t="n">
         <v>5</v>
@@ -32201,19 +32225,19 @@
         <v>22</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H524" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I524" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="K524" s="3" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="L524" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D524-1)/Inputs!$B$12,0))</f>
@@ -32222,22 +32246,22 @@
       <c r="M524" s="2"/>
       <c r="N524" s="2"/>
       <c r="O524" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P524" s="3"/>
       <c r="Q524" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R524" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B525" s="2" t="n">
         <v>5</v>
@@ -32255,19 +32279,19 @@
         <v>22</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H525" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="L525" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D525-1)/Inputs!$B$12,0))</f>
@@ -32276,22 +32300,22 @@
       <c r="M525" s="2"/>
       <c r="N525" s="2"/>
       <c r="O525" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P525" s="3"/>
       <c r="Q525" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R525" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S525" s="2" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B526" s="2" t="n">
         <v>5</v>
@@ -32309,19 +32333,19 @@
         <v>22</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H526" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I526" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="K526" s="3" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="L526" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D526-1)/Inputs!$B$12,0))</f>
@@ -32330,22 +32354,22 @@
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
       <c r="O526" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P526" s="3"/>
       <c r="Q526" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R526" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S526" s="2" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>5</v>
@@ -32363,19 +32387,19 @@
         <v>22</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H527" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I527" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="K527" s="3" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="L527" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D527-1)/Inputs!$B$12,0))</f>
@@ -32384,22 +32408,22 @@
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
       <c r="O527" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P527" s="3"/>
       <c r="Q527" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R527" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S527" s="2" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B528" s="4" t="n">
         <v>5</v>
@@ -32417,19 +32441,19 @@
         <v>55</v>
       </c>
       <c r="G528" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H528" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I528" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="K528" s="5" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="L528" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D528-1)/Inputs!$B$12,0))</f>
@@ -32438,22 +32462,22 @@
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
       <c r="O528" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P528" s="5"/>
       <c r="Q528" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R528" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S528" s="4" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B529" s="4" t="n">
         <v>5</v>
@@ -32471,19 +32495,19 @@
         <v>55</v>
       </c>
       <c r="G529" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H529" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I529" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="K529" s="5" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="L529" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D529-1)/Inputs!$B$12,0))</f>
@@ -32492,22 +32516,22 @@
       <c r="M529" s="4"/>
       <c r="N529" s="4"/>
       <c r="O529" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P529" s="5"/>
       <c r="Q529" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R529" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S529" s="4" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B530" s="4" t="n">
         <v>5</v>
@@ -32525,19 +32549,19 @@
         <v>55</v>
       </c>
       <c r="G530" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H530" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I530" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="K530" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="L530" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D530-1)/Inputs!$B$12,0))</f>
@@ -32546,22 +32570,22 @@
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
       <c r="O530" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P530" s="5"/>
       <c r="Q530" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R530" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S530" s="4" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B531" s="6" t="n">
         <v>5</v>
@@ -32579,17 +32603,17 @@
         <v>91</v>
       </c>
       <c r="G531" s="6" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H531" s="7" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="I531" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J531" s="6"/>
       <c r="K531" s="7" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="L531" s="6" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D531-1)/Inputs!$B$12*3.66,0))</f>
@@ -32598,11 +32622,11 @@
       <c r="M531" s="6"/>
       <c r="N531" s="6"/>
       <c r="O531" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P531" s="7"/>
       <c r="Q531" s="6" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="R531" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32614,7 +32638,7 @@
     </row>
     <row r="532" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B532" s="2" t="n">
         <v>6</v>
@@ -32632,19 +32656,19 @@
         <v>22</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="H532" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="K532" s="3" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="L532" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D532-1)/Inputs!$B$12,0))</f>
@@ -32653,22 +32677,22 @@
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
       <c r="O532" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P532" s="3"/>
       <c r="Q532" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="R532" s="2" t="n">
         <v>100</v>
       </c>
       <c r="S532" s="2" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B533" s="2" t="n">
         <v>6</v>
@@ -32686,19 +32710,19 @@
         <v>22</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="H533" s="3" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="K533" s="3" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="L533" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D533-1)/Inputs!$B$12,0))</f>
@@ -32707,22 +32731,22 @@
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
       <c r="O533" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P533" s="3"/>
       <c r="Q533" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="R533" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S533" s="2" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B534" s="2" t="n">
         <v>6</v>
@@ -32740,19 +32764,19 @@
         <v>22</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H534" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I534" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="K534" s="3" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="L534" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D534-1)/Inputs!$B$12,0))</f>
@@ -32761,22 +32785,22 @@
       <c r="M534" s="2"/>
       <c r="N534" s="2"/>
       <c r="O534" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P534" s="3"/>
       <c r="Q534" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R534" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S534" s="2" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B535" s="2" t="n">
         <v>6</v>
@@ -32794,19 +32818,19 @@
         <v>22</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="K535" s="3" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="L535" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D535-1)/Inputs!$B$12,0))</f>
@@ -32815,22 +32839,22 @@
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
       <c r="O535" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P535" s="3"/>
       <c r="Q535" s="2" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="R535" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S535" s="2" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B536" s="2" t="n">
         <v>6</v>
@@ -32848,19 +32872,19 @@
         <v>22</v>
       </c>
       <c r="G536" s="2" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H536" s="3" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="I536" s="2" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="J536" s="2" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="K536" s="3" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="L536" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D536-1)/Inputs!$B$12,0))</f>
@@ -32869,22 +32893,22 @@
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
       <c r="O536" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P536" s="3"/>
       <c r="Q536" s="2" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="R536" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S536" s="2" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>6</v>
@@ -32902,19 +32926,19 @@
         <v>22</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="H537" s="3" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="I537" s="2" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="K537" s="3" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="L537" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D537-1)/Inputs!$B$12,0))</f>
@@ -32923,22 +32947,22 @@
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
       <c r="O537" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P537" s="3"/>
       <c r="Q537" s="2" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="R537" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S537" s="2" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B538" s="4" t="n">
         <v>6</v>
@@ -32956,19 +32980,19 @@
         <v>55</v>
       </c>
       <c r="G538" s="4" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="H538" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="I538" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="J538" s="4" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="K538" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="L538" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D538-1)/Inputs!$B$12,0))</f>
@@ -32977,22 +33001,22 @@
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
       <c r="O538" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P538" s="5"/>
       <c r="Q538" s="4" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="R538" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S538" s="4" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B539" s="4" t="n">
         <v>6</v>
@@ -33010,19 +33034,19 @@
         <v>55</v>
       </c>
       <c r="G539" s="4" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="H539" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="I539" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J539" s="4" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="K539" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="L539" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D539-1)/Inputs!$B$12,0))</f>
@@ -33031,22 +33055,22 @@
       <c r="M539" s="4"/>
       <c r="N539" s="4"/>
       <c r="O539" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P539" s="5"/>
       <c r="Q539" s="4" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="R539" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S539" s="4" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="4" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B540" s="4" t="n">
         <v>6</v>
@@ -33064,19 +33088,19 @@
         <v>55</v>
       </c>
       <c r="G540" s="4" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="H540" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="I540" s="4" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="J540" s="4" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="K540" s="5" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="L540" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D540-1)/Inputs!$B$12,0))</f>
@@ -33085,22 +33109,22 @@
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
       <c r="O540" s="4" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P540" s="5"/>
       <c r="Q540" s="4" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="R540" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S540" s="4" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="6" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B541" s="6" t="n">
         <v>6</v>
@@ -33118,17 +33142,17 @@
         <v>91</v>
       </c>
       <c r="G541" s="6" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="H541" s="7" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="I541" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J541" s="6"/>
       <c r="K541" s="7" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="L541" s="6" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D541-1)/Inputs!$B$12*3.66,0))</f>
@@ -33137,11 +33161,11 @@
       <c r="M541" s="6"/>
       <c r="N541" s="6"/>
       <c r="O541" s="6" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="P541" s="7"/>
       <c r="Q541" s="6" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="R541" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -33180,12 +33204,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>2</v>
@@ -33193,7 +33217,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.1</v>
@@ -33201,7 +33225,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1.15</v>
@@ -33209,7 +33233,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1.25</v>
@@ -33217,7 +33241,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2</v>
@@ -33225,7 +33249,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>10</v>
@@ -33233,7 +33257,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1.5</v>
@@ -33241,7 +33265,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">(B6^10-1)/(B6-1)</f>
@@ -33253,13 +33277,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33267,13 +33291,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>570</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33281,13 +33305,13 @@
         <v>331</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>930</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33295,13 +33319,13 @@
         <v>413</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33309,13 +33333,13 @@
         <v>493</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>210</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33323,13 +33347,13 @@
         <v>562</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>330</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33337,41 +33361,41 @@
         <v>642</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>420</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>82</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33379,28 +33403,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -33427,7 +33451,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33435,22 +33459,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33458,22 +33482,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33481,17 +33505,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33499,22 +33523,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33522,22 +33546,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33545,22 +33569,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33568,37 +33592,37 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33606,42 +33630,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33649,32 +33673,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33682,32 +33706,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33715,27 +33739,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33743,32 +33767,32 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33776,22 +33800,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33799,47 +33823,47 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33847,22 +33871,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33870,22 +33894,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33893,42 +33917,42 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33936,42 +33960,42 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33979,17 +34003,17 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
     </row>
   </sheetData>
@@ -34017,12 +34041,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="B3" s="17" t="n">
         <v>100</v>
@@ -34030,7 +34054,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>5</v>
@@ -34038,7 +34062,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>100</v>
@@ -34049,25 +34073,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34252,7 +34276,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>99</v>
@@ -34282,27 +34306,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>0.05</v>
@@ -34310,7 +34334,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>0.01</v>
@@ -34318,7 +34342,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>12.5</v>
@@ -34326,7 +34350,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>6.25</v>
@@ -34337,22 +34361,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34531,12 +34555,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -34573,16 +34597,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35427,7 +35451,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>1</v>
@@ -35447,7 +35471,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>2</v>
@@ -35467,7 +35491,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>3</v>
@@ -35487,7 +35511,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>4</v>
@@ -35507,7 +35531,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>5</v>
@@ -35527,7 +35551,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>6</v>
@@ -35547,7 +35571,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>1</v>
@@ -35567,7 +35591,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>2</v>
@@ -35587,7 +35611,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>3</v>
@@ -35607,7 +35631,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>4</v>
@@ -35627,7 +35651,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>5</v>
@@ -35647,7 +35671,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>6</v>
@@ -35700,31 +35724,31 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35732,10 +35756,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35766,10 +35790,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D3" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35800,10 +35824,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35834,10 +35858,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35868,7 +35892,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>490</v>
@@ -35902,10 +35926,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>1088</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>1080</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35936,10 +35960,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35970,10 +35994,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36004,10 +36028,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36038,7 +36062,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>490</v>
@@ -36072,10 +36096,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36106,10 +36130,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36140,10 +36164,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36174,10 +36198,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36208,7 +36232,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>490</v>
@@ -36242,10 +36266,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36276,10 +36300,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36310,10 +36334,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36344,10 +36368,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36378,7 +36402,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>490</v>
@@ -36412,10 +36436,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36446,10 +36470,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36480,10 +36504,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36514,10 +36538,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36548,7 +36572,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>490</v>
@@ -36582,10 +36606,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36616,10 +36640,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36650,10 +36674,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36684,10 +36708,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36718,7 +36742,7 @@
         <v>6</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>490</v>
@@ -36778,16 +36802,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36911,7 +36935,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>10</v>
@@ -36928,7 +36952,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>10</v>
@@ -36945,7 +36969,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>90</v>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1125">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -2485,25 +2485,22 @@
     <t xml:space="preserve">MAJOR: Second Wind</t>
   </si>
   <si>
-    <t xml:space="preserve">Each win in a multi-hack run restores 25% of max anonymity (anonymity carries over between fights)</t>
+    <t xml:space="preserve">Each win in a multi-hack run restores 15% of max anonymity (anonymity carries over between fights)</t>
   </si>
   <si>
     <t xml:space="preserve">hacking.second_wind</t>
   </si>
   <si>
-    <t xml:space="preserve">+25 dmg, +0.1 heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 dmg</t>
+    <t xml:space="preserve">+10 dmg, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Legal assistant cache</t>
   </si>
   <si>
-    <t xml:space="preserve">+3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 firewall dmg</t>
+    <t xml:space="preserve">5 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">2.5 /s bandwidth regen</t>
@@ -2551,13 +2548,13 @@
     <t xml:space="preserve">+38 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">88 dmg</t>
+    <t xml:space="preserve">73 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Receptionist cache</t>
   </si>
   <si>
-    <t xml:space="preserve">11 firewall dmg</t>
+    <t xml:space="preserve">10 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">3.5 /s bandwidth regen</t>
@@ -2605,7 +2602,7 @@
     <t xml:space="preserve">+50 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">138 dmg</t>
+    <t xml:space="preserve">123 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Teller Cache</t>
@@ -2614,7 +2611,7 @@
     <t xml:space="preserve">+6</t>
   </si>
   <si>
-    <t xml:space="preserve">17 firewall dmg</t>
+    <t xml:space="preserve">16 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">4.5 /s bandwidth regen</t>
@@ -2662,7 +2659,7 @@
     <t xml:space="preserve">+62 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">200 dmg</t>
+    <t xml:space="preserve">185 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Secretary cache</t>
@@ -2671,7 +2668,7 @@
     <t xml:space="preserve">+7</t>
   </si>
   <si>
-    <t xml:space="preserve">24 firewall dmg</t>
+    <t xml:space="preserve">23 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">5.5 /s bandwidth regen</t>
@@ -2719,7 +2716,7 @@
     <t xml:space="preserve">+100 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">300 dmg</t>
+    <t xml:space="preserve">285 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Clerk Cache</t>
@@ -2728,7 +2725,7 @@
     <t xml:space="preserve">+12</t>
   </si>
   <si>
-    <t xml:space="preserve">36 firewall dmg</t>
+    <t xml:space="preserve">35 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">6.5 /s bandwidth regen</t>
@@ -30528,7 +30525,7 @@
         <v>769</v>
       </c>
       <c r="R492" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="S492" s="2" t="s">
         <v>766</v>
@@ -30560,10 +30557,10 @@
         <v>772</v>
       </c>
       <c r="I493" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="J493" s="2" t="s">
         <v>823</v>
-      </c>
-      <c r="J493" s="2" t="s">
-        <v>824</v>
       </c>
       <c r="K493" s="3" t="s">
         <v>822</v>
@@ -30582,7 +30579,7 @@
         <v>775</v>
       </c>
       <c r="R493" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S493" s="2" t="s">
         <v>774</v>
@@ -30617,10 +30614,10 @@
         <v>779</v>
       </c>
       <c r="J494" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="K494" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="K494" s="3" t="s">
-        <v>826</v>
       </c>
       <c r="L494" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D494-1)/Inputs!$B$12,0))</f>
@@ -30671,10 +30668,10 @@
         <v>779</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="K495" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L495" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D495-1)/Inputs!$B$12,0))</f>
@@ -30693,7 +30690,7 @@
         <v>0.5</v>
       </c>
       <c r="S495" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30725,10 +30722,10 @@
         <v>787</v>
       </c>
       <c r="J496" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="K496" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="K496" s="3" t="s">
-        <v>829</v>
       </c>
       <c r="L496" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D496-1)/Inputs!$B$12,0))</f>
@@ -30779,10 +30776,10 @@
         <v>794</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K497" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L497" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D497-1)/Inputs!$B$12,0))</f>
@@ -30833,10 +30830,10 @@
         <v>800</v>
       </c>
       <c r="J498" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="K498" s="5" t="s">
         <v>831</v>
-      </c>
-      <c r="K498" s="5" t="s">
-        <v>832</v>
       </c>
       <c r="L498" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D498-1)/Inputs!$B$12,0))</f>
@@ -30887,10 +30884,10 @@
         <v>355</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="K499" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="L499" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D499-1)/Inputs!$B$12,0))</f>
@@ -30941,10 +30938,10 @@
         <v>812</v>
       </c>
       <c r="J500" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="K500" s="5" t="s">
         <v>834</v>
-      </c>
-      <c r="K500" s="5" t="s">
-        <v>835</v>
       </c>
       <c r="L500" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D500-1)/Inputs!$B$12,0))</f>
@@ -30986,17 +30983,17 @@
         <v>91</v>
       </c>
       <c r="G501" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H501" s="7" t="s">
         <v>836</v>
-      </c>
-      <c r="H501" s="7" t="s">
-        <v>837</v>
       </c>
       <c r="I501" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L501" s="6" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D501-1)/Inputs!$B$12*3.66,0))</f>
@@ -31009,7 +31006,7 @@
       </c>
       <c r="P501" s="7"/>
       <c r="Q501" s="6" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="R501" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31045,13 +31042,13 @@
         <v>764</v>
       </c>
       <c r="I502" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="J502" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="J502" s="2" t="s">
+      <c r="K502" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="K502" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="L502" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D502-1)/Inputs!$B$12,0))</f>
@@ -31102,10 +31099,10 @@
         <v>787</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="K503" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L503" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D503-1)/Inputs!$B$12,0))</f>
@@ -31124,7 +31121,7 @@
         <v>5</v>
       </c>
       <c r="S503" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31156,10 +31153,10 @@
         <v>779</v>
       </c>
       <c r="J504" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="K504" s="3" t="s">
         <v>843</v>
-      </c>
-      <c r="K504" s="3" t="s">
-        <v>844</v>
       </c>
       <c r="L504" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D504-1)/Inputs!$B$12,0))</f>
@@ -31178,7 +31175,7 @@
         <v>0.5</v>
       </c>
       <c r="S504" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31210,10 +31207,10 @@
         <v>779</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K505" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="L505" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D505-1)/Inputs!$B$12,0))</f>
@@ -31232,7 +31229,7 @@
         <v>0.5</v>
       </c>
       <c r="S505" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31264,10 +31261,10 @@
         <v>787</v>
       </c>
       <c r="J506" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="K506" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="K506" s="3" t="s">
-        <v>847</v>
       </c>
       <c r="L506" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D506-1)/Inputs!$B$12,0))</f>
@@ -31286,7 +31283,7 @@
         <v>5</v>
       </c>
       <c r="S506" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31318,10 +31315,10 @@
         <v>794</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="K507" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="L507" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D507-1)/Inputs!$B$12,0))</f>
@@ -31340,7 +31337,7 @@
         <v>0.01</v>
       </c>
       <c r="S507" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31372,10 +31369,10 @@
         <v>800</v>
       </c>
       <c r="J508" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="K508" s="5" t="s">
         <v>849</v>
-      </c>
-      <c r="K508" s="5" t="s">
-        <v>850</v>
       </c>
       <c r="L508" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D508-1)/Inputs!$B$12,0))</f>
@@ -31394,7 +31391,7 @@
         <v>1</v>
       </c>
       <c r="S508" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31426,10 +31423,10 @@
         <v>355</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K509" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L509" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D509-1)/Inputs!$B$12,0))</f>
@@ -31448,7 +31445,7 @@
         <v>0.1</v>
       </c>
       <c r="S509" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31480,10 +31477,10 @@
         <v>812</v>
       </c>
       <c r="J510" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="K510" s="5" t="s">
         <v>852</v>
-      </c>
-      <c r="K510" s="5" t="s">
-        <v>853</v>
       </c>
       <c r="L510" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D510-1)/Inputs!$B$12,0))</f>
@@ -31502,7 +31499,7 @@
         <v>0.1</v>
       </c>
       <c r="S510" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31525,17 +31522,17 @@
         <v>91</v>
       </c>
       <c r="G511" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="H511" s="7" t="s">
         <v>854</v>
-      </c>
-      <c r="H511" s="7" t="s">
-        <v>855</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J511" s="6"/>
       <c r="K511" s="7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="L511" s="6" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D511-1)/Inputs!$B$12*3.66,0))</f>
@@ -31548,7 +31545,7 @@
       </c>
       <c r="P511" s="7"/>
       <c r="Q511" s="6" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="R511" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31584,13 +31581,13 @@
         <v>764</v>
       </c>
       <c r="I512" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="J512" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="J512" s="2" t="s">
+      <c r="K512" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="K512" s="3" t="s">
-        <v>859</v>
       </c>
       <c r="L512" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D512-1)/Inputs!$B$12,0))</f>
@@ -31609,7 +31606,7 @@
         <v>50</v>
       </c>
       <c r="S512" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31638,13 +31635,13 @@
         <v>772</v>
       </c>
       <c r="I513" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="J513" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="J513" s="2" t="s">
-        <v>861</v>
-      </c>
       <c r="K513" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="L513" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D513-1)/Inputs!$B$12,0))</f>
@@ -31663,7 +31660,7 @@
         <v>6</v>
       </c>
       <c r="S513" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31695,10 +31692,10 @@
         <v>779</v>
       </c>
       <c r="J514" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="K514" s="3" t="s">
         <v>862</v>
-      </c>
-      <c r="K514" s="3" t="s">
-        <v>863</v>
       </c>
       <c r="L514" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D514-1)/Inputs!$B$12,0))</f>
@@ -31717,7 +31714,7 @@
         <v>0.5</v>
       </c>
       <c r="S514" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31749,10 +31746,10 @@
         <v>779</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K515" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="L515" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D515-1)/Inputs!$B$12,0))</f>
@@ -31771,7 +31768,7 @@
         <v>0.5</v>
       </c>
       <c r="S515" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31803,10 +31800,10 @@
         <v>787</v>
       </c>
       <c r="J516" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="K516" s="3" t="s">
         <v>865</v>
-      </c>
-      <c r="K516" s="3" t="s">
-        <v>866</v>
       </c>
       <c r="L516" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D516-1)/Inputs!$B$12,0))</f>
@@ -31825,7 +31822,7 @@
         <v>5</v>
       </c>
       <c r="S516" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31857,10 +31854,10 @@
         <v>794</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K517" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="L517" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D517-1)/Inputs!$B$12,0))</f>
@@ -31879,7 +31876,7 @@
         <v>0.01</v>
       </c>
       <c r="S517" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31911,10 +31908,10 @@
         <v>800</v>
       </c>
       <c r="J518" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="K518" s="5" t="s">
         <v>868</v>
-      </c>
-      <c r="K518" s="5" t="s">
-        <v>869</v>
       </c>
       <c r="L518" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D518-1)/Inputs!$B$12,0))</f>
@@ -31933,7 +31930,7 @@
         <v>1</v>
       </c>
       <c r="S518" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31965,10 +31962,10 @@
         <v>355</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K519" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="L519" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D519-1)/Inputs!$B$12,0))</f>
@@ -31987,7 +31984,7 @@
         <v>0.1</v>
       </c>
       <c r="S519" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32019,10 +32016,10 @@
         <v>812</v>
       </c>
       <c r="J520" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="K520" s="5" t="s">
         <v>871</v>
-      </c>
-      <c r="K520" s="5" t="s">
-        <v>872</v>
       </c>
       <c r="L520" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D520-1)/Inputs!$B$12,0))</f>
@@ -32041,7 +32038,7 @@
         <v>0.1</v>
       </c>
       <c r="S520" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32064,17 +32061,17 @@
         <v>91</v>
       </c>
       <c r="G521" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="H521" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="H521" s="7" t="s">
-        <v>874</v>
       </c>
       <c r="I521" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J521" s="6"/>
       <c r="K521" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="L521" s="6" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D521-1)/Inputs!$B$12*3.66,0))</f>
@@ -32087,7 +32084,7 @@
       </c>
       <c r="P521" s="7"/>
       <c r="Q521" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="R521" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32123,13 +32120,13 @@
         <v>764</v>
       </c>
       <c r="I522" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="J522" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="J522" s="2" t="s">
+      <c r="K522" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="K522" s="3" t="s">
-        <v>878</v>
       </c>
       <c r="L522" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D522-1)/Inputs!$B$12,0))</f>
@@ -32148,7 +32145,7 @@
         <v>62</v>
       </c>
       <c r="S522" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32177,13 +32174,13 @@
         <v>772</v>
       </c>
       <c r="I523" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="J523" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="J523" s="2" t="s">
-        <v>880</v>
-      </c>
       <c r="K523" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="L523" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D523-1)/Inputs!$B$12,0))</f>
@@ -32202,7 +32199,7 @@
         <v>7</v>
       </c>
       <c r="S523" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32234,10 +32231,10 @@
         <v>779</v>
       </c>
       <c r="J524" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="K524" s="3" t="s">
         <v>881</v>
-      </c>
-      <c r="K524" s="3" t="s">
-        <v>882</v>
       </c>
       <c r="L524" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D524-1)/Inputs!$B$12,0))</f>
@@ -32256,7 +32253,7 @@
         <v>0.5</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32288,10 +32285,10 @@
         <v>779</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="L525" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D525-1)/Inputs!$B$12,0))</f>
@@ -32310,7 +32307,7 @@
         <v>0.5</v>
       </c>
       <c r="S525" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32342,10 +32339,10 @@
         <v>787</v>
       </c>
       <c r="J526" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="K526" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="K526" s="3" t="s">
-        <v>885</v>
       </c>
       <c r="L526" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D526-1)/Inputs!$B$12,0))</f>
@@ -32364,7 +32361,7 @@
         <v>5</v>
       </c>
       <c r="S526" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32396,10 +32393,10 @@
         <v>794</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K527" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="L527" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D527-1)/Inputs!$B$12,0))</f>
@@ -32418,7 +32415,7 @@
         <v>0.01</v>
       </c>
       <c r="S527" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32450,10 +32447,10 @@
         <v>800</v>
       </c>
       <c r="J528" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="K528" s="5" t="s">
         <v>887</v>
-      </c>
-      <c r="K528" s="5" t="s">
-        <v>888</v>
       </c>
       <c r="L528" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D528-1)/Inputs!$B$12,0))</f>
@@ -32472,7 +32469,7 @@
         <v>1</v>
       </c>
       <c r="S528" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32504,10 +32501,10 @@
         <v>355</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="K529" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="L529" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D529-1)/Inputs!$B$12,0))</f>
@@ -32526,7 +32523,7 @@
         <v>0.1</v>
       </c>
       <c r="S529" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32558,10 +32555,10 @@
         <v>812</v>
       </c>
       <c r="J530" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="K530" s="5" t="s">
         <v>890</v>
-      </c>
-      <c r="K530" s="5" t="s">
-        <v>891</v>
       </c>
       <c r="L530" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D530-1)/Inputs!$B$12,0))</f>
@@ -32580,7 +32577,7 @@
         <v>0.1</v>
       </c>
       <c r="S530" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32603,17 +32600,17 @@
         <v>91</v>
       </c>
       <c r="G531" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="H531" s="7" t="s">
         <v>892</v>
-      </c>
-      <c r="H531" s="7" t="s">
-        <v>893</v>
       </c>
       <c r="I531" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J531" s="6"/>
       <c r="K531" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="L531" s="6" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D531-1)/Inputs!$B$12*3.66,0))</f>
@@ -32626,7 +32623,7 @@
       </c>
       <c r="P531" s="7"/>
       <c r="Q531" s="6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R531" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32662,13 +32659,13 @@
         <v>764</v>
       </c>
       <c r="I532" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="J532" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="J532" s="2" t="s">
+      <c r="K532" s="3" t="s">
         <v>896</v>
-      </c>
-      <c r="K532" s="3" t="s">
-        <v>897</v>
       </c>
       <c r="L532" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D532-1)/Inputs!$B$12,0))</f>
@@ -32687,7 +32684,7 @@
         <v>100</v>
       </c>
       <c r="S532" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32716,13 +32713,13 @@
         <v>772</v>
       </c>
       <c r="I533" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="J533" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="J533" s="2" t="s">
-        <v>899</v>
-      </c>
       <c r="K533" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L533" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D533-1)/Inputs!$B$12,0))</f>
@@ -32741,7 +32738,7 @@
         <v>12</v>
       </c>
       <c r="S533" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32773,10 +32770,10 @@
         <v>779</v>
       </c>
       <c r="J534" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="K534" s="3" t="s">
         <v>900</v>
-      </c>
-      <c r="K534" s="3" t="s">
-        <v>901</v>
       </c>
       <c r="L534" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D534-1)/Inputs!$B$12,0))</f>
@@ -32795,7 +32792,7 @@
         <v>0.5</v>
       </c>
       <c r="S534" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32827,10 +32824,10 @@
         <v>779</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="K535" s="3" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="L535" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D535-1)/Inputs!$B$12,0))</f>
@@ -32849,7 +32846,7 @@
         <v>0.5</v>
       </c>
       <c r="S535" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32881,10 +32878,10 @@
         <v>787</v>
       </c>
       <c r="J536" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="K536" s="3" t="s">
         <v>903</v>
-      </c>
-      <c r="K536" s="3" t="s">
-        <v>904</v>
       </c>
       <c r="L536" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D536-1)/Inputs!$B$12,0))</f>
@@ -32903,7 +32900,7 @@
         <v>5</v>
       </c>
       <c r="S536" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32935,10 +32932,10 @@
         <v>794</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="K537" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L537" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D537-1)/Inputs!$B$12,0))</f>
@@ -32957,7 +32954,7 @@
         <v>0.01</v>
       </c>
       <c r="S537" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32989,10 +32986,10 @@
         <v>800</v>
       </c>
       <c r="J538" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="K538" s="5" t="s">
         <v>906</v>
-      </c>
-      <c r="K538" s="5" t="s">
-        <v>907</v>
       </c>
       <c r="L538" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D538-1)/Inputs!$B$12,0))</f>
@@ -33011,7 +33008,7 @@
         <v>1</v>
       </c>
       <c r="S538" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33043,10 +33040,10 @@
         <v>355</v>
       </c>
       <c r="J539" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="K539" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L539" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D539-1)/Inputs!$B$12,0))</f>
@@ -33065,7 +33062,7 @@
         <v>0.1</v>
       </c>
       <c r="S539" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33097,10 +33094,10 @@
         <v>812</v>
       </c>
       <c r="J540" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="K540" s="5" t="s">
         <v>909</v>
-      </c>
-      <c r="K540" s="5" t="s">
-        <v>910</v>
       </c>
       <c r="L540" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D540-1)/Inputs!$B$12,0))</f>
@@ -33119,7 +33116,7 @@
         <v>0.1</v>
       </c>
       <c r="S540" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33142,17 +33139,17 @@
         <v>91</v>
       </c>
       <c r="G541" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="H541" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="H541" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="I541" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J541" s="6"/>
       <c r="K541" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L541" s="6" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D541-1)/Inputs!$B$12*3.66,0))</f>
@@ -33165,7 +33162,7 @@
       </c>
       <c r="P541" s="7"/>
       <c r="Q541" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="R541" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -33204,12 +33201,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>2</v>
@@ -33217,7 +33214,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.1</v>
@@ -33225,7 +33222,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1.15</v>
@@ -33233,7 +33230,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1.25</v>
@@ -33241,7 +33238,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2</v>
@@ -33249,7 +33246,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>10</v>
@@ -33257,7 +33254,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1.5</v>
@@ -33265,7 +33262,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">(B6^10-1)/(B6-1)</f>
@@ -33277,13 +33274,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>923</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="13" t="s">
         <v>924</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33291,13 +33288,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>570</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33305,13 +33302,13 @@
         <v>331</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>930</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33319,13 +33316,13 @@
         <v>413</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33333,13 +33330,13 @@
         <v>493</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>210</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33347,13 +33344,13 @@
         <v>562</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>330</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33361,13 +33358,13 @@
         <v>642</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>4500</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33375,13 +33372,13 @@
         <v>712</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>420</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33389,13 +33386,13 @@
         <v>768</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>82</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33403,28 +33400,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
   </sheetData>
@@ -33451,7 +33448,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33459,22 +33456,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33482,22 +33479,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33505,17 +33502,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33523,22 +33520,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33546,22 +33543,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33569,22 +33566,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33592,37 +33589,37 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33630,42 +33627,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33673,32 +33670,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33706,32 +33703,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33739,27 +33736,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33767,32 +33764,32 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33800,22 +33797,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33823,47 +33820,47 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33871,22 +33868,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33894,22 +33891,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33917,42 +33914,42 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33960,42 +33957,42 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34003,17 +34000,17 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
   </sheetData>
@@ -34041,12 +34038,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B3" s="17" t="n">
         <v>100</v>
@@ -34054,7 +34051,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>5</v>
@@ -34062,7 +34059,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>100</v>
@@ -34073,25 +34070,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>1053</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="D7" s="18" t="s">
         <v>1054</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>1055</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>1056</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="G7" s="18" t="s">
         <v>1057</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>1058</v>
-      </c>
       <c r="H7" s="18" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34276,7 +34273,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>99</v>
@@ -34306,27 +34303,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>0.05</v>
@@ -34334,7 +34331,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>0.01</v>
@@ -34342,7 +34339,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>12.5</v>
@@ -34350,7 +34347,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>6.25</v>
@@ -34361,22 +34358,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="18" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>1068</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="D26" s="18" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>1069</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E26" s="18" t="s">
+      <c r="F26" s="18" t="s">
         <v>1070</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="G26" s="18" t="s">
         <v>1071</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34555,12 +34552,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
   </sheetData>
@@ -34597,16 +34594,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>1075</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>1076</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35724,31 +35721,31 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>1078</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>1079</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>1080</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>1081</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>1082</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>1083</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>1084</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>1085</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35756,10 +35753,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>1087</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>1088</v>
       </c>
       <c r="D2" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35790,10 +35787,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>1089</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>1090</v>
       </c>
       <c r="D3" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35824,10 +35821,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>1091</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>1092</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35858,10 +35855,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>1093</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>1094</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35892,7 +35889,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>490</v>
@@ -35926,10 +35923,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35960,10 +35957,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35994,10 +35991,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36028,10 +36025,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36062,7 +36059,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>490</v>
@@ -36096,10 +36093,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36130,10 +36127,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36164,10 +36161,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36198,10 +36195,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36232,7 +36229,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>490</v>
@@ -36266,10 +36263,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36300,10 +36297,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36334,10 +36331,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36368,10 +36365,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36402,7 +36399,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>490</v>
@@ -36436,10 +36433,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36470,10 +36467,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36504,10 +36501,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36538,10 +36535,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36572,7 +36569,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>490</v>
@@ -36606,10 +36603,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36640,10 +36637,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36674,10 +36671,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36708,10 +36705,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36742,7 +36739,7 @@
         <v>6</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>490</v>
@@ -36802,16 +36799,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>1121</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>1122</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>1123</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36969,7 +36966,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>90</v>

--- a/tools/upgrades/idleos_upgrades.xlsx
+++ b/tools/upgrades/idleos_upgrades.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6774" uniqueCount="1140">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -1966,12 +1966,27 @@
     <t xml:space="preserve">Decode cycle speed</t>
   </si>
   <si>
-    <t xml:space="preserve">Each process's efficiency x(1 + bonus): Cache / Deep Scan bonus basics, Skim +50% basics, Intel finds, Salvage doubles; +20% of its own at max</t>
+    <t xml:space="preserve">Bonus basic resources from every cache (Cache and Deep Scan): +2.5% per install, +30% at max (2026-10-30: was +1.67% of each process's own efficiency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+2.5% basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 % bonus basics</t>
   </si>
   <si>
     <t xml:space="preserve">decoding.efficiency</t>
   </si>
   <si>
+    <t xml:space="preserve">0 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus basic resources from every cache, flat (+30% at max)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yield</t>
   </si>
   <si>
@@ -2044,6 +2059,12 @@
     <t xml:space="preserve">Archives (decoded from caches)</t>
   </si>
   <si>
+    <t xml:space="preserve">7.5 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">20 % more basics</t>
   </si>
   <si>
@@ -2068,6 +2089,12 @@
     <t xml:space="preserve">Metadata (decoded from caches)</t>
   </si>
   <si>
+    <t xml:space="preserve">12.5 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">30 % more basics</t>
   </si>
   <si>
@@ -2092,6 +2119,12 @@
     <t xml:space="preserve">Cookies (decoded from caches)</t>
   </si>
   <si>
+    <t xml:space="preserve">17.5 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">40 % more basics</t>
   </si>
   <si>
@@ -2116,6 +2149,12 @@
     <t xml:space="preserve">Repositories (decoded from caches)</t>
   </si>
   <si>
+    <t xml:space="preserve">22.5 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">50 % more basics</t>
   </si>
   <si>
@@ -2137,6 +2176,12 @@
     <t xml:space="preserve">Databases (decoded from caches)</t>
   </si>
   <si>
+    <t xml:space="preserve">27.5 % bonus basics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 % bonus basics</t>
+  </si>
+  <si>
     <t xml:space="preserve">60 % more basics</t>
   </si>
   <si>
@@ -2536,6 +2581,60 @@
     <t xml:space="preserve">Partner cache</t>
   </si>
   <si>
+    <t xml:space="preserve">MAJOR: Win Streak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 5th win in a row of one 'hack &lt;target&gt;=5' (or more) or 'hack &lt;target&gt; -r' run also gives the target's rare item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hacking.win_streak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+25% attack speed, +0.1 heat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receptionist cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 firewall dmg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 /s bandwidth regen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orderly cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 /s bandwidth regen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 max bandwidth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nurse cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 % of max anonymity per spoof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 mod slots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctor cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 % auto-spoof threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 % charge gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chief of medicine cache</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAJOR: Evasion</t>
   </si>
   <si>
@@ -2545,64 +2644,10 @@
     <t xml:space="preserve">hacking.evasion</t>
   </si>
   <si>
-    <t xml:space="preserve">+38 dmg, +0.1 heat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73 dmg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Receptionist cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 firewall dmg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5 /s bandwidth regen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orderly cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 /s bandwidth regen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 max bandwidth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nurse cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 % of max anonymity per spoof</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 mod slots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctor cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 % auto-spoof threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 % charge gain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chief of medicine cache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAJOR: Recycler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50% chance an SQL Injector is not consumed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hacking.recycler</t>
-  </si>
-  <si>
     <t xml:space="preserve">+50 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">123 dmg</t>
+    <t xml:space="preserve">85 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Teller Cache</t>
@@ -2611,7 +2656,7 @@
     <t xml:space="preserve">+6</t>
   </si>
   <si>
-    <t xml:space="preserve">16 firewall dmg</t>
+    <t xml:space="preserve">14 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">4.5 /s bandwidth regen</t>
@@ -2659,7 +2704,7 @@
     <t xml:space="preserve">+62 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">185 dmg</t>
+    <t xml:space="preserve">147 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Secretary cache</t>
@@ -2668,7 +2713,7 @@
     <t xml:space="preserve">+7</t>
   </si>
   <si>
-    <t xml:space="preserve">23 firewall dmg</t>
+    <t xml:space="preserve">21 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">5.5 /s bandwidth regen</t>
@@ -2716,7 +2761,7 @@
     <t xml:space="preserve">+100 dmg, +0.1 heat</t>
   </si>
   <si>
-    <t xml:space="preserve">285 dmg</t>
+    <t xml:space="preserve">247 dmg</t>
   </si>
   <si>
     <t xml:space="preserve">Clerk Cache</t>
@@ -2725,7 +2770,7 @@
     <t xml:space="preserve">+12</t>
   </si>
   <si>
-    <t xml:space="preserve">35 firewall dmg</t>
+    <t xml:space="preserve">33 firewall dmg</t>
   </si>
   <si>
     <t xml:space="preserve">6.5 /s bandwidth regen</t>
@@ -2839,7 +2884,7 @@
     <t xml:space="preserve">Tier mined item from caches</t>
   </si>
   <si>
-    <t xml:space="preserve">Measured 120 caches/h x ~37.5 Logs per Student cache</t>
+    <t xml:space="preserve">2026-10-30: /4 (was 4500, priced Decoding ~8x the other skills; caches no longer guarantee basics)</t>
   </si>
   <si>
     <t xml:space="preserve">Tier payload</t>
@@ -2953,7 +2998,7 @@
     <t xml:space="preserve">  • At max: SQL attack heat 0.9 - 0.6 System heat reduction = 0.3 net, the same as an attack makes today.</t>
   </si>
   <si>
-    <t xml:space="preserve">  • Capstones: Second Wind, Evasion, Recycler, Siphon, Dead Man's Switch, Exploit Kit (decided).</t>
+    <t xml:space="preserve">  • Capstones: Second Wind, Win Streak, Evasion, Siphon, Dead Man's Switch, Exploit Kit (2026-10-30: Win Streak replaced Recycler).</t>
   </si>
   <si>
     <t xml:space="preserve">  • Unused alternates: Multi-Thread, Chain Breach, Overkill Carry.</t>
@@ -23506,7 +23551,7 @@
       </c>
       <c r="L362" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B362-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D362-1)/Inputs!$B$12,0))</f>
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="M362" s="2"/>
       <c r="N362" s="2"/>
@@ -23560,7 +23605,7 @@
       </c>
       <c r="L363" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B363-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D363-1)/Inputs!$B$12,0))</f>
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="M363" s="2"/>
       <c r="N363" s="2"/>
@@ -23614,7 +23659,7 @@
       </c>
       <c r="L364" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B364-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D364-1)/Inputs!$B$12,0))</f>
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="M364" s="2"/>
       <c r="N364" s="2"/>
@@ -23658,17 +23703,17 @@
         <v>645</v>
       </c>
       <c r="I365" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J365" s="2" t="s">
-        <v>567</v>
+        <v>647</v>
       </c>
       <c r="K365" s="3" t="s">
         <v>641</v>
       </c>
       <c r="L365" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B365-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D365-1)/Inputs!$B$12,0))</f>
-        <v>253</v>
+        <v>63</v>
       </c>
       <c r="M365" s="2"/>
       <c r="N365" s="2"/>
@@ -23677,13 +23722,13 @@
       </c>
       <c r="P365" s="3"/>
       <c r="Q365" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R365" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S365" s="2" t="s">
-        <v>569</v>
+        <v>649</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23709,20 +23754,20 @@
         <v>232</v>
       </c>
       <c r="H366" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I366" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J366" s="2" t="s">
-        <v>571</v>
+        <v>651</v>
       </c>
       <c r="K366" s="3" t="s">
         <v>641</v>
       </c>
       <c r="L366" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B366-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D366-1)/Inputs!$B$12,0))</f>
-        <v>291</v>
+        <v>73</v>
       </c>
       <c r="M366" s="2"/>
       <c r="N366" s="2"/>
@@ -23731,13 +23776,13 @@
       </c>
       <c r="P366" s="3"/>
       <c r="Q366" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R366" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S366" s="2" t="s">
-        <v>567</v>
+        <v>647</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23760,23 +23805,23 @@
         <v>22</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H367" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I367" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J367" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="K367" s="3" t="s">
         <v>641</v>
       </c>
       <c r="L367" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B367-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D367-1)/Inputs!$B$12,0))</f>
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="M367" s="2"/>
       <c r="N367" s="2"/>
@@ -23785,13 +23830,13 @@
       </c>
       <c r="P367" s="3"/>
       <c r="Q367" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R367" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S367" s="2" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23814,23 +23859,23 @@
         <v>55</v>
       </c>
       <c r="G368" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H368" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I368" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="K368" s="5" t="s">
         <v>641</v>
       </c>
       <c r="L368" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B368-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D368-1)/Inputs!$B$12,0))</f>
-        <v>384</v>
+        <v>96</v>
       </c>
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
@@ -23839,13 +23884,13 @@
       </c>
       <c r="P368" s="5"/>
       <c r="Q368" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R368" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S368" s="4" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23868,23 +23913,23 @@
         <v>55</v>
       </c>
       <c r="G369" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H369" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I369" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="K369" s="5" t="s">
         <v>641</v>
       </c>
       <c r="L369" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B369-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D369-1)/Inputs!$B$12,0))</f>
-        <v>442</v>
+        <v>111</v>
       </c>
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
@@ -23893,13 +23938,13 @@
       </c>
       <c r="P369" s="5"/>
       <c r="Q369" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R369" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S369" s="4" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23922,23 +23967,23 @@
         <v>55</v>
       </c>
       <c r="G370" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H370" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I370" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="K370" s="5" t="s">
         <v>641</v>
       </c>
       <c r="L370" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B370-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D370-1)/Inputs!$B$12,0))</f>
-        <v>508</v>
+        <v>127</v>
       </c>
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
@@ -23947,13 +23992,13 @@
       </c>
       <c r="P370" s="5"/>
       <c r="Q370" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R370" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S370" s="4" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23990,7 +24035,7 @@
       </c>
       <c r="L371" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B371-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D371-1)/Inputs!$B$12*3.66,0))</f>
-        <v>2140</v>
+        <v>535</v>
       </c>
       <c r="M371" s="6"/>
       <c r="N371" s="6"/>
@@ -23999,7 +24044,7 @@
       </c>
       <c r="P371" s="7"/>
       <c r="Q371" s="6" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="R371" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24041,11 +24086,11 @@
         <v>264</v>
       </c>
       <c r="K372" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L372" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B372-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D372-1)/Inputs!$B$12,0))</f>
-        <v>427</v>
+        <v>107</v>
       </c>
       <c r="M372" s="2"/>
       <c r="N372" s="2"/>
@@ -24095,11 +24140,11 @@
         <v>265</v>
       </c>
       <c r="K373" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L373" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B373-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D373-1)/Inputs!$B$12,0))</f>
-        <v>491</v>
+        <v>123</v>
       </c>
       <c r="M373" s="2"/>
       <c r="N373" s="2"/>
@@ -24149,11 +24194,11 @@
         <v>266</v>
       </c>
       <c r="K374" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L374" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B374-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D374-1)/Inputs!$B$12,0))</f>
-        <v>564</v>
+        <v>141</v>
       </c>
       <c r="M374" s="2"/>
       <c r="N374" s="2"/>
@@ -24197,17 +24242,17 @@
         <v>645</v>
       </c>
       <c r="I375" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J375" s="2" t="s">
-        <v>595</v>
+        <v>676</v>
       </c>
       <c r="K375" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L375" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B375-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D375-1)/Inputs!$B$12,0))</f>
-        <v>649</v>
+        <v>162</v>
       </c>
       <c r="M375" s="2"/>
       <c r="N375" s="2"/>
@@ -24216,13 +24261,13 @@
       </c>
       <c r="P375" s="3"/>
       <c r="Q375" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R375" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S375" s="2" t="s">
-        <v>571</v>
+        <v>651</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24248,20 +24293,20 @@
         <v>232</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I376" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J376" s="2" t="s">
-        <v>596</v>
+        <v>677</v>
       </c>
       <c r="K376" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L376" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B376-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D376-1)/Inputs!$B$12,0))</f>
-        <v>746</v>
+        <v>187</v>
       </c>
       <c r="M376" s="2"/>
       <c r="N376" s="2"/>
@@ -24270,13 +24315,13 @@
       </c>
       <c r="P376" s="3"/>
       <c r="Q376" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R376" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S376" s="2" t="s">
-        <v>595</v>
+        <v>676</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24299,23 +24344,23 @@
         <v>22</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H377" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I377" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J377" s="2" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="K377" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L377" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B377-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D377-1)/Inputs!$B$12,0))</f>
-        <v>858</v>
+        <v>215</v>
       </c>
       <c r="M377" s="2"/>
       <c r="N377" s="2"/>
@@ -24324,13 +24369,13 @@
       </c>
       <c r="P377" s="3"/>
       <c r="Q377" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R377" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S377" s="2" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24353,23 +24398,23 @@
         <v>55</v>
       </c>
       <c r="G378" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H378" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I378" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="K378" s="5" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L378" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B378-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D378-1)/Inputs!$B$12,0))</f>
-        <v>987</v>
+        <v>247</v>
       </c>
       <c r="M378" s="4"/>
       <c r="N378" s="4"/>
@@ -24378,13 +24423,13 @@
       </c>
       <c r="P378" s="5"/>
       <c r="Q378" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R378" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S378" s="4" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24407,23 +24452,23 @@
         <v>55</v>
       </c>
       <c r="G379" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H379" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I379" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="K379" s="5" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L379" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B379-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D379-1)/Inputs!$B$12,0))</f>
-        <v>1135</v>
+        <v>284</v>
       </c>
       <c r="M379" s="4"/>
       <c r="N379" s="4"/>
@@ -24432,13 +24477,13 @@
       </c>
       <c r="P379" s="5"/>
       <c r="Q379" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R379" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S379" s="4" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24461,23 +24506,23 @@
         <v>55</v>
       </c>
       <c r="G380" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H380" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I380" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="K380" s="5" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L380" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B380-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D380-1)/Inputs!$B$12,0))</f>
-        <v>1305</v>
+        <v>326</v>
       </c>
       <c r="M380" s="4"/>
       <c r="N380" s="4"/>
@@ -24486,13 +24531,13 @@
       </c>
       <c r="P380" s="5"/>
       <c r="Q380" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R380" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S380" s="4" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24515,21 +24560,21 @@
         <v>91</v>
       </c>
       <c r="G381" s="6" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="I381" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J381" s="6"/>
       <c r="K381" s="7" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="L381" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B381-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D381-1)/Inputs!$B$12*3.66,0))</f>
-        <v>5493</v>
+        <v>1373</v>
       </c>
       <c r="M381" s="6"/>
       <c r="N381" s="6"/>
@@ -24538,7 +24583,7 @@
       </c>
       <c r="P381" s="7"/>
       <c r="Q381" s="6" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="R381" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -24580,11 +24625,11 @@
         <v>277</v>
       </c>
       <c r="K382" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L382" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B382-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D382-1)/Inputs!$B$12,0))</f>
-        <v>570</v>
+        <v>142</v>
       </c>
       <c r="M382" s="2"/>
       <c r="N382" s="2"/>
@@ -24634,11 +24679,11 @@
         <v>278</v>
       </c>
       <c r="K383" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L383" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B383-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D383-1)/Inputs!$B$12,0))</f>
-        <v>655</v>
+        <v>164</v>
       </c>
       <c r="M383" s="2"/>
       <c r="N383" s="2"/>
@@ -24688,11 +24733,11 @@
         <v>279</v>
       </c>
       <c r="K384" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L384" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B384-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D384-1)/Inputs!$B$12,0))</f>
-        <v>754</v>
+        <v>188</v>
       </c>
       <c r="M384" s="2"/>
       <c r="N384" s="2"/>
@@ -24736,17 +24781,17 @@
         <v>645</v>
       </c>
       <c r="I385" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J385" s="2" t="s">
-        <v>604</v>
+        <v>686</v>
       </c>
       <c r="K385" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L385" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B385-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D385-1)/Inputs!$B$12,0))</f>
-        <v>867</v>
+        <v>217</v>
       </c>
       <c r="M385" s="2"/>
       <c r="N385" s="2"/>
@@ -24755,13 +24800,13 @@
       </c>
       <c r="P385" s="3"/>
       <c r="Q385" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R385" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S385" s="2" t="s">
-        <v>596</v>
+        <v>677</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24787,20 +24832,20 @@
         <v>232</v>
       </c>
       <c r="H386" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I386" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J386" s="2" t="s">
-        <v>605</v>
+        <v>687</v>
       </c>
       <c r="K386" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L386" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B386-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D386-1)/Inputs!$B$12,0))</f>
-        <v>997</v>
+        <v>249</v>
       </c>
       <c r="M386" s="2"/>
       <c r="N386" s="2"/>
@@ -24809,13 +24854,13 @@
       </c>
       <c r="P386" s="3"/>
       <c r="Q386" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R386" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S386" s="2" t="s">
-        <v>604</v>
+        <v>686</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24838,23 +24883,23 @@
         <v>22</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H387" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I387" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J387" s="2" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
       <c r="K387" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L387" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B387-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D387-1)/Inputs!$B$12,0))</f>
-        <v>1146</v>
+        <v>287</v>
       </c>
       <c r="M387" s="2"/>
       <c r="N387" s="2"/>
@@ -24863,13 +24908,13 @@
       </c>
       <c r="P387" s="3"/>
       <c r="Q387" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R387" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S387" s="2" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24892,23 +24937,23 @@
         <v>55</v>
       </c>
       <c r="G388" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H388" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I388" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
       <c r="K388" s="5" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L388" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B388-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D388-1)/Inputs!$B$12,0))</f>
-        <v>1318</v>
+        <v>330</v>
       </c>
       <c r="M388" s="4"/>
       <c r="N388" s="4"/>
@@ -24917,13 +24962,13 @@
       </c>
       <c r="P388" s="5"/>
       <c r="Q388" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R388" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S388" s="4" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24946,23 +24991,23 @@
         <v>55</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H389" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I389" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
       <c r="K389" s="5" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L389" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B389-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D389-1)/Inputs!$B$12,0))</f>
-        <v>1516</v>
+        <v>379</v>
       </c>
       <c r="M389" s="4"/>
       <c r="N389" s="4"/>
@@ -24971,13 +25016,13 @@
       </c>
       <c r="P389" s="5"/>
       <c r="Q389" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R389" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S389" s="4" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25000,23 +25045,23 @@
         <v>55</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H390" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I390" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
       <c r="K390" s="5" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L390" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B390-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D390-1)/Inputs!$B$12,0))</f>
-        <v>1743</v>
+        <v>436</v>
       </c>
       <c r="M390" s="4"/>
       <c r="N390" s="4"/>
@@ -25025,13 +25070,13 @@
       </c>
       <c r="P390" s="5"/>
       <c r="Q390" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R390" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S390" s="4" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25054,21 +25099,21 @@
         <v>91</v>
       </c>
       <c r="G391" s="6" t="s">
-        <v>683</v>
+        <v>692</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>684</v>
+        <v>693</v>
       </c>
       <c r="I391" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J391" s="6"/>
       <c r="K391" s="7" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L391" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B391-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D391-1)/Inputs!$B$12*3.66,0))</f>
-        <v>7337</v>
+        <v>1834</v>
       </c>
       <c r="M391" s="6"/>
       <c r="N391" s="6"/>
@@ -25077,7 +25122,7 @@
       </c>
       <c r="P391" s="7"/>
       <c r="Q391" s="6" t="s">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="R391" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25119,11 +25164,11 @@
         <v>290</v>
       </c>
       <c r="K392" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L392" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B392-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D392-1)/Inputs!$B$12,0))</f>
-        <v>553</v>
+        <v>138</v>
       </c>
       <c r="M392" s="2"/>
       <c r="N392" s="2"/>
@@ -25173,11 +25218,11 @@
         <v>291</v>
       </c>
       <c r="K393" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L393" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B393-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D393-1)/Inputs!$B$12,0))</f>
-        <v>636</v>
+        <v>159</v>
       </c>
       <c r="M393" s="2"/>
       <c r="N393" s="2"/>
@@ -25227,11 +25272,11 @@
         <v>292</v>
       </c>
       <c r="K394" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L394" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B394-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D394-1)/Inputs!$B$12,0))</f>
-        <v>731</v>
+        <v>183</v>
       </c>
       <c r="M394" s="2"/>
       <c r="N394" s="2"/>
@@ -25275,17 +25320,17 @@
         <v>645</v>
       </c>
       <c r="I395" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J395" s="2" t="s">
-        <v>613</v>
+        <v>696</v>
       </c>
       <c r="K395" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L395" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B395-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D395-1)/Inputs!$B$12,0))</f>
-        <v>841</v>
+        <v>210</v>
       </c>
       <c r="M395" s="2"/>
       <c r="N395" s="2"/>
@@ -25294,13 +25339,13 @@
       </c>
       <c r="P395" s="3"/>
       <c r="Q395" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R395" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S395" s="2" t="s">
-        <v>605</v>
+        <v>687</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25326,20 +25371,20 @@
         <v>232</v>
       </c>
       <c r="H396" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I396" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J396" s="2" t="s">
-        <v>614</v>
+        <v>697</v>
       </c>
       <c r="K396" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L396" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B396-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D396-1)/Inputs!$B$12,0))</f>
-        <v>967</v>
+        <v>242</v>
       </c>
       <c r="M396" s="2"/>
       <c r="N396" s="2"/>
@@ -25348,13 +25393,13 @@
       </c>
       <c r="P396" s="3"/>
       <c r="Q396" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R396" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S396" s="2" t="s">
-        <v>613</v>
+        <v>696</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25377,23 +25422,23 @@
         <v>22</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H397" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I397" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J397" s="2" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="K397" s="3" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L397" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B397-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D397-1)/Inputs!$B$12,0))</f>
-        <v>1113</v>
+        <v>278</v>
       </c>
       <c r="M397" s="2"/>
       <c r="N397" s="2"/>
@@ -25402,13 +25447,13 @@
       </c>
       <c r="P397" s="3"/>
       <c r="Q397" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R397" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S397" s="2" t="s">
-        <v>679</v>
+        <v>688</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25431,23 +25476,23 @@
         <v>55</v>
       </c>
       <c r="G398" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H398" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I398" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="K398" s="5" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L398" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B398-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D398-1)/Inputs!$B$12,0))</f>
-        <v>1279</v>
+        <v>320</v>
       </c>
       <c r="M398" s="4"/>
       <c r="N398" s="4"/>
@@ -25456,13 +25501,13 @@
       </c>
       <c r="P398" s="5"/>
       <c r="Q398" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R398" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S398" s="4" t="s">
-        <v>680</v>
+        <v>689</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25485,23 +25530,23 @@
         <v>55</v>
       </c>
       <c r="G399" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H399" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I399" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="K399" s="5" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L399" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B399-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D399-1)/Inputs!$B$12,0))</f>
-        <v>1471</v>
+        <v>368</v>
       </c>
       <c r="M399" s="4"/>
       <c r="N399" s="4"/>
@@ -25510,13 +25555,13 @@
       </c>
       <c r="P399" s="5"/>
       <c r="Q399" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R399" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S399" s="4" t="s">
-        <v>681</v>
+        <v>690</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25539,23 +25584,23 @@
         <v>55</v>
       </c>
       <c r="G400" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H400" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I400" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="K400" s="5" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L400" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B400-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D400-1)/Inputs!$B$12,0))</f>
-        <v>1692</v>
+        <v>423</v>
       </c>
       <c r="M400" s="4"/>
       <c r="N400" s="4"/>
@@ -25564,13 +25609,13 @@
       </c>
       <c r="P400" s="5"/>
       <c r="Q400" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R400" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S400" s="4" t="s">
-        <v>682</v>
+        <v>691</v>
       </c>
     </row>
     <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25593,21 +25638,21 @@
         <v>91</v>
       </c>
       <c r="G401" s="6" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="I401" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J401" s="6"/>
       <c r="K401" s="7" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
       <c r="L401" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B401-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D401-1)/Inputs!$B$12*3.66,0))</f>
-        <v>7122</v>
+        <v>1780</v>
       </c>
       <c r="M401" s="6"/>
       <c r="N401" s="6"/>
@@ -25616,7 +25661,7 @@
       </c>
       <c r="P401" s="7"/>
       <c r="Q401" s="6" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="R401" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -25658,11 +25703,11 @@
         <v>303</v>
       </c>
       <c r="K402" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L402" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B402-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D402-1)/Inputs!$B$12,0))</f>
-        <v>608</v>
+        <v>152</v>
       </c>
       <c r="M402" s="2"/>
       <c r="N402" s="2"/>
@@ -25712,11 +25757,11 @@
         <v>304</v>
       </c>
       <c r="K403" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L403" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B403-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D403-1)/Inputs!$B$12,0))</f>
-        <v>700</v>
+        <v>175</v>
       </c>
       <c r="M403" s="2"/>
       <c r="N403" s="2"/>
@@ -25766,11 +25811,11 @@
         <v>305</v>
       </c>
       <c r="K404" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L404" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B404-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D404-1)/Inputs!$B$12,0))</f>
-        <v>805</v>
+        <v>201</v>
       </c>
       <c r="M404" s="2"/>
       <c r="N404" s="2"/>
@@ -25814,17 +25859,17 @@
         <v>645</v>
       </c>
       <c r="I405" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J405" s="2" t="s">
-        <v>622</v>
+        <v>706</v>
       </c>
       <c r="K405" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L405" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B405-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D405-1)/Inputs!$B$12,0))</f>
-        <v>925</v>
+        <v>231</v>
       </c>
       <c r="M405" s="2"/>
       <c r="N405" s="2"/>
@@ -25833,13 +25878,13 @@
       </c>
       <c r="P405" s="3"/>
       <c r="Q405" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R405" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S405" s="2" t="s">
-        <v>614</v>
+        <v>697</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25865,20 +25910,20 @@
         <v>232</v>
       </c>
       <c r="H406" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I406" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J406" s="2" t="s">
-        <v>623</v>
+        <v>707</v>
       </c>
       <c r="K406" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L406" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B406-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D406-1)/Inputs!$B$12,0))</f>
-        <v>1064</v>
+        <v>266</v>
       </c>
       <c r="M406" s="2"/>
       <c r="N406" s="2"/>
@@ -25887,13 +25932,13 @@
       </c>
       <c r="P406" s="3"/>
       <c r="Q406" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R406" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S406" s="2" t="s">
-        <v>622</v>
+        <v>706</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25916,23 +25961,23 @@
         <v>22</v>
       </c>
       <c r="G407" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H407" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I407" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J407" s="2" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="K407" s="3" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L407" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B407-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D407-1)/Inputs!$B$12,0))</f>
-        <v>1224</v>
+        <v>306</v>
       </c>
       <c r="M407" s="2"/>
       <c r="N407" s="2"/>
@@ -25941,13 +25986,13 @@
       </c>
       <c r="P407" s="3"/>
       <c r="Q407" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R407" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S407" s="2" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25970,23 +26015,23 @@
         <v>55</v>
       </c>
       <c r="G408" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H408" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I408" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="K408" s="5" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L408" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B408-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D408-1)/Inputs!$B$12,0))</f>
-        <v>1407</v>
+        <v>352</v>
       </c>
       <c r="M408" s="4"/>
       <c r="N408" s="4"/>
@@ -25995,13 +26040,13 @@
       </c>
       <c r="P408" s="5"/>
       <c r="Q408" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R408" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S408" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26024,23 +26069,23 @@
         <v>55</v>
       </c>
       <c r="G409" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H409" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I409" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="K409" s="5" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L409" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B409-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D409-1)/Inputs!$B$12,0))</f>
-        <v>1618</v>
+        <v>405</v>
       </c>
       <c r="M409" s="4"/>
       <c r="N409" s="4"/>
@@ -26049,13 +26094,13 @@
       </c>
       <c r="P409" s="5"/>
       <c r="Q409" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R409" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S409" s="4" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26078,23 +26123,23 @@
         <v>55</v>
       </c>
       <c r="G410" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H410" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I410" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="K410" s="5" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L410" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B410-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D410-1)/Inputs!$B$12,0))</f>
-        <v>1861</v>
+        <v>465</v>
       </c>
       <c r="M410" s="4"/>
       <c r="N410" s="4"/>
@@ -26103,13 +26148,13 @@
       </c>
       <c r="P410" s="5"/>
       <c r="Q410" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R410" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S410" s="4" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26135,18 +26180,18 @@
         <v>312</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="I411" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J411" s="6"/>
       <c r="K411" s="7" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="L411" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B411-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D411-1)/Inputs!$B$12*3.66,0))</f>
-        <v>7834</v>
+        <v>1958</v>
       </c>
       <c r="M411" s="6"/>
       <c r="N411" s="6"/>
@@ -26155,7 +26200,7 @@
       </c>
       <c r="P411" s="7"/>
       <c r="Q411" s="6" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="R411" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26197,11 +26242,11 @@
         <v>316</v>
       </c>
       <c r="K412" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L412" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B412-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D412-1)/Inputs!$B$12,0))</f>
-        <v>892</v>
+        <v>223</v>
       </c>
       <c r="M412" s="2"/>
       <c r="N412" s="2"/>
@@ -26251,11 +26296,11 @@
         <v>317</v>
       </c>
       <c r="K413" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L413" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B413-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D413-1)/Inputs!$B$12,0))</f>
-        <v>1026</v>
+        <v>257</v>
       </c>
       <c r="M413" s="2"/>
       <c r="N413" s="2"/>
@@ -26305,11 +26350,11 @@
         <v>318</v>
       </c>
       <c r="K414" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L414" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B414-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D414-1)/Inputs!$B$12,0))</f>
-        <v>1180</v>
+        <v>295</v>
       </c>
       <c r="M414" s="2"/>
       <c r="N414" s="2"/>
@@ -26353,17 +26398,17 @@
         <v>645</v>
       </c>
       <c r="I415" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J415" s="2" t="s">
-        <v>630</v>
+        <v>715</v>
       </c>
       <c r="K415" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L415" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B415-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D415-1)/Inputs!$B$12,0))</f>
-        <v>1357</v>
+        <v>339</v>
       </c>
       <c r="M415" s="2"/>
       <c r="N415" s="2"/>
@@ -26372,13 +26417,13 @@
       </c>
       <c r="P415" s="3"/>
       <c r="Q415" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R415" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S415" s="2" t="s">
-        <v>623</v>
+        <v>707</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26404,20 +26449,20 @@
         <v>232</v>
       </c>
       <c r="H416" s="3" t="s">
-        <v>570</v>
+        <v>650</v>
       </c>
       <c r="I416" s="2" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="J416" s="2" t="s">
-        <v>631</v>
+        <v>716</v>
       </c>
       <c r="K416" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L416" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B416-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D416-1)/Inputs!$B$12,0))</f>
-        <v>1561</v>
+        <v>390</v>
       </c>
       <c r="M416" s="2"/>
       <c r="N416" s="2"/>
@@ -26426,13 +26471,13 @@
       </c>
       <c r="P416" s="3"/>
       <c r="Q416" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="R416" s="2" t="n">
-        <v>0.016667</v>
+        <v>0.025</v>
       </c>
       <c r="S416" s="2" t="s">
-        <v>630</v>
+        <v>715</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26455,23 +26500,23 @@
         <v>22</v>
       </c>
       <c r="G417" s="2" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="H417" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="I417" s="2" t="s">
         <v>355</v>
       </c>
       <c r="J417" s="2" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="K417" s="3" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L417" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B417-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D417-1)/Inputs!$B$12,0))</f>
-        <v>1795</v>
+        <v>449</v>
       </c>
       <c r="M417" s="2"/>
       <c r="N417" s="2"/>
@@ -26480,13 +26525,13 @@
       </c>
       <c r="P417" s="3"/>
       <c r="Q417" s="2" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="R417" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="S417" s="2" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26509,23 +26554,23 @@
         <v>55</v>
       </c>
       <c r="G418" s="4" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H418" s="5" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="I418" s="4" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="K418" s="5" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L418" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B418-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D418-1)/Inputs!$B$12,0))</f>
-        <v>2064</v>
+        <v>516</v>
       </c>
       <c r="M418" s="4"/>
       <c r="N418" s="4"/>
@@ -26534,13 +26579,13 @@
       </c>
       <c r="P418" s="5"/>
       <c r="Q418" s="4" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="R418" s="4" t="n">
         <v>0.0025</v>
       </c>
       <c r="S418" s="4" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26563,23 +26608,23 @@
         <v>55</v>
       </c>
       <c r="G419" s="4" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="H419" s="5" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="I419" s="4" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="K419" s="5" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L419" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B419-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D419-1)/Inputs!$B$12,0))</f>
-        <v>2374</v>
+        <v>593</v>
       </c>
       <c r="M419" s="4"/>
       <c r="N419" s="4"/>
@@ -26588,13 +26633,13 @@
       </c>
       <c r="P419" s="5"/>
       <c r="Q419" s="4" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="R419" s="4" t="n">
         <v>0.02</v>
       </c>
       <c r="S419" s="4" t="s">
-        <v>697</v>
+        <v>710</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26617,23 +26662,23 @@
         <v>55</v>
       </c>
       <c r="G420" s="4" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="H420" s="5" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="I420" s="4" t="s">
         <v>58</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>705</v>
+        <v>720</v>
       </c>
       <c r="K420" s="5" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L420" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B420-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D420-1)/Inputs!$B$12,0))</f>
-        <v>2730</v>
+        <v>682</v>
       </c>
       <c r="M420" s="4"/>
       <c r="N420" s="4"/>
@@ -26642,13 +26687,13 @@
       </c>
       <c r="P420" s="5"/>
       <c r="Q420" s="4" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R420" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S420" s="4" t="s">
-        <v>698</v>
+        <v>711</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26671,21 +26716,21 @@
         <v>91</v>
       </c>
       <c r="G421" s="6" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="I421" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J421" s="6"/>
       <c r="K421" s="7" t="s">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="L421" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B421-1)*INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D421-1)/Inputs!$B$12*3.66,0))</f>
-        <v>11490</v>
+        <v>2872</v>
       </c>
       <c r="M421" s="6"/>
       <c r="N421" s="6"/>
@@ -26694,7 +26739,7 @@
       </c>
       <c r="P421" s="7"/>
       <c r="Q421" s="6" t="s">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="R421" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -26706,7 +26751,7 @@
     </row>
     <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>1</v>
@@ -26727,7 +26772,7 @@
         <v>223</v>
       </c>
       <c r="H422" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I422" s="2" t="s">
         <v>225</v>
@@ -26736,7 +26781,7 @@
         <v>226</v>
       </c>
       <c r="K422" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L422" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B422-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D422-1)/Inputs!$B$12,0))</f>
@@ -26745,11 +26790,11 @@
       <c r="M422" s="2"/>
       <c r="N422" s="2"/>
       <c r="O422" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P422" s="3"/>
       <c r="Q422" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R422" s="2" t="n">
         <v>0.1667</v>
@@ -26760,7 +26805,7 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>1</v>
@@ -26781,7 +26826,7 @@
         <v>223</v>
       </c>
       <c r="H423" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I423" s="2" t="s">
         <v>225</v>
@@ -26790,7 +26835,7 @@
         <v>230</v>
       </c>
       <c r="K423" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L423" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B423-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D423-1)/Inputs!$B$12,0))</f>
@@ -26799,11 +26844,11 @@
       <c r="M423" s="2"/>
       <c r="N423" s="2"/>
       <c r="O423" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P423" s="3"/>
       <c r="Q423" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R423" s="2" t="n">
         <v>0.1667</v>
@@ -26814,7 +26859,7 @@
     </row>
     <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>1</v>
@@ -26835,7 +26880,7 @@
         <v>223</v>
       </c>
       <c r="H424" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I424" s="2" t="s">
         <v>225</v>
@@ -26844,7 +26889,7 @@
         <v>231</v>
       </c>
       <c r="K424" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L424" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B424-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D424-1)/Inputs!$B$12,0))</f>
@@ -26853,11 +26898,11 @@
       <c r="M424" s="2"/>
       <c r="N424" s="2"/>
       <c r="O424" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P424" s="3"/>
       <c r="Q424" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R424" s="2" t="n">
         <v>0.1667</v>
@@ -26868,7 +26913,7 @@
     </row>
     <row r="425" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>1</v>
@@ -26889,7 +26934,7 @@
         <v>232</v>
       </c>
       <c r="H425" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I425" s="2" t="s">
         <v>566</v>
@@ -26898,7 +26943,7 @@
         <v>567</v>
       </c>
       <c r="K425" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L425" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B425-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D425-1)/Inputs!$B$12,0))</f>
@@ -26907,11 +26952,11 @@
       <c r="M425" s="2"/>
       <c r="N425" s="2"/>
       <c r="O425" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P425" s="3"/>
       <c r="Q425" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R425" s="2" t="n">
         <v>0.016667</v>
@@ -26922,7 +26967,7 @@
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>1</v>
@@ -26943,7 +26988,7 @@
         <v>232</v>
       </c>
       <c r="H426" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I426" s="2" t="s">
         <v>566</v>
@@ -26952,7 +26997,7 @@
         <v>571</v>
       </c>
       <c r="K426" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L426" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B426-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D426-1)/Inputs!$B$12,0))</f>
@@ -26961,11 +27006,11 @@
       <c r="M426" s="2"/>
       <c r="N426" s="2"/>
       <c r="O426" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P426" s="3"/>
       <c r="Q426" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R426" s="2" t="n">
         <v>0.016667</v>
@@ -26976,7 +27021,7 @@
     </row>
     <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>1</v>
@@ -26997,7 +27042,7 @@
         <v>422</v>
       </c>
       <c r="H427" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I427" s="2" t="s">
         <v>335</v>
@@ -27006,7 +27051,7 @@
         <v>502</v>
       </c>
       <c r="K427" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L427" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B427-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D427-1)/Inputs!$B$12,0))</f>
@@ -27015,11 +27060,11 @@
       <c r="M427" s="2"/>
       <c r="N427" s="2"/>
       <c r="O427" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P427" s="3"/>
       <c r="Q427" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R427" s="2" t="n">
         <v>0.016667</v>
@@ -27030,7 +27075,7 @@
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>1</v>
@@ -27060,7 +27105,7 @@
         <v>506</v>
       </c>
       <c r="K428" s="3" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L428" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B428-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D428-1)/Inputs!$B$12,0))</f>
@@ -27069,11 +27114,11 @@
       <c r="M428" s="2"/>
       <c r="N428" s="2"/>
       <c r="O428" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P428" s="3"/>
       <c r="Q428" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R428" s="2" t="n">
         <v>0.016667</v>
@@ -27084,7 +27129,7 @@
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B429" s="4" t="n">
         <v>1</v>
@@ -27102,19 +27147,19 @@
         <v>55</v>
       </c>
       <c r="G429" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H429" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I429" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="K429" s="5" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L429" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B429-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D429-1)/Inputs!$B$12,0))</f>
@@ -27123,22 +27168,22 @@
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
       <c r="O429" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P429" s="5"/>
       <c r="Q429" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R429" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S429" s="4" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B430" s="4" t="n">
         <v>1</v>
@@ -27156,19 +27201,19 @@
         <v>55</v>
       </c>
       <c r="G430" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="H430" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="I430" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="J430" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="K430" s="5" t="s">
         <v>726</v>
-      </c>
-      <c r="H430" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="I430" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="J430" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="K430" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="L430" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B430-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D430-1)/Inputs!$B$12,0))</f>
@@ -27177,22 +27222,22 @@
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
       <c r="O430" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P430" s="5"/>
       <c r="Q430" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R430" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S430" s="4" t="s">
-        <v>730</v>
+        <v>745</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B431" s="6" t="n">
         <v>1</v>
@@ -27213,14 +27258,14 @@
         <v>260</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="I431" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J431" s="6"/>
       <c r="K431" s="7" t="s">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="L431" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.3*Inputs!$B$4*Inputs!$B$5^(B431-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D431-1)/Inputs!$B$12*3.66,0))</f>
@@ -27229,11 +27274,11 @@
       <c r="M431" s="6"/>
       <c r="N431" s="6"/>
       <c r="O431" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P431" s="7"/>
       <c r="Q431" s="6" t="s">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="R431" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27245,7 +27290,7 @@
     </row>
     <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>2</v>
@@ -27266,7 +27311,7 @@
         <v>223</v>
       </c>
       <c r="H432" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I432" s="2" t="s">
         <v>263</v>
@@ -27275,7 +27320,7 @@
         <v>264</v>
       </c>
       <c r="K432" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L432" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B432-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D432-1)/Inputs!$B$12,0))</f>
@@ -27284,11 +27329,11 @@
       <c r="M432" s="2"/>
       <c r="N432" s="2"/>
       <c r="O432" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P432" s="3"/>
       <c r="Q432" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R432" s="2" t="n">
         <v>0.25</v>
@@ -27299,7 +27344,7 @@
     </row>
     <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>2</v>
@@ -27320,7 +27365,7 @@
         <v>223</v>
       </c>
       <c r="H433" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I433" s="2" t="s">
         <v>263</v>
@@ -27329,7 +27374,7 @@
         <v>265</v>
       </c>
       <c r="K433" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L433" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B433-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D433-1)/Inputs!$B$12,0))</f>
@@ -27338,11 +27383,11 @@
       <c r="M433" s="2"/>
       <c r="N433" s="2"/>
       <c r="O433" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P433" s="3"/>
       <c r="Q433" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R433" s="2" t="n">
         <v>0.25</v>
@@ -27353,7 +27398,7 @@
     </row>
     <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>2</v>
@@ -27374,7 +27419,7 @@
         <v>223</v>
       </c>
       <c r="H434" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I434" s="2" t="s">
         <v>263</v>
@@ -27383,7 +27428,7 @@
         <v>266</v>
       </c>
       <c r="K434" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L434" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B434-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D434-1)/Inputs!$B$12,0))</f>
@@ -27392,11 +27437,11 @@
       <c r="M434" s="2"/>
       <c r="N434" s="2"/>
       <c r="O434" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P434" s="3"/>
       <c r="Q434" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R434" s="2" t="n">
         <v>0.25</v>
@@ -27407,7 +27452,7 @@
     </row>
     <row r="435" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>2</v>
@@ -27428,7 +27473,7 @@
         <v>232</v>
       </c>
       <c r="H435" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I435" s="2" t="s">
         <v>566</v>
@@ -27437,7 +27482,7 @@
         <v>595</v>
       </c>
       <c r="K435" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L435" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B435-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D435-1)/Inputs!$B$12,0))</f>
@@ -27446,11 +27491,11 @@
       <c r="M435" s="2"/>
       <c r="N435" s="2"/>
       <c r="O435" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P435" s="3"/>
       <c r="Q435" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R435" s="2" t="n">
         <v>0.016667</v>
@@ -27461,7 +27506,7 @@
     </row>
     <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>2</v>
@@ -27482,7 +27527,7 @@
         <v>232</v>
       </c>
       <c r="H436" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I436" s="2" t="s">
         <v>566</v>
@@ -27491,7 +27536,7 @@
         <v>596</v>
       </c>
       <c r="K436" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L436" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B436-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D436-1)/Inputs!$B$12,0))</f>
@@ -27500,11 +27545,11 @@
       <c r="M436" s="2"/>
       <c r="N436" s="2"/>
       <c r="O436" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P436" s="3"/>
       <c r="Q436" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R436" s="2" t="n">
         <v>0.016667</v>
@@ -27515,7 +27560,7 @@
     </row>
     <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>2</v>
@@ -27536,7 +27581,7 @@
         <v>422</v>
       </c>
       <c r="H437" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I437" s="2" t="s">
         <v>335</v>
@@ -27545,7 +27590,7 @@
         <v>520</v>
       </c>
       <c r="K437" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L437" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B437-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D437-1)/Inputs!$B$12,0))</f>
@@ -27554,11 +27599,11 @@
       <c r="M437" s="2"/>
       <c r="N437" s="2"/>
       <c r="O437" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P437" s="3"/>
       <c r="Q437" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R437" s="2" t="n">
         <v>0.016667</v>
@@ -27569,7 +27614,7 @@
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>2</v>
@@ -27599,7 +27644,7 @@
         <v>521</v>
       </c>
       <c r="K438" s="3" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L438" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B438-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D438-1)/Inputs!$B$12,0))</f>
@@ -27608,11 +27653,11 @@
       <c r="M438" s="2"/>
       <c r="N438" s="2"/>
       <c r="O438" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P438" s="3"/>
       <c r="Q438" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R438" s="2" t="n">
         <v>0.016667</v>
@@ -27623,7 +27668,7 @@
     </row>
     <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B439" s="4" t="n">
         <v>2</v>
@@ -27641,19 +27686,19 @@
         <v>55</v>
       </c>
       <c r="G439" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H439" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I439" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="K439" s="5" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L439" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B439-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D439-1)/Inputs!$B$12,0))</f>
@@ -27662,22 +27707,22 @@
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
       <c r="O439" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P439" s="5"/>
       <c r="Q439" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R439" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S439" s="4" t="s">
-        <v>723</v>
+        <v>738</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B440" s="4" t="n">
         <v>2</v>
@@ -27695,19 +27740,19 @@
         <v>55</v>
       </c>
       <c r="G440" s="4" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="H440" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="I440" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="K440" s="5" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L440" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B440-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D440-1)/Inputs!$B$12,0))</f>
@@ -27716,22 +27761,22 @@
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
       <c r="O440" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P440" s="5"/>
       <c r="Q440" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R440" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S440" s="4" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B441" s="6" t="n">
         <v>2</v>
@@ -27749,17 +27794,17 @@
         <v>91</v>
       </c>
       <c r="G441" s="6" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="I441" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J441" s="6"/>
       <c r="K441" s="7" t="s">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="L441" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.7*Inputs!$B$4*Inputs!$B$5^(B441-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D441-1)/Inputs!$B$12*3.66,0))</f>
@@ -27768,11 +27813,11 @@
       <c r="M441" s="6"/>
       <c r="N441" s="6"/>
       <c r="O441" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P441" s="7"/>
       <c r="Q441" s="6" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="R441" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -27784,7 +27829,7 @@
     </row>
     <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B442" s="2" t="n">
         <v>3</v>
@@ -27805,7 +27850,7 @@
         <v>223</v>
       </c>
       <c r="H442" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I442" s="2" t="s">
         <v>276</v>
@@ -27814,7 +27859,7 @@
         <v>277</v>
       </c>
       <c r="K442" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L442" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B442-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D442-1)/Inputs!$B$12,0))</f>
@@ -27823,11 +27868,11 @@
       <c r="M442" s="2"/>
       <c r="N442" s="2"/>
       <c r="O442" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P442" s="3"/>
       <c r="Q442" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R442" s="2" t="n">
         <v>0.375</v>
@@ -27838,7 +27883,7 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B443" s="2" t="n">
         <v>3</v>
@@ -27859,7 +27904,7 @@
         <v>223</v>
       </c>
       <c r="H443" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I443" s="2" t="s">
         <v>276</v>
@@ -27868,7 +27913,7 @@
         <v>278</v>
       </c>
       <c r="K443" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L443" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B443-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D443-1)/Inputs!$B$12,0))</f>
@@ -27877,11 +27922,11 @@
       <c r="M443" s="2"/>
       <c r="N443" s="2"/>
       <c r="O443" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P443" s="3"/>
       <c r="Q443" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R443" s="2" t="n">
         <v>0.375</v>
@@ -27892,7 +27937,7 @@
     </row>
     <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B444" s="2" t="n">
         <v>3</v>
@@ -27913,7 +27958,7 @@
         <v>223</v>
       </c>
       <c r="H444" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I444" s="2" t="s">
         <v>276</v>
@@ -27922,7 +27967,7 @@
         <v>279</v>
       </c>
       <c r="K444" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L444" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B444-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D444-1)/Inputs!$B$12,0))</f>
@@ -27931,11 +27976,11 @@
       <c r="M444" s="2"/>
       <c r="N444" s="2"/>
       <c r="O444" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P444" s="3"/>
       <c r="Q444" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R444" s="2" t="n">
         <v>0.375</v>
@@ -27946,7 +27991,7 @@
     </row>
     <row r="445" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B445" s="2" t="n">
         <v>3</v>
@@ -27967,7 +28012,7 @@
         <v>232</v>
       </c>
       <c r="H445" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I445" s="2" t="s">
         <v>566</v>
@@ -27976,7 +28021,7 @@
         <v>604</v>
       </c>
       <c r="K445" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L445" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B445-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D445-1)/Inputs!$B$12,0))</f>
@@ -27985,11 +28030,11 @@
       <c r="M445" s="2"/>
       <c r="N445" s="2"/>
       <c r="O445" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P445" s="3"/>
       <c r="Q445" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R445" s="2" t="n">
         <v>0.016667</v>
@@ -28000,7 +28045,7 @@
     </row>
     <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B446" s="2" t="n">
         <v>3</v>
@@ -28021,7 +28066,7 @@
         <v>232</v>
       </c>
       <c r="H446" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I446" s="2" t="s">
         <v>566</v>
@@ -28030,7 +28075,7 @@
         <v>605</v>
       </c>
       <c r="K446" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L446" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B446-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D446-1)/Inputs!$B$12,0))</f>
@@ -28039,11 +28084,11 @@
       <c r="M446" s="2"/>
       <c r="N446" s="2"/>
       <c r="O446" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P446" s="3"/>
       <c r="Q446" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R446" s="2" t="n">
         <v>0.016667</v>
@@ -28054,7 +28099,7 @@
     </row>
     <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B447" s="2" t="n">
         <v>3</v>
@@ -28075,7 +28120,7 @@
         <v>422</v>
       </c>
       <c r="H447" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I447" s="2" t="s">
         <v>335</v>
@@ -28084,7 +28129,7 @@
         <v>528</v>
       </c>
       <c r="K447" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L447" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B447-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D447-1)/Inputs!$B$12,0))</f>
@@ -28093,11 +28138,11 @@
       <c r="M447" s="2"/>
       <c r="N447" s="2"/>
       <c r="O447" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P447" s="3"/>
       <c r="Q447" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R447" s="2" t="n">
         <v>0.016667</v>
@@ -28108,7 +28153,7 @@
     </row>
     <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B448" s="2" t="n">
         <v>3</v>
@@ -28138,7 +28183,7 @@
         <v>529</v>
       </c>
       <c r="K448" s="3" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L448" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B448-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D448-1)/Inputs!$B$12,0))</f>
@@ -28147,11 +28192,11 @@
       <c r="M448" s="2"/>
       <c r="N448" s="2"/>
       <c r="O448" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P448" s="3"/>
       <c r="Q448" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R448" s="2" t="n">
         <v>0.016667</v>
@@ -28162,7 +28207,7 @@
     </row>
     <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B449" s="4" t="n">
         <v>3</v>
@@ -28180,19 +28225,19 @@
         <v>55</v>
       </c>
       <c r="G449" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H449" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I449" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="K449" s="5" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L449" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B449-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D449-1)/Inputs!$B$12,0))</f>
@@ -28201,22 +28246,22 @@
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
       <c r="O449" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P449" s="5"/>
       <c r="Q449" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R449" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S449" s="4" t="s">
-        <v>734</v>
+        <v>749</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B450" s="4" t="n">
         <v>3</v>
@@ -28234,19 +28279,19 @@
         <v>55</v>
       </c>
       <c r="G450" s="4" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="H450" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="I450" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="K450" s="5" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L450" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B450-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D450-1)/Inputs!$B$12,0))</f>
@@ -28255,22 +28300,22 @@
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
       <c r="O450" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P450" s="5"/>
       <c r="Q450" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R450" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S450" s="4" t="s">
-        <v>735</v>
+        <v>750</v>
       </c>
     </row>
     <row r="451" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B451" s="6" t="n">
         <v>3</v>
@@ -28288,17 +28333,17 @@
         <v>91</v>
       </c>
       <c r="G451" s="6" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="H451" s="7" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="I451" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J451" s="6"/>
       <c r="K451" s="7" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="L451" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.85*Inputs!$B$4*Inputs!$B$5^(B451-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D451-1)/Inputs!$B$12*3.66,0))</f>
@@ -28307,11 +28352,11 @@
       <c r="M451" s="6"/>
       <c r="N451" s="6"/>
       <c r="O451" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P451" s="7"/>
       <c r="Q451" s="6" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="R451" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28323,7 +28368,7 @@
     </row>
     <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B452" s="2" t="n">
         <v>4</v>
@@ -28344,7 +28389,7 @@
         <v>223</v>
       </c>
       <c r="H452" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I452" s="2" t="s">
         <v>289</v>
@@ -28353,7 +28398,7 @@
         <v>290</v>
       </c>
       <c r="K452" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L452" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B452-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D452-1)/Inputs!$B$12,0))</f>
@@ -28362,11 +28407,11 @@
       <c r="M452" s="2"/>
       <c r="N452" s="2"/>
       <c r="O452" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P452" s="3"/>
       <c r="Q452" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R452" s="2" t="n">
         <v>0.5625</v>
@@ -28377,7 +28422,7 @@
     </row>
     <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B453" s="2" t="n">
         <v>4</v>
@@ -28398,7 +28443,7 @@
         <v>223</v>
       </c>
       <c r="H453" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I453" s="2" t="s">
         <v>289</v>
@@ -28407,7 +28452,7 @@
         <v>291</v>
       </c>
       <c r="K453" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L453" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B453-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D453-1)/Inputs!$B$12,0))</f>
@@ -28416,11 +28461,11 @@
       <c r="M453" s="2"/>
       <c r="N453" s="2"/>
       <c r="O453" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P453" s="3"/>
       <c r="Q453" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R453" s="2" t="n">
         <v>0.5625</v>
@@ -28431,7 +28476,7 @@
     </row>
     <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B454" s="2" t="n">
         <v>4</v>
@@ -28452,7 +28497,7 @@
         <v>223</v>
       </c>
       <c r="H454" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I454" s="2" t="s">
         <v>289</v>
@@ -28461,7 +28506,7 @@
         <v>292</v>
       </c>
       <c r="K454" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L454" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B454-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D454-1)/Inputs!$B$12,0))</f>
@@ -28470,11 +28515,11 @@
       <c r="M454" s="2"/>
       <c r="N454" s="2"/>
       <c r="O454" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P454" s="3"/>
       <c r="Q454" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R454" s="2" t="n">
         <v>0.5625</v>
@@ -28485,7 +28530,7 @@
     </row>
     <row r="455" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B455" s="2" t="n">
         <v>4</v>
@@ -28506,7 +28551,7 @@
         <v>232</v>
       </c>
       <c r="H455" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I455" s="2" t="s">
         <v>566</v>
@@ -28515,7 +28560,7 @@
         <v>613</v>
       </c>
       <c r="K455" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L455" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B455-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D455-1)/Inputs!$B$12,0))</f>
@@ -28524,11 +28569,11 @@
       <c r="M455" s="2"/>
       <c r="N455" s="2"/>
       <c r="O455" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P455" s="3"/>
       <c r="Q455" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R455" s="2" t="n">
         <v>0.016667</v>
@@ -28539,7 +28584,7 @@
     </row>
     <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B456" s="2" t="n">
         <v>4</v>
@@ -28560,7 +28605,7 @@
         <v>232</v>
       </c>
       <c r="H456" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I456" s="2" t="s">
         <v>566</v>
@@ -28569,7 +28614,7 @@
         <v>614</v>
       </c>
       <c r="K456" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L456" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B456-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D456-1)/Inputs!$B$12,0))</f>
@@ -28578,11 +28623,11 @@
       <c r="M456" s="2"/>
       <c r="N456" s="2"/>
       <c r="O456" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P456" s="3"/>
       <c r="Q456" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R456" s="2" t="n">
         <v>0.016667</v>
@@ -28593,7 +28638,7 @@
     </row>
     <row r="457" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B457" s="2" t="n">
         <v>4</v>
@@ -28614,7 +28659,7 @@
         <v>422</v>
       </c>
       <c r="H457" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I457" s="2" t="s">
         <v>335</v>
@@ -28623,7 +28668,7 @@
         <v>537</v>
       </c>
       <c r="K457" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L457" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B457-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D457-1)/Inputs!$B$12,0))</f>
@@ -28632,11 +28677,11 @@
       <c r="M457" s="2"/>
       <c r="N457" s="2"/>
       <c r="O457" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P457" s="3"/>
       <c r="Q457" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R457" s="2" t="n">
         <v>0.016667</v>
@@ -28647,7 +28692,7 @@
     </row>
     <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B458" s="2" t="n">
         <v>4</v>
@@ -28677,7 +28722,7 @@
         <v>538</v>
       </c>
       <c r="K458" s="3" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L458" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B458-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D458-1)/Inputs!$B$12,0))</f>
@@ -28686,11 +28731,11 @@
       <c r="M458" s="2"/>
       <c r="N458" s="2"/>
       <c r="O458" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P458" s="3"/>
       <c r="Q458" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R458" s="2" t="n">
         <v>0.016667</v>
@@ -28701,7 +28746,7 @@
     </row>
     <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B459" s="4" t="n">
         <v>4</v>
@@ -28719,19 +28764,19 @@
         <v>55</v>
       </c>
       <c r="G459" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H459" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I459" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="K459" s="5" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L459" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B459-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D459-1)/Inputs!$B$12,0))</f>
@@ -28740,22 +28785,22 @@
       <c r="M459" s="4"/>
       <c r="N459" s="4"/>
       <c r="O459" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P459" s="5"/>
       <c r="Q459" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R459" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S459" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B460" s="4" t="n">
         <v>4</v>
@@ -28773,19 +28818,19 @@
         <v>55</v>
       </c>
       <c r="G460" s="4" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="H460" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="I460" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="K460" s="5" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L460" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B460-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D460-1)/Inputs!$B$12,0))</f>
@@ -28794,22 +28839,22 @@
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
       <c r="O460" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P460" s="5"/>
       <c r="Q460" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R460" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S460" s="4" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B461" s="6" t="n">
         <v>4</v>
@@ -28827,17 +28872,17 @@
         <v>91</v>
       </c>
       <c r="G461" s="6" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="H461" s="7" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="I461" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J461" s="6"/>
       <c r="K461" s="7" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="L461" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B461-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D461-1)/Inputs!$B$12*3.66,0))</f>
@@ -28846,11 +28891,11 @@
       <c r="M461" s="6"/>
       <c r="N461" s="6"/>
       <c r="O461" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P461" s="7"/>
       <c r="Q461" s="6" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="R461" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -28862,7 +28907,7 @@
     </row>
     <row r="462" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B462" s="2" t="n">
         <v>5</v>
@@ -28883,7 +28928,7 @@
         <v>223</v>
       </c>
       <c r="H462" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I462" s="2" t="s">
         <v>302</v>
@@ -28892,7 +28937,7 @@
         <v>303</v>
       </c>
       <c r="K462" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L462" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B462-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D462-1)/Inputs!$B$12,0))</f>
@@ -28901,11 +28946,11 @@
       <c r="M462" s="2"/>
       <c r="N462" s="2"/>
       <c r="O462" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P462" s="3"/>
       <c r="Q462" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R462" s="2" t="n">
         <v>0.8438</v>
@@ -28916,7 +28961,7 @@
     </row>
     <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B463" s="2" t="n">
         <v>5</v>
@@ -28937,7 +28982,7 @@
         <v>223</v>
       </c>
       <c r="H463" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I463" s="2" t="s">
         <v>302</v>
@@ -28946,7 +28991,7 @@
         <v>304</v>
       </c>
       <c r="K463" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L463" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B463-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D463-1)/Inputs!$B$12,0))</f>
@@ -28955,11 +29000,11 @@
       <c r="M463" s="2"/>
       <c r="N463" s="2"/>
       <c r="O463" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P463" s="3"/>
       <c r="Q463" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R463" s="2" t="n">
         <v>0.8438</v>
@@ -28970,7 +29015,7 @@
     </row>
     <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B464" s="2" t="n">
         <v>5</v>
@@ -28991,7 +29036,7 @@
         <v>223</v>
       </c>
       <c r="H464" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I464" s="2" t="s">
         <v>302</v>
@@ -29000,7 +29045,7 @@
         <v>305</v>
       </c>
       <c r="K464" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L464" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B464-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D464-1)/Inputs!$B$12,0))</f>
@@ -29009,11 +29054,11 @@
       <c r="M464" s="2"/>
       <c r="N464" s="2"/>
       <c r="O464" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P464" s="3"/>
       <c r="Q464" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R464" s="2" t="n">
         <v>0.8438</v>
@@ -29024,7 +29069,7 @@
     </row>
     <row r="465" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B465" s="2" t="n">
         <v>5</v>
@@ -29045,7 +29090,7 @@
         <v>232</v>
       </c>
       <c r="H465" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I465" s="2" t="s">
         <v>566</v>
@@ -29054,7 +29099,7 @@
         <v>622</v>
       </c>
       <c r="K465" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L465" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B465-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D465-1)/Inputs!$B$12,0))</f>
@@ -29063,11 +29108,11 @@
       <c r="M465" s="2"/>
       <c r="N465" s="2"/>
       <c r="O465" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P465" s="3"/>
       <c r="Q465" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R465" s="2" t="n">
         <v>0.016667</v>
@@ -29078,7 +29123,7 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B466" s="2" t="n">
         <v>5</v>
@@ -29099,7 +29144,7 @@
         <v>232</v>
       </c>
       <c r="H466" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I466" s="2" t="s">
         <v>566</v>
@@ -29108,7 +29153,7 @@
         <v>623</v>
       </c>
       <c r="K466" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L466" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B466-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D466-1)/Inputs!$B$12,0))</f>
@@ -29117,11 +29162,11 @@
       <c r="M466" s="2"/>
       <c r="N466" s="2"/>
       <c r="O466" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P466" s="3"/>
       <c r="Q466" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R466" s="2" t="n">
         <v>0.016667</v>
@@ -29132,7 +29177,7 @@
     </row>
     <row r="467" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B467" s="2" t="n">
         <v>5</v>
@@ -29153,7 +29198,7 @@
         <v>422</v>
       </c>
       <c r="H467" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I467" s="2" t="s">
         <v>335</v>
@@ -29162,7 +29207,7 @@
         <v>545</v>
       </c>
       <c r="K467" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L467" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B467-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D467-1)/Inputs!$B$12,0))</f>
@@ -29171,11 +29216,11 @@
       <c r="M467" s="2"/>
       <c r="N467" s="2"/>
       <c r="O467" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P467" s="3"/>
       <c r="Q467" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R467" s="2" t="n">
         <v>0.016667</v>
@@ -29186,7 +29231,7 @@
     </row>
     <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B468" s="2" t="n">
         <v>5</v>
@@ -29216,7 +29261,7 @@
         <v>546</v>
       </c>
       <c r="K468" s="3" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L468" s="2" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B468-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D468-1)/Inputs!$B$12,0))</f>
@@ -29225,11 +29270,11 @@
       <c r="M468" s="2"/>
       <c r="N468" s="2"/>
       <c r="O468" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P468" s="3"/>
       <c r="Q468" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R468" s="2" t="n">
         <v>0.016667</v>
@@ -29240,7 +29285,7 @@
     </row>
     <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B469" s="4" t="n">
         <v>5</v>
@@ -29258,19 +29303,19 @@
         <v>55</v>
       </c>
       <c r="G469" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H469" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I469" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="K469" s="5" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L469" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B469-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D469-1)/Inputs!$B$12,0))</f>
@@ -29279,22 +29324,22 @@
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
       <c r="O469" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P469" s="5"/>
       <c r="Q469" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R469" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S469" s="4" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B470" s="4" t="n">
         <v>5</v>
@@ -29312,19 +29357,19 @@
         <v>55</v>
       </c>
       <c r="G470" s="4" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="H470" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="I470" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="K470" s="5" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L470" s="4" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B470-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D470-1)/Inputs!$B$12,0))</f>
@@ -29333,22 +29378,22 @@
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
       <c r="O470" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P470" s="5"/>
       <c r="Q470" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R470" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S470" s="4" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B471" s="6" t="n">
         <v>5</v>
@@ -29369,14 +29414,14 @@
         <v>312</v>
       </c>
       <c r="H471" s="7" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="I471" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J471" s="6"/>
       <c r="K471" s="7" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="L471" s="6" t="n">
         <f aca="false">MAX(1,ROUND(0.75*Inputs!$B$4*Inputs!$B$5^(B471-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D471-1)/Inputs!$B$12*3.66,0))</f>
@@ -29385,11 +29430,11 @@
       <c r="M471" s="6"/>
       <c r="N471" s="6"/>
       <c r="O471" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P471" s="7"/>
       <c r="Q471" s="6" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="R471" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -29401,7 +29446,7 @@
     </row>
     <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B472" s="2" t="n">
         <v>6</v>
@@ -29422,7 +29467,7 @@
         <v>223</v>
       </c>
       <c r="H472" s="3" t="s">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="I472" s="2" t="s">
         <v>315</v>
@@ -29431,7 +29476,7 @@
         <v>316</v>
       </c>
       <c r="K472" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L472" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B472-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D472-1)/Inputs!$B$12,0))</f>
@@ -29440,11 +29485,11 @@
       <c r="M472" s="2"/>
       <c r="N472" s="2"/>
       <c r="O472" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P472" s="3"/>
       <c r="Q472" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R472" s="2" t="n">
         <v>1.2656</v>
@@ -29455,7 +29500,7 @@
     </row>
     <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B473" s="2" t="n">
         <v>6</v>
@@ -29476,7 +29521,7 @@
         <v>223</v>
       </c>
       <c r="H473" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I473" s="2" t="s">
         <v>315</v>
@@ -29485,7 +29530,7 @@
         <v>317</v>
       </c>
       <c r="K473" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L473" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B473-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D473-1)/Inputs!$B$12,0))</f>
@@ -29494,11 +29539,11 @@
       <c r="M473" s="2"/>
       <c r="N473" s="2"/>
       <c r="O473" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P473" s="3"/>
       <c r="Q473" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R473" s="2" t="n">
         <v>1.2656</v>
@@ -29509,7 +29554,7 @@
     </row>
     <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B474" s="2" t="n">
         <v>6</v>
@@ -29530,7 +29575,7 @@
         <v>223</v>
       </c>
       <c r="H474" s="3" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="I474" s="2" t="s">
         <v>315</v>
@@ -29539,7 +29584,7 @@
         <v>318</v>
       </c>
       <c r="K474" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L474" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B474-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D474-1)/Inputs!$B$12,0))</f>
@@ -29548,11 +29593,11 @@
       <c r="M474" s="2"/>
       <c r="N474" s="2"/>
       <c r="O474" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P474" s="3"/>
       <c r="Q474" s="2" t="s">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="R474" s="2" t="n">
         <v>1.2656</v>
@@ -29563,7 +29608,7 @@
     </row>
     <row r="475" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B475" s="2" t="n">
         <v>6</v>
@@ -29584,7 +29629,7 @@
         <v>232</v>
       </c>
       <c r="H475" s="3" t="s">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="I475" s="2" t="s">
         <v>566</v>
@@ -29593,7 +29638,7 @@
         <v>630</v>
       </c>
       <c r="K475" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L475" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B475-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D475-1)/Inputs!$B$12,0))</f>
@@ -29602,11 +29647,11 @@
       <c r="M475" s="2"/>
       <c r="N475" s="2"/>
       <c r="O475" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P475" s="3"/>
       <c r="Q475" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R475" s="2" t="n">
         <v>0.016667</v>
@@ -29617,7 +29662,7 @@
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B476" s="2" t="n">
         <v>6</v>
@@ -29638,7 +29683,7 @@
         <v>232</v>
       </c>
       <c r="H476" s="3" t="s">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="I476" s="2" t="s">
         <v>566</v>
@@ -29647,7 +29692,7 @@
         <v>631</v>
       </c>
       <c r="K476" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L476" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B476-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D476-1)/Inputs!$B$12,0))</f>
@@ -29656,11 +29701,11 @@
       <c r="M476" s="2"/>
       <c r="N476" s="2"/>
       <c r="O476" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P476" s="3"/>
       <c r="Q476" s="2" t="s">
-        <v>716</v>
+        <v>731</v>
       </c>
       <c r="R476" s="2" t="n">
         <v>0.016667</v>
@@ -29671,7 +29716,7 @@
     </row>
     <row r="477" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B477" s="2" t="n">
         <v>6</v>
@@ -29692,7 +29737,7 @@
         <v>422</v>
       </c>
       <c r="H477" s="3" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="I477" s="2" t="s">
         <v>335</v>
@@ -29701,7 +29746,7 @@
         <v>553</v>
       </c>
       <c r="K477" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L477" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B477-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D477-1)/Inputs!$B$12,0))</f>
@@ -29710,11 +29755,11 @@
       <c r="M477" s="2"/>
       <c r="N477" s="2"/>
       <c r="O477" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P477" s="3"/>
       <c r="Q477" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R477" s="2" t="n">
         <v>0.016667</v>
@@ -29725,7 +29770,7 @@
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="2" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B478" s="2" t="n">
         <v>6</v>
@@ -29755,7 +29800,7 @@
         <v>554</v>
       </c>
       <c r="K478" s="3" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L478" s="2" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B478-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D478-1)/Inputs!$B$12,0))</f>
@@ -29764,11 +29809,11 @@
       <c r="M478" s="2"/>
       <c r="N478" s="2"/>
       <c r="O478" s="2" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P478" s="3"/>
       <c r="Q478" s="2" t="s">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="R478" s="2" t="n">
         <v>0.016667</v>
@@ -29779,7 +29824,7 @@
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B479" s="4" t="n">
         <v>6</v>
@@ -29797,19 +29842,19 @@
         <v>55</v>
       </c>
       <c r="G479" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="H479" s="5" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="I479" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="K479" s="5" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L479" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B479-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D479-1)/Inputs!$B$12,0))</f>
@@ -29818,22 +29863,22 @@
       <c r="M479" s="4"/>
       <c r="N479" s="4"/>
       <c r="O479" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P479" s="5"/>
       <c r="Q479" s="4" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="R479" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S479" s="4" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="4" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B480" s="4" t="n">
         <v>6</v>
@@ -29851,19 +29896,19 @@
         <v>55</v>
       </c>
       <c r="G480" s="4" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="H480" s="5" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="I480" s="4" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="K480" s="5" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L480" s="4" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B480-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D480-1)/Inputs!$B$12,0))</f>
@@ -29872,22 +29917,22 @@
       <c r="M480" s="4"/>
       <c r="N480" s="4"/>
       <c r="O480" s="4" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P480" s="5"/>
       <c r="Q480" s="4" t="s">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="R480" s="4" t="n">
         <v>0.025</v>
       </c>
       <c r="S480" s="4" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="6" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B481" s="6" t="n">
         <v>6</v>
@@ -29905,17 +29950,17 @@
         <v>91</v>
       </c>
       <c r="G481" s="6" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="I481" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J481" s="6"/>
       <c r="K481" s="7" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="L481" s="6" t="n">
         <f aca="false">MAX(1,ROUND(1*Inputs!$B$4*Inputs!$B$5^(B481-1)*INDEX(Inputs!$C$15:$C$23,MATCH("compiling",Inputs!$A$15:$A$23,0))*Inputs!$B$7*Inputs!$B$6^(D481-1)/Inputs!$B$12*3.66,0))</f>
@@ -29924,11 +29969,11 @@
       <c r="M481" s="6"/>
       <c r="N481" s="6"/>
       <c r="O481" s="6" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="P481" s="7"/>
       <c r="Q481" s="6" t="s">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="R481" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -29940,7 +29985,7 @@
     </row>
     <row r="482" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B482" s="2" t="n">
         <v>1</v>
@@ -29958,19 +30003,19 @@
         <v>22</v>
       </c>
       <c r="G482" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H482" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I482" s="2" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="J482" s="2" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="K482" s="3" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="L482" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D482-1)/Inputs!$B$12,0))</f>
@@ -29979,22 +30024,22 @@
       <c r="M482" s="2"/>
       <c r="N482" s="2"/>
       <c r="O482" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P482" s="3"/>
       <c r="Q482" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R482" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S482" s="2" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>1</v>
@@ -30012,19 +30057,19 @@
         <v>22</v>
       </c>
       <c r="G483" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H483" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I483" s="2" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="J483" s="2" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="K483" s="3" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="L483" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D483-1)/Inputs!$B$12,0))</f>
@@ -30033,22 +30078,22 @@
       <c r="M483" s="2"/>
       <c r="N483" s="2"/>
       <c r="O483" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P483" s="3"/>
       <c r="Q483" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R483" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S483" s="2" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>1</v>
@@ -30066,19 +30111,19 @@
         <v>22</v>
       </c>
       <c r="G484" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H484" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I484" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J484" s="2" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="K484" s="3" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="L484" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D484-1)/Inputs!$B$12,0))</f>
@@ -30087,22 +30132,22 @@
       <c r="M484" s="2"/>
       <c r="N484" s="2"/>
       <c r="O484" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P484" s="3"/>
       <c r="Q484" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R484" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S484" s="2" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B485" s="2" t="n">
         <v>1</v>
@@ -30120,19 +30165,19 @@
         <v>22</v>
       </c>
       <c r="G485" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H485" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I485" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J485" s="2" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="K485" s="3" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="L485" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D485-1)/Inputs!$B$12,0))</f>
@@ -30141,22 +30186,22 @@
       <c r="M485" s="2"/>
       <c r="N485" s="2"/>
       <c r="O485" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P485" s="3"/>
       <c r="Q485" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R485" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S485" s="2" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B486" s="2" t="n">
         <v>1</v>
@@ -30174,19 +30219,19 @@
         <v>22</v>
       </c>
       <c r="G486" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H486" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I486" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J486" s="2" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="K486" s="3" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="L486" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D486-1)/Inputs!$B$12,0))</f>
@@ -30195,22 +30240,22 @@
       <c r="M486" s="2"/>
       <c r="N486" s="2"/>
       <c r="O486" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P486" s="3"/>
       <c r="Q486" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R486" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S486" s="2" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B487" s="2" t="n">
         <v>1</v>
@@ -30228,19 +30273,19 @@
         <v>22</v>
       </c>
       <c r="G487" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H487" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I487" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J487" s="2" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="K487" s="3" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="L487" s="2" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D487-1)/Inputs!$B$12,0))</f>
@@ -30249,22 +30294,22 @@
       <c r="M487" s="2"/>
       <c r="N487" s="2"/>
       <c r="O487" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P487" s="3"/>
       <c r="Q487" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R487" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S487" s="2" t="s">
-        <v>797</v>
+        <v>812</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B488" s="4" t="n">
         <v>1</v>
@@ -30282,19 +30327,19 @@
         <v>55</v>
       </c>
       <c r="G488" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H488" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I488" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="K488" s="5" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="L488" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D488-1)/Inputs!$B$12,0))</f>
@@ -30303,22 +30348,22 @@
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
       <c r="O488" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P488" s="5"/>
       <c r="Q488" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R488" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S488" s="4" t="s">
-        <v>804</v>
+        <v>819</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B489" s="4" t="n">
         <v>1</v>
@@ -30336,19 +30381,19 @@
         <v>55</v>
       </c>
       <c r="G489" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H489" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I489" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="K489" s="5" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="L489" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D489-1)/Inputs!$B$12,0))</f>
@@ -30357,22 +30402,22 @@
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
       <c r="O489" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P489" s="5"/>
       <c r="Q489" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R489" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S489" s="4" t="s">
-        <v>809</v>
+        <v>824</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B490" s="4" t="n">
         <v>1</v>
@@ -30390,19 +30435,19 @@
         <v>55</v>
       </c>
       <c r="G490" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H490" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I490" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="K490" s="5" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="L490" s="4" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D490-1)/Inputs!$B$12,0))</f>
@@ -30411,22 +30456,22 @@
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
       <c r="O490" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P490" s="5"/>
       <c r="Q490" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R490" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S490" s="4" t="s">
-        <v>816</v>
+        <v>831</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B491" s="6" t="n">
         <v>1</v>
@@ -30444,17 +30489,17 @@
         <v>91</v>
       </c>
       <c r="G491" s="6" t="s">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="H491" s="7" t="s">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="I491" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J491" s="6"/>
       <c r="K491" s="7" t="s">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="L491" s="6" t="n">
         <f aca="false">MAX(1,ROUND(10*Inputs!$B$6^(D491-1)/Inputs!$B$12*3.66,0))</f>
@@ -30463,11 +30508,11 @@
       <c r="M491" s="6"/>
       <c r="N491" s="6"/>
       <c r="O491" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P491" s="7"/>
       <c r="Q491" s="6" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="R491" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -30479,7 +30524,7 @@
     </row>
     <row r="492" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B492" s="2" t="n">
         <v>2</v>
@@ -30497,19 +30542,19 @@
         <v>22</v>
       </c>
       <c r="G492" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H492" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I492" s="2" t="s">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="J492" s="2" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="K492" s="3" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="L492" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D492-1)/Inputs!$B$12,0))</f>
@@ -30518,22 +30563,22 @@
       <c r="M492" s="2"/>
       <c r="N492" s="2"/>
       <c r="O492" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P492" s="3"/>
       <c r="Q492" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R492" s="2" t="n">
         <v>10</v>
       </c>
       <c r="S492" s="2" t="s">
-        <v>766</v>
+        <v>781</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B493" s="2" t="n">
         <v>2</v>
@@ -30551,19 +30596,19 @@
         <v>22</v>
       </c>
       <c r="G493" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H493" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I493" s="2" t="s">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="J493" s="2" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="K493" s="3" t="s">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="L493" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D493-1)/Inputs!$B$12,0))</f>
@@ -30572,22 +30617,22 @@
       <c r="M493" s="2"/>
       <c r="N493" s="2"/>
       <c r="O493" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P493" s="3"/>
       <c r="Q493" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R493" s="2" t="n">
         <v>2</v>
       </c>
       <c r="S493" s="2" t="s">
-        <v>774</v>
+        <v>789</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>2</v>
@@ -30605,19 +30650,19 @@
         <v>22</v>
       </c>
       <c r="G494" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I494" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J494" s="2" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="K494" s="3" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="L494" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D494-1)/Inputs!$B$12,0))</f>
@@ -30626,22 +30671,22 @@
       <c r="M494" s="2"/>
       <c r="N494" s="2"/>
       <c r="O494" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P494" s="3"/>
       <c r="Q494" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R494" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S494" s="2" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>2</v>
@@ -30659,19 +30704,19 @@
         <v>22</v>
       </c>
       <c r="G495" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I495" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J495" s="2" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="K495" s="3" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="L495" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D495-1)/Inputs!$B$12,0))</f>
@@ -30680,22 +30725,22 @@
       <c r="M495" s="2"/>
       <c r="N495" s="2"/>
       <c r="O495" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P495" s="3"/>
       <c r="Q495" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R495" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S495" s="2" t="s">
-        <v>824</v>
+        <v>839</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B496" s="2" t="n">
         <v>2</v>
@@ -30713,19 +30758,19 @@
         <v>22</v>
       </c>
       <c r="G496" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I496" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J496" s="2" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="K496" s="3" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="L496" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D496-1)/Inputs!$B$12,0))</f>
@@ -30734,22 +30779,22 @@
       <c r="M496" s="2"/>
       <c r="N496" s="2"/>
       <c r="O496" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P496" s="3"/>
       <c r="Q496" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R496" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S496" s="2" t="s">
-        <v>788</v>
+        <v>803</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B497" s="2" t="n">
         <v>2</v>
@@ -30767,19 +30812,19 @@
         <v>22</v>
       </c>
       <c r="G497" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I497" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J497" s="2" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="K497" s="3" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="L497" s="2" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D497-1)/Inputs!$B$12,0))</f>
@@ -30788,22 +30833,22 @@
       <c r="M497" s="2"/>
       <c r="N497" s="2"/>
       <c r="O497" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P497" s="3"/>
       <c r="Q497" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R497" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S497" s="2" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B498" s="4" t="n">
         <v>2</v>
@@ -30821,19 +30866,19 @@
         <v>55</v>
       </c>
       <c r="G498" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H498" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I498" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J498" s="4" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="K498" s="5" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="L498" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D498-1)/Inputs!$B$12,0))</f>
@@ -30842,22 +30887,22 @@
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
       <c r="O498" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P498" s="5"/>
       <c r="Q498" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R498" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S498" s="4" t="s">
-        <v>801</v>
+        <v>816</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B499" s="4" t="n">
         <v>2</v>
@@ -30875,19 +30920,19 @@
         <v>55</v>
       </c>
       <c r="G499" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H499" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I499" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="K499" s="5" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="L499" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D499-1)/Inputs!$B$12,0))</f>
@@ -30896,22 +30941,22 @@
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
       <c r="O499" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P499" s="5"/>
       <c r="Q499" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R499" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S499" s="4" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B500" s="4" t="n">
         <v>2</v>
@@ -30929,19 +30974,19 @@
         <v>55</v>
       </c>
       <c r="G500" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H500" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I500" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J500" s="4" t="s">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="K500" s="5" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="L500" s="4" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D500-1)/Inputs!$B$12,0))</f>
@@ -30950,22 +30995,22 @@
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
       <c r="O500" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P500" s="5"/>
       <c r="Q500" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R500" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S500" s="4" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="501" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="501" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B501" s="6" t="n">
         <v>2</v>
@@ -30983,17 +31028,17 @@
         <v>91</v>
       </c>
       <c r="G501" s="6" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="H501" s="7" t="s">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="I501" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="7" t="s">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="L501" s="6" t="n">
         <f aca="false">MAX(1,ROUND(15*Inputs!$B$6^(D501-1)/Inputs!$B$12*3.66,0))</f>
@@ -31002,11 +31047,11 @@
       <c r="M501" s="6"/>
       <c r="N501" s="6"/>
       <c r="O501" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P501" s="7"/>
       <c r="Q501" s="6" t="s">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="R501" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31018,7 +31063,7 @@
     </row>
     <row r="502" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B502" s="2" t="n">
         <v>3</v>
@@ -31036,19 +31081,19 @@
         <v>22</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H502" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="J502" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="K502" s="3" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="L502" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D502-1)/Inputs!$B$12,0))</f>
@@ -31057,22 +31102,22 @@
       <c r="M502" s="2"/>
       <c r="N502" s="2"/>
       <c r="O502" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P502" s="3"/>
       <c r="Q502" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R502" s="2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S502" s="2" t="s">
-        <v>821</v>
+        <v>836</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B503" s="2" t="n">
         <v>3</v>
@@ -31090,19 +31135,19 @@
         <v>22</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H503" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I503" s="2" t="s">
-        <v>787</v>
+        <v>855</v>
       </c>
       <c r="J503" s="2" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="K503" s="3" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
       <c r="L503" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D503-1)/Inputs!$B$12,0))</f>
@@ -31111,22 +31156,22 @@
       <c r="M503" s="2"/>
       <c r="N503" s="2"/>
       <c r="O503" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P503" s="3"/>
       <c r="Q503" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R503" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S503" s="2" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B504" s="2" t="n">
         <v>3</v>
@@ -31144,19 +31189,19 @@
         <v>22</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H504" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I504" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J504" s="2" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
       <c r="K504" s="3" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="L504" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D504-1)/Inputs!$B$12,0))</f>
@@ -31165,22 +31210,22 @@
       <c r="M504" s="2"/>
       <c r="N504" s="2"/>
       <c r="O504" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P504" s="3"/>
       <c r="Q504" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R504" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S504" s="2" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B505" s="2" t="n">
         <v>3</v>
@@ -31198,19 +31243,19 @@
         <v>22</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H505" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I505" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J505" s="2" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="K505" s="3" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="L505" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D505-1)/Inputs!$B$12,0))</f>
@@ -31219,22 +31264,22 @@
       <c r="M505" s="2"/>
       <c r="N505" s="2"/>
       <c r="O505" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P505" s="3"/>
       <c r="Q505" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R505" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S505" s="2" t="s">
-        <v>842</v>
+        <v>857</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B506" s="2" t="n">
         <v>3</v>
@@ -31252,19 +31297,19 @@
         <v>22</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H506" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I506" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J506" s="2" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="K506" s="3" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="L506" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D506-1)/Inputs!$B$12,0))</f>
@@ -31273,22 +31318,22 @@
       <c r="M506" s="2"/>
       <c r="N506" s="2"/>
       <c r="O506" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P506" s="3"/>
       <c r="Q506" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R506" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S506" s="2" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
     </row>
     <row r="507" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B507" s="2" t="n">
         <v>3</v>
@@ -31306,19 +31351,19 @@
         <v>22</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I507" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J507" s="2" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="K507" s="3" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="L507" s="2" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D507-1)/Inputs!$B$12,0))</f>
@@ -31327,22 +31372,22 @@
       <c r="M507" s="2"/>
       <c r="N507" s="2"/>
       <c r="O507" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P507" s="3"/>
       <c r="Q507" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R507" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S507" s="2" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B508" s="4" t="n">
         <v>3</v>
@@ -31360,19 +31405,19 @@
         <v>55</v>
       </c>
       <c r="G508" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H508" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I508" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J508" s="4" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="K508" s="5" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="L508" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D508-1)/Inputs!$B$12,0))</f>
@@ -31381,22 +31426,22 @@
       <c r="M508" s="4"/>
       <c r="N508" s="4"/>
       <c r="O508" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P508" s="5"/>
       <c r="Q508" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R508" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S508" s="4" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B509" s="4" t="n">
         <v>3</v>
@@ -31414,19 +31459,19 @@
         <v>55</v>
       </c>
       <c r="G509" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H509" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I509" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J509" s="4" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="K509" s="5" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="L509" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D509-1)/Inputs!$B$12,0))</f>
@@ -31435,22 +31480,22 @@
       <c r="M509" s="4"/>
       <c r="N509" s="4"/>
       <c r="O509" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P509" s="5"/>
       <c r="Q509" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R509" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S509" s="4" t="s">
-        <v>832</v>
+        <v>847</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B510" s="4" t="n">
         <v>3</v>
@@ -31468,19 +31513,19 @@
         <v>55</v>
       </c>
       <c r="G510" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H510" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I510" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J510" s="4" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="K510" s="5" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="L510" s="4" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D510-1)/Inputs!$B$12,0))</f>
@@ -31489,22 +31534,22 @@
       <c r="M510" s="4"/>
       <c r="N510" s="4"/>
       <c r="O510" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P510" s="5"/>
       <c r="Q510" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R510" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S510" s="4" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="511" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B511" s="6" t="n">
         <v>3</v>
@@ -31522,17 +31567,17 @@
         <v>91</v>
       </c>
       <c r="G511" s="6" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="H511" s="7" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="I511" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J511" s="6"/>
       <c r="K511" s="7" t="s">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="L511" s="6" t="n">
         <f aca="false">MAX(1,ROUND(22*Inputs!$B$6^(D511-1)/Inputs!$B$12*3.66,0))</f>
@@ -31541,11 +31586,11 @@
       <c r="M511" s="6"/>
       <c r="N511" s="6"/>
       <c r="O511" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P511" s="7"/>
       <c r="Q511" s="6" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="R511" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -31557,7 +31602,7 @@
     </row>
     <row r="512" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B512" s="2" t="n">
         <v>4</v>
@@ -31575,19 +31620,19 @@
         <v>22</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H512" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I512" s="2" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="J512" s="2" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
       <c r="K512" s="3" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="L512" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D512-1)/Inputs!$B$12,0))</f>
@@ -31596,22 +31641,22 @@
       <c r="M512" s="2"/>
       <c r="N512" s="2"/>
       <c r="O512" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P512" s="3"/>
       <c r="Q512" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R512" s="2" t="n">
         <v>50</v>
       </c>
       <c r="S512" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B513" s="2" t="n">
         <v>4</v>
@@ -31629,19 +31674,19 @@
         <v>22</v>
       </c>
       <c r="G513" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H513" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I513" s="2" t="s">
-        <v>859</v>
+        <v>874</v>
       </c>
       <c r="J513" s="2" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="K513" s="3" t="s">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="L513" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D513-1)/Inputs!$B$12,0))</f>
@@ -31650,22 +31695,22 @@
       <c r="M513" s="2"/>
       <c r="N513" s="2"/>
       <c r="O513" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P513" s="3"/>
       <c r="Q513" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R513" s="2" t="n">
         <v>6</v>
       </c>
       <c r="S513" s="2" t="s">
-        <v>841</v>
+        <v>856</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B514" s="2" t="n">
         <v>4</v>
@@ -31683,19 +31728,19 @@
         <v>22</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H514" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I514" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J514" s="2" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="K514" s="3" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="L514" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D514-1)/Inputs!$B$12,0))</f>
@@ -31704,22 +31749,22 @@
       <c r="M514" s="2"/>
       <c r="N514" s="2"/>
       <c r="O514" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P514" s="3"/>
       <c r="Q514" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R514" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S514" s="2" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B515" s="2" t="n">
         <v>4</v>
@@ -31737,19 +31782,19 @@
         <v>22</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H515" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I515" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J515" s="2" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="K515" s="3" t="s">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="L515" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D515-1)/Inputs!$B$12,0))</f>
@@ -31758,22 +31803,22 @@
       <c r="M515" s="2"/>
       <c r="N515" s="2"/>
       <c r="O515" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P515" s="3"/>
       <c r="Q515" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R515" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S515" s="2" t="s">
-        <v>861</v>
+        <v>876</v>
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>4</v>
@@ -31791,19 +31836,19 @@
         <v>22</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H516" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I516" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J516" s="2" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="K516" s="3" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="L516" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D516-1)/Inputs!$B$12,0))</f>
@@ -31812,22 +31857,22 @@
       <c r="M516" s="2"/>
       <c r="N516" s="2"/>
       <c r="O516" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P516" s="3"/>
       <c r="Q516" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R516" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S516" s="2" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>4</v>
@@ -31845,19 +31890,19 @@
         <v>22</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H517" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I517" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J517" s="2" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="K517" s="3" t="s">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="L517" s="2" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D517-1)/Inputs!$B$12,0))</f>
@@ -31866,22 +31911,22 @@
       <c r="M517" s="2"/>
       <c r="N517" s="2"/>
       <c r="O517" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P517" s="3"/>
       <c r="Q517" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R517" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S517" s="2" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B518" s="4" t="n">
         <v>4</v>
@@ -31899,19 +31944,19 @@
         <v>55</v>
       </c>
       <c r="G518" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H518" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I518" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J518" s="4" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="K518" s="5" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="L518" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D518-1)/Inputs!$B$12,0))</f>
@@ -31920,22 +31965,22 @@
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
       <c r="O518" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P518" s="5"/>
       <c r="Q518" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R518" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S518" s="4" t="s">
-        <v>848</v>
+        <v>863</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B519" s="4" t="n">
         <v>4</v>
@@ -31953,19 +31998,19 @@
         <v>55</v>
       </c>
       <c r="G519" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H519" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I519" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J519" s="4" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="K519" s="5" t="s">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="L519" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D519-1)/Inputs!$B$12,0))</f>
@@ -31974,22 +32019,22 @@
       <c r="M519" s="4"/>
       <c r="N519" s="4"/>
       <c r="O519" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P519" s="5"/>
       <c r="Q519" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R519" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S519" s="4" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B520" s="4" t="n">
         <v>4</v>
@@ -32007,19 +32052,19 @@
         <v>55</v>
       </c>
       <c r="G520" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H520" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I520" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J520" s="4" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="K520" s="5" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="L520" s="4" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D520-1)/Inputs!$B$12,0))</f>
@@ -32028,22 +32073,22 @@
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
       <c r="O520" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P520" s="5"/>
       <c r="Q520" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R520" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S520" s="4" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B521" s="6" t="n">
         <v>4</v>
@@ -32061,17 +32106,17 @@
         <v>91</v>
       </c>
       <c r="G521" s="6" t="s">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="H521" s="7" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="I521" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J521" s="6"/>
       <c r="K521" s="7" t="s">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="L521" s="6" t="n">
         <f aca="false">MAX(1,ROUND(28*Inputs!$B$6^(D521-1)/Inputs!$B$12*3.66,0))</f>
@@ -32080,11 +32125,11 @@
       <c r="M521" s="6"/>
       <c r="N521" s="6"/>
       <c r="O521" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P521" s="7"/>
       <c r="Q521" s="6" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="R521" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32096,7 +32141,7 @@
     </row>
     <row r="522" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B522" s="2" t="n">
         <v>5</v>
@@ -32114,19 +32159,19 @@
         <v>22</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H522" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I522" s="2" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="J522" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="K522" s="3" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="L522" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D522-1)/Inputs!$B$12,0))</f>
@@ -32135,22 +32180,22 @@
       <c r="M522" s="2"/>
       <c r="N522" s="2"/>
       <c r="O522" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P522" s="3"/>
       <c r="Q522" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R522" s="2" t="n">
         <v>62</v>
       </c>
       <c r="S522" s="2" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B523" s="2" t="n">
         <v>5</v>
@@ -32168,19 +32213,19 @@
         <v>22</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H523" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I523" s="2" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="J523" s="2" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="K523" s="3" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="L523" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D523-1)/Inputs!$B$12,0))</f>
@@ -32189,22 +32234,22 @@
       <c r="M523" s="2"/>
       <c r="N523" s="2"/>
       <c r="O523" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P523" s="3"/>
       <c r="Q523" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R523" s="2" t="n">
         <v>7</v>
       </c>
       <c r="S523" s="2" t="s">
-        <v>860</v>
+        <v>875</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B524" s="2" t="n">
         <v>5</v>
@@ -32222,19 +32267,19 @@
         <v>22</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H524" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I524" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J524" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="K524" s="3" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="L524" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D524-1)/Inputs!$B$12,0))</f>
@@ -32243,22 +32288,22 @@
       <c r="M524" s="2"/>
       <c r="N524" s="2"/>
       <c r="O524" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P524" s="3"/>
       <c r="Q524" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R524" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S524" s="2" t="s">
-        <v>863</v>
+        <v>878</v>
       </c>
     </row>
     <row r="525" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B525" s="2" t="n">
         <v>5</v>
@@ -32276,19 +32321,19 @@
         <v>22</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H525" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I525" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J525" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="K525" s="3" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="L525" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D525-1)/Inputs!$B$12,0))</f>
@@ -32297,22 +32342,22 @@
       <c r="M525" s="2"/>
       <c r="N525" s="2"/>
       <c r="O525" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P525" s="3"/>
       <c r="Q525" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R525" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S525" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B526" s="2" t="n">
         <v>5</v>
@@ -32330,19 +32375,19 @@
         <v>22</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H526" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I526" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J526" s="2" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="K526" s="3" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="L526" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D526-1)/Inputs!$B$12,0))</f>
@@ -32351,22 +32396,22 @@
       <c r="M526" s="2"/>
       <c r="N526" s="2"/>
       <c r="O526" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P526" s="3"/>
       <c r="Q526" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R526" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S526" s="2" t="s">
-        <v>864</v>
+        <v>879</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>5</v>
@@ -32384,19 +32429,19 @@
         <v>22</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H527" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I527" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J527" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="K527" s="3" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="L527" s="2" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D527-1)/Inputs!$B$12,0))</f>
@@ -32405,22 +32450,22 @@
       <c r="M527" s="2"/>
       <c r="N527" s="2"/>
       <c r="O527" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P527" s="3"/>
       <c r="Q527" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R527" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S527" s="2" t="s">
-        <v>866</v>
+        <v>881</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B528" s="4" t="n">
         <v>5</v>
@@ -32438,19 +32483,19 @@
         <v>55</v>
       </c>
       <c r="G528" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H528" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I528" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J528" s="4" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="K528" s="5" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="L528" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D528-1)/Inputs!$B$12,0))</f>
@@ -32459,22 +32504,22 @@
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
       <c r="O528" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P528" s="5"/>
       <c r="Q528" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R528" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S528" s="4" t="s">
-        <v>867</v>
+        <v>882</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B529" s="4" t="n">
         <v>5</v>
@@ -32492,19 +32537,19 @@
         <v>55</v>
       </c>
       <c r="G529" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H529" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I529" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J529" s="4" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="K529" s="5" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="L529" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D529-1)/Inputs!$B$12,0))</f>
@@ -32513,22 +32558,22 @@
       <c r="M529" s="4"/>
       <c r="N529" s="4"/>
       <c r="O529" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P529" s="5"/>
       <c r="Q529" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R529" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S529" s="4" t="s">
-        <v>869</v>
+        <v>884</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B530" s="4" t="n">
         <v>5</v>
@@ -32546,19 +32591,19 @@
         <v>55</v>
       </c>
       <c r="G530" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H530" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I530" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J530" s="4" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
       <c r="K530" s="5" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="L530" s="4" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D530-1)/Inputs!$B$12,0))</f>
@@ -32567,22 +32612,22 @@
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
       <c r="O530" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P530" s="5"/>
       <c r="Q530" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R530" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S530" s="4" t="s">
-        <v>870</v>
+        <v>885</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B531" s="6" t="n">
         <v>5</v>
@@ -32600,17 +32645,17 @@
         <v>91</v>
       </c>
       <c r="G531" s="6" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="H531" s="7" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="I531" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J531" s="6"/>
       <c r="K531" s="7" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="L531" s="6" t="n">
         <f aca="false">MAX(1,ROUND(34*Inputs!$B$6^(D531-1)/Inputs!$B$12*3.66,0))</f>
@@ -32619,11 +32664,11 @@
       <c r="M531" s="6"/>
       <c r="N531" s="6"/>
       <c r="O531" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P531" s="7"/>
       <c r="Q531" s="6" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="R531" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -32635,7 +32680,7 @@
     </row>
     <row r="532" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B532" s="2" t="n">
         <v>6</v>
@@ -32653,19 +32698,19 @@
         <v>22</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="H532" s="3" t="s">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="I532" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="J532" s="2" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="K532" s="3" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="L532" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D532-1)/Inputs!$B$12,0))</f>
@@ -32674,22 +32719,22 @@
       <c r="M532" s="2"/>
       <c r="N532" s="2"/>
       <c r="O532" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P532" s="3"/>
       <c r="Q532" s="2" t="s">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="R532" s="2" t="n">
         <v>100</v>
       </c>
       <c r="S532" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
     </row>
     <row r="533" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B533" s="2" t="n">
         <v>6</v>
@@ -32707,19 +32752,19 @@
         <v>22</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="H533" s="3" t="s">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="I533" s="2" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="J533" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="K533" s="3" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="L533" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D533-1)/Inputs!$B$12,0))</f>
@@ -32728,22 +32773,22 @@
       <c r="M533" s="2"/>
       <c r="N533" s="2"/>
       <c r="O533" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P533" s="3"/>
       <c r="Q533" s="2" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="R533" s="2" t="n">
         <v>12</v>
       </c>
       <c r="S533" s="2" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
     </row>
     <row r="534" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B534" s="2" t="n">
         <v>6</v>
@@ -32761,19 +32806,19 @@
         <v>22</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H534" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I534" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J534" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="K534" s="3" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="L534" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D534-1)/Inputs!$B$12,0))</f>
@@ -32782,22 +32827,22 @@
       <c r="M534" s="2"/>
       <c r="N534" s="2"/>
       <c r="O534" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P534" s="3"/>
       <c r="Q534" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R534" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S534" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B535" s="2" t="n">
         <v>6</v>
@@ -32815,19 +32860,19 @@
         <v>22</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="H535" s="3" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="I535" s="2" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="J535" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="K535" s="3" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="L535" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D535-1)/Inputs!$B$12,0))</f>
@@ -32836,22 +32881,22 @@
       <c r="M535" s="2"/>
       <c r="N535" s="2"/>
       <c r="O535" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P535" s="3"/>
       <c r="Q535" s="2" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="R535" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="S535" s="2" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
     </row>
     <row r="536" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B536" s="2" t="n">
         <v>6</v>
@@ -32869,19 +32914,19 @@
         <v>22</v>
       </c>
       <c r="G536" s="2" t="s">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="H536" s="3" t="s">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="I536" s="2" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="J536" s="2" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="K536" s="3" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="L536" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D536-1)/Inputs!$B$12,0))</f>
@@ -32890,22 +32935,22 @@
       <c r="M536" s="2"/>
       <c r="N536" s="2"/>
       <c r="O536" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P536" s="3"/>
       <c r="Q536" s="2" t="s">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="R536" s="2" t="n">
         <v>5</v>
       </c>
       <c r="S536" s="2" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="2" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>6</v>
@@ -32923,19 +32968,19 @@
         <v>22</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="H537" s="3" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="I537" s="2" t="s">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="J537" s="2" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="K537" s="3" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="L537" s="2" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D537-1)/Inputs!$B$12,0))</f>
@@ -32944,22 +32989,22 @@
       <c r="M537" s="2"/>
       <c r="N537" s="2"/>
       <c r="O537" s="2" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P537" s="3"/>
       <c r="Q537" s="2" t="s">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="R537" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="S537" s="2" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B538" s="4" t="n">
         <v>6</v>
@@ -32977,19 +33022,19 @@
         <v>55</v>
       </c>
       <c r="G538" s="4" t="s">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="H538" s="5" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="I538" s="4" t="s">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="J538" s="4" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="K538" s="5" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="L538" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D538-1)/Inputs!$B$12,0))</f>
@@ -32998,22 +33043,22 @@
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
       <c r="O538" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P538" s="5"/>
       <c r="Q538" s="4" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="R538" s="4" t="n">
         <v>1</v>
       </c>
       <c r="S538" s="4" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B539" s="4" t="n">
         <v>6</v>
@@ -33031,19 +33076,19 @@
         <v>55</v>
       </c>
       <c r="G539" s="4" t="s">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="H539" s="5" t="s">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="I539" s="4" t="s">
         <v>355</v>
       </c>
       <c r="J539" s="4" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="K539" s="5" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="L539" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D539-1)/Inputs!$B$12,0))</f>
@@ -33052,22 +33097,22 @@
       <c r="M539" s="4"/>
       <c r="N539" s="4"/>
       <c r="O539" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P539" s="5"/>
       <c r="Q539" s="4" t="s">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="R539" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S539" s="4" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="4" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B540" s="4" t="n">
         <v>6</v>
@@ -33085,19 +33130,19 @@
         <v>55</v>
       </c>
       <c r="G540" s="4" t="s">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="H540" s="5" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="I540" s="4" t="s">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="J540" s="4" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="K540" s="5" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="L540" s="4" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D540-1)/Inputs!$B$12,0))</f>
@@ -33106,22 +33151,22 @@
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
       <c r="O540" s="4" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P540" s="5"/>
       <c r="Q540" s="4" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="R540" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="S540" s="4" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="6" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B541" s="6" t="n">
         <v>6</v>
@@ -33139,17 +33184,17 @@
         <v>91</v>
       </c>
       <c r="G541" s="6" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="H541" s="7" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="I541" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J541" s="6"/>
       <c r="K541" s="7" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="L541" s="6" t="n">
         <f aca="false">MAX(1,ROUND(40*Inputs!$B$6^(D541-1)/Inputs!$B$12*3.66,0))</f>
@@ -33158,11 +33203,11 @@
       <c r="M541" s="6"/>
       <c r="N541" s="6"/>
       <c r="O541" s="6" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="P541" s="7"/>
       <c r="Q541" s="6" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="R541" s="8" t="b">
         <f aca="false">TRUE()</f>
@@ -33201,12 +33246,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
       <c r="B4" s="11" t="n">
         <v>2</v>
@@ -33214,7 +33259,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>1.1</v>
@@ -33222,7 +33267,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1.15</v>
@@ -33230,7 +33275,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1.25</v>
@@ -33238,7 +33283,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>2</v>
@@ -33246,7 +33291,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>10</v>
@@ -33254,7 +33299,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>1.5</v>
@@ -33262,7 +33307,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">(B6^10-1)/(B6-1)</f>
@@ -33274,13 +33319,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33288,13 +33333,13 @@
         <v>28</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>570</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33302,13 +33347,13 @@
         <v>331</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>927</v>
+        <v>942</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>930</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33316,13 +33361,13 @@
         <v>413</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>929</v>
+        <v>944</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>375</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>930</v>
+        <v>945</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33330,13 +33375,13 @@
         <v>493</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>931</v>
+        <v>946</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>210</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>932</v>
+        <v>947</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33344,13 +33389,13 @@
         <v>562</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>330</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>934</v>
+        <v>949</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33358,41 +33403,41 @@
         <v>642</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>935</v>
+        <v>950</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>4500</v>
+        <v>1125</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>936</v>
+        <v>951</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>937</v>
+        <v>952</v>
       </c>
       <c r="C21" s="11" t="n">
         <v>420</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>938</v>
+        <v>953</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>939</v>
+        <v>954</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>82</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>940</v>
+        <v>955</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33400,28 +33445,28 @@
         <v>44</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>941</v>
+        <v>956</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>942</v>
+        <v>957</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>943</v>
+        <v>958</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -33448,7 +33493,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>946</v>
+        <v>961</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33456,22 +33501,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>947</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>949</v>
+        <v>964</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33479,22 +33524,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33502,17 +33547,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33520,22 +33565,22 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33543,22 +33588,22 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33566,22 +33611,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33589,37 +33634,37 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>975</v>
+        <v>990</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33627,42 +33672,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>977</v>
+        <v>992</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>978</v>
+        <v>993</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>979</v>
+        <v>994</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>980</v>
+        <v>995</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>981</v>
+        <v>996</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>982</v>
+        <v>997</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>983</v>
+        <v>998</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33670,32 +33715,32 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>985</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>986</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>987</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>988</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>989</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>990</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33703,32 +33748,32 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>995</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>996</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33736,27 +33781,27 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>998</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>999</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>1000</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>1001</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33764,32 +33809,32 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>1002</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>1005</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>1006</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>1007</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33797,22 +33842,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>1008</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>1010</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>1011</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33820,47 +33865,47 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>1012</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>1013</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>1014</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>1015</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>1017</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="10" t="s">
-        <v>1018</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>1019</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>1020</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33868,22 +33913,22 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>1021</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>1022</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>1023</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="10" t="s">
-        <v>1024</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33891,22 +33936,22 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="10" t="s">
-        <v>1025</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="10" t="s">
-        <v>1026</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="10" t="s">
-        <v>1027</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="10" t="s">
-        <v>1028</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33914,42 +33959,42 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="10" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="10" t="s">
-        <v>1030</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="10" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="10" t="s">
-        <v>1032</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="10" t="s">
-        <v>1033</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="10" t="s">
-        <v>1034</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="10" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="10" t="s">
-        <v>1036</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33957,42 +34002,42 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="10" t="s">
-        <v>1037</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="10" t="s">
-        <v>1038</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="10" t="s">
-        <v>1039</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="10" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="10" t="s">
-        <v>1041</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="10" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="10" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="10" t="s">
-        <v>1044</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34000,17 +34045,17 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="16" t="s">
-        <v>1045</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="10" t="s">
-        <v>1046</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="10" t="s">
-        <v>1047</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -34038,12 +34083,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>1048</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="B3" s="17" t="n">
         <v>100</v>
@@ -34051,7 +34096,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
       <c r="B4" s="17" t="n">
         <v>5</v>
@@ -34059,7 +34104,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1051</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>100</v>
@@ -34070,25 +34115,25 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>1052</v>
+        <v>1067</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>1053</v>
+        <v>1068</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>1054</v>
+        <v>1069</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>1055</v>
+        <v>1070</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>1057</v>
+        <v>1072</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34273,7 +34318,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>1058</v>
+        <v>1073</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>99</v>
@@ -34303,27 +34348,27 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>1059</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>1060</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>1061</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>1062</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>1063</v>
+        <v>1078</v>
       </c>
       <c r="B21" s="21" t="n">
         <v>0.05</v>
@@ -34331,7 +34376,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="B22" s="21" t="n">
         <v>0.01</v>
@@ -34339,7 +34384,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="B23" s="17" t="n">
         <v>12.5</v>
@@ -34347,7 +34392,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="B24" s="17" t="n">
         <v>6.25</v>
@@ -34358,22 +34403,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="C26" s="18" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>1068</v>
       </c>
-      <c r="D26" s="18" t="s">
-        <v>1053</v>
-      </c>
       <c r="E26" s="18" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34552,12 +34597,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>1073</v>
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
@@ -34594,16 +34639,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1074</v>
+        <v>1089</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1076</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35335,11 +35380,11 @@
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>4929</v>
+        <v>1234</v>
       </c>
       <c r="D38" s="23" t="n">
         <f aca="false">C38/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>0.876266666666667</v>
+        <v>0.877511111111111</v>
       </c>
       <c r="E38" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A38,'All Upgrades'!$B$2:$B$541,B38)</f>
@@ -35355,11 +35400,11 @@
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A39,'All Upgrades'!$B$2:$B$541,B39,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>12655</v>
+        <v>3165</v>
       </c>
       <c r="D39" s="23" t="n">
         <f aca="false">C39/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.24977777777778</v>
+        <v>2.25066666666667</v>
       </c>
       <c r="E39" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A39,'All Upgrades'!$B$2:$B$541,B39)</f>
@@ -35375,11 +35420,11 @@
       </c>
       <c r="C40" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A40,'All Upgrades'!$B$2:$B$541,B40,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>16903</v>
+        <v>4226</v>
       </c>
       <c r="D40" s="23" t="n">
         <f aca="false">C40/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>3.00497777777778</v>
+        <v>3.00515555555556</v>
       </c>
       <c r="E40" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A40,'All Upgrades'!$B$2:$B$541,B40)</f>
@@ -35395,11 +35440,11 @@
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A41,'All Upgrades'!$B$2:$B$541,B41,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>16405</v>
+        <v>4101</v>
       </c>
       <c r="D41" s="23" t="n">
         <f aca="false">C41/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>2.91644444444444</v>
+        <v>2.91626666666667</v>
       </c>
       <c r="E41" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A41,'All Upgrades'!$B$2:$B$541,B41)</f>
@@ -35415,11 +35460,11 @@
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A42,'All Upgrades'!$B$2:$B$541,B42,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>18046</v>
+        <v>4511</v>
       </c>
       <c r="D42" s="23" t="n">
         <f aca="false">C42/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>3.20817777777778</v>
+        <v>3.20782222222222</v>
       </c>
       <c r="E42" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A42,'All Upgrades'!$B$2:$B$541,B42)</f>
@@ -35435,11 +35480,11 @@
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$L$2:$L$541,'All Upgrades'!$A$2:$A$541,A43,'All Upgrades'!$B$2:$B$541,B43,'All Upgrades'!$O$2:$O$541,"&lt;&gt;tokens")</f>
-        <v>26469</v>
+        <v>6616</v>
       </c>
       <c r="D43" s="23" t="n">
         <f aca="false">C43/INDEX(Inputs!$C$15:$C$23,MATCH("decoding",Inputs!$A$15:$A$23,0))/Inputs!$B$7</f>
-        <v>4.7056</v>
+        <v>4.70471111111111</v>
       </c>
       <c r="E43" s="10" t="n">
         <f aca="false">SUMIFS('All Upgrades'!$N$2:$N$541,'All Upgrades'!$A$2:$A$541,A43,'All Upgrades'!$B$2:$B$541,B43)</f>
@@ -35448,7 +35493,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B44" s="10" t="n">
         <v>1</v>
@@ -35468,7 +35513,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B45" s="10" t="n">
         <v>2</v>
@@ -35488,7 +35533,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B46" s="10" t="n">
         <v>3</v>
@@ -35508,7 +35553,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B47" s="10" t="n">
         <v>4</v>
@@ -35528,7 +35573,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B48" s="10" t="n">
         <v>5</v>
@@ -35548,7 +35593,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B49" s="10" t="n">
         <v>6</v>
@@ -35568,7 +35613,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B50" s="10" t="n">
         <v>1</v>
@@ -35588,7 +35633,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B51" s="10" t="n">
         <v>2</v>
@@ -35608,7 +35653,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B52" s="10" t="n">
         <v>3</v>
@@ -35628,7 +35673,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B53" s="10" t="n">
         <v>4</v>
@@ -35648,7 +35693,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B54" s="10" t="n">
         <v>5</v>
@@ -35668,7 +35713,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B55" s="10" t="n">
         <v>6</v>
@@ -35721,31 +35766,31 @@
         <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1077</v>
+        <v>1092</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>1084</v>
+        <v>1099</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35753,10 +35798,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1086</v>
+        <v>1101</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D2" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35787,10 +35832,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1088</v>
+        <v>1103</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D3" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35821,10 +35866,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35855,10 +35900,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1092</v>
+        <v>1107</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35889,7 +35934,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>1094</v>
+        <v>1109</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>490</v>
@@ -35923,10 +35968,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35957,10 +36002,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -35991,10 +36036,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1097</v>
+        <v>1112</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D9" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36025,10 +36070,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>1098</v>
+        <v>1113</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D10" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36059,7 +36104,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>490</v>
@@ -36093,10 +36138,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D12" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36127,10 +36172,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36161,10 +36206,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36195,10 +36240,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>1103</v>
+        <v>1118</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D15" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36229,7 +36274,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>490</v>
@@ -36263,10 +36308,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D17" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36297,10 +36342,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D18" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36331,10 +36376,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D19" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36365,10 +36410,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>1108</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>1093</v>
       </c>
       <c r="D20" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36399,7 +36444,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>1109</v>
+        <v>1124</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>490</v>
@@ -36433,10 +36478,10 @@
         <v>5</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D22" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36467,10 +36512,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>1111</v>
+        <v>1126</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D23" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36501,10 +36546,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D24" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36535,10 +36580,10 @@
         <v>5</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D25" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36569,7 +36614,7 @@
         <v>5</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>490</v>
@@ -36603,10 +36648,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="D27" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36637,10 +36682,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="D28" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36671,10 +36716,10 @@
         <v>6</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="D29" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36705,10 +36750,10 @@
         <v>6</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="D30" s="10" t="n">
         <f aca="false">2*Inputs!$B$8</f>
@@ -36739,7 +36784,7 @@
         <v>6</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>1119</v>
+        <v>1134</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>490</v>
@@ -36799,16 +36844,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>1123</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36932,7 +36977,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>10</v>
@@ -36949,7 +36994,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>10</v>
@@ -36966,7 +37011,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>1124</v>
+        <v>1139</v>
       </c>
       <c r="B11" s="20" t="n">
         <v>90</v>
